--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roita\מעקב הוצאות כלים\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9363EC9BE71201D4762D76C9D9D56AED991232E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_3260EC9B897A43C1FC2D768769115A3B29942CE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1051,7 +1051,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-997A-452D-9B8A-982F13E839D3}"/>
+              <c16:uniqueId val="{00000000-8E1A-424C-A6A5-6ECF3DC33095}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1734,7 +1734,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1929,7 +1929,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2048,7 +2048,7 @@
     <mergeCell ref="A6:C6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3763,16 +3763,16 @@
     <mergeCell ref="B3:C3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" location="יולי 2025!A1" display="יולי 2025_x000a_(July 2025)" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
-    <hyperlink ref="D3" location="אוגוסט 2025!A1" display="אוגוסט 2025_x000a_(August 2025)" xr:uid="{00000000-0004-0000-0C00-000001000000}"/>
-    <hyperlink ref="F3" location="ספטמבר 2025!A1" display="ספטמבר 2025_x000a_(September 2025)" xr:uid="{00000000-0004-0000-0C00-000002000000}"/>
-    <hyperlink ref="H3" location="אוקטובר 2025!A1" display="אוקטובר 2025_x000a_(October 2025)" xr:uid="{00000000-0004-0000-0C00-000003000000}"/>
-    <hyperlink ref="J3" location="נובמבר 2025!A1" display="נובמבר 2025_x000a_(November 2025)" xr:uid="{00000000-0004-0000-0C00-000004000000}"/>
-    <hyperlink ref="L3" location="דצמבר 2025!A1" display="דצמבר 2025_x000a_(December 2025)" xr:uid="{00000000-0004-0000-0C00-000005000000}"/>
-    <hyperlink ref="N3" location="ינואר 2026!A1" display="ינואר 2026_x000a_(January 2026)" xr:uid="{00000000-0004-0000-0C00-000006000000}"/>
-    <hyperlink ref="P3" location="פברואר 2026!A1" display="פברואר 2026_x000a_(February 2026)" xr:uid="{00000000-0004-0000-0C00-000007000000}"/>
-    <hyperlink ref="R3" location="מרץ 2026!A1" display="מרץ 2026_x000a_(March 2026)" xr:uid="{00000000-0004-0000-0C00-000008000000}"/>
-    <hyperlink ref="T3" location="אפריל 2026!A1" display="אפריל 2026_x000a_(April 2026)" xr:uid="{00000000-0004-0000-0C00-000009000000}"/>
+    <hyperlink ref="B3" location="'יולי 2025'!A1" display="יולי 2025_x000a_(July 2025)" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
+    <hyperlink ref="D3" location="'אוגוסט 2025'!A1" display="אוגוסט 2025_x000a_(August 2025)" xr:uid="{00000000-0004-0000-0C00-000001000000}"/>
+    <hyperlink ref="F3" location="'ספטמבר 2025'!A1" display="ספטמבר 2025_x000a_(September 2025)" xr:uid="{00000000-0004-0000-0C00-000002000000}"/>
+    <hyperlink ref="H3" location="'אוקטובר 2025'!A1" display="אוקטובר 2025_x000a_(October 2025)" xr:uid="{00000000-0004-0000-0C00-000003000000}"/>
+    <hyperlink ref="J3" location="'נובמבר 2025'!A1" display="נובמבר 2025_x000a_(November 2025)" xr:uid="{00000000-0004-0000-0C00-000004000000}"/>
+    <hyperlink ref="L3" location="'דצמבר 2025'!A1" display="דצמבר 2025_x000a_(December 2025)" xr:uid="{00000000-0004-0000-0C00-000005000000}"/>
+    <hyperlink ref="N3" location="'ינואר 2026'!A1" display="ינואר 2026_x000a_(January 2026)" xr:uid="{00000000-0004-0000-0C00-000006000000}"/>
+    <hyperlink ref="P3" location="'פברואר 2026'!A1" display="פברואר 2026_x000a_(February 2026)" xr:uid="{00000000-0004-0000-0C00-000007000000}"/>
+    <hyperlink ref="R3" location="'מרץ 2026'!A1" display="מרץ 2026_x000a_(March 2026)" xr:uid="{00000000-0004-0000-0C00-000008000000}"/>
+    <hyperlink ref="T3" location="'אפריל 2026'!A1" display="אפריל 2026_x000a_(April 2026)" xr:uid="{00000000-0004-0000-0C00-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4093,16 +4093,16 @@
     <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="יולי 2025!A1" display="יולי 2025" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
-    <hyperlink ref="A5" location="אוגוסט 2025!A1" display="אוגוסט 2025" xr:uid="{00000000-0004-0000-0D00-000001000000}"/>
-    <hyperlink ref="A6" location="ספטמבר 2025!A1" display="ספטמבר 2025" xr:uid="{00000000-0004-0000-0D00-000002000000}"/>
-    <hyperlink ref="A7" location="אוקטובר 2025!A1" display="אוקטובר 2025" xr:uid="{00000000-0004-0000-0D00-000003000000}"/>
-    <hyperlink ref="A8" location="נובמבר 2025!A1" display="נובמבר 2025" xr:uid="{00000000-0004-0000-0D00-000004000000}"/>
-    <hyperlink ref="A9" location="דצמבר 2025!A1" display="דצמבר 2025" xr:uid="{00000000-0004-0000-0D00-000005000000}"/>
-    <hyperlink ref="A10" location="ינואר 2026!A1" display="ינואר 2026" xr:uid="{00000000-0004-0000-0D00-000006000000}"/>
-    <hyperlink ref="A11" location="פברואר 2026!A1" display="פברואר 2026" xr:uid="{00000000-0004-0000-0D00-000007000000}"/>
-    <hyperlink ref="A12" location="מרץ 2026!A1" display="מרץ 2026" xr:uid="{00000000-0004-0000-0D00-000008000000}"/>
-    <hyperlink ref="A13" location="אפריל 2026!A1" display="אפריל 2026" xr:uid="{00000000-0004-0000-0D00-000009000000}"/>
+    <hyperlink ref="A4" location="'יולי 2025'!A1" display="יולי 2025" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
+    <hyperlink ref="A5" location="'אוגוסט 2025'!A1" display="אוגוסט 2025" xr:uid="{00000000-0004-0000-0D00-000001000000}"/>
+    <hyperlink ref="A6" location="'ספטמבר 2025'!A1" display="ספטמבר 2025" xr:uid="{00000000-0004-0000-0D00-000002000000}"/>
+    <hyperlink ref="A7" location="'אוקטובר 2025'!A1" display="אוקטובר 2025" xr:uid="{00000000-0004-0000-0D00-000003000000}"/>
+    <hyperlink ref="A8" location="'נובמבר 2025'!A1" display="נובמבר 2025" xr:uid="{00000000-0004-0000-0D00-000004000000}"/>
+    <hyperlink ref="A9" location="'דצמבר 2025'!A1" display="דצמבר 2025" xr:uid="{00000000-0004-0000-0D00-000005000000}"/>
+    <hyperlink ref="A10" location="'ינואר 2026'!A1" display="ינואר 2026" xr:uid="{00000000-0004-0000-0D00-000006000000}"/>
+    <hyperlink ref="A11" location="'פברואר 2026'!A1" display="פברואר 2026" xr:uid="{00000000-0004-0000-0D00-000007000000}"/>
+    <hyperlink ref="A12" location="'מרץ 2026'!A1" display="מרץ 2026" xr:uid="{00000000-0004-0000-0D00-000008000000}"/>
+    <hyperlink ref="A13" location="'אפריל 2026'!A1" display="אפריל 2026" xr:uid="{00000000-0004-0000-0D00-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5416,7 +5416,7 @@
     <mergeCell ref="A11:C11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5649,7 +5649,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5806,7 +5806,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5925,7 +5925,7 @@
     <mergeCell ref="A6:C6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6120,7 +6120,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6239,7 @@
     <mergeCell ref="A6:C6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6434,7 +6434,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="סיכום חודשי!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roita\מעקב הוצאות כלים\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3260EC9B897A43C1FC2D768769115A3B29942CE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C93FFF2C68F48BE1FB05EC776C46B23A5EE984C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="160">
   <si>
     <t>דוח שנתי – AI Tool Expenses</t>
   </si>
@@ -417,7 +417,25 @@
     <t>Creator (first month 50% off)</t>
   </si>
   <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>Lite plan</t>
+  </si>
+  <si>
     <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>IONOS</t>
+  </si>
+  <si>
+    <t>Instant Domain</t>
   </si>
   <si>
     <t>סה"כ"</t>
@@ -1041,17 +1059,17 @@
                   <c:v>156</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>146.61000000000001</c:v>
+                  <c:v>151.61000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25</c:v>
+                  <c:v>47.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8E1A-424C-A6A5-6ECF3DC33095}"/>
+              <c16:uniqueId val="{00000000-0DB0-4721-B2D9-D60992237236}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1562,7 +1580,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -1572,7 +1590,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1714,7 +1732,7 @@
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
@@ -1745,7 +1763,7 @@
   <sheetPr>
     <tabColor rgb="FF9DC3E6"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1757,7 +1775,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -1767,7 +1785,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1907,26 +1925,45 @@
       </c>
       <c r="F9" s="24"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="16">
-        <f>SUM(D4:D9)</f>
-        <v>146.61000000000001</v>
-      </c>
-      <c r="E10" s="17">
-        <f>SUM(E4:E9)</f>
-        <v>535.12649999999996</v>
-      </c>
-      <c r="F10" s="26"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="20">
+        <v>5</v>
+      </c>
+      <c r="E10" s="21">
+        <f>D10*הגדרות!$B$4</f>
+        <v>18.25</v>
+      </c>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="16">
+        <f>SUM(D4:D10)</f>
+        <v>151.61000000000001</v>
+      </c>
+      <c r="E11" s="17">
+        <f>SUM(E4:E10)</f>
+        <v>553.37649999999996</v>
+      </c>
+      <c r="F11" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
@@ -1940,7 +1977,7 @@
   <sheetPr>
     <tabColor rgb="FF9DC3E6"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1952,7 +1989,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -1962,7 +1999,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1990,7 +2027,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>52</v>
@@ -2009,7 +2046,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>52</v>
@@ -2026,26 +2063,64 @@
       </c>
       <c r="F5" s="24"/>
     </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="20">
+        <v>2.25</v>
+      </c>
+      <c r="E6" s="21">
+        <f>D6*הגדרות!$B$4</f>
+        <v>8.2125000000000004</v>
+      </c>
+      <c r="F6" s="19"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="16">
-        <f>SUM(D4:D5)</f>
-        <v>25</v>
-      </c>
-      <c r="E6" s="17">
-        <f>SUM(E4:E5)</f>
-        <v>91.25</v>
-      </c>
-      <c r="F6" s="26"/>
+      <c r="B7" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="22">
+        <v>20</v>
+      </c>
+      <c r="E7" s="23">
+        <f>D7*הגדרות!$B$4</f>
+        <v>73</v>
+      </c>
+      <c r="F7" s="24"/>
+    </row>
+    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="16">
+        <f>SUM(D4:D7)</f>
+        <v>47.25</v>
+      </c>
+      <c r="E8" s="17">
+        <f>SUM(E4:E7)</f>
+        <v>172.46250000000001</v>
+      </c>
+      <c r="F8" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" location="'סיכום חודשי'!A1" display="← חזרה לסיכום חודשי" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
@@ -2059,7 +2134,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2089,7 +2164,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -2115,7 +2190,7 @@
     </row>
     <row r="2" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="66" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B2" s="53"/>
       <c r="C2" s="53"/>
@@ -2144,119 +2219,119 @@
         <v>38</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C3" s="53"/>
       <c r="D3" s="67" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E3" s="53"/>
       <c r="F3" s="67" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G3" s="53"/>
       <c r="H3" s="67" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I3" s="53"/>
       <c r="J3" s="67" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K3" s="53"/>
       <c r="L3" s="67" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M3" s="53"/>
       <c r="N3" s="67" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O3" s="53"/>
       <c r="P3" s="67" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q3" s="53"/>
       <c r="R3" s="67" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="S3" s="53"/>
       <c r="T3" s="67" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="U3" s="53"/>
       <c r="V3" s="14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="W3" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="L4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="M4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="V4" s="28" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="W4" s="28" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -2344,7 +2419,7 @@
         <v>91.25</v>
       </c>
       <c r="V5" s="32">
-        <f t="shared" ref="V5:V19" si="0">SUM(B5,D5,F5,H5,J5,L5,N5,P5,R5,T5)</f>
+        <f t="shared" ref="V5:V20" si="0">SUM(B5,D5,F5,H5,J5,L5,N5,P5,R5,T5)</f>
         <v>180</v>
       </c>
       <c r="W5" s="33">
@@ -2726,1025 +2801,1118 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="36" t="str">
+        <f>IF(B10&gt;0,B10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="36" t="str">
+        <f>IF(D10&gt;0,D10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="36" t="str">
+        <f>IF(F10&gt;0,F10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="36" t="str">
+        <f>IF(H10&gt;0,H10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="36" t="str">
+        <f>IF(J10&gt;0,J10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="36" t="str">
+        <f>IF(L10&gt;0,L10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="36" t="str">
+        <f>IF(N10&gt;0,N10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="36" t="str">
+        <f>IF(P10&gt;0,P10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="36" t="str">
+        <f>IF(R10&gt;0,R10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T10" s="35">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <v>20</v>
+      </c>
+      <c r="U10" s="36">
+        <f>IF(T10&gt;0,T10*הגדרות!$B$4,"")</f>
+        <v>73</v>
+      </c>
+      <c r="V10" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W10" s="33">
+        <f>IF(V10&gt;0,V10*הגדרות!$B$4,"")</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="35">
+      <c r="B11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>185.14</v>
       </c>
-      <c r="C10" s="36">
-        <f>IF(B10&gt;0,B10*הגדרות!$B$4,"")</f>
+      <c r="C11" s="31">
+        <f>IF(B11&gt;0,B11*הגדרות!$B$4,"")</f>
         <v>675.76099999999997</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="36" t="str">
-        <f>IF(D10&gt;0,D10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="35">
+      <c r="E11" s="31" t="str">
+        <f>IF(D11&gt;0,D11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="G10" s="36" t="str">
-        <f>IF(F10&gt;0,F10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="35">
+      <c r="G11" s="31" t="str">
+        <f>IF(F11&gt;0,F11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="36" t="str">
-        <f>IF(H10&gt;0,H10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="35">
+      <c r="I11" s="31" t="str">
+        <f>IF(H11&gt;0,H11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="36" t="str">
-        <f>IF(J10&gt;0,J10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="L10" s="35">
+      <c r="K11" s="31" t="str">
+        <f>IF(J11&gt;0,J11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M10" s="36" t="str">
-        <f>IF(L10&gt;0,L10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N10" s="35">
+      <c r="M11" s="31" t="str">
+        <f>IF(L11&gt;0,L11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="O10" s="36" t="str">
-        <f>IF(N10&gt;0,N10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="P10" s="35">
+      <c r="O11" s="31" t="str">
+        <f>IF(N11&gt;0,N11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="36" t="str">
-        <f>IF(P10&gt;0,P10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="R10" s="35">
+      <c r="Q11" s="31" t="str">
+        <f>IF(P11&gt;0,P11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>0</v>
       </c>
-      <c r="S10" s="36" t="str">
-        <f>IF(R10&gt;0,R10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="T10" s="35">
+      <c r="S11" s="31" t="str">
+        <f>IF(R11&gt;0,R11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T11" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U10" s="36" t="str">
-        <f>IF(T10&gt;0,T10*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V10" s="32">
+      <c r="U11" s="31" t="str">
+        <f>IF(T11&gt;0,T11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V11" s="32">
         <f t="shared" si="0"/>
         <v>185.14</v>
       </c>
-      <c r="W10" s="33">
-        <f>IF(V10&gt;0,V10*הגדרות!$B$4,"")</f>
+      <c r="W11" s="33">
+        <f>IF(V11&gt;0,V11*הגדרות!$B$4,"")</f>
         <v>675.76099999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>0</v>
       </c>
-      <c r="C11" s="31" t="str">
-        <f>IF(B11&gt;0,B11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="30">
+      <c r="C12" s="36" t="str">
+        <f>IF(B12&gt;0,B12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="31" t="str">
-        <f>IF(D11&gt;0,D11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="30">
+      <c r="E12" s="36" t="str">
+        <f>IF(D12&gt;0,D12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="G11" s="31" t="str">
-        <f>IF(F11&gt;0,F11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="30">
+      <c r="G12" s="36" t="str">
+        <f>IF(F12&gt;0,F12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="31" t="str">
-        <f>IF(H11&gt;0,H11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="30">
+      <c r="I12" s="36" t="str">
+        <f>IF(H12&gt;0,H12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="K11" s="31" t="str">
-        <f>IF(J11&gt;0,J11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="L11" s="30">
+      <c r="K12" s="36" t="str">
+        <f>IF(J12&gt;0,J12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M11" s="31" t="str">
-        <f>IF(L11&gt;0,L11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N11" s="30">
+      <c r="M12" s="36" t="str">
+        <f>IF(L12&gt;0,L12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="O11" s="31" t="str">
-        <f>IF(N11&gt;0,N11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="P11" s="30">
+      <c r="O12" s="36" t="str">
+        <f>IF(N12&gt;0,N12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>75</v>
       </c>
-      <c r="Q11" s="31">
-        <f>IF(P11&gt;0,P11*הגדרות!$B$4,"")</f>
+      <c r="Q12" s="36">
+        <f>IF(P12&gt;0,P12*הגדרות!$B$4,"")</f>
         <v>273.75</v>
       </c>
-      <c r="R11" s="30">
+      <c r="R12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="31" t="str">
-        <f>IF(R11&gt;0,R11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="T11" s="30">
+        <v>5</v>
+      </c>
+      <c r="S12" s="36">
+        <f>IF(R12&gt;0,R12*הגדרות!$B$4,"")</f>
+        <v>18.25</v>
+      </c>
+      <c r="T12" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U11" s="31" t="str">
-        <f>IF(T11&gt;0,T11*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V11" s="32">
+      <c r="U12" s="36" t="str">
+        <f>IF(T12&gt;0,T12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V12" s="32">
         <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="W11" s="33">
-        <f>IF(V11&gt;0,V11*הגדרות!$B$4,"")</f>
-        <v>273.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="W12" s="33">
+        <f>IF(V12&gt;0,V12*הגדרות!$B$4,"")</f>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>10.59</v>
       </c>
-      <c r="C12" s="36">
-        <f>IF(B12&gt;0,B12*הגדרות!$B$4,"")</f>
+      <c r="C13" s="31">
+        <f>IF(B13&gt;0,B13*הגדרות!$B$4,"")</f>
         <v>38.653500000000001</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>10.59</v>
       </c>
-      <c r="E12" s="36">
-        <f>IF(D12&gt;0,D12*הגדרות!$B$4,"")</f>
+      <c r="E13" s="31">
+        <f>IF(D13&gt;0,D13*הגדרות!$B$4,"")</f>
         <v>38.653500000000001</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>10.59</v>
       </c>
-      <c r="G12" s="36">
-        <f>IF(F12&gt;0,F12*הגדרות!$B$4,"")</f>
+      <c r="G13" s="31">
+        <f>IF(F13&gt;0,F13*הגדרות!$B$4,"")</f>
         <v>38.653500000000001</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="36" t="str">
-        <f>IF(H12&gt;0,H12*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="35">
+      <c r="I13" s="31" t="str">
+        <f>IF(H13&gt;0,H13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="36" t="str">
-        <f>IF(J12&gt;0,J12*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="L12" s="35">
+      <c r="K13" s="31" t="str">
+        <f>IF(J13&gt;0,J13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M12" s="36" t="str">
-        <f>IF(L12&gt;0,L12*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N12" s="35">
+      <c r="M13" s="31" t="str">
+        <f>IF(L13&gt;0,L13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="O12" s="36" t="str">
-        <f>IF(N12&gt;0,N12*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="P12" s="35">
+      <c r="O13" s="31" t="str">
+        <f>IF(N13&gt;0,N13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="36" t="str">
-        <f>IF(P12&gt;0,P12*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="R12" s="35">
+      <c r="Q13" s="31" t="str">
+        <f>IF(P13&gt;0,P13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>0</v>
       </c>
-      <c r="S12" s="36" t="str">
-        <f>IF(R12&gt;0,R12*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="T12" s="35">
+      <c r="S13" s="31" t="str">
+        <f>IF(R13&gt;0,R13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T13" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U12" s="36" t="str">
-        <f>IF(T12&gt;0,T12*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V12" s="32">
+      <c r="U13" s="31" t="str">
+        <f>IF(T13&gt;0,T13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V13" s="32">
         <f t="shared" si="0"/>
         <v>31.77</v>
       </c>
-      <c r="W12" s="33">
-        <f>IF(V12&gt;0,V12*הגדרות!$B$4,"")</f>
+      <c r="W13" s="33">
+        <f>IF(V13&gt;0,V13*הגדרות!$B$4,"")</f>
         <v>115.9605</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>0</v>
       </c>
-      <c r="C13" s="31" t="str">
-        <f>IF(B13&gt;0,B13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="30">
+      <c r="C14" s="36" t="str">
+        <f>IF(B14&gt;0,B14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>19</v>
       </c>
-      <c r="E13" s="31">
-        <f>IF(D13&gt;0,D13*הגדרות!$B$4,"")</f>
+      <c r="E14" s="36">
+        <f>IF(D14&gt;0,D14*הגדרות!$B$4,"")</f>
         <v>69.349999999999994</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="G13" s="31" t="str">
-        <f>IF(F13&gt;0,F13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="30">
+      <c r="G14" s="36" t="str">
+        <f>IF(F14&gt;0,F14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="31" t="str">
-        <f>IF(H13&gt;0,H13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="30">
+      <c r="I14" s="36" t="str">
+        <f>IF(H14&gt;0,H14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="K13" s="31" t="str">
-        <f>IF(J13&gt;0,J13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="L13" s="30">
+      <c r="K14" s="36" t="str">
+        <f>IF(J14&gt;0,J14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M13" s="31" t="str">
-        <f>IF(L13&gt;0,L13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N13" s="30">
+      <c r="M14" s="36" t="str">
+        <f>IF(L14&gt;0,L14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="O13" s="31" t="str">
-        <f>IF(N13&gt;0,N13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="P13" s="30">
+      <c r="O14" s="36" t="str">
+        <f>IF(N14&gt;0,N14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="31" t="str">
-        <f>IF(P13&gt;0,P13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="R13" s="30">
+      <c r="Q14" s="36" t="str">
+        <f>IF(P14&gt;0,P14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>0</v>
       </c>
-      <c r="S13" s="31" t="str">
-        <f>IF(R13&gt;0,R13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="T13" s="30">
+      <c r="S14" s="36" t="str">
+        <f>IF(R14&gt;0,R14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T14" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U13" s="31" t="str">
-        <f>IF(T13&gt;0,T13*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V13" s="32">
+      <c r="U14" s="36" t="str">
+        <f>IF(T14&gt;0,T14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V14" s="32">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="W13" s="33">
-        <f>IF(V13&gt;0,V13*הגדרות!$B$4,"")</f>
+      <c r="W14" s="33">
+        <f>IF(V14&gt;0,V14*הגדרות!$B$4,"")</f>
         <v>69.349999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>0</v>
       </c>
-      <c r="C14" s="36" t="str">
-        <f>IF(B14&gt;0,B14*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="35">
+      <c r="C15" s="31" t="str">
+        <f>IF(B15&gt;0,B15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>0</v>
       </c>
-      <c r="E14" s="36" t="str">
-        <f>IF(D14&gt;0,D14*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="35">
+      <c r="E15" s="31" t="str">
+        <f>IF(D15&gt;0,D15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="G14" s="36" t="str">
-        <f>IF(F14&gt;0,F14*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="35">
+      <c r="G15" s="31" t="str">
+        <f>IF(F15&gt;0,F15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="36" t="str">
-        <f>IF(H14&gt;0,H14*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="35">
+      <c r="I15" s="31" t="str">
+        <f>IF(H15&gt;0,H15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="K14" s="36" t="str">
-        <f>IF(J14&gt;0,J14*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="L14" s="35">
+      <c r="K15" s="31" t="str">
+        <f>IF(J15&gt;0,J15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>15</v>
       </c>
-      <c r="M14" s="36">
-        <f>IF(L14&gt;0,L14*הגדרות!$B$4,"")</f>
+      <c r="M15" s="31">
+        <f>IF(L15&gt;0,L15*הגדרות!$B$4,"")</f>
         <v>54.75</v>
       </c>
-      <c r="N14" s="35">
+      <c r="N15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>15</v>
       </c>
-      <c r="O14" s="36">
-        <f>IF(N14&gt;0,N14*הגדרות!$B$4,"")</f>
+      <c r="O15" s="31">
+        <f>IF(N15&gt;0,N15*הגדרות!$B$4,"")</f>
         <v>54.75</v>
       </c>
-      <c r="P14" s="35">
+      <c r="P15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="36" t="str">
-        <f>IF(P14&gt;0,P14*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="R14" s="35">
+      <c r="Q15" s="31" t="str">
+        <f>IF(P15&gt;0,P15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>0</v>
       </c>
-      <c r="S14" s="36" t="str">
-        <f>IF(R14&gt;0,R14*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="T14" s="35">
+      <c r="S15" s="31" t="str">
+        <f>IF(R15&gt;0,R15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T15" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U14" s="36" t="str">
-        <f>IF(T14&gt;0,T14*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V14" s="32">
+      <c r="U15" s="31" t="str">
+        <f>IF(T15&gt;0,T15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V15" s="32">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="W14" s="33">
-        <f>IF(V14&gt;0,V14*הגדרות!$B$4,"")</f>
+      <c r="W15" s="33">
+        <f>IF(V15&gt;0,V15*הגדרות!$B$4,"")</f>
         <v>109.5</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>0</v>
       </c>
-      <c r="C15" s="31" t="str">
-        <f>IF(B15&gt;0,B15*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="30">
+      <c r="C16" s="36" t="str">
+        <f>IF(B16&gt;0,B16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="31" t="str">
-        <f>IF(D15&gt;0,D15*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="30">
+      <c r="E16" s="36" t="str">
+        <f>IF(D16&gt;0,D16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="G15" s="31" t="str">
-        <f>IF(F15&gt;0,F15*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="30">
+      <c r="G16" s="36" t="str">
+        <f>IF(F16&gt;0,F16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="31" t="str">
-        <f>IF(H15&gt;0,H15*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="30">
+      <c r="I16" s="36" t="str">
+        <f>IF(H16&gt;0,H16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="K15" s="31" t="str">
-        <f>IF(J15&gt;0,J15*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="L15" s="30">
+      <c r="K16" s="36" t="str">
+        <f>IF(J16&gt;0,J16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M15" s="31" t="str">
-        <f>IF(L15&gt;0,L15*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N15" s="30">
+      <c r="M16" s="36" t="str">
+        <f>IF(L16&gt;0,L16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="O15" s="31" t="str">
-        <f>IF(N15&gt;0,N15*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="P15" s="30">
+      <c r="O16" s="36" t="str">
+        <f>IF(N16&gt;0,N16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>51</v>
       </c>
-      <c r="Q15" s="31">
-        <f>IF(P15&gt;0,P15*הגדרות!$B$4,"")</f>
+      <c r="Q16" s="36">
+        <f>IF(P16&gt;0,P16*הגדרות!$B$4,"")</f>
         <v>186.15</v>
       </c>
-      <c r="R15" s="30">
+      <c r="R16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>91.11</v>
       </c>
-      <c r="S15" s="31">
-        <f>IF(R15&gt;0,R15*הגדרות!$B$4,"")</f>
+      <c r="S16" s="36">
+        <f>IF(R16&gt;0,R16*הגדרות!$B$4,"")</f>
         <v>332.55149999999998</v>
       </c>
-      <c r="T15" s="30">
+      <c r="T16" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
-        <v>0</v>
-      </c>
-      <c r="U15" s="31" t="str">
-        <f>IF(T15&gt;0,T15*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V15" s="32">
+        <v>2.25</v>
+      </c>
+      <c r="U16" s="36">
+        <f>IF(T16&gt;0,T16*הגדרות!$B$4,"")</f>
+        <v>8.2125000000000004</v>
+      </c>
+      <c r="V16" s="32">
         <f t="shared" si="0"/>
-        <v>142.11000000000001</v>
-      </c>
-      <c r="W15" s="33">
-        <f>IF(V15&gt;0,V15*הגדרות!$B$4,"")</f>
-        <v>518.70150000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" s="34" t="s">
+        <v>144.36000000000001</v>
+      </c>
+      <c r="W16" s="33">
+        <f>IF(V16&gt;0,V16*הגדרות!$B$4,"")</f>
+        <v>526.91399999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>1</v>
       </c>
-      <c r="C16" s="36">
-        <f>IF(B16&gt;0,B16*הגדרות!$B$4,"")</f>
+      <c r="C17" s="31">
+        <f>IF(B17&gt;0,B17*הגדרות!$B$4,"")</f>
         <v>3.65</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>12</v>
       </c>
-      <c r="E16" s="36">
-        <f>IF(D16&gt;0,D16*הגדרות!$B$4,"")</f>
+      <c r="E17" s="31">
+        <f>IF(D17&gt;0,D17*הגדרות!$B$4,"")</f>
         <v>43.8</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="G16" s="36" t="str">
-        <f>IF(F16&gt;0,F16*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="35">
+      <c r="G17" s="31" t="str">
+        <f>IF(F17&gt;0,F17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="36" t="str">
-        <f>IF(H16&gt;0,H16*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="35">
+      <c r="I17" s="31" t="str">
+        <f>IF(H17&gt;0,H17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>12</v>
       </c>
-      <c r="K16" s="36">
-        <f>IF(J16&gt;0,J16*הגדרות!$B$4,"")</f>
+      <c r="K17" s="31">
+        <f>IF(J17&gt;0,J17*הגדרות!$B$4,"")</f>
         <v>43.8</v>
       </c>
-      <c r="L16" s="35">
+      <c r="L17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M16" s="36" t="str">
-        <f>IF(L16&gt;0,L16*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N16" s="35">
+      <c r="M17" s="31" t="str">
+        <f>IF(L17&gt;0,L17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="O16" s="36" t="str">
-        <f>IF(N16&gt;0,N16*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="P16" s="35">
+      <c r="O17" s="31" t="str">
+        <f>IF(N17&gt;0,N17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="36" t="str">
-        <f>IF(P16&gt;0,P16*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="R16" s="35">
+      <c r="Q17" s="31" t="str">
+        <f>IF(P17&gt;0,P17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>0</v>
       </c>
-      <c r="S16" s="36" t="str">
-        <f>IF(R16&gt;0,R16*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="T16" s="35">
+      <c r="S17" s="31" t="str">
+        <f>IF(R17&gt;0,R17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T17" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U16" s="36" t="str">
-        <f>IF(T16&gt;0,T16*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V16" s="32">
+      <c r="U17" s="31" t="str">
+        <f>IF(T17&gt;0,T17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V17" s="32">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="W16" s="33">
-        <f>IF(V16&gt;0,V16*הגדרות!$B$4,"")</f>
+      <c r="W17" s="33">
+        <f>IF(V17&gt;0,V17*הגדרות!$B$4,"")</f>
         <v>91.25</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>10</v>
       </c>
-      <c r="C17" s="31">
-        <f>IF(B17&gt;0,B17*הגדרות!$B$4,"")</f>
+      <c r="C18" s="36">
+        <f>IF(B18&gt;0,B18*הגדרות!$B$4,"")</f>
         <v>36.5</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>0.9</v>
       </c>
-      <c r="E17" s="31">
-        <f>IF(D17&gt;0,D17*הגדרות!$B$4,"")</f>
+      <c r="E18" s="36">
+        <f>IF(D18&gt;0,D18*הגדרות!$B$4,"")</f>
         <v>3.2850000000000001</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>2.79</v>
       </c>
-      <c r="G17" s="31">
-        <f>IF(F17&gt;0,F17*הגדרות!$B$4,"")</f>
+      <c r="G18" s="36">
+        <f>IF(F18&gt;0,F18*הגדרות!$B$4,"")</f>
         <v>10.1835</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="31" t="str">
-        <f>IF(H17&gt;0,H17*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="30">
+      <c r="I18" s="36" t="str">
+        <f>IF(H18&gt;0,H18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="K17" s="31" t="str">
-        <f>IF(J17&gt;0,J17*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="30">
+      <c r="K18" s="36" t="str">
+        <f>IF(J18&gt;0,J18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M17" s="31" t="str">
-        <f>IF(L17&gt;0,L17*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="30">
+      <c r="M18" s="36" t="str">
+        <f>IF(L18&gt;0,L18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="O17" s="31" t="str">
-        <f>IF(N17&gt;0,N17*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="P17" s="30">
+      <c r="O18" s="36" t="str">
+        <f>IF(N18&gt;0,N18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="31" t="str">
-        <f>IF(P17&gt;0,P17*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="R17" s="30">
+      <c r="Q18" s="36" t="str">
+        <f>IF(P18&gt;0,P18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>0</v>
       </c>
-      <c r="S17" s="31" t="str">
-        <f>IF(R17&gt;0,R17*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="T17" s="30">
+      <c r="S18" s="36" t="str">
+        <f>IF(R18&gt;0,R18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T18" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U17" s="31" t="str">
-        <f>IF(T17&gt;0,T17*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V17" s="32">
+      <c r="U18" s="36" t="str">
+        <f>IF(T18&gt;0,T18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V18" s="32">
         <f t="shared" si="0"/>
         <v>13.690000000000001</v>
       </c>
-      <c r="W17" s="33">
-        <f>IF(V17&gt;0,V17*הגדרות!$B$4,"")</f>
+      <c r="W18" s="33">
+        <f>IF(V18&gt;0,V18*הגדרות!$B$4,"")</f>
         <v>49.968500000000006</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>13.5</v>
       </c>
-      <c r="C18" s="36">
-        <f>IF(B18&gt;0,B18*הגדרות!$B$4,"")</f>
+      <c r="C19" s="31">
+        <f>IF(B19&gt;0,B19*הגדרות!$B$4,"")</f>
         <v>49.274999999999999</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>26.25</v>
       </c>
-      <c r="E18" s="36">
-        <f>IF(D18&gt;0,D18*הגדרות!$B$4,"")</f>
+      <c r="E19" s="31">
+        <f>IF(D19&gt;0,D19*הגדרות!$B$4,"")</f>
         <v>95.8125</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="G18" s="36" t="str">
-        <f>IF(F18&gt;0,F18*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="35">
+      <c r="G19" s="31" t="str">
+        <f>IF(F19&gt;0,F19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I18" s="36" t="str">
-        <f>IF(H18&gt;0,H18*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="35">
+      <c r="I19" s="31" t="str">
+        <f>IF(H19&gt;0,H19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>15</v>
       </c>
-      <c r="K18" s="36">
-        <f>IF(J18&gt;0,J18*הגדרות!$B$4,"")</f>
+      <c r="K19" s="31">
+        <f>IF(J19&gt;0,J19*הגדרות!$B$4,"")</f>
         <v>54.75</v>
       </c>
-      <c r="L18" s="35">
+      <c r="L19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M18" s="36" t="str">
-        <f>IF(L18&gt;0,L18*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N18" s="35">
+      <c r="M19" s="31" t="str">
+        <f>IF(L19&gt;0,L19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="O18" s="36" t="str">
-        <f>IF(N18&gt;0,N18*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="P18" s="35">
+      <c r="O19" s="31" t="str">
+        <f>IF(N19&gt;0,N19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="36" t="str">
-        <f>IF(P18&gt;0,P18*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="R18" s="35">
+      <c r="Q19" s="31" t="str">
+        <f>IF(P19&gt;0,P19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>0</v>
       </c>
-      <c r="S18" s="36" t="str">
-        <f>IF(R18&gt;0,R18*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="T18" s="35">
+      <c r="S19" s="31" t="str">
+        <f>IF(R19&gt;0,R19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T19" s="30">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U18" s="36" t="str">
-        <f>IF(T18&gt;0,T18*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V18" s="32">
+      <c r="U19" s="31" t="str">
+        <f>IF(T19&gt;0,T19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V19" s="32">
         <f t="shared" si="0"/>
         <v>54.75</v>
       </c>
-      <c r="W18" s="33">
-        <f>IF(V18&gt;0,V18*הגדרות!$B$4,"")</f>
+      <c r="W19" s="33">
+        <f>IF(V19&gt;0,V19*הגדרות!$B$4,"")</f>
         <v>199.83750000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v>0</v>
       </c>
-      <c r="C19" s="31" t="str">
-        <f>IF(B19&gt;0,B19*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="30">
+      <c r="C20" s="36" t="str">
+        <f>IF(B20&gt;0,B20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="31" t="str">
-        <f>IF(D19&gt;0,D19*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="30">
+      <c r="E20" s="36" t="str">
+        <f>IF(D20&gt;0,D20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="G19" s="31" t="str">
-        <f>IF(F19&gt;0,F19*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="30">
+      <c r="G20" s="36" t="str">
+        <f>IF(F20&gt;0,F20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="31" t="str">
-        <f>IF(H19&gt;0,H19*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="30">
+      <c r="I20" s="36" t="str">
+        <f>IF(H20&gt;0,H20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="K19" s="31" t="str">
-        <f>IF(J19&gt;0,J19*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="L19" s="30">
+      <c r="K20" s="36" t="str">
+        <f>IF(J20&gt;0,J20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v>0</v>
       </c>
-      <c r="M19" s="31" t="str">
-        <f>IF(L19&gt;0,L19*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="N19" s="30">
+      <c r="M20" s="36" t="str">
+        <f>IF(L20&gt;0,L20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v>14.5</v>
       </c>
-      <c r="O19" s="31">
-        <f>IF(N19&gt;0,N19*הגדרות!$B$4,"")</f>
+      <c r="O20" s="36">
+        <f>IF(N20&gt;0,N20*הגדרות!$B$4,"")</f>
         <v>52.924999999999997</v>
       </c>
-      <c r="P19" s="30">
+      <c r="P20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="31" t="str">
-        <f>IF(P19&gt;0,P19*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="R19" s="30">
+      <c r="Q20" s="36" t="str">
+        <f>IF(P20&gt;0,P20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v>14.5</v>
       </c>
-      <c r="S19" s="31">
-        <f>IF(R19&gt;0,R19*הגדרות!$B$4,"")</f>
+      <c r="S20" s="36">
+        <f>IF(R20&gt;0,R20*הגדרות!$B$4,"")</f>
         <v>52.924999999999997</v>
       </c>
-      <c r="T19" s="30">
+      <c r="T20" s="35">
         <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v>0</v>
       </c>
-      <c r="U19" s="31" t="str">
-        <f>IF(T19&gt;0,T19*הגדרות!$B$4,"")</f>
-        <v/>
-      </c>
-      <c r="V19" s="32">
+      <c r="U20" s="36" t="str">
+        <f>IF(T20&gt;0,T20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V20" s="32">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="W19" s="33">
-        <f>IF(V19&gt;0,V19*הגדרות!$B$4,"")</f>
+      <c r="W20" s="33">
+        <f>IF(V20&gt;0,V20*הגדרות!$B$4,"")</f>
         <v>105.85</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="16">
-        <f t="shared" ref="B20:W20" si="1">SUM(B5:B19)</f>
+    <row r="21" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21" s="16">
+        <f t="shared" ref="B21:W21" si="1">SUM(B5:B20)</f>
         <v>240.23</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C21" s="17">
         <f t="shared" si="1"/>
         <v>876.83949999999993</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D21" s="16">
         <f t="shared" si="1"/>
         <v>93.740000000000009</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E21" s="17">
         <f t="shared" si="1"/>
         <v>342.15099999999995</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F21" s="16">
         <f t="shared" si="1"/>
         <v>38.380000000000003</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G21" s="17">
         <f t="shared" si="1"/>
         <v>140.08700000000002</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H21" s="16">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I21" s="17">
         <f t="shared" si="1"/>
         <v>91.25</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J21" s="16">
         <f t="shared" si="1"/>
         <v>73.8</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K21" s="17">
         <f t="shared" si="1"/>
         <v>269.37</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L21" s="16">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M20" s="17">
+      <c r="M21" s="17">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N21" s="16">
         <f t="shared" si="1"/>
         <v>214.42</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O21" s="17">
         <f t="shared" si="1"/>
         <v>782.63299999999992</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P21" s="16">
         <f t="shared" si="1"/>
         <v>156</v>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q21" s="17">
         <f t="shared" si="1"/>
         <v>569.4</v>
       </c>
-      <c r="R20" s="16">
+      <c r="R21" s="16">
         <f t="shared" si="1"/>
-        <v>146.61000000000001</v>
-      </c>
-      <c r="S20" s="17">
+        <v>151.61000000000001</v>
+      </c>
+      <c r="S21" s="17">
         <f t="shared" si="1"/>
-        <v>535.12649999999996</v>
-      </c>
-      <c r="T20" s="16">
+        <v>553.37649999999996</v>
+      </c>
+      <c r="T21" s="16">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="U20" s="17">
+        <v>47.25</v>
+      </c>
+      <c r="U21" s="17">
         <f t="shared" si="1"/>
-        <v>91.25</v>
-      </c>
-      <c r="V20" s="37">
+        <v>172.46250000000001</v>
+      </c>
+      <c r="V21" s="37">
         <f t="shared" si="1"/>
-        <v>1033.18</v>
-      </c>
-      <c r="W20" s="38">
+        <v>1060.43</v>
+      </c>
+      <c r="W21" s="38">
         <f t="shared" si="1"/>
-        <v>3771.107</v>
+        <v>3870.5694999999996</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +4018,7 @@
       </c>
       <c r="E4" s="42">
         <f>IF(C15&gt;0,C4/C15,0)</f>
-        <v>0.23251514740897036</v>
+        <v>0.2265401770979697</v>
       </c>
       <c r="F4" s="19"/>
     </row>
@@ -3871,7 +4039,7 @@
       </c>
       <c r="E5" s="46">
         <f>IF(C15&gt;0,C5/C15,0)</f>
-        <v>9.0729592133026185E-2</v>
+        <v>8.8398102656469538E-2</v>
       </c>
       <c r="F5" s="24"/>
     </row>
@@ -3892,7 +4060,7 @@
       </c>
       <c r="E6" s="42">
         <f>IF(C15&gt;0,C6/C15,0)</f>
-        <v>3.7147447685785623E-2</v>
+        <v>3.619286515847344E-2</v>
       </c>
       <c r="F6" s="19"/>
     </row>
@@ -3913,7 +4081,7 @@
       </c>
       <c r="E7" s="46">
         <f>IF(C15&gt;0,C7/C15,0)</f>
-        <v>2.4197138930292881E-2</v>
+        <v>2.3575342078213553E-2</v>
       </c>
       <c r="F7" s="24"/>
     </row>
@@ -3934,7 +4102,7 @@
       </c>
       <c r="E8" s="42">
         <f>IF(C15&gt;0,C8/C15,0)</f>
-        <v>7.1429954122224582E-2</v>
+        <v>6.9594409814886404E-2</v>
       </c>
       <c r="F8" s="19"/>
     </row>
@@ -3955,7 +4123,7 @@
       </c>
       <c r="E9" s="46">
         <f>IF(C15&gt;0,C9/C15,0)</f>
-        <v>1.9357711144234305E-2</v>
+        <v>1.8860273662570842E-2</v>
       </c>
       <c r="F9" s="24"/>
     </row>
@@ -3976,7 +4144,7 @@
       </c>
       <c r="E10" s="42">
         <f>IF(C15&gt;0,C10/C15,0)</f>
-        <v>0.20753402117733596</v>
+        <v>0.20220099393642199</v>
       </c>
       <c r="F10" s="19"/>
     </row>
@@ -3997,7 +4165,7 @@
       </c>
       <c r="E11" s="46">
         <f>IF(C15&gt;0,C11/C15,0)</f>
-        <v>0.15099014692502757</v>
+        <v>0.14711013456805258</v>
       </c>
       <c r="F11" s="24"/>
     </row>
@@ -4010,15 +4178,15 @@
       </c>
       <c r="C12" s="40">
         <f>SUMIF('כל ההוצאות'!$F:$F,"מרץ 2026",'כל ההוצאות'!$D:$D)</f>
-        <v>146.61000000000001</v>
+        <v>151.61000000000001</v>
       </c>
       <c r="D12" s="41">
         <f>C12*הגדרות!$B$4</f>
-        <v>535.12650000000008</v>
+        <v>553.37650000000008</v>
       </c>
       <c r="E12" s="42">
         <f>IF(C15&gt;0,C12/C15,0)</f>
-        <v>0.14190170154280959</v>
+        <v>0.14297030449911829</v>
       </c>
       <c r="F12" s="19"/>
     </row>
@@ -4031,15 +4199,15 @@
       </c>
       <c r="C13" s="44">
         <f>SUMIF('כל ההוצאות'!$F:$F,"אפריל 2026",'כל ההוצאות'!$D:$D)</f>
-        <v>25</v>
+        <v>47.25</v>
       </c>
       <c r="D13" s="45">
         <f>C13*הגדרות!$B$4</f>
-        <v>91.25</v>
+        <v>172.46250000000001</v>
       </c>
       <c r="E13" s="46">
         <f>IF(C15&gt;0,C13/C15,0)</f>
-        <v>2.4197138930292881E-2</v>
+        <v>4.4557396527823617E-2</v>
       </c>
       <c r="F13" s="24"/>
     </row>
@@ -4058,11 +4226,11 @@
       <c r="B15" s="58"/>
       <c r="C15" s="47">
         <f>SUM(C4:C13)</f>
-        <v>1033.18</v>
+        <v>1060.43</v>
       </c>
       <c r="D15" s="48">
         <f>C15*הגדרות!$B$4</f>
-        <v>3771.107</v>
+        <v>3870.5695000000001</v>
       </c>
       <c r="E15" s="49" t="s">
         <v>29</v>
@@ -4076,11 +4244,11 @@
       <c r="B16" s="55"/>
       <c r="C16" s="50">
         <f>AVERAGE(C4:C13)</f>
-        <v>103.31800000000001</v>
+        <v>106.04300000000001</v>
       </c>
       <c r="D16" s="51">
         <f>AVERAGE(D4:D13)</f>
-        <v>377.11070000000001</v>
+        <v>387.05695000000003</v>
       </c>
       <c r="E16" s="19"/>
       <c r="F16" s="19"/>
@@ -4114,7 +4282,7 @@
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5146,63 +5314,126 @@
         <v>123</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="D50" s="12">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E50" s="13">
         <f>D50*הגדרות!$B$4</f>
-        <v>73</v>
+        <v>18.25</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="D51" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E51" s="9">
         <f>D51*הגדרות!$B$4</f>
-        <v>18.25</v>
+        <v>73</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="62" t="s">
-        <v>124</v>
-      </c>
-      <c r="B52" s="63"/>
-      <c r="C52" s="63"/>
-      <c r="D52" s="16">
-        <f>SUM(D3:D51)</f>
-        <v>1033.1799999999998</v>
-      </c>
-      <c r="E52" s="17">
-        <f>SUM(E3:E51)</f>
-        <v>3771.1070000000004</v>
-      </c>
-      <c r="F52" s="15"/>
+      <c r="A52" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" s="12">
+        <v>5</v>
+      </c>
+      <c r="E52" s="13">
+        <f>D52*הגדרות!$B$4</f>
+        <v>18.25</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="8">
+        <v>2.25</v>
+      </c>
+      <c r="E53" s="9">
+        <f>D53*הגדרות!$B$4</f>
+        <v>8.2125000000000004</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D54" s="12">
+        <v>20</v>
+      </c>
+      <c r="E54" s="13">
+        <f>D54*הגדרות!$B$4</f>
+        <v>73</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="16">
+        <f>SUM(D3:D54)</f>
+        <v>1060.4299999999998</v>
+      </c>
+      <c r="E55" s="17">
+        <f>SUM(E3:E54)</f>
+        <v>3870.5695000000005</v>
+      </c>
+      <c r="F55" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A55:C55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5225,7 +5456,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -5235,7 +5466,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -5396,7 +5627,7 @@
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
@@ -5439,7 +5670,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -5449,7 +5680,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -5629,7 +5860,7 @@
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
@@ -5672,7 +5903,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -5682,7 +5913,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -5786,7 +6017,7 @@
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B8" s="58"/>
       <c r="C8" s="58"/>
@@ -5829,7 +6060,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -5839,7 +6070,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -5905,7 +6136,7 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
@@ -5948,7 +6179,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -5958,7 +6189,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -6100,7 +6331,7 @@
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
@@ -6143,7 +6374,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -6153,7 +6384,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -6219,7 +6450,7 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
@@ -6262,7 +6493,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -6272,7 +6503,7 @@
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -6414,7 +6645,7 @@
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="13" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="14" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="סיכום חודשי" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="דוח שנתי" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="סיכום חודשי" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="דוח שנתי" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,12 +511,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'דוח שנתי'!$A$4:$A$13</f>
+              <f>'דוח שנתי'!$A$4:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'דוח שנתי'!$C$4:$C$13</f>
+              <f>'דוח שנתי'!$C$4:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -591,7 +592,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="4320000"/>
@@ -902,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -953,9 +954,24 @@
     </row>
     <row r="7"/>
     <row r="8"/>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>חיובים קבועים:</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>OpenAI / ChatGPT Plus – $20 בכל 16 לחודש. החיוב מתווסף אוטומטית לכל חודש בדוחות, בגליונות ובדשבורד, וכאשר תגיע חשבונית OpenAI במייל היא אמורה להיות מזוהה תחת אותו כלי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B10:E12"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B6:E8"/>
   </mergeCells>
@@ -970,7 +986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1081,21 +1097,21 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Pro – Feb 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.67</v>
+        <v>31.42</v>
       </c>
       <c r="E6" s="26">
         <f>D6*הגדרות!$B$4</f>
@@ -1106,21 +1122,21 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Pro – Feb 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20</v>
+        <v>13.67</v>
       </c>
       <c r="E7" s="28">
         <f>D7*הגדרות!$B$4</f>
@@ -1131,21 +1147,21 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E8" s="26">
         <f>D8*הגדרות!$B$4</f>
@@ -1156,17 +1172,17 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
@@ -1181,21 +1197,21 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E10" s="26">
         <f>D10*הגדרות!$B$4</f>
@@ -1206,21 +1222,21 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E11" s="28">
         <f>D11*הגדרות!$B$4</f>
@@ -1231,21 +1247,21 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>On-Demand credits 500</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E12" s="26">
         <f>D12*הגדרות!$B$4</f>
@@ -1253,27 +1269,127 @@
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Pro2 monthly</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" s="28">
+        <f>D13*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F13" s="29" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>51</v>
+      </c>
+      <c r="E14" s="26">
+        <f>D14*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F14" s="24" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="28">
+        <f>D15*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F15" s="29" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Balance Top-up</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="26">
+        <f>D16*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="20">
-        <f>SUM(D4:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="21">
-        <f>SUM(E4:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="20">
+        <f>SUM(D4:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>SUM(E4:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -1290,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1356,16 +1472,16 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="E4" s="26">
         <f>D4*הגדרות!$B$4</f>
@@ -1376,21 +1492,21 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Timeless</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Feb 2026 (₪75.90)</t>
+          <t>Pro monthly (50% off)</t>
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>20.79</v>
+        <v>14.5</v>
       </c>
       <c r="E5" s="28">
         <f>D5*הגדרות!$B$4</f>
@@ -1401,21 +1517,21 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Business Plus – Feb 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>40.11</v>
+        <v>20.79</v>
       </c>
       <c r="E6" s="26">
         <f>D6*הגדרות!$B$4</f>
@@ -1426,21 +1542,21 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Pro – Mar 2026 (₪49.90)</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>13.67</v>
+        <v>10</v>
       </c>
       <c r="E7" s="28">
         <f>D7*הגדרות!$B$4</f>
@@ -1451,7 +1567,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -1465,7 +1581,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>51</v>
+        <v>40.11</v>
       </c>
       <c r="E8" s="26">
         <f>D8*הגדרות!$B$4</f>
@@ -1476,21 +1592,21 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Pro – Mar 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20</v>
+        <v>13.67</v>
       </c>
       <c r="E9" s="28">
         <f>D9*הגדרות!$B$4</f>
@@ -1501,21 +1617,21 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="E10" s="26">
         <f>D10*הגדרות!$B$4</f>
@@ -1526,21 +1642,21 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E11" s="28">
         <f>D11*הגדרות!$B$4</f>
@@ -1551,21 +1667,21 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E12" s="26">
         <f>D12*הגדרות!$B$4</f>
@@ -1573,28 +1689,103 @@
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Credit purchase</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="28">
+        <f>D13*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F13" s="29" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Creator (first month 50% off)</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" s="26">
+        <f>D14*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F14" s="24" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Lite plan</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="28">
+        <f>D15*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="20">
-        <f>SUM(D4:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="21">
-        <f>SUM(E4:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="31" t="n"/>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="20">
+        <f>SUM(D4:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>SUM(E4:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -1610,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1746,7 +1937,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -1760,7 +1951,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>2.25</v>
+        <v>51</v>
       </c>
       <c r="E7" s="28">
         <f>D7*הגדרות!$B$4</f>
@@ -1771,21 +1962,21 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="E8" s="26">
         <f>D8*הגדרות!$B$4</f>
@@ -1793,28 +1984,78 @@
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>IONOS</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Instant Domain</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="28">
+        <f>D9*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F9" s="29" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="26">
+        <f>D10*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n"/>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="20">
-        <f>SUM(D4:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="21">
-        <f>SUM(E4:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="31" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="20">
+        <f>SUM(D4:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>SUM(E4:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -1826,11 +2067,131 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>מאי 2026  |  May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="20">
+        <f>SUM(D4:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>SUM(E4:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1854,21 +2215,23 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>סיכום חודשי לפי כלי  |  יולי 2025 – אפריל 2026</t>
+          <t>סיכום חודשי לפי כלי  |  יולי 2025 – מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="32" t="inlineStr">
         <is>
-          <t>לחץ על שם חודש כדי לצפייה בגליון המפורט ↓</t>
+          <t>לחץ על שם חודש כדי לצפייה בגליון המפורט ↓  |  OpenAI / ChatGPT Plus מתווסף אוטומטית ב-16 לכל חודש</t>
         </is>
       </c>
     </row>
@@ -1938,12 +2301,18 @@
 (April 2026)</t>
         </is>
       </c>
-      <c r="V3" s="18" t="inlineStr">
+      <c r="V3" s="33" t="inlineStr">
+        <is>
+          <t>מאי 2026
+(May 2026)</t>
+        </is>
+      </c>
+      <c r="X3" s="18" t="inlineStr">
         <is>
           <t>סה"כ ($)</t>
         </is>
       </c>
-      <c r="W3" s="18" t="inlineStr">
+      <c r="Y3" s="18" t="inlineStr">
         <is>
           <t>סה"כ (₪)</t>
         </is>
@@ -2051,12 +2420,22 @@
           <t>₪</t>
         </is>
       </c>
-      <c r="V4" s="35" t="inlineStr">
+      <c r="V4" s="34" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="W4" s="35" t="inlineStr">
+      <c r="W4" s="34" t="inlineStr">
+        <is>
+          <t>₪</t>
+        </is>
+      </c>
+      <c r="X4" s="35" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="Y4" s="35" t="inlineStr">
         <is>
           <t>₪</t>
         </is>
@@ -2148,12 +2527,20 @@
         <f>IF(T5&gt;0,T5*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V5" s="39">
-        <f>SUM(B5,D5,F5,H5,J5,L5,N5,P5,R5,T5)</f>
-        <v/>
-      </c>
-      <c r="W5" s="40">
+      <c r="V5" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W5" s="38">
         <f>IF(V5&gt;0,V5*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X5" s="39">
+        <f>SUM(B5,D5,F5,H5,J5,L5,N5,P5,R5,T5,V5)</f>
+        <v/>
+      </c>
+      <c r="Y5" s="40">
+        <f>IF(X5&gt;0,X5*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2243,12 +2630,20 @@
         <f>IF(T6&gt;0,T6*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V6" s="39">
-        <f>SUM(B6,D6,F6,H6,J6,L6,N6,P6,R6,T6)</f>
-        <v/>
-      </c>
-      <c r="W6" s="40">
+      <c r="V6" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W6" s="43">
         <f>IF(V6&gt;0,V6*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X6" s="39">
+        <f>SUM(B6,D6,F6,H6,J6,L6,N6,P6,R6,T6,V6)</f>
+        <v/>
+      </c>
+      <c r="Y6" s="40">
+        <f>IF(X6&gt;0,X6*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2338,12 +2733,20 @@
         <f>IF(T7&gt;0,T7*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V7" s="39">
-        <f>SUM(B7,D7,F7,H7,J7,L7,N7,P7,R7,T7)</f>
-        <v/>
-      </c>
-      <c r="W7" s="40">
+      <c r="V7" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W7" s="38">
         <f>IF(V7&gt;0,V7*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X7" s="39">
+        <f>SUM(B7,D7,F7,H7,J7,L7,N7,P7,R7,T7,V7)</f>
+        <v/>
+      </c>
+      <c r="Y7" s="40">
+        <f>IF(X7&gt;0,X7*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2433,12 +2836,20 @@
         <f>IF(T8&gt;0,T8*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V8" s="39">
-        <f>SUM(B8,D8,F8,H8,J8,L8,N8,P8,R8,T8)</f>
-        <v/>
-      </c>
-      <c r="W8" s="40">
+      <c r="V8" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W8" s="43">
         <f>IF(V8&gt;0,V8*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X8" s="39">
+        <f>SUM(B8,D8,F8,H8,J8,L8,N8,P8,R8,T8,V8)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="40">
+        <f>IF(X8&gt;0,X8*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2528,12 +2939,20 @@
         <f>IF(T9&gt;0,T9*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V9" s="39">
-        <f>SUM(B9,D9,F9,H9,J9,L9,N9,P9,R9,T9)</f>
-        <v/>
-      </c>
-      <c r="W9" s="40">
+      <c r="V9" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W9" s="38">
         <f>IF(V9&gt;0,V9*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X9" s="39">
+        <f>SUM(B9,D9,F9,H9,J9,L9,N9,P9,R9,T9,V9)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="40">
+        <f>IF(X9&gt;0,X9*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2623,12 +3042,20 @@
         <f>IF(T10&gt;0,T10*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V10" s="39">
-        <f>SUM(B10,D10,F10,H10,J10,L10,N10,P10,R10,T10)</f>
-        <v/>
-      </c>
-      <c r="W10" s="40">
+      <c r="V10" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W10" s="43">
         <f>IF(V10&gt;0,V10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X10" s="39">
+        <f>SUM(B10,D10,F10,H10,J10,L10,N10,P10,R10,T10,V10)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="40">
+        <f>IF(X10&gt;0,X10*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2718,12 +3145,20 @@
         <f>IF(T11&gt;0,T11*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V11" s="39">
-        <f>SUM(B11,D11,F11,H11,J11,L11,N11,P11,R11,T11)</f>
-        <v/>
-      </c>
-      <c r="W11" s="40">
+      <c r="V11" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W11" s="38">
         <f>IF(V11&gt;0,V11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X11" s="39">
+        <f>SUM(B11,D11,F11,H11,J11,L11,N11,P11,R11,T11,V11)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="40">
+        <f>IF(X11&gt;0,X11*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2813,12 +3248,20 @@
         <f>IF(T12&gt;0,T12*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V12" s="39">
-        <f>SUM(B12,D12,F12,H12,J12,L12,N12,P12,R12,T12)</f>
-        <v/>
-      </c>
-      <c r="W12" s="40">
+      <c r="V12" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W12" s="43">
         <f>IF(V12&gt;0,V12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X12" s="39">
+        <f>SUM(B12,D12,F12,H12,J12,L12,N12,P12,R12,T12,V12)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="40">
+        <f>IF(X12&gt;0,X12*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2908,12 +3351,20 @@
         <f>IF(T13&gt;0,T13*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V13" s="39">
-        <f>SUM(B13,D13,F13,H13,J13,L13,N13,P13,R13,T13)</f>
-        <v/>
-      </c>
-      <c r="W13" s="40">
+      <c r="V13" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W13" s="38">
         <f>IF(V13&gt;0,V13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X13" s="39">
+        <f>SUM(B13,D13,F13,H13,J13,L13,N13,P13,R13,T13,V13)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="40">
+        <f>IF(X13&gt;0,X13*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3003,12 +3454,20 @@
         <f>IF(T14&gt;0,T14*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V14" s="39">
-        <f>SUM(B14,D14,F14,H14,J14,L14,N14,P14,R14,T14)</f>
-        <v/>
-      </c>
-      <c r="W14" s="40">
+      <c r="V14" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W14" s="43">
         <f>IF(V14&gt;0,V14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X14" s="39">
+        <f>SUM(B14,D14,F14,H14,J14,L14,N14,P14,R14,T14,V14)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="40">
+        <f>IF(X14&gt;0,X14*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3098,12 +3557,20 @@
         <f>IF(T15&gt;0,T15*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V15" s="39">
-        <f>SUM(B15,D15,F15,H15,J15,L15,N15,P15,R15,T15)</f>
-        <v/>
-      </c>
-      <c r="W15" s="40">
+      <c r="V15" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W15" s="38">
         <f>IF(V15&gt;0,V15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X15" s="39">
+        <f>SUM(B15,D15,F15,H15,J15,L15,N15,P15,R15,T15,V15)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="40">
+        <f>IF(X15&gt;0,X15*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3193,12 +3660,20 @@
         <f>IF(T16&gt;0,T16*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V16" s="39">
-        <f>SUM(B16,D16,F16,H16,J16,L16,N16,P16,R16,T16)</f>
-        <v/>
-      </c>
-      <c r="W16" s="40">
+      <c r="V16" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W16" s="43">
         <f>IF(V16&gt;0,V16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X16" s="39">
+        <f>SUM(B16,D16,F16,H16,J16,L16,N16,P16,R16,T16,V16)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="40">
+        <f>IF(X16&gt;0,X16*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3288,12 +3763,20 @@
         <f>IF(T17&gt;0,T17*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V17" s="39">
-        <f>SUM(B17,D17,F17,H17,J17,L17,N17,P17,R17,T17)</f>
-        <v/>
-      </c>
-      <c r="W17" s="40">
+      <c r="V17" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W17" s="38">
         <f>IF(V17&gt;0,V17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X17" s="39">
+        <f>SUM(B17,D17,F17,H17,J17,L17,N17,P17,R17,T17,V17)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="40">
+        <f>IF(X17&gt;0,X17*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3383,12 +3866,20 @@
         <f>IF(T18&gt;0,T18*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V18" s="39">
-        <f>SUM(B18,D18,F18,H18,J18,L18,N18,P18,R18,T18)</f>
-        <v/>
-      </c>
-      <c r="W18" s="40">
+      <c r="V18" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W18" s="43">
         <f>IF(V18&gt;0,V18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X18" s="39">
+        <f>SUM(B18,D18,F18,H18,J18,L18,N18,P18,R18,T18,V18)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="40">
+        <f>IF(X18&gt;0,X18*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3478,23 +3969,31 @@
         <f>IF(T19&gt;0,T19*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V19" s="39">
-        <f>SUM(B19,D19,F19,H19,J19,L19,N19,P19,R19,T19)</f>
-        <v/>
-      </c>
-      <c r="W19" s="40">
+      <c r="V19" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W19" s="38">
         <f>IF(V19&gt;0,V19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X19" s="39">
+        <f>SUM(B19,D19,F19,H19,J19,L19,N19,P19,R19,T19,V19)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="40">
+        <f>IF(X19&gt;0,X19*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
-          <t>Recraft</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C20" s="43">
@@ -3502,7 +4001,7 @@
         <v/>
       </c>
       <c r="D20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E20" s="43">
@@ -3510,7 +4009,7 @@
         <v/>
       </c>
       <c r="F20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G20" s="43">
@@ -3518,7 +4017,7 @@
         <v/>
       </c>
       <c r="H20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I20" s="43">
@@ -3526,7 +4025,7 @@
         <v/>
       </c>
       <c r="J20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K20" s="43">
@@ -3534,7 +4033,7 @@
         <v/>
       </c>
       <c r="L20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M20" s="43">
@@ -3542,7 +4041,7 @@
         <v/>
       </c>
       <c r="N20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O20" s="43">
@@ -3550,7 +4049,7 @@
         <v/>
       </c>
       <c r="P20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q20" s="43">
@@ -3558,7 +4057,7 @@
         <v/>
       </c>
       <c r="R20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S20" s="43">
@@ -3566,30 +4065,38 @@
         <v/>
       </c>
       <c r="T20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U20" s="43">
         <f>IF(T20&gt;0,T20*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V20" s="39">
-        <f>SUM(B20,D20,F20,H20,J20,L20,N20,P20,R20,T20)</f>
-        <v/>
-      </c>
-      <c r="W20" s="40">
+      <c r="V20" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W20" s="43">
         <f>IF(V20&gt;0,V20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X20" s="39">
+        <f>SUM(B20,D20,F20,H20,J20,L20,N20,P20,R20,T20,V20)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="40">
+        <f>IF(X20&gt;0,X20*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="36" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Recraft</t>
         </is>
       </c>
       <c r="B21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C21" s="38">
@@ -3597,7 +4104,7 @@
         <v/>
       </c>
       <c r="D21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E21" s="38">
@@ -3605,7 +4112,7 @@
         <v/>
       </c>
       <c r="F21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G21" s="38">
@@ -3613,7 +4120,7 @@
         <v/>
       </c>
       <c r="H21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I21" s="38">
@@ -3621,7 +4128,7 @@
         <v/>
       </c>
       <c r="J21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K21" s="38">
@@ -3629,7 +4136,7 @@
         <v/>
       </c>
       <c r="L21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M21" s="38">
@@ -3637,7 +4144,7 @@
         <v/>
       </c>
       <c r="N21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O21" s="38">
@@ -3645,7 +4152,7 @@
         <v/>
       </c>
       <c r="P21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q21" s="38">
@@ -3653,7 +4160,7 @@
         <v/>
       </c>
       <c r="R21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S21" s="38">
@@ -3661,30 +4168,38 @@
         <v/>
       </c>
       <c r="T21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U21" s="38">
         <f>IF(T21&gt;0,T21*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V21" s="39">
-        <f>SUM(B21,D21,F21,H21,J21,L21,N21,P21,R21,T21)</f>
-        <v/>
-      </c>
-      <c r="W21" s="40">
+      <c r="V21" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W21" s="38">
         <f>IF(V21&gt;0,V21*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X21" s="39">
+        <f>SUM(B21,D21,F21,H21,J21,L21,N21,P21,R21,T21,V21)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="40">
+        <f>IF(X21&gt;0,X21*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="41" t="inlineStr">
         <is>
-          <t>Runway ML</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="B22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C22" s="43">
@@ -3692,7 +4207,7 @@
         <v/>
       </c>
       <c r="D22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E22" s="43">
@@ -3700,7 +4215,7 @@
         <v/>
       </c>
       <c r="F22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G22" s="43">
@@ -3708,7 +4223,7 @@
         <v/>
       </c>
       <c r="H22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I22" s="43">
@@ -3716,7 +4231,7 @@
         <v/>
       </c>
       <c r="J22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K22" s="43">
@@ -3724,7 +4239,7 @@
         <v/>
       </c>
       <c r="L22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M22" s="43">
@@ -3732,7 +4247,7 @@
         <v/>
       </c>
       <c r="N22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O22" s="43">
@@ -3740,7 +4255,7 @@
         <v/>
       </c>
       <c r="P22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q22" s="43">
@@ -3748,7 +4263,7 @@
         <v/>
       </c>
       <c r="R22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S22" s="43">
@@ -3756,30 +4271,38 @@
         <v/>
       </c>
       <c r="T22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U22" s="43">
         <f>IF(T22&gt;0,T22*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V22" s="39">
-        <f>SUM(B22,D22,F22,H22,J22,L22,N22,P22,R22,T22)</f>
-        <v/>
-      </c>
-      <c r="W22" s="40">
+      <c r="V22" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W22" s="43">
         <f>IF(V22&gt;0,V22*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X22" s="39">
+        <f>SUM(B22,D22,F22,H22,J22,L22,N22,P22,R22,T22,V22)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="40">
+        <f>IF(X22&gt;0,X22*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="36" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Runway ML</t>
         </is>
       </c>
       <c r="B23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C23" s="38">
@@ -3787,7 +4310,7 @@
         <v/>
       </c>
       <c r="D23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E23" s="38">
@@ -3795,7 +4318,7 @@
         <v/>
       </c>
       <c r="F23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G23" s="38">
@@ -3803,7 +4326,7 @@
         <v/>
       </c>
       <c r="H23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I23" s="38">
@@ -3811,7 +4334,7 @@
         <v/>
       </c>
       <c r="J23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K23" s="38">
@@ -3819,7 +4342,7 @@
         <v/>
       </c>
       <c r="L23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M23" s="38">
@@ -3827,7 +4350,7 @@
         <v/>
       </c>
       <c r="N23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O23" s="38">
@@ -3835,7 +4358,7 @@
         <v/>
       </c>
       <c r="P23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q23" s="38">
@@ -3843,7 +4366,7 @@
         <v/>
       </c>
       <c r="R23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S23" s="38">
@@ -3851,129 +4374,249 @@
         <v/>
       </c>
       <c r="T23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U23" s="38">
         <f>IF(T23&gt;0,T23*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="V23" s="39">
-        <f>SUM(B23,D23,F23,H23,J23,L23,N23,P23,R23,T23)</f>
-        <v/>
-      </c>
-      <c r="W23" s="40">
+      <c r="V23" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W23" s="38">
         <f>IF(V23&gt;0,V23*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="X23" s="39">
+        <f>SUM(B23,D23,F23,H23,J23,L23,N23,P23,R23,T23,V23)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="40">
+        <f>IF(X23&gt;0,X23*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>Timeless</t>
+        </is>
+      </c>
+      <c r="B24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <v/>
+      </c>
+      <c r="C24" s="43">
+        <f>IF(B24&gt;0,B24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <v/>
+      </c>
+      <c r="E24" s="43">
+        <f>IF(D24&gt;0,D24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="G24" s="43">
+        <f>IF(F24&gt;0,F24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <v/>
+      </c>
+      <c r="I24" s="43">
+        <f>IF(H24&gt;0,H24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="K24" s="43">
+        <f>IF(J24&gt;0,J24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="M24" s="43">
+        <f>IF(L24&gt;0,L24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <v/>
+      </c>
+      <c r="O24" s="43">
+        <f>IF(N24&gt;0,N24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="43">
+        <f>IF(P24&gt;0,P24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="R24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <v/>
+      </c>
+      <c r="S24" s="43">
+        <f>IF(R24&gt;0,R24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="T24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <v/>
+      </c>
+      <c r="U24" s="43">
+        <f>IF(T24&gt;0,T24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="V24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W24" s="43">
+        <f>IF(V24&gt;0,V24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="X24" s="39">
+        <f>SUM(B24,D24,F24,H24,J24,L24,N24,P24,R24,T24,V24)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="40">
+        <f>IF(X24&gt;0,X24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודשי</t>
         </is>
       </c>
-      <c r="B24" s="20">
-        <f>SUM(B5:B23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="21">
-        <f>SUM(C5:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="20">
-        <f>SUM(D5:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>SUM(E5:E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="20">
-        <f>SUM(F5:F23)</f>
-        <v/>
-      </c>
-      <c r="G24" s="21">
-        <f>SUM(G5:G23)</f>
-        <v/>
-      </c>
-      <c r="H24" s="20">
-        <f>SUM(H5:H23)</f>
-        <v/>
-      </c>
-      <c r="I24" s="21">
-        <f>SUM(I5:I23)</f>
-        <v/>
-      </c>
-      <c r="J24" s="20">
-        <f>SUM(J5:J23)</f>
-        <v/>
-      </c>
-      <c r="K24" s="21">
-        <f>SUM(K5:K23)</f>
-        <v/>
-      </c>
-      <c r="L24" s="20">
-        <f>SUM(L5:L23)</f>
-        <v/>
-      </c>
-      <c r="M24" s="21">
-        <f>SUM(M5:M23)</f>
-        <v/>
-      </c>
-      <c r="N24" s="20">
-        <f>SUM(N5:N23)</f>
-        <v/>
-      </c>
-      <c r="O24" s="21">
-        <f>SUM(O5:O23)</f>
-        <v/>
-      </c>
-      <c r="P24" s="20">
-        <f>SUM(P5:P23)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="21">
-        <f>SUM(Q5:Q23)</f>
-        <v/>
-      </c>
-      <c r="R24" s="20">
-        <f>SUM(R5:R23)</f>
-        <v/>
-      </c>
-      <c r="S24" s="21">
-        <f>SUM(S5:S23)</f>
-        <v/>
-      </c>
-      <c r="T24" s="20">
-        <f>SUM(T5:T23)</f>
-        <v/>
-      </c>
-      <c r="U24" s="21">
-        <f>SUM(U5:U23)</f>
-        <v/>
-      </c>
-      <c r="V24" s="44">
-        <f>SUM(V5:V23)</f>
-        <v/>
-      </c>
-      <c r="W24" s="45">
-        <f>SUM(W5:W23)</f>
+      <c r="B25" s="20">
+        <f>SUM(B5:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="21">
+        <f>SUM(C5:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="20">
+        <f>SUM(D5:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>SUM(E5:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="20">
+        <f>SUM(F5:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f>SUM(G5:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="20">
+        <f>SUM(H5:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="21">
+        <f>SUM(I5:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="20">
+        <f>SUM(J5:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="21">
+        <f>SUM(K5:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="20">
+        <f>SUM(L5:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="21">
+        <f>SUM(M5:M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="20">
+        <f>SUM(N5:N24)</f>
+        <v/>
+      </c>
+      <c r="O25" s="21">
+        <f>SUM(O5:O24)</f>
+        <v/>
+      </c>
+      <c r="P25" s="20">
+        <f>SUM(P5:P24)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="21">
+        <f>SUM(Q5:Q24)</f>
+        <v/>
+      </c>
+      <c r="R25" s="20">
+        <f>SUM(R5:R24)</f>
+        <v/>
+      </c>
+      <c r="S25" s="21">
+        <f>SUM(S5:S24)</f>
+        <v/>
+      </c>
+      <c r="T25" s="20">
+        <f>SUM(T5:T24)</f>
+        <v/>
+      </c>
+      <c r="U25" s="21">
+        <f>SUM(U5:U24)</f>
+        <v/>
+      </c>
+      <c r="V25" s="20">
+        <f>SUM(V5:V24)</f>
+        <v/>
+      </c>
+      <c r="W25" s="21">
+        <f>SUM(W5:W24)</f>
+        <v/>
+      </c>
+      <c r="X25" s="44">
+        <f>SUM(X5:X24)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="45">
+        <f>SUM(Y5:Y24)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A2:V2"/>
+  <mergeCells count="13">
     <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:X2"/>
     <mergeCell ref="R3:S3"/>
+    <mergeCell ref="A1:X1"/>
     <mergeCell ref="D3:E3"/>
+    <mergeCell ref="V3:W3"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="H3:I3"/>
   </mergeCells>
@@ -3988,19 +4631,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4021,7 +4665,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="46" t="inlineStr">
         <is>
-          <t>סיכום הוצאות לפי חודש – יולי 2025 עד אפריל 2026</t>
+          <t>סיכום הוצאות לפי חודש – יולי 2025 – מאי 2026</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4721,7 @@
         <v/>
       </c>
       <c r="E4" s="50">
-        <f>IF(C15&gt;0,C4/C15,0)</f>
+        <f>IF(C16&gt;0,C4/C16,0)</f>
         <v/>
       </c>
       <c r="F4" s="24" t="n"/>
@@ -4102,7 +4746,7 @@
         <v/>
       </c>
       <c r="E5" s="54">
-        <f>IF(C15&gt;0,C5/C15,0)</f>
+        <f>IF(C16&gt;0,C5/C16,0)</f>
         <v/>
       </c>
       <c r="F5" s="29" t="n"/>
@@ -4127,7 +4771,7 @@
         <v/>
       </c>
       <c r="E6" s="50">
-        <f>IF(C15&gt;0,C6/C15,0)</f>
+        <f>IF(C16&gt;0,C6/C16,0)</f>
         <v/>
       </c>
       <c r="F6" s="24" t="n"/>
@@ -4152,7 +4796,7 @@
         <v/>
       </c>
       <c r="E7" s="54">
-        <f>IF(C15&gt;0,C7/C15,0)</f>
+        <f>IF(C16&gt;0,C7/C16,0)</f>
         <v/>
       </c>
       <c r="F7" s="29" t="n"/>
@@ -4177,7 +4821,7 @@
         <v/>
       </c>
       <c r="E8" s="50">
-        <f>IF(C15&gt;0,C8/C15,0)</f>
+        <f>IF(C16&gt;0,C8/C16,0)</f>
         <v/>
       </c>
       <c r="F8" s="24" t="n"/>
@@ -4202,7 +4846,7 @@
         <v/>
       </c>
       <c r="E9" s="54">
-        <f>IF(C15&gt;0,C9/C15,0)</f>
+        <f>IF(C16&gt;0,C9/C16,0)</f>
         <v/>
       </c>
       <c r="F9" s="29" t="n"/>
@@ -4227,7 +4871,7 @@
         <v/>
       </c>
       <c r="E10" s="50">
-        <f>IF(C15&gt;0,C10/C15,0)</f>
+        <f>IF(C16&gt;0,C10/C16,0)</f>
         <v/>
       </c>
       <c r="F10" s="24" t="n"/>
@@ -4252,7 +4896,7 @@
         <v/>
       </c>
       <c r="E11" s="54">
-        <f>IF(C15&gt;0,C11/C15,0)</f>
+        <f>IF(C16&gt;0,C11/C16,0)</f>
         <v/>
       </c>
       <c r="F11" s="29" t="n"/>
@@ -4277,7 +4921,7 @@
         <v/>
       </c>
       <c r="E12" s="50">
-        <f>IF(C15&gt;0,C12/C15,0)</f>
+        <f>IF(C16&gt;0,C12/C16,0)</f>
         <v/>
       </c>
       <c r="F12" s="24" t="n"/>
@@ -4302,65 +4946,90 @@
         <v/>
       </c>
       <c r="E13" s="54">
-        <f>IF(C15&gt;0,C13/C15,0)</f>
+        <f>IF(C16&gt;0,C13/C16,0)</f>
         <v/>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="24" t="n"/>
-      <c r="B14" s="24" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="24" t="n"/>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>מאי 2026</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="48">
+        <f>SUMIF('כל ההוצאות'!$F:$F,"מאי 2026",'כל ההוצאות'!$D:$D)</f>
+        <v/>
+      </c>
+      <c r="D14" s="49">
+        <f>C14*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E14" s="50">
+        <f>IF(C16&gt;0,C14/C16,0)</f>
+        <v/>
+      </c>
       <c r="F14" s="24" t="n"/>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="55" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="24" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="55" t="inlineStr">
         <is>
           <t>סה"כ שנתי</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="56">
-        <f>SUM(C4:C13)</f>
-        <v/>
-      </c>
-      <c r="D15" s="57">
-        <f>C15*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="E15" s="58" t="inlineStr">
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="56">
+        <f>SUM(C4:C14)</f>
+        <v/>
+      </c>
+      <c r="D16" s="57">
+        <f>C16*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E16" s="58" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F15" s="31" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="F16" s="31" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>ממוצע חודשי</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="60">
-        <f>AVERAGE(C4:C13)</f>
-        <v/>
-      </c>
-      <c r="D16" s="61">
-        <f>AVERAGE(D4:D13)</f>
-        <v/>
-      </c>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="24" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="60">
+        <f>AVERAGE(C4:C14)</f>
+        <v/>
+      </c>
+      <c r="D17" s="61">
+        <f>AVERAGE(D4:D14)</f>
+        <v/>
+      </c>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -4373,9 +5042,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
 </worksheet>
 </file>
 
@@ -4386,7 +5056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4400,7 +5070,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>כל ההוצאות – כלי AI  |  יולי 2025 – אפריל 2026</t>
+          <t>כל ההוצאות – כלי AI  |  יולי 2025 – מאי 2026</t>
         </is>
       </c>
     </row>
@@ -4555,21 +5225,21 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Runway ML</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Standard (10% affiliate off)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="E7" s="13">
         <f>D7*הגדרות!$B$4</f>
@@ -4584,21 +5254,21 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Runway ML</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Early card charge</t>
+          <t>Standard (10% affiliate off)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="E8" s="17">
         <f>D8*הגדרות!$B$4</f>
@@ -4642,21 +5312,21 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Jul 2025 (₪56.93)</t>
+          <t>Early card charge</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E10" s="17">
         <f>D10*הגדרות!$B$4</f>
@@ -4664,28 +5334,28 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2025</t>
+          <t>יולי 2025</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Runway ML</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Credits 1,500</t>
+          <t>Business Plus – Jul 2025 (₪56.93)</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="E11" s="13">
         <f>D11*הגדרות!$B$4</f>
@@ -4700,21 +5370,21 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Recraft</t>
+          <t>Runway ML</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Basic monthly</t>
+          <t>Credits 1,500</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12" s="17">
         <f>D12*הגדרות!$B$4</f>
@@ -4729,21 +5399,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Recraft</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Usage - July</t>
+          <t>Basic monthly</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.9</v>
+        <v>12</v>
       </c>
       <c r="E13" s="13">
         <f>D13*הגדרות!$B$4</f>
@@ -4758,21 +5428,21 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Manus AI</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Basic monthly</t>
+          <t>Usage - July</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>19</v>
+        <v>0.9</v>
       </c>
       <c r="E14" s="17">
         <f>D14*הגדרות!$B$4</f>
@@ -4787,21 +5457,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Make</t>
+          <t>Manus AI</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Core plan 10k ops/month</t>
+          <t>Basic monthly</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>10.59</v>
+        <v>19</v>
       </c>
       <c r="E15" s="13">
         <f>D15*הגדרות!$B$4</f>
@@ -4816,21 +5486,21 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Core plan 10k ops/month</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>20</v>
+        <v>10.59</v>
       </c>
       <c r="E16" s="17">
         <f>D16*הגדרות!$B$4</f>
@@ -4845,21 +5515,21 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Runway ML</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Standard (25% off)</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>11.25</v>
+        <v>20</v>
       </c>
       <c r="E17" s="13">
         <f>D17*הגדרות!$B$4</f>
@@ -4874,21 +5544,21 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" s="17">
         <f>D18*הגדרות!$B$4</f>
@@ -4903,21 +5573,21 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Aug 2025 (₪56.93)</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>15.6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="13">
         <f>D19*הגדרות!$B$4</f>
@@ -4925,28 +5595,28 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2025</t>
+          <t>אוגוסט 2025</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Runway ML</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Usage - August</t>
+          <t>Standard (25% off)</t>
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>2.79</v>
+        <v>11.25</v>
       </c>
       <c r="E20" s="17">
         <f>D20*הגדרות!$B$4</f>
@@ -4954,28 +5624,28 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2025</t>
+          <t>אוגוסט 2025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Make</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Core plan 10k ops/month</t>
+          <t>Business Plus – Aug 2025 (₪56.93)</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>10.59</v>
+        <v>15.6</v>
       </c>
       <c r="E21" s="13">
         <f>D21*הגדרות!$B$4</f>
@@ -4990,21 +5660,21 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Usage - August</t>
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>20</v>
+        <v>2.79</v>
       </c>
       <c r="E22" s="17">
         <f>D22*הגדרות!$B$4</f>
@@ -5019,21 +5689,21 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Core plan 10k ops/month</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>5</v>
+        <v>10.59</v>
       </c>
       <c r="E23" s="13">
         <f>D23*הגדרות!$B$4</f>
@@ -5048,21 +5718,21 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Sep 2025 (₪56.93)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E24" s="17">
         <f>D24*הגדרות!$B$4</f>
@@ -5070,14 +5740,14 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2025</t>
+          <t>ספטמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -5099,14 +5769,14 @@
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2025</t>
+          <t>ספטמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
@@ -5128,28 +5798,28 @@
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2025</t>
+          <t>ספטמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Recraft</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Pro 1k credits</t>
+          <t>Business Plus – Sep 2025 (₪56.93)</t>
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="E27" s="13">
         <f>D27*הגדרות!$B$4</f>
@@ -5157,28 +5827,28 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2025</t>
+          <t>אוקטובר 2025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Astria</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Credits x10 + 18% VAT</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="E28" s="17">
         <f>D28*הגדרות!$B$4</f>
@@ -5186,28 +5856,28 @@
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2025</t>
+          <t>אוקטובר 2025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Runway ML</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Standard monthly</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E29" s="13">
         <f>D29*הגדרות!$B$4</f>
@@ -5215,28 +5885,28 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2025</t>
+          <t>אוקטובר 2025</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Hedra</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Extra Small Credit Pack</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E30" s="17">
         <f>D30*הגדרות!$B$4</f>
@@ -5244,28 +5914,28 @@
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2025</t>
+          <t>אוקטובר 2025</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Recraft</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Pro 1k credits</t>
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E31" s="13">
         <f>D31*הגדרות!$B$4</f>
@@ -5280,21 +5950,21 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Astria</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Credits x10 + 18% VAT</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" s="17">
         <f>D32*הגדרות!$B$4</f>
@@ -5309,21 +5979,21 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Runway ML</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Nov 2025 (₪75.90)</t>
+          <t>Standard monthly</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>20.79</v>
+        <v>15</v>
       </c>
       <c r="E33" s="13">
         <f>D33*הגדרות!$B$4</f>
@@ -5331,28 +6001,28 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>דצמבר 2025</t>
+          <t>נובמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Manychat</t>
+          <t>Hedra</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly</t>
+          <t>Extra Small Credit Pack</t>
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E34" s="17">
         <f>D34*הגדרות!$B$4</f>
@@ -5360,28 +6030,28 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>דצמבר 2025</t>
+          <t>נובמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E35" s="13">
         <f>D35*הגדרות!$B$4</f>
@@ -5389,28 +6059,28 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>דצמבר 2025</t>
+          <t>נובמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Dec 2025 (₪75.90)</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>20.79</v>
+        <v>20</v>
       </c>
       <c r="E36" s="17">
         <f>D36*הגדרות!$B$4</f>
@@ -5418,28 +6088,28 @@
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>ינואר 2026</t>
+          <t>נובמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Genspark</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Plus Annual (happynewyear26 promo)</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>139.92</v>
+        <v>5</v>
       </c>
       <c r="E37" s="13">
         <f>D37*הגדרות!$B$4</f>
@@ -5447,28 +6117,28 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>ינואר 2026</t>
+          <t>נובמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Manychat</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly</t>
+          <t>Business Plus – Nov 2025 (₪75.90)</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>15</v>
+        <v>20.79</v>
       </c>
       <c r="E38" s="17">
         <f>D38*הגדרות!$B$4</f>
@@ -5476,28 +6146,28 @@
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>ינואר 2026</t>
+          <t>דצמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Genspark</t>
+          <t>Manychat</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Credits Pack</t>
+          <t>Pro monthly</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E39" s="13">
         <f>D39*הגדרות!$B$4</f>
@@ -5505,28 +6175,28 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>ינואר 2026</t>
+          <t>דצמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Genspark</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Credits Pack</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>20</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E40" s="17">
         <f>D40*הגדרות!$B$4</f>
@@ -5534,28 +6204,28 @@
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>ינואר 2026</t>
+          <t>דצמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Pro – Jan 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>13.67</v>
+        <v>30</v>
       </c>
       <c r="E41" s="13">
         <f>D41*הגדרות!$B$4</f>
@@ -5563,28 +6233,28 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>ינואר 2026</t>
+          <t>דצמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>14.5</v>
+        <v>33</v>
       </c>
       <c r="E42" s="17">
         <f>D42*הגדרות!$B$4</f>
@@ -5592,28 +6262,28 @@
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>ינואר 2026</t>
+          <t>דצמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E43" s="13">
         <f>D43*הגדרות!$B$4</f>
@@ -5621,28 +6291,28 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>ינואר 2026</t>
+          <t>דצמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Upgrade Pro1 -&gt; Pro2 (prorated)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E44" s="17">
         <f>D44*הגדרות!$B$4</f>
@@ -5650,28 +6320,28 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>דצמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Jan 2026 (₪75.90)</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>20.79</v>
+        <v>5</v>
       </c>
       <c r="E45" s="13">
         <f>D45*הגדרות!$B$4</f>
@@ -5679,28 +6349,28 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>דצמבר 2025</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Pro – Feb 2026 (₪49.90)</t>
+          <t>Business Plus – Dec 2025 (₪75.90)</t>
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>13.67</v>
+        <v>20.79</v>
       </c>
       <c r="E46" s="17">
         <f>D46*הגדרות!$B$4</f>
@@ -5708,28 +6378,28 @@
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Genspark</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Plus Annual (happynewyear26 promo)</t>
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>20</v>
+        <v>139.92</v>
       </c>
       <c r="E47" s="13">
         <f>D47*הגדרות!$B$4</f>
@@ -5737,28 +6407,28 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Manychat</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Pro monthly</t>
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E48" s="17">
         <f>D48*הגדרות!$B$4</f>
@@ -5766,28 +6436,28 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20</v>
+        <v>19.43</v>
       </c>
       <c r="E49" s="13">
         <f>D49*הגדרות!$B$4</f>
@@ -5795,28 +6465,28 @@
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Genspark</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Credits Pack</t>
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E50" s="17">
         <f>D50*הגדרות!$B$4</f>
@@ -5824,28 +6494,28 @@
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Genspark</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>Credits Pack</t>
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E51" s="13">
         <f>D51*הגדרות!$B$4</f>
@@ -5853,28 +6523,28 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Pro – Jan 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>5</v>
+        <v>13.67</v>
       </c>
       <c r="E52" s="17">
         <f>D52*הגדרות!$B$4</f>
@@ -5882,28 +6552,28 @@
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="E53" s="13">
         <f>D53*הגדרות!$B$4</f>
@@ -5911,28 +6581,28 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Feb 2026 (₪75.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>20.79</v>
+        <v>39</v>
       </c>
       <c r="E54" s="17">
         <f>D54*הגדרות!$B$4</f>
@@ -5940,28 +6610,28 @@
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro 1 monthly</t>
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>40.11</v>
+        <v>25</v>
       </c>
       <c r="E55" s="13">
         <f>D55*הגדרות!$B$4</f>
@@ -5969,28 +6639,28 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Pro – Mar 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>13.67</v>
+        <v>43</v>
       </c>
       <c r="E56" s="17">
         <f>D56*הגדרות!$B$4</f>
@@ -5998,28 +6668,28 @@
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E57" s="13">
         <f>D57*הגדרות!$B$4</f>
@@ -6027,28 +6697,28 @@
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Timeless</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Pro monthly (50% off)</t>
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="E58" s="17">
         <f>D58*הגדרות!$B$4</f>
@@ -6056,28 +6726,28 @@
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Upgrade Pro1 -&gt; Pro2 (prorated)</t>
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E59" s="13">
         <f>D59*הגדרות!$B$4</f>
@@ -6085,28 +6755,28 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Business Plus – Jan 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>11</v>
+        <v>20.79</v>
       </c>
       <c r="E60" s="17">
         <f>D60*הגדרות!$B$4</f>
@@ -6114,28 +6784,28 @@
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>5</v>
+        <v>31.42</v>
       </c>
       <c r="E61" s="13">
         <f>D61*הגדרות!$B$4</f>
@@ -6143,28 +6813,28 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Pro – Feb 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>20</v>
+        <v>13.67</v>
       </c>
       <c r="E62" s="17">
         <f>D62*הגדרות!$B$4</f>
@@ -6172,28 +6842,28 @@
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E63" s="13">
         <f>D63*הגדרות!$B$4</f>
@@ -6201,28 +6871,28 @@
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.79</v>
+        <v>20</v>
       </c>
       <c r="E64" s="17">
         <f>D64*הגדרות!$B$4</f>
@@ -6230,28 +6900,28 @@
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="E65" s="13">
         <f>D65*הגדרות!$B$4</f>
@@ -6259,24 +6929,24 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D66" s="16" t="n">
@@ -6288,31 +6958,756 @@
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Higgsfield</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>On-Demand credits 500</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E67" s="13">
+        <f>D67*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>Pro2 monthly</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E68" s="17">
+        <f>D68*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="E69" s="13">
+        <f>D69*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="17">
+        <f>D70*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Balance Top-up</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" s="13">
+        <f>D71*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Balance Top-up</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" s="17">
+        <f>D72*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Timeless</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Pro monthly (50% off)</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E73" s="13">
+        <f>D73*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Feb 2026 (₪75.90)</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E74" s="17">
+        <f>D74*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Balance Top-up</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" s="13">
+        <f>D75*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="E76" s="17">
+        <f>D76*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Pro – Mar 2026 (₪49.90)</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="E77" s="13">
+        <f>D77*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="E78" s="17">
+        <f>D78*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E79" s="13">
+        <f>D79*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E80" s="17">
+        <f>D80*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Credit purchase</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" s="13">
+        <f>D81*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Creator (first month 50% off)</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E82" s="17">
+        <f>D82*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Lite plan</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" s="13">
+        <f>D83*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E84" s="17">
+        <f>D84*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
           <t>אפריל 2026</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Credit purchase</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" s="13">
+        <f>D85*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E86" s="17">
+        <f>D86*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="E87" s="13">
+        <f>D87*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E88" s="17">
+        <f>D88*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>IONOS</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Instant Domain</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E89" s="13">
+        <f>D89*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E90" s="17">
+        <f>D90*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E91" s="13">
+        <f>D91*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>מאי 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B67" s="19" t="n"/>
-      <c r="C67" s="19" t="n"/>
-      <c r="D67" s="20">
-        <f>SUM(D3:D66)</f>
-        <v/>
-      </c>
-      <c r="E67" s="21">
-        <f>SUM(E3:E66)</f>
-        <v/>
-      </c>
-      <c r="F67" s="19" t="n"/>
+      <c r="B92" s="19" t="n"/>
+      <c r="C92" s="19" t="n"/>
+      <c r="D92" s="20">
+        <f>SUM(D3:D91)</f>
+        <v/>
+      </c>
+      <c r="E92" s="21">
+        <f>SUM(E3:E91)</f>
+        <v/>
+      </c>
+      <c r="F92" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A92:C92"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6320,6 +7715,1086 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>יולי 2025  |  July 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Recraft</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Basic – first month promo</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Ideogram AI</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Ideogram Basic – annual</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="E5" s="28">
+        <f>D5*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F5" s="29" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Core plan 10k ops/month</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="E6" s="26">
+        <f>D6*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" s="28">
+        <f>D7*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="26">
+        <f>D8*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F8" s="24" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Runway ML</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Standard (10% affiliate off)</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E9" s="28">
+        <f>D9*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F9" s="29" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Ideogram AI</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Upgrade -&gt; Plus Annual</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>113.14</v>
+      </c>
+      <c r="E10" s="26">
+        <f>D10*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F10" s="24" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Replicate</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Early card charge</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="28">
+        <f>D11*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F11" s="29" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="20">
+        <f>SUM(D4:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>SUM(E4:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025  |  August 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Jul 2025 (₪56.93)</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Runway ML</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Credits 1,500</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="28">
+        <f>D5*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F5" s="29" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Recraft</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Basic monthly</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="26">
+        <f>D6*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Replicate</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Usage - July</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" s="28">
+        <f>D7*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Manus AI</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Basic monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" s="26">
+        <f>D8*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F8" s="24" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Core plan 10k ops/month</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="E9" s="28">
+        <f>D9*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F9" s="29" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="26">
+        <f>D10*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F10" s="24" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="28">
+        <f>D11*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F11" s="29" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="26">
+        <f>D12*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F12" s="24" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Runway ML</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Standard (25% off)</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E13" s="28">
+        <f>D13*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F13" s="29" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="20">
+        <f>SUM(D4:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>SUM(E4:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>ספטמבר 2025  |  September 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Aug 2025 (₪56.93)</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Replicate</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Usage - August</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E5" s="28">
+        <f>D5*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F5" s="29" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Core plan 10k ops/month</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="E6" s="26">
+        <f>D6*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" s="28">
+        <f>D7*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="26">
+        <f>D8*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F8" s="24" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="28">
+        <f>D9*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F9" s="29" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="31" t="n"/>
+      <c r="D10" s="20">
+        <f>SUM(D4:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>SUM(E4:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>אוקטובר 2025  |  October 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Sep 2025 (₪56.93)</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="28">
+        <f>D5*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F5" s="29" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="26">
+        <f>D6*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="28">
+        <f>D7*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="20">
+        <f>SUM(D4:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>SUM(E4:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009DC3E6"/>
@@ -6340,7 +8815,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>יולי 2025  |  July 2025</t>
+          <t>נובמבר 2025  |  November 2025</t>
         </is>
       </c>
     </row>
@@ -6387,7 +8862,7 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -6397,11 +8872,11 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Basic – first month promo</t>
+          <t>Pro 1k credits</t>
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E4" s="26">
         <f>D4*הגדרות!$B$4</f>
@@ -6412,21 +8887,21 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ideogram AI</t>
+          <t>Astria</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Ideogram Basic – annual</t>
+          <t>Credits x10 + 18% VAT</t>
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>72</v>
+        <v>11.8</v>
       </c>
       <c r="E5" s="28">
         <f>D5*הגדרות!$B$4</f>
@@ -6437,21 +8912,21 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Make</t>
+          <t>Runway ML</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Core plan 10k ops/month</t>
+          <t>Standard monthly</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.59</v>
+        <v>15</v>
       </c>
       <c r="E6" s="26">
         <f>D6*הגדרות!$B$4</f>
@@ -6462,21 +8937,21 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Hedra</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Extra Small Credit Pack</t>
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E7" s="28">
         <f>D7*הגדרות!$B$4</f>
@@ -6487,21 +8962,21 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Runway ML</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Standard (10% affiliate off)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="E8" s="26">
         <f>D8*הגדרות!$B$4</f>
@@ -6512,21 +8987,21 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Early card charge</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E9" s="28">
         <f>D9*הגדרות!$B$4</f>
@@ -6537,21 +9012,21 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Ideogram AI</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Upgrade -&gt; Plus Annual</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>113.14</v>
+        <v>5</v>
       </c>
       <c r="E10" s="26">
         <f>D10*הגדרות!$B$4</f>
@@ -6589,1132 +9064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="009DC3E6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025  |  August 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>← חזרה לסיכום חודשי</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>תאריך</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>כלי</t>
-        </is>
-      </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>תיאור</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>סכום ($)</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>סכום (₪)</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Jul 2025 (₪56.93)</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F4" s="24" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Runway ML</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Credits 1,500</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F5" s="29" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Recraft</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Basic monthly</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F6" s="24" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Replicate</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Usage - July</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F7" s="29" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Manus AI</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Basic monthly</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>19</v>
-      </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F8" s="24" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Make</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Core plan 10k ops/month</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F9" s="29" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F10" s="24" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Runway ML</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Standard (25% off)</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="E11" s="28">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F11" s="29" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="26">
-        <f>D12*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F12" s="24" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>סה"כ חודש"</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="20">
-        <f>SUM(D4:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="21">
-        <f>SUM(E4:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="31" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="009DC3E6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>ספטמבר 2025  |  September 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>← חזרה לסיכום חודשי</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>תאריך</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>כלי</t>
-        </is>
-      </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>תיאור</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>סכום ($)</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>סכום (₪)</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Aug 2025 (₪56.93)</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F4" s="24" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Replicate</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Usage - August</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F5" s="29" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Make</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Core plan 10k ops/month</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F6" s="24" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F7" s="29" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>סה"כ חודש"</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="n"/>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="20">
-        <f>SUM(D4:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="21">
-        <f>SUM(E4:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="31" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="009DC3E6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>אוקטובר 2025  |  October 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>← חזרה לסיכום חודשי</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>תאריך</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>כלי</t>
-        </is>
-      </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>תיאור</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>סכום ($)</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>סכום (₪)</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Sep 2025 (₪56.93)</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F4" s="24" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F5" s="29" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>סה"כ חודש"</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="20">
-        <f>SUM(D4:D6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="21">
-        <f>SUM(E4:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="31" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="009DC3E6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>נובמבר 2025  |  November 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>← חזרה לסיכום חודשי</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>תאריך</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>כלי</t>
-        </is>
-      </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>תיאור</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>סכום ($)</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>סכום (₪)</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Recraft</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Pro 1k credits</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F4" s="24" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Astria</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Credits x10 + 18% VAT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F5" s="29" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Runway ML</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Standard monthly</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F6" s="24" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Hedra</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Extra Small Credit Pack</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F7" s="29" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F8" s="24" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F9" s="29" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>סה"כ חודש"</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n"/>
-      <c r="C10" s="31" t="n"/>
-      <c r="D10" s="20">
-        <f>SUM(D4:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="21">
-        <f>SUM(E4:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="31" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="009DC3E6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>דצמבר 2025  |  December 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>← חזרה לסיכום חודשי</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>תאריך</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>כלי</t>
-        </is>
-      </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>תיאור</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>סכום ($)</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>סכום (₪)</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Nov 2025 (₪75.90)</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F4" s="24" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Manychat</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Pro monthly</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F5" s="29" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>סה"כ חודש"</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="20">
-        <f>SUM(D4:D6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="21">
-        <f>SUM(E4:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="31" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009DC3E6"/>
@@ -7735,7 +9085,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>ינואר 2026  |  January 2026</t>
+          <t>דצמבר 2025  |  December 2025</t>
         </is>
       </c>
     </row>
@@ -7782,7 +9132,7 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -7792,7 +9142,7 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Dec 2025 (₪75.90)</t>
+          <t>Business Plus – Nov 2025 (₪75.90)</t>
         </is>
       </c>
       <c r="D4" s="25" t="n">
@@ -7807,21 +9157,21 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Genspark</t>
+          <t>Manychat</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Plus Annual (happynewyear26 promo)</t>
+          <t>Pro monthly</t>
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>139.92</v>
+        <v>15</v>
       </c>
       <c r="E5" s="28">
         <f>D5*הגדרות!$B$4</f>
@@ -7832,21 +9182,21 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Manychat</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E6" s="26">
         <f>D6*הגדרות!$B$4</f>
@@ -7857,21 +9207,21 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Genspark</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Credits Pack</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E7" s="28">
         <f>D7*הגדרות!$B$4</f>
@@ -7882,21 +9232,21 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Genspark</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Credits Pack</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E8" s="26">
         <f>D8*הגדרות!$B$4</f>
@@ -7907,21 +9257,21 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Pro – Jan 2026 (₪49.90)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>13.67</v>
+        <v>20</v>
       </c>
       <c r="E9" s="28">
         <f>D9*הגדרות!$B$4</f>
@@ -7932,21 +9282,21 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="E10" s="26">
         <f>D10*הגדרות!$B$4</f>
@@ -7957,7 +9307,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -8007,4 +9357,424 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>ינואר 2026  |  January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Dec 2025 (₪75.90)</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Genspark</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Plus Annual (happynewyear26 promo)</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>139.92</v>
+      </c>
+      <c r="E5" s="28">
+        <f>D5*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F5" s="29" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Manychat</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Pro monthly</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="26">
+        <f>D6*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="E7" s="28">
+        <f>D7*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Genspark</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Credits Pack</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="26">
+        <f>D8*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F8" s="24" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Genspark</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Credits Pack</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="28">
+        <f>D9*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F9" s="29" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Pro – Jan 2026 (₪49.90)</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="E10" s="26">
+        <f>D10*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F10" s="24" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="28">
+        <f>D11*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F11" s="29" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="E12" s="26">
+        <f>D12*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F12" s="24" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Pro 1 monthly</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="28">
+        <f>D13*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F13" s="29" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="E14" s="26">
+        <f>D14*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F14" s="24" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="28">
+        <f>D15*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F15" s="29" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Timeless</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Pro monthly (50% off)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E16" s="26">
+        <f>D16*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="20">
+        <f>SUM(D4:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>SUM(E4:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="14" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,8 +20,15 @@
     <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="סיכום חודשי" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="דוח שנתי" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,7 +493,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Monthly AI Tool Expenses (USD)</a:t>
+              <a:t>Monthly AI &amp; Business Tools Expenses (USD)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -511,12 +518,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'דוח שנתי'!$A$4:$A$14</f>
+              <f>'דוח שנתי'!$A$4:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'דוח שנתי'!$C$4:$C$14</f>
+              <f>'דוח שנתי'!$C$4:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -592,7 +599,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="4320000"/>
@@ -914,7 +921,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  הגדרות ופרמטרים – AI Tool Expenses</t>
+          <t xml:space="preserve">  הגדרות ופרמטרים – AI &amp; Business Tools Expenses</t>
         </is>
       </c>
     </row>
@@ -2187,11 +2194,3719 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>יוני 2026  |  June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="20">
+        <f>SUM(D4:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>SUM(E4:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>יולי 2026  |  July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="20">
+        <f>SUM(D4:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>SUM(E4:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>אוגוסט 2026  |  August 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="20">
+        <f>SUM(D4:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>SUM(E4:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>ספטמבר 2026  |  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="20">
+        <f>SUM(D4:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>SUM(E4:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>אוקטובר 2026  |  October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="20">
+        <f>SUM(D4:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>SUM(E4:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>נובמבר 2026  |  November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="20">
+        <f>SUM(D4:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>SUM(E4:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>כל ההוצאות – כלי AI  |  יולי 2025 – דצמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>חודש</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Recraft</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Basic – first month promo</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13">
+        <f>D3*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>יולי 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Ideogram AI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Ideogram Basic – annual</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="E4" s="17">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>יולי 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Core plan 10k ops/month</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="E5" s="13">
+        <f>D5*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>יולי 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="17">
+        <f>D6*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>יולי 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" s="13">
+        <f>D7*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>יולי 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Runway ML</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Standard (10% affiliate off)</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E8" s="17">
+        <f>D8*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>יולי 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Ideogram AI</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Upgrade -&gt; Plus Annual</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>113.14</v>
+      </c>
+      <c r="E9" s="13">
+        <f>D9*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>יולי 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Replicate</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Early card charge</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="17">
+        <f>D10*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>יולי 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Business Plus – Jul 2025 (₪56.93)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" s="13">
+        <f>D11*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Runway ML</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Credits 1,500</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="17">
+        <f>D12*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Recraft</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Basic monthly</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="13">
+        <f>D13*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Replicate</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Usage - July</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E14" s="17">
+        <f>D14*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Manus AI</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Basic monthly</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="E15" s="13">
+        <f>D15*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Core plan 10k ops/month</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="E16" s="17">
+        <f>D16*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13">
+        <f>D17*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" s="17">
+        <f>D18*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="13">
+        <f>D19*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Runway ML</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Standard (25% off)</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E20" s="17">
+        <f>D20*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>אוגוסט 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Business Plus – Aug 2025 (₪56.93)</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E21" s="13">
+        <f>D21*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>ספטמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Replicate</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Usage - August</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E22" s="17">
+        <f>D22*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>ספטמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Core plan 10k ops/month</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="E23" s="13">
+        <f>D23*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>ספטמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" s="17">
+        <f>D24*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>ספטמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13">
+        <f>D25*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>ספטמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="17">
+        <f>D26*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>ספטמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Business Plus – Sep 2025 (₪56.93)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E27" s="13">
+        <f>D27*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>אוקטובר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="17">
+        <f>D28*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>אוקטובר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13">
+        <f>D29*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>אוקטובר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="17">
+        <f>D30*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>אוקטובר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Recraft</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Pro 1k credits</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="13">
+        <f>D31*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>נובמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Astria</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Credits x10 + 18% VAT</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" s="17">
+        <f>D32*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>נובמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Runway ML</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Standard monthly</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" s="13">
+        <f>D33*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>נובמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Hedra</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Extra Small Credit Pack</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" s="17">
+        <f>D34*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>נובמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" s="13">
+        <f>D35*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>נובמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="17">
+        <f>D36*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>נובמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="13">
+        <f>D37*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>נובמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Nov 2025 (₪75.90)</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E38" s="17">
+        <f>D38*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>דצמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Manychat</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Pro monthly</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="13">
+        <f>D39*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>דצמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="E40" s="17">
+        <f>D40*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>דצמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E41" s="13">
+        <f>D41*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>דצמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="E42" s="17">
+        <f>D42*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>דצמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" s="13">
+        <f>D43*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>דצמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="E44" s="17">
+        <f>D44*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>דצמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="13">
+        <f>D45*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>דצמבר 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Dec 2025 (₪75.90)</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E46" s="17">
+        <f>D46*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Genspark</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Plus Annual (happynewyear26 promo)</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>139.92</v>
+      </c>
+      <c r="E47" s="13">
+        <f>D47*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Manychat</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Pro monthly</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="17">
+        <f>D48*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="E49" s="13">
+        <f>D49*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Genspark</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Credits Pack</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" s="17">
+        <f>D50*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Genspark</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>Credits Pack</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E51" s="13">
+        <f>D51*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Pro – Jan 2026 (₪49.90)</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="E52" s="17">
+        <f>D52*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E53" s="13">
+        <f>D53*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E54" s="17">
+        <f>D54*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>Pro 1 monthly</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E55" s="13">
+        <f>D55*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="E56" s="17">
+        <f>D56*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" s="13">
+        <f>D57*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Timeless</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Pro monthly (50% off)</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E58" s="17">
+        <f>D58*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>ינואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Upgrade Pro1 -&gt; Pro2 (prorated)</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E59" s="13">
+        <f>D59*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Jan 2026 (₪75.90)</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E60" s="17">
+        <f>D60*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="E61" s="13">
+        <f>D61*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>Pro – Feb 2026 (₪49.90)</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="E62" s="17">
+        <f>D62*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="E63" s="13">
+        <f>D63*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E64" s="17">
+        <f>D64*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>Credit purchase</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" s="13">
+        <f>D65*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E66" s="17">
+        <f>D66*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Higgsfield</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>On-Demand credits 500</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E67" s="13">
+        <f>D67*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>Pro2 monthly</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E68" s="17">
+        <f>D68*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="E69" s="13">
+        <f>D69*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="17">
+        <f>D70*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Balance Top-up</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" s="13">
+        <f>D71*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>פברואר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Balance Top-up</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" s="17">
+        <f>D72*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Timeless</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Pro monthly (50% off)</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E73" s="13">
+        <f>D73*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Feb 2026 (₪75.90)</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E74" s="17">
+        <f>D74*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Balance Top-up</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" s="13">
+        <f>D75*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="E76" s="17">
+        <f>D76*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Pro – Mar 2026 (₪49.90)</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="E77" s="13">
+        <f>D77*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="E78" s="17">
+        <f>D78*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E79" s="13">
+        <f>D79*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E80" s="17">
+        <f>D80*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Credit purchase</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" s="13">
+        <f>D81*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Creator (first month 50% off)</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E82" s="17">
+        <f>D82*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Lite plan</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" s="13">
+        <f>D83*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>מרץ 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Claude Pro</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E84" s="17">
+        <f>D84*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Credit purchase</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" s="13">
+        <f>D85*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E86" s="17">
+        <f>D86*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="E87" s="13">
+        <f>D87*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>Meta (Ads)</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Facebook Ads</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E88" s="17">
+        <f>D88*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>IONOS</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Instant Domain</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E89" s="13">
+        <f>D89*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E90" s="17">
+        <f>D90*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>אפריל 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E91" s="13">
+        <f>D91*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>מאי 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E92" s="17">
+        <f>D92*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>יוני 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" s="13">
+        <f>D93*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>יולי 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E94" s="17">
+        <f>D94*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>אוגוסט 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E95" s="13">
+        <f>D95*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>ספטמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E96" s="17">
+        <f>D96*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>אוקטובר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E97" s="13">
+        <f>D97*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E98" s="17">
+        <f>D98*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>דצמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="18" t="inlineStr">
+        <is>
+          <t>סה"כ"</t>
+        </is>
+      </c>
+      <c r="B99" s="19" t="n"/>
+      <c r="C99" s="19" t="n"/>
+      <c r="D99" s="20">
+        <f>SUM(D3:D98)</f>
+        <v/>
+      </c>
+      <c r="E99" s="21">
+        <f>SUM(E3:E98)</f>
+        <v/>
+      </c>
+      <c r="F99" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009DC3E6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>דצמבר 2026  |  December 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>← חזרה לסיכום חודשי</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>כלי</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>סכום ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>סכום (₪)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="26">
+        <f>D4*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>סה"כ חודש"</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="20">
+        <f>SUM(D4:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>SUM(E4:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:AM25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2217,14 +5932,28 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="14" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>סיכום חודשי לפי כלי  |  יולי 2025 – מאי 2026</t>
+          <t>סיכום חודשי לפי כלי  |  יולי 2025 – דצמבר 2026</t>
         </is>
       </c>
     </row>
@@ -2307,12 +6036,54 @@
 (May 2026)</t>
         </is>
       </c>
-      <c r="X3" s="18" t="inlineStr">
+      <c r="X3" s="33" t="inlineStr">
+        <is>
+          <t>יוני 2026
+(June 2026)</t>
+        </is>
+      </c>
+      <c r="Z3" s="33" t="inlineStr">
+        <is>
+          <t>יולי 2026
+(July 2026)</t>
+        </is>
+      </c>
+      <c r="AB3" s="33" t="inlineStr">
+        <is>
+          <t>אוגוסט 2026
+(August 2026)</t>
+        </is>
+      </c>
+      <c r="AD3" s="33" t="inlineStr">
+        <is>
+          <t>ספטמבר 2026
+(September 2026)</t>
+        </is>
+      </c>
+      <c r="AF3" s="33" t="inlineStr">
+        <is>
+          <t>אוקטובר 2026
+(October 2026)</t>
+        </is>
+      </c>
+      <c r="AH3" s="33" t="inlineStr">
+        <is>
+          <t>נובמבר 2026
+(November 2026)</t>
+        </is>
+      </c>
+      <c r="AJ3" s="33" t="inlineStr">
+        <is>
+          <t>דצמבר 2026
+(December 2026)</t>
+        </is>
+      </c>
+      <c r="AL3" s="18" t="inlineStr">
         <is>
           <t>סה"כ ($)</t>
         </is>
       </c>
-      <c r="Y3" s="18" t="inlineStr">
+      <c r="AM3" s="18" t="inlineStr">
         <is>
           <t>סה"כ (₪)</t>
         </is>
@@ -2430,12 +6201,82 @@
           <t>₪</t>
         </is>
       </c>
-      <c r="X4" s="35" t="inlineStr">
+      <c r="X4" s="34" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="Y4" s="35" t="inlineStr">
+      <c r="Y4" s="34" t="inlineStr">
+        <is>
+          <t>₪</t>
+        </is>
+      </c>
+      <c r="Z4" s="34" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="AA4" s="34" t="inlineStr">
+        <is>
+          <t>₪</t>
+        </is>
+      </c>
+      <c r="AB4" s="34" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="AC4" s="34" t="inlineStr">
+        <is>
+          <t>₪</t>
+        </is>
+      </c>
+      <c r="AD4" s="34" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="AE4" s="34" t="inlineStr">
+        <is>
+          <t>₪</t>
+        </is>
+      </c>
+      <c r="AF4" s="34" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="AG4" s="34" t="inlineStr">
+        <is>
+          <t>₪</t>
+        </is>
+      </c>
+      <c r="AH4" s="34" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="AI4" s="34" t="inlineStr">
+        <is>
+          <t>₪</t>
+        </is>
+      </c>
+      <c r="AJ4" s="34" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="AK4" s="34" t="inlineStr">
+        <is>
+          <t>₪</t>
+        </is>
+      </c>
+      <c r="AL4" s="35" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="AM4" s="35" t="inlineStr">
         <is>
           <t>₪</t>
         </is>
@@ -2535,12 +6376,68 @@
         <f>IF(V5&gt;0,V5*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X5" s="39">
-        <f>SUM(B5,D5,F5,H5,J5,L5,N5,P5,R5,T5,V5)</f>
-        <v/>
-      </c>
-      <c r="Y5" s="40">
+      <c r="X5" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y5" s="38">
         <f>IF(X5&gt;0,X5*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z5" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA5" s="38">
+        <f>IF(Z5&gt;0,Z5*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB5" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC5" s="38">
+        <f>IF(AB5&gt;0,AB5*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD5" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE5" s="38">
+        <f>IF(AD5&gt;0,AD5*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF5" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG5" s="38">
+        <f>IF(AF5&gt;0,AF5*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH5" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI5" s="38">
+        <f>IF(AH5&gt;0,AH5*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK5" s="38">
+        <f>IF(AJ5&gt;0,AJ5*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL5" s="39">
+        <f>SUM(B5,D5,F5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5,AB5,AD5,AF5,AH5,AJ5)</f>
+        <v/>
+      </c>
+      <c r="AM5" s="40">
+        <f>IF(AL5&gt;0,AL5*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2638,12 +6535,68 @@
         <f>IF(V6&gt;0,V6*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X6" s="39">
-        <f>SUM(B6,D6,F6,H6,J6,L6,N6,P6,R6,T6,V6)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="40">
+      <c r="X6" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y6" s="43">
         <f>IF(X6&gt;0,X6*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z6" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA6" s="43">
+        <f>IF(Z6&gt;0,Z6*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB6" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC6" s="43">
+        <f>IF(AB6&gt;0,AB6*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD6" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE6" s="43">
+        <f>IF(AD6&gt;0,AD6*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF6" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG6" s="43">
+        <f>IF(AF6&gt;0,AF6*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH6" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI6" s="43">
+        <f>IF(AH6&gt;0,AH6*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK6" s="43">
+        <f>IF(AJ6&gt;0,AJ6*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL6" s="39">
+        <f>SUM(B6,D6,F6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6,AB6,AD6,AF6,AH6,AJ6)</f>
+        <v/>
+      </c>
+      <c r="AM6" s="40">
+        <f>IF(AL6&gt;0,AL6*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2741,12 +6694,68 @@
         <f>IF(V7&gt;0,V7*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X7" s="39">
-        <f>SUM(B7,D7,F7,H7,J7,L7,N7,P7,R7,T7,V7)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="40">
+      <c r="X7" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y7" s="38">
         <f>IF(X7&gt;0,X7*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z7" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA7" s="38">
+        <f>IF(Z7&gt;0,Z7*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB7" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC7" s="38">
+        <f>IF(AB7&gt;0,AB7*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD7" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE7" s="38">
+        <f>IF(AD7&gt;0,AD7*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF7" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG7" s="38">
+        <f>IF(AF7&gt;0,AF7*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH7" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI7" s="38">
+        <f>IF(AH7&gt;0,AH7*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK7" s="38">
+        <f>IF(AJ7&gt;0,AJ7*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL7" s="39">
+        <f>SUM(B7,D7,F7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7,AB7,AD7,AF7,AH7,AJ7)</f>
+        <v/>
+      </c>
+      <c r="AM7" s="40">
+        <f>IF(AL7&gt;0,AL7*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2844,12 +6853,68 @@
         <f>IF(V8&gt;0,V8*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X8" s="39">
-        <f>SUM(B8,D8,F8,H8,J8,L8,N8,P8,R8,T8,V8)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="40">
+      <c r="X8" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y8" s="43">
         <f>IF(X8&gt;0,X8*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z8" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA8" s="43">
+        <f>IF(Z8&gt;0,Z8*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB8" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC8" s="43">
+        <f>IF(AB8&gt;0,AB8*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD8" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE8" s="43">
+        <f>IF(AD8&gt;0,AD8*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF8" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG8" s="43">
+        <f>IF(AF8&gt;0,AF8*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH8" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI8" s="43">
+        <f>IF(AH8&gt;0,AH8*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK8" s="43">
+        <f>IF(AJ8&gt;0,AJ8*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL8" s="39">
+        <f>SUM(B8,D8,F8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8,AB8,AD8,AF8,AH8,AJ8)</f>
+        <v/>
+      </c>
+      <c r="AM8" s="40">
+        <f>IF(AL8&gt;0,AL8*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -2947,12 +7012,68 @@
         <f>IF(V9&gt;0,V9*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X9" s="39">
-        <f>SUM(B9,D9,F9,H9,J9,L9,N9,P9,R9,T9,V9)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="40">
+      <c r="X9" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y9" s="38">
         <f>IF(X9&gt;0,X9*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z9" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA9" s="38">
+        <f>IF(Z9&gt;0,Z9*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB9" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC9" s="38">
+        <f>IF(AB9&gt;0,AB9*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD9" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE9" s="38">
+        <f>IF(AD9&gt;0,AD9*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF9" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG9" s="38">
+        <f>IF(AF9&gt;0,AF9*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH9" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI9" s="38">
+        <f>IF(AH9&gt;0,AH9*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK9" s="38">
+        <f>IF(AJ9&gt;0,AJ9*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL9" s="39">
+        <f>SUM(B9,D9,F9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9,AB9,AD9,AF9,AH9,AJ9)</f>
+        <v/>
+      </c>
+      <c r="AM9" s="40">
+        <f>IF(AL9&gt;0,AL9*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3050,12 +7171,68 @@
         <f>IF(V10&gt;0,V10*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X10" s="39">
-        <f>SUM(B10,D10,F10,H10,J10,L10,N10,P10,R10,T10,V10)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="40">
+      <c r="X10" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y10" s="43">
         <f>IF(X10&gt;0,X10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z10" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA10" s="43">
+        <f>IF(Z10&gt;0,Z10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB10" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC10" s="43">
+        <f>IF(AB10&gt;0,AB10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD10" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE10" s="43">
+        <f>IF(AD10&gt;0,AD10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF10" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG10" s="43">
+        <f>IF(AF10&gt;0,AF10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH10" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI10" s="43">
+        <f>IF(AH10&gt;0,AH10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK10" s="43">
+        <f>IF(AJ10&gt;0,AJ10*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL10" s="39">
+        <f>SUM(B10,D10,F10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10,AB10,AD10,AF10,AH10,AJ10)</f>
+        <v/>
+      </c>
+      <c r="AM10" s="40">
+        <f>IF(AL10&gt;0,AL10*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3153,12 +7330,68 @@
         <f>IF(V11&gt;0,V11*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X11" s="39">
-        <f>SUM(B11,D11,F11,H11,J11,L11,N11,P11,R11,T11,V11)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="40">
+      <c r="X11" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y11" s="38">
         <f>IF(X11&gt;0,X11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z11" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA11" s="38">
+        <f>IF(Z11&gt;0,Z11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB11" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC11" s="38">
+        <f>IF(AB11&gt;0,AB11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD11" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE11" s="38">
+        <f>IF(AD11&gt;0,AD11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF11" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG11" s="38">
+        <f>IF(AF11&gt;0,AF11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH11" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI11" s="38">
+        <f>IF(AH11&gt;0,AH11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK11" s="38">
+        <f>IF(AJ11&gt;0,AJ11*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL11" s="39">
+        <f>SUM(B11,D11,F11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11,AB11,AD11,AF11,AH11,AJ11)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="40">
+        <f>IF(AL11&gt;0,AL11*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3256,12 +7489,68 @@
         <f>IF(V12&gt;0,V12*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X12" s="39">
-        <f>SUM(B12,D12,F12,H12,J12,L12,N12,P12,R12,T12,V12)</f>
-        <v/>
-      </c>
-      <c r="Y12" s="40">
+      <c r="X12" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y12" s="43">
         <f>IF(X12&gt;0,X12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z12" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA12" s="43">
+        <f>IF(Z12&gt;0,Z12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB12" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC12" s="43">
+        <f>IF(AB12&gt;0,AB12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD12" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE12" s="43">
+        <f>IF(AD12&gt;0,AD12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF12" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG12" s="43">
+        <f>IF(AF12&gt;0,AF12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH12" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI12" s="43">
+        <f>IF(AH12&gt;0,AH12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK12" s="43">
+        <f>IF(AJ12&gt;0,AJ12*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL12" s="39">
+        <f>SUM(B12,D12,F12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12,AB12,AD12,AF12,AH12,AJ12)</f>
+        <v/>
+      </c>
+      <c r="AM12" s="40">
+        <f>IF(AL12&gt;0,AL12*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3359,12 +7648,68 @@
         <f>IF(V13&gt;0,V13*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X13" s="39">
-        <f>SUM(B13,D13,F13,H13,J13,L13,N13,P13,R13,T13,V13)</f>
-        <v/>
-      </c>
-      <c r="Y13" s="40">
+      <c r="X13" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y13" s="38">
         <f>IF(X13&gt;0,X13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z13" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA13" s="38">
+        <f>IF(Z13&gt;0,Z13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB13" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC13" s="38">
+        <f>IF(AB13&gt;0,AB13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD13" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE13" s="38">
+        <f>IF(AD13&gt;0,AD13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF13" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG13" s="38">
+        <f>IF(AF13&gt;0,AF13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH13" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI13" s="38">
+        <f>IF(AH13&gt;0,AH13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK13" s="38">
+        <f>IF(AJ13&gt;0,AJ13*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL13" s="39">
+        <f>SUM(B13,D13,F13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13,AB13,AD13,AF13,AH13,AJ13)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="40">
+        <f>IF(AL13&gt;0,AL13*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3462,12 +7807,68 @@
         <f>IF(V14&gt;0,V14*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X14" s="39">
-        <f>SUM(B14,D14,F14,H14,J14,L14,N14,P14,R14,T14,V14)</f>
-        <v/>
-      </c>
-      <c r="Y14" s="40">
+      <c r="X14" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y14" s="43">
         <f>IF(X14&gt;0,X14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z14" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA14" s="43">
+        <f>IF(Z14&gt;0,Z14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB14" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC14" s="43">
+        <f>IF(AB14&gt;0,AB14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD14" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE14" s="43">
+        <f>IF(AD14&gt;0,AD14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF14" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG14" s="43">
+        <f>IF(AF14&gt;0,AF14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH14" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI14" s="43">
+        <f>IF(AH14&gt;0,AH14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK14" s="43">
+        <f>IF(AJ14&gt;0,AJ14*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL14" s="39">
+        <f>SUM(B14,D14,F14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14,AB14,AD14,AF14,AH14,AJ14)</f>
+        <v/>
+      </c>
+      <c r="AM14" s="40">
+        <f>IF(AL14&gt;0,AL14*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3565,12 +7966,68 @@
         <f>IF(V15&gt;0,V15*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X15" s="39">
-        <f>SUM(B15,D15,F15,H15,J15,L15,N15,P15,R15,T15,V15)</f>
-        <v/>
-      </c>
-      <c r="Y15" s="40">
+      <c r="X15" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y15" s="38">
         <f>IF(X15&gt;0,X15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z15" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA15" s="38">
+        <f>IF(Z15&gt;0,Z15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB15" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC15" s="38">
+        <f>IF(AB15&gt;0,AB15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD15" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE15" s="38">
+        <f>IF(AD15&gt;0,AD15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF15" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG15" s="38">
+        <f>IF(AF15&gt;0,AF15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH15" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI15" s="38">
+        <f>IF(AH15&gt;0,AH15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK15" s="38">
+        <f>IF(AJ15&gt;0,AJ15*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL15" s="39">
+        <f>SUM(B15,D15,F15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15,AB15,AD15,AF15,AH15,AJ15)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="40">
+        <f>IF(AL15&gt;0,AL15*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3668,12 +8125,68 @@
         <f>IF(V16&gt;0,V16*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X16" s="39">
-        <f>SUM(B16,D16,F16,H16,J16,L16,N16,P16,R16,T16,V16)</f>
-        <v/>
-      </c>
-      <c r="Y16" s="40">
+      <c r="X16" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y16" s="43">
         <f>IF(X16&gt;0,X16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z16" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA16" s="43">
+        <f>IF(Z16&gt;0,Z16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB16" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC16" s="43">
+        <f>IF(AB16&gt;0,AB16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD16" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE16" s="43">
+        <f>IF(AD16&gt;0,AD16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF16" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG16" s="43">
+        <f>IF(AF16&gt;0,AF16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH16" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI16" s="43">
+        <f>IF(AH16&gt;0,AH16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK16" s="43">
+        <f>IF(AJ16&gt;0,AJ16*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL16" s="39">
+        <f>SUM(B16,D16,F16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16,AB16,AD16,AF16,AH16,AJ16)</f>
+        <v/>
+      </c>
+      <c r="AM16" s="40">
+        <f>IF(AL16&gt;0,AL16*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3771,12 +8284,68 @@
         <f>IF(V17&gt;0,V17*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X17" s="39">
-        <f>SUM(B17,D17,F17,H17,J17,L17,N17,P17,R17,T17,V17)</f>
-        <v/>
-      </c>
-      <c r="Y17" s="40">
+      <c r="X17" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y17" s="38">
         <f>IF(X17&gt;0,X17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z17" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA17" s="38">
+        <f>IF(Z17&gt;0,Z17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB17" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC17" s="38">
+        <f>IF(AB17&gt;0,AB17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD17" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE17" s="38">
+        <f>IF(AD17&gt;0,AD17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF17" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG17" s="38">
+        <f>IF(AF17&gt;0,AF17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH17" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI17" s="38">
+        <f>IF(AH17&gt;0,AH17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK17" s="38">
+        <f>IF(AJ17&gt;0,AJ17*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL17" s="39">
+        <f>SUM(B17,D17,F17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17,AB17,AD17,AF17,AH17,AJ17)</f>
+        <v/>
+      </c>
+      <c r="AM17" s="40">
+        <f>IF(AL17&gt;0,AL17*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3874,12 +8443,68 @@
         <f>IF(V18&gt;0,V18*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X18" s="39">
-        <f>SUM(B18,D18,F18,H18,J18,L18,N18,P18,R18,T18,V18)</f>
-        <v/>
-      </c>
-      <c r="Y18" s="40">
+      <c r="X18" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y18" s="43">
         <f>IF(X18&gt;0,X18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z18" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA18" s="43">
+        <f>IF(Z18&gt;0,Z18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB18" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC18" s="43">
+        <f>IF(AB18&gt;0,AB18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD18" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE18" s="43">
+        <f>IF(AD18&gt;0,AD18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF18" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG18" s="43">
+        <f>IF(AF18&gt;0,AF18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH18" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI18" s="43">
+        <f>IF(AH18&gt;0,AH18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK18" s="43">
+        <f>IF(AJ18&gt;0,AJ18*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL18" s="39">
+        <f>SUM(B18,D18,F18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18,AB18,AD18,AF18,AH18,AJ18)</f>
+        <v/>
+      </c>
+      <c r="AM18" s="40">
+        <f>IF(AL18&gt;0,AL18*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -3977,12 +8602,68 @@
         <f>IF(V19&gt;0,V19*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X19" s="39">
-        <f>SUM(B19,D19,F19,H19,J19,L19,N19,P19,R19,T19,V19)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="40">
+      <c r="X19" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y19" s="38">
         <f>IF(X19&gt;0,X19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z19" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA19" s="38">
+        <f>IF(Z19&gt;0,Z19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB19" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC19" s="38">
+        <f>IF(AB19&gt;0,AB19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD19" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE19" s="38">
+        <f>IF(AD19&gt;0,AD19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF19" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG19" s="38">
+        <f>IF(AF19&gt;0,AF19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH19" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI19" s="38">
+        <f>IF(AH19&gt;0,AH19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK19" s="38">
+        <f>IF(AJ19&gt;0,AJ19*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL19" s="39">
+        <f>SUM(B19,D19,F19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19,AB19,AD19,AF19,AH19,AJ19)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="40">
+        <f>IF(AL19&gt;0,AL19*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -4080,12 +8761,68 @@
         <f>IF(V20&gt;0,V20*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X20" s="39">
-        <f>SUM(B20,D20,F20,H20,J20,L20,N20,P20,R20,T20,V20)</f>
-        <v/>
-      </c>
-      <c r="Y20" s="40">
+      <c r="X20" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y20" s="43">
         <f>IF(X20&gt;0,X20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z20" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA20" s="43">
+        <f>IF(Z20&gt;0,Z20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB20" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC20" s="43">
+        <f>IF(AB20&gt;0,AB20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE20" s="43">
+        <f>IF(AD20&gt;0,AD20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF20" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG20" s="43">
+        <f>IF(AF20&gt;0,AF20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH20" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI20" s="43">
+        <f>IF(AH20&gt;0,AH20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK20" s="43">
+        <f>IF(AJ20&gt;0,AJ20*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL20" s="39">
+        <f>SUM(B20,D20,F20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20,AB20,AD20,AF20,AH20,AJ20)</f>
+        <v/>
+      </c>
+      <c r="AM20" s="40">
+        <f>IF(AL20&gt;0,AL20*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -4183,12 +8920,68 @@
         <f>IF(V21&gt;0,V21*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X21" s="39">
-        <f>SUM(B21,D21,F21,H21,J21,L21,N21,P21,R21,T21,V21)</f>
-        <v/>
-      </c>
-      <c r="Y21" s="40">
+      <c r="X21" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y21" s="38">
         <f>IF(X21&gt;0,X21*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z21" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA21" s="38">
+        <f>IF(Z21&gt;0,Z21*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB21" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC21" s="38">
+        <f>IF(AB21&gt;0,AB21*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE21" s="38">
+        <f>IF(AD21&gt;0,AD21*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF21" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG21" s="38">
+        <f>IF(AF21&gt;0,AF21*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH21" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI21" s="38">
+        <f>IF(AH21&gt;0,AH21*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK21" s="38">
+        <f>IF(AJ21&gt;0,AJ21*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL21" s="39">
+        <f>SUM(B21,D21,F21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21,AB21,AD21,AF21,AH21,AJ21)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="40">
+        <f>IF(AL21&gt;0,AL21*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -4286,12 +9079,68 @@
         <f>IF(V22&gt;0,V22*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X22" s="39">
-        <f>SUM(B22,D22,F22,H22,J22,L22,N22,P22,R22,T22,V22)</f>
-        <v/>
-      </c>
-      <c r="Y22" s="40">
+      <c r="X22" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="43">
         <f>IF(X22&gt;0,X22*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z22" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA22" s="43">
+        <f>IF(Z22&gt;0,Z22*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB22" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC22" s="43">
+        <f>IF(AB22&gt;0,AB22*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE22" s="43">
+        <f>IF(AD22&gt;0,AD22*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF22" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG22" s="43">
+        <f>IF(AF22&gt;0,AF22*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH22" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI22" s="43">
+        <f>IF(AH22&gt;0,AH22*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK22" s="43">
+        <f>IF(AJ22&gt;0,AJ22*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL22" s="39">
+        <f>SUM(B22,D22,F22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22,AB22,AD22,AF22,AH22,AJ22)</f>
+        <v/>
+      </c>
+      <c r="AM22" s="40">
+        <f>IF(AL22&gt;0,AL22*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -4389,12 +9238,68 @@
         <f>IF(V23&gt;0,V23*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X23" s="39">
-        <f>SUM(B23,D23,F23,H23,J23,L23,N23,P23,R23,T23,V23)</f>
-        <v/>
-      </c>
-      <c r="Y23" s="40">
+      <c r="X23" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y23" s="38">
         <f>IF(X23&gt;0,X23*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z23" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA23" s="38">
+        <f>IF(Z23&gt;0,Z23*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB23" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC23" s="38">
+        <f>IF(AB23&gt;0,AB23*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE23" s="38">
+        <f>IF(AD23&gt;0,AD23*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF23" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG23" s="38">
+        <f>IF(AF23&gt;0,AF23*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH23" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI23" s="38">
+        <f>IF(AH23&gt;0,AH23*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK23" s="38">
+        <f>IF(AJ23&gt;0,AJ23*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL23" s="39">
+        <f>SUM(B23,D23,F23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23,AB23,AD23,AF23,AH23,AJ23)</f>
+        <v/>
+      </c>
+      <c r="AM23" s="40">
+        <f>IF(AL23&gt;0,AL23*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -4492,12 +9397,68 @@
         <f>IF(V24&gt;0,V24*הגדרות!$B$4,"")</f>
         <v/>
       </c>
-      <c r="X24" s="39">
-        <f>SUM(B24,D24,F24,H24,J24,L24,N24,P24,R24,T24,V24)</f>
-        <v/>
-      </c>
-      <c r="Y24" s="40">
+      <c r="X24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y24" s="43">
         <f>IF(X24&gt;0,X24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="Z24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA24" s="43">
+        <f>IF(Z24&gt;0,Z24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AB24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC24" s="43">
+        <f>IF(AB24&gt;0,AB24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AD24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE24" s="43">
+        <f>IF(AD24&gt;0,AD24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AF24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG24" s="43">
+        <f>IF(AF24&gt;0,AF24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AH24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI24" s="43">
+        <f>IF(AH24&gt;0,AH24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK24" s="43">
+        <f>IF(AJ24&gt;0,AJ24*הגדרות!$B$4,"")</f>
+        <v/>
+      </c>
+      <c r="AL24" s="39">
+        <f>SUM(B24,D24,F24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24,AB24,AD24,AF24,AH24,AJ24)</f>
+        <v/>
+      </c>
+      <c r="AM24" s="40">
+        <f>IF(AL24&gt;0,AL24*הגדרות!$B$4,"")</f>
         <v/>
       </c>
     </row>
@@ -4595,30 +9556,93 @@
         <f>SUM(W5:W24)</f>
         <v/>
       </c>
-      <c r="X25" s="44">
+      <c r="X25" s="20">
         <f>SUM(X5:X24)</f>
         <v/>
       </c>
-      <c r="Y25" s="45">
+      <c r="Y25" s="21">
         <f>SUM(Y5:Y24)</f>
         <v/>
       </c>
+      <c r="Z25" s="20">
+        <f>SUM(Z5:Z24)</f>
+        <v/>
+      </c>
+      <c r="AA25" s="21">
+        <f>SUM(AA5:AA24)</f>
+        <v/>
+      </c>
+      <c r="AB25" s="20">
+        <f>SUM(AB5:AB24)</f>
+        <v/>
+      </c>
+      <c r="AC25" s="21">
+        <f>SUM(AC5:AC24)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="20">
+        <f>SUM(AD5:AD24)</f>
+        <v/>
+      </c>
+      <c r="AE25" s="21">
+        <f>SUM(AE5:AE24)</f>
+        <v/>
+      </c>
+      <c r="AF25" s="20">
+        <f>SUM(AF5:AF24)</f>
+        <v/>
+      </c>
+      <c r="AG25" s="21">
+        <f>SUM(AG5:AG24)</f>
+        <v/>
+      </c>
+      <c r="AH25" s="20">
+        <f>SUM(AH5:AH24)</f>
+        <v/>
+      </c>
+      <c r="AI25" s="21">
+        <f>SUM(AI5:AI24)</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="20">
+        <f>SUM(AJ5:AJ24)</f>
+        <v/>
+      </c>
+      <c r="AK25" s="21">
+        <f>SUM(AK5:AK24)</f>
+        <v/>
+      </c>
+      <c r="AL25" s="44">
+        <f>SUM(AL5:AL24)</f>
+        <v/>
+      </c>
+      <c r="AM25" s="45">
+        <f>SUM(AM5:AM24)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="20">
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A1:AL1"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A2:AL2"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="T3:U3"/>
     <mergeCell ref="V3:W3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="AB3:AC3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
@@ -4632,19 +9656,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z3" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD3" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF3" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH3" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ3" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4658,14 +9689,14 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>דוח שנתי – AI Tool Expenses</t>
+          <t>דוח שנתי – AI &amp; Business Tools Expenses</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="46" t="inlineStr">
         <is>
-          <t>סיכום הוצאות לפי חודש – יולי 2025 – מאי 2026</t>
+          <t>סיכום הוצאות לפי חודש – יולי 2025 – דצמבר 2026</t>
         </is>
       </c>
     </row>
@@ -4721,7 +9752,7 @@
         <v/>
       </c>
       <c r="E4" s="50">
-        <f>IF(C16&gt;0,C4/C16,0)</f>
+        <f>IF(C23&gt;0,C4/C23,0)</f>
         <v/>
       </c>
       <c r="F4" s="24" t="n"/>
@@ -4746,7 +9777,7 @@
         <v/>
       </c>
       <c r="E5" s="54">
-        <f>IF(C16&gt;0,C5/C16,0)</f>
+        <f>IF(C23&gt;0,C5/C23,0)</f>
         <v/>
       </c>
       <c r="F5" s="29" t="n"/>
@@ -4771,7 +9802,7 @@
         <v/>
       </c>
       <c r="E6" s="50">
-        <f>IF(C16&gt;0,C6/C16,0)</f>
+        <f>IF(C23&gt;0,C6/C23,0)</f>
         <v/>
       </c>
       <c r="F6" s="24" t="n"/>
@@ -4796,7 +9827,7 @@
         <v/>
       </c>
       <c r="E7" s="54">
-        <f>IF(C16&gt;0,C7/C16,0)</f>
+        <f>IF(C23&gt;0,C7/C23,0)</f>
         <v/>
       </c>
       <c r="F7" s="29" t="n"/>
@@ -4821,7 +9852,7 @@
         <v/>
       </c>
       <c r="E8" s="50">
-        <f>IF(C16&gt;0,C8/C16,0)</f>
+        <f>IF(C23&gt;0,C8/C23,0)</f>
         <v/>
       </c>
       <c r="F8" s="24" t="n"/>
@@ -4846,7 +9877,7 @@
         <v/>
       </c>
       <c r="E9" s="54">
-        <f>IF(C16&gt;0,C9/C16,0)</f>
+        <f>IF(C23&gt;0,C9/C23,0)</f>
         <v/>
       </c>
       <c r="F9" s="29" t="n"/>
@@ -4871,7 +9902,7 @@
         <v/>
       </c>
       <c r="E10" s="50">
-        <f>IF(C16&gt;0,C10/C16,0)</f>
+        <f>IF(C23&gt;0,C10/C23,0)</f>
         <v/>
       </c>
       <c r="F10" s="24" t="n"/>
@@ -4896,7 +9927,7 @@
         <v/>
       </c>
       <c r="E11" s="54">
-        <f>IF(C16&gt;0,C11/C16,0)</f>
+        <f>IF(C23&gt;0,C11/C23,0)</f>
         <v/>
       </c>
       <c r="F11" s="29" t="n"/>
@@ -4921,7 +9952,7 @@
         <v/>
       </c>
       <c r="E12" s="50">
-        <f>IF(C16&gt;0,C12/C16,0)</f>
+        <f>IF(C23&gt;0,C12/C23,0)</f>
         <v/>
       </c>
       <c r="F12" s="24" t="n"/>
@@ -4946,7 +9977,7 @@
         <v/>
       </c>
       <c r="E13" s="54">
-        <f>IF(C16&gt;0,C13/C16,0)</f>
+        <f>IF(C23&gt;0,C13/C23,0)</f>
         <v/>
       </c>
       <c r="F13" s="29" t="n"/>
@@ -4971,65 +10002,240 @@
         <v/>
       </c>
       <c r="E14" s="50">
-        <f>IF(C16&gt;0,C14/C16,0)</f>
+        <f>IF(C23&gt;0,C14/C23,0)</f>
         <v/>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="24" t="n"/>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="24" t="n"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="55" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>יוני 2026</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="52">
+        <f>SUMIF('כל ההוצאות'!$F:$F,"יוני 2026",'כל ההוצאות'!$D:$D)</f>
+        <v/>
+      </c>
+      <c r="D15" s="53">
+        <f>C15*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E15" s="54">
+        <f>IF(C23&gt;0,C15/C23,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>יולי 2026</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="48">
+        <f>SUMIF('כל ההוצאות'!$F:$F,"יולי 2026",'כל ההוצאות'!$D:$D)</f>
+        <v/>
+      </c>
+      <c r="D16" s="49">
+        <f>C16*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E16" s="50">
+        <f>IF(C23&gt;0,C16/C23,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>אוגוסט 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="52">
+        <f>SUMIF('כל ההוצאות'!$F:$F,"אוגוסט 2026",'כל ההוצאות'!$D:$D)</f>
+        <v/>
+      </c>
+      <c r="D17" s="53">
+        <f>C17*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E17" s="54">
+        <f>IF(C23&gt;0,C17/C23,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="47" t="inlineStr">
+        <is>
+          <t>ספטמבר 2026</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="48">
+        <f>SUMIF('כל ההוצאות'!$F:$F,"ספטמבר 2026",'כל ההוצאות'!$D:$D)</f>
+        <v/>
+      </c>
+      <c r="D18" s="49">
+        <f>C18*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E18" s="50">
+        <f>IF(C23&gt;0,C18/C23,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t>אוקטובר 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="52">
+        <f>SUMIF('כל ההוצאות'!$F:$F,"אוקטובר 2026",'כל ההוצאות'!$D:$D)</f>
+        <v/>
+      </c>
+      <c r="D19" s="53">
+        <f>C19*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E19" s="54">
+        <f>IF(C23&gt;0,C19/C23,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="29" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="47" t="inlineStr">
+        <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+      <c r="C20" s="48">
+        <f>SUMIF('כל ההוצאות'!$F:$F,"נובמבר 2026",'כל ההוצאות'!$D:$D)</f>
+        <v/>
+      </c>
+      <c r="D20" s="49">
+        <f>C20*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E20" s="50">
+        <f>IF(C23&gt;0,C20/C23,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="51" t="inlineStr">
+        <is>
+          <t>דצמבר 2026</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>December 2026</t>
+        </is>
+      </c>
+      <c r="C21" s="52">
+        <f>SUMIF('כל ההוצאות'!$F:$F,"דצמבר 2026",'כל ההוצאות'!$D:$D)</f>
+        <v/>
+      </c>
+      <c r="D21" s="53">
+        <f>C21*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E21" s="54">
+        <f>IF(C23&gt;0,C21/C23,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="29" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>סה"כ שנתי</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="56">
-        <f>SUM(C4:C14)</f>
-        <v/>
-      </c>
-      <c r="D16" s="57">
-        <f>C16*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="E16" s="58" t="inlineStr">
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="56">
+        <f>SUM(C4:C21)</f>
+        <v/>
+      </c>
+      <c r="D23" s="57">
+        <f>C23*הגדרות!$B$4</f>
+        <v/>
+      </c>
+      <c r="E23" s="58" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F16" s="31" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="F23" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>ממוצע חודשי</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="60">
-        <f>AVERAGE(C4:C14)</f>
-        <v/>
-      </c>
-      <c r="D17" s="61">
-        <f>AVERAGE(D4:D14)</f>
-        <v/>
-      </c>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="60">
+        <f>AVERAGE(C4:C21)</f>
+        <v/>
+      </c>
+      <c r="D24" s="61">
+        <f>AVERAGE(D4:D21)</f>
+        <v/>
+      </c>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -5043,2674 +10249,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002E75B6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F92"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>כל ההוצאות – כלי AI  |  יולי 2025 – מאי 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>תאריך</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>כלי</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>תיאור</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>סכום ($)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>סכום (₪)</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>חודש</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Recraft</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Basic – first month promo</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="13">
-        <f>D3*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>יולי 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Ideogram AI</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Ideogram Basic – annual</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>72</v>
-      </c>
-      <c r="E4" s="17">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>יולי 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Make</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Core plan 10k ops/month</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="E5" s="13">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>יולי 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" s="17">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>יולי 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" s="13">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>יולי 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Runway ML</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Standard (10% affiliate off)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E8" s="17">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>יולי 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Ideogram AI</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Upgrade -&gt; Plus Annual</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>113.14</v>
-      </c>
-      <c r="E9" s="13">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>יולי 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Replicate</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Early card charge</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="17">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>יולי 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Business Plus – Jul 2025 (₪56.93)</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E11" s="13">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Runway ML</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Credits 1,500</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E12" s="17">
-        <f>D12*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Recraft</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Basic monthly</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" s="13">
-        <f>D13*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Replicate</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Usage - July</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E14" s="17">
-        <f>D14*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Manus AI</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Basic monthly</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="E15" s="13">
-        <f>D15*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Make</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Core plan 10k ops/month</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="E16" s="17">
-        <f>D16*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13">
-        <f>D17*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E18" s="17">
-        <f>D18*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="13">
-        <f>D19*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Runway ML</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Standard (25% off)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="E20" s="17">
-        <f>D20*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>אוגוסט 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Business Plus – Aug 2025 (₪56.93)</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E21" s="13">
-        <f>D21*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>ספטמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Replicate</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Usage - August</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E22" s="17">
-        <f>D22*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>ספטמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Make</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Core plan 10k ops/month</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="E23" s="13">
-        <f>D23*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>ספטמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E24" s="17">
-        <f>D24*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>ספטמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13">
-        <f>D25*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>ספטמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="17">
-        <f>D26*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>ספטמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Business Plus – Sep 2025 (₪56.93)</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E27" s="13">
-        <f>D27*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>אוקטובר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E28" s="17">
-        <f>D28*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>אוקטובר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13">
-        <f>D29*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>אוקטובר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" s="17">
-        <f>D30*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>אוקטובר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Recraft</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Pro 1k credits</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E31" s="13">
-        <f>D31*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>נובמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>Astria</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Credits x10 + 18% VAT</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E32" s="17">
-        <f>D32*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>נובמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Runway ML</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Standard monthly</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="E33" s="13">
-        <f>D33*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>נובמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Hedra</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Extra Small Credit Pack</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" s="17">
-        <f>D34*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>נובמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E35" s="13">
-        <f>D35*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>נובמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E36" s="17">
-        <f>D36*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>נובמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E37" s="13">
-        <f>D37*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>נובמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Nov 2025 (₪75.90)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E38" s="17">
-        <f>D38*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>דצמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Manychat</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Pro monthly</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="E39" s="13">
-        <f>D39*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="E40" s="17">
-        <f>D40*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>דצמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="E41" s="13">
-        <f>D41*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="E42" s="17">
-        <f>D42*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>דצמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E43" s="13">
-        <f>D43*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="E44" s="17">
-        <f>D44*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>דצמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E45" s="13">
-        <f>D45*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Dec 2025 (₪75.90)</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E46" s="17">
-        <f>D46*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>Genspark</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>Plus Annual (happynewyear26 promo)</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>139.92</v>
-      </c>
-      <c r="E47" s="13">
-        <f>D47*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>Manychat</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>Pro monthly</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E48" s="17">
-        <f>D48*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="E49" s="13">
-        <f>D49*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Genspark</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>Credits Pack</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E50" s="17">
-        <f>D50*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Genspark</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>Credits Pack</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E51" s="13">
-        <f>D51*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>CapCut</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>Pro – Jan 2026 (₪49.90)</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="E52" s="17">
-        <f>D52*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E53" s="13">
-        <f>D53*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="E54" s="17">
-        <f>D54*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F54" s="14" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>Pro 1 monthly</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="E55" s="13">
-        <f>D55*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="E56" s="17">
-        <f>D56*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E57" s="13">
-        <f>D57*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>Timeless</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>Pro monthly (50% off)</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E58" s="17">
-        <f>D58*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
-        <is>
-          <t>ינואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>Upgrade Pro1 -&gt; Pro2 (prorated)</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="E59" s="13">
-        <f>D59*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Jan 2026 (₪75.90)</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E60" s="17">
-        <f>D60*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="E61" s="13">
-        <f>D61*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>CapCut</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Pro – Feb 2026 (₪49.90)</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="E62" s="17">
-        <f>D62*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F62" s="14" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D63" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="E63" s="13">
-        <f>D63*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B64" s="15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E64" s="17">
-        <f>D64*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>Credit purchase</t>
-        </is>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E65" s="13">
-        <f>D65*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E66" s="17">
-        <f>D66*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>Higgsfield</t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="inlineStr">
-        <is>
-          <t>On-Demand credits 500</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E67" s="13">
-        <f>D67*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>Pro2 monthly</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="E68" s="17">
-        <f>D68*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="E69" s="13">
-        <f>D69*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
-        <is>
-          <t>Starter monthly</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E70" s="17">
-        <f>D70*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F70" s="14" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E71" s="13">
-        <f>D71*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>פברואר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
-        </is>
-      </c>
-      <c r="D72" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E72" s="17">
-        <f>D72*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F72" s="14" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>Timeless</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>Pro monthly (50% off)</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E73" s="13">
-        <f>D73*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Feb 2026 (₪75.90)</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E74" s="17">
-        <f>D74*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F74" s="14" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E75" s="13">
-        <f>D75*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="n">
-        <v>40.11</v>
-      </c>
-      <c r="E76" s="17">
-        <f>D76*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F76" s="14" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t>CapCut</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>Pro – Mar 2026 (₪49.90)</t>
-        </is>
-      </c>
-      <c r="D77" s="12" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="E77" s="13">
-        <f>D77*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="B78" s="15" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D78" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="E78" s="17">
-        <f>D78*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F78" s="14" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E79" s="13">
-        <f>D79*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D80" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E80" s="17">
-        <f>D80*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F80" s="14" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C81" s="11" t="inlineStr">
-        <is>
-          <t>Credit purchase</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E81" s="13">
-        <f>D81*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="B82" s="15" t="inlineStr">
-        <is>
-          <t>Eleven Labs</t>
-        </is>
-      </c>
-      <c r="C82" s="15" t="inlineStr">
-        <is>
-          <t>Creator (first month 50% off)</t>
-        </is>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="E82" s="17">
-        <f>D82*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F82" s="14" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C83" s="11" t="inlineStr">
-        <is>
-          <t>Lite plan</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E83" s="13">
-        <f>D83*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>מרץ 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
-        <is>
-          <t>Claude Pro</t>
-        </is>
-      </c>
-      <c r="D84" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E84" s="17">
-        <f>D84*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F84" s="14" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C85" s="11" t="inlineStr">
-        <is>
-          <t>Credit purchase</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E85" s="13">
-        <f>D85*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B86" s="15" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="inlineStr">
-        <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
-        </is>
-      </c>
-      <c r="D86" s="16" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E86" s="17">
-        <f>D86*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F86" s="14" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="E87" s="13">
-        <f>D87*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="B88" s="15" t="inlineStr">
-        <is>
-          <t>Meta (Ads)</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>Facebook Ads</t>
-        </is>
-      </c>
-      <c r="D88" s="16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E88" s="17">
-        <f>D88*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F88" s="14" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>IONOS</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr">
-        <is>
-          <t>Instant Domain</t>
-        </is>
-      </c>
-      <c r="D89" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E89" s="13">
-        <f>D89*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D90" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E90" s="17">
-        <f>D90*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F90" s="14" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D91" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E91" s="13">
-        <f>D91*הגדרות!$B$4</f>
-        <v/>
-      </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t>מאי 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>סה"כ"</t>
-        </is>
-      </c>
-      <c r="B92" s="19" t="n"/>
-      <c r="C92" s="19" t="n"/>
-      <c r="D92" s="20">
-        <f>SUM(D3:D91)</f>
-        <v/>
-      </c>
-      <c r="E92" s="21">
-        <f>SUM(E3:E91)</f>
-        <v/>
-      </c>
-      <c r="F92" s="19" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
 </worksheet>
 </file>
 

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -935,15 +935,15 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>שער USD → ILS (לעדכון ידני)</t>
+          <t>שער USD → ILS (מתעדכן אוטומטית)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.65</v>
+        <v>3.142</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← ניתן לעדכן שיעור זה בכל עת</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-07</t>
         </is>
       </c>
     </row>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1070,9 +1070,8 @@
       <c r="D4" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>78.55</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1095,9 +1094,8 @@
       <c r="D5" s="27" t="n">
         <v>20.79</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1120,9 +1118,8 @@
       <c r="D6" s="25" t="n">
         <v>31.42</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>98.72</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -1145,9 +1142,8 @@
       <c r="D7" s="27" t="n">
         <v>13.67</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>49.9</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -1170,9 +1166,8 @@
       <c r="D8" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>147.67</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -1195,9 +1190,8 @@
       <c r="D9" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -1220,9 +1214,8 @@
       <c r="D10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="26" t="n">
+        <v>15.71</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -1245,9 +1238,8 @@
       <c r="D11" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E11" s="28">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
+      <c r="E11" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -1270,9 +1262,8 @@
       <c r="D12" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="26">
-        <f>D12*הגדרות!$B$4</f>
-        <v/>
+      <c r="E12" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1295,9 +1286,8 @@
       <c r="D13" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="E13" s="28">
-        <f>D13*הגדרות!$B$4</f>
-        <v/>
+      <c r="E13" s="28" t="n">
+        <v>157.1</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1320,9 +1310,8 @@
       <c r="D14" s="25" t="n">
         <v>51</v>
       </c>
-      <c r="E14" s="26">
-        <f>D14*הגדרות!$B$4</f>
-        <v/>
+      <c r="E14" s="26" t="n">
+        <v>160.24</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1345,9 +1334,8 @@
       <c r="D15" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="28">
-        <f>D15*הגדרות!$B$4</f>
-        <v/>
+      <c r="E15" s="28" t="n">
+        <v>15.71</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1370,9 +1358,8 @@
       <c r="D16" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="26">
-        <f>D16*הגדרות!$B$4</f>
-        <v/>
+      <c r="E16" s="26" t="n">
+        <v>31.42</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -1490,9 +1477,8 @@
       <c r="D4" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>31.42</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1515,9 +1501,8 @@
       <c r="D5" s="27" t="n">
         <v>14.5</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>45.56</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1540,9 +1525,8 @@
       <c r="D6" s="25" t="n">
         <v>20.79</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -1565,9 +1549,8 @@
       <c r="D7" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>31.42</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -1590,9 +1573,8 @@
       <c r="D8" s="25" t="n">
         <v>40.11</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>126.03</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -1615,9 +1597,8 @@
       <c r="D9" s="27" t="n">
         <v>13.67</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>49.9</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -1640,9 +1621,8 @@
       <c r="D10" s="25" t="n">
         <v>51</v>
       </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="26" t="n">
+        <v>160.24</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -1665,9 +1645,8 @@
       <c r="D11" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E11" s="28">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
+      <c r="E11" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -1690,9 +1669,8 @@
       <c r="D12" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="26">
-        <f>D12*הגדרות!$B$4</f>
-        <v/>
+      <c r="E12" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1715,9 +1693,8 @@
       <c r="D13" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="28">
-        <f>D13*הגדרות!$B$4</f>
-        <v/>
+      <c r="E13" s="28" t="n">
+        <v>31.42</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1740,9 +1717,8 @@
       <c r="D14" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="26">
-        <f>D14*הגדרות!$B$4</f>
-        <v/>
+      <c r="E14" s="26" t="n">
+        <v>34.56</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1765,9 +1741,8 @@
       <c r="D15" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="28">
-        <f>D15*הגדרות!$B$4</f>
-        <v/>
+      <c r="E15" s="28" t="n">
+        <v>15.71</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1885,9 +1860,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1910,9 +1884,8 @@
       <c r="D5" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>15.71</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1935,9 +1908,8 @@
       <c r="D6" s="25" t="n">
         <v>20.79</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -1960,9 +1932,8 @@
       <c r="D7" s="27" t="n">
         <v>51</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>160.24</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -1985,9 +1956,8 @@
       <c r="D8" s="25" t="n">
         <v>2.25</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>7.07</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -2010,9 +1980,8 @@
       <c r="D9" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -2035,9 +2004,8 @@
       <c r="D10" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -2155,9 +2123,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2275,9 +2242,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2395,9 +2361,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2515,9 +2480,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2635,9 +2599,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2755,9 +2718,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2875,9 +2837,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2987,9 +2948,8 @@
       <c r="D3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="13">
-        <f>D3*הגדרות!$B$4</f>
-        <v/>
+      <c r="E3" s="13" t="n">
+        <v>3.14</v>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
@@ -3016,9 +2976,8 @@
       <c r="D4" s="16" t="n">
         <v>72</v>
       </c>
-      <c r="E4" s="17">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="17" t="n">
+        <v>226.22</v>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
@@ -3045,9 +3004,8 @@
       <c r="D5" s="12" t="n">
         <v>10.59</v>
       </c>
-      <c r="E5" s="13">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="13" t="n">
+        <v>33.27</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -3074,9 +3032,8 @@
       <c r="D6" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="17">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
@@ -3103,9 +3060,8 @@
       <c r="D7" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="13">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -3132,9 +3088,8 @@
       <c r="D8" s="16" t="n">
         <v>13.5</v>
       </c>
-      <c r="E8" s="17">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="17" t="n">
+        <v>42.42</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
@@ -3161,9 +3116,8 @@
       <c r="D9" s="12" t="n">
         <v>113.14</v>
       </c>
-      <c r="E9" s="13">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="13" t="n">
+        <v>355.49</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -3190,9 +3144,8 @@
       <c r="D10" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="E10" s="17">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="17" t="n">
+        <v>31.42</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
@@ -3219,9 +3172,8 @@
       <c r="D11" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="E11" s="13">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
+      <c r="E11" s="13" t="n">
+        <v>56.93</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -3248,9 +3200,8 @@
       <c r="D12" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="E12" s="17">
-        <f>D12*הגדרות!$B$4</f>
-        <v/>
+      <c r="E12" s="17" t="n">
+        <v>47.13</v>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
@@ -3277,9 +3228,8 @@
       <c r="D13" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="13">
-        <f>D13*הגדרות!$B$4</f>
-        <v/>
+      <c r="E13" s="13" t="n">
+        <v>37.7</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -3306,9 +3256,8 @@
       <c r="D14" s="16" t="n">
         <v>0.9</v>
       </c>
-      <c r="E14" s="17">
-        <f>D14*הגדרות!$B$4</f>
-        <v/>
+      <c r="E14" s="17" t="n">
+        <v>2.83</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
@@ -3335,9 +3284,8 @@
       <c r="D15" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="E15" s="13">
-        <f>D15*הגדרות!$B$4</f>
-        <v/>
+      <c r="E15" s="13" t="n">
+        <v>59.7</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -3364,9 +3312,8 @@
       <c r="D16" s="16" t="n">
         <v>10.59</v>
       </c>
-      <c r="E16" s="17">
-        <f>D16*הגדרות!$B$4</f>
-        <v/>
+      <c r="E16" s="17" t="n">
+        <v>33.27</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
@@ -3393,9 +3340,8 @@
       <c r="D17" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E17" s="13">
-        <f>D17*הגדרות!$B$4</f>
-        <v/>
+      <c r="E17" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -3422,9 +3368,8 @@
       <c r="D18" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E18" s="17">
-        <f>D18*הגדרות!$B$4</f>
-        <v/>
+      <c r="E18" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
@@ -3451,9 +3396,8 @@
       <c r="D19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="13">
-        <f>D19*הגדרות!$B$4</f>
-        <v/>
+      <c r="E19" s="13" t="n">
+        <v>15.71</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -3480,9 +3424,8 @@
       <c r="D20" s="16" t="n">
         <v>11.25</v>
       </c>
-      <c r="E20" s="17">
-        <f>D20*הגדרות!$B$4</f>
-        <v/>
+      <c r="E20" s="17" t="n">
+        <v>35.35</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
@@ -3509,9 +3452,8 @@
       <c r="D21" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="E21" s="13">
-        <f>D21*הגדרות!$B$4</f>
-        <v/>
+      <c r="E21" s="13" t="n">
+        <v>56.93</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -3538,9 +3480,8 @@
       <c r="D22" s="16" t="n">
         <v>2.79</v>
       </c>
-      <c r="E22" s="17">
-        <f>D22*הגדרות!$B$4</f>
-        <v/>
+      <c r="E22" s="17" t="n">
+        <v>8.77</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
@@ -3567,9 +3508,8 @@
       <c r="D23" s="12" t="n">
         <v>10.59</v>
       </c>
-      <c r="E23" s="13">
-        <f>D23*הגדרות!$B$4</f>
-        <v/>
+      <c r="E23" s="13" t="n">
+        <v>33.27</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -3596,9 +3536,8 @@
       <c r="D24" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E24" s="17">
-        <f>D24*הגדרות!$B$4</f>
-        <v/>
+      <c r="E24" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -3625,9 +3564,8 @@
       <c r="D25" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E25" s="13">
-        <f>D25*הגדרות!$B$4</f>
-        <v/>
+      <c r="E25" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -3654,9 +3592,8 @@
       <c r="D26" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="17">
-        <f>D26*הגדרות!$B$4</f>
-        <v/>
+      <c r="E26" s="17" t="n">
+        <v>15.71</v>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
@@ -3683,9 +3620,8 @@
       <c r="D27" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="E27" s="13">
-        <f>D27*הגדרות!$B$4</f>
-        <v/>
+      <c r="E27" s="13" t="n">
+        <v>56.93</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -3712,9 +3648,8 @@
       <c r="D28" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E28" s="17">
-        <f>D28*הגדרות!$B$4</f>
-        <v/>
+      <c r="E28" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
@@ -3741,9 +3676,8 @@
       <c r="D29" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E29" s="13">
-        <f>D29*הגדרות!$B$4</f>
-        <v/>
+      <c r="E29" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -3770,9 +3704,8 @@
       <c r="D30" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="17">
-        <f>D30*הגדרות!$B$4</f>
-        <v/>
+      <c r="E30" s="17" t="n">
+        <v>15.71</v>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
@@ -3799,9 +3732,8 @@
       <c r="D31" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="E31" s="13">
-        <f>D31*הגדרות!$B$4</f>
-        <v/>
+      <c r="E31" s="13" t="n">
+        <v>37.7</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -3828,9 +3760,8 @@
       <c r="D32" s="16" t="n">
         <v>11.8</v>
       </c>
-      <c r="E32" s="17">
-        <f>D32*הגדרות!$B$4</f>
-        <v/>
+      <c r="E32" s="17" t="n">
+        <v>37.08</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -3857,9 +3788,8 @@
       <c r="D33" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E33" s="13">
-        <f>D33*הגדרות!$B$4</f>
-        <v/>
+      <c r="E33" s="13" t="n">
+        <v>47.13</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -3886,9 +3816,8 @@
       <c r="D34" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="E34" s="17">
-        <f>D34*הגדרות!$B$4</f>
-        <v/>
+      <c r="E34" s="17" t="n">
+        <v>31.42</v>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
@@ -3915,9 +3844,8 @@
       <c r="D35" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E35" s="13">
-        <f>D35*הגדרות!$B$4</f>
-        <v/>
+      <c r="E35" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -3944,9 +3872,8 @@
       <c r="D36" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E36" s="17">
-        <f>D36*הגדרות!$B$4</f>
-        <v/>
+      <c r="E36" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
@@ -3973,9 +3900,8 @@
       <c r="D37" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="13">
-        <f>D37*הגדרות!$B$4</f>
-        <v/>
+      <c r="E37" s="13" t="n">
+        <v>15.71</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -4002,9 +3928,8 @@
       <c r="D38" s="16" t="n">
         <v>20.79</v>
       </c>
-      <c r="E38" s="17">
-        <f>D38*הגדרות!$B$4</f>
-        <v/>
+      <c r="E38" s="17" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
@@ -4031,9 +3956,8 @@
       <c r="D39" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E39" s="13">
-        <f>D39*הגדרות!$B$4</f>
-        <v/>
+      <c r="E39" s="13" t="n">
+        <v>47.13</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -4060,9 +3984,8 @@
       <c r="D40" s="16" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="E40" s="17">
-        <f>D40*הגדרות!$B$4</f>
-        <v/>
+      <c r="E40" s="17" t="n">
+        <v>30.54</v>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
@@ -4089,9 +4012,8 @@
       <c r="D41" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="E41" s="13">
-        <f>D41*הגדרות!$B$4</f>
-        <v/>
+      <c r="E41" s="13" t="n">
+        <v>94.26000000000001</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -4118,9 +4040,8 @@
       <c r="D42" s="16" t="n">
         <v>33</v>
       </c>
-      <c r="E42" s="17">
-        <f>D42*הגדרות!$B$4</f>
-        <v/>
+      <c r="E42" s="17" t="n">
+        <v>103.69</v>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
@@ -4147,9 +4068,8 @@
       <c r="D43" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E43" s="13">
-        <f>D43*הגדרות!$B$4</f>
-        <v/>
+      <c r="E43" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -4176,9 +4096,8 @@
       <c r="D44" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E44" s="17">
-        <f>D44*הגדרות!$B$4</f>
-        <v/>
+      <c r="E44" s="17" t="n">
+        <v>113.11</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
@@ -4205,9 +4124,8 @@
       <c r="D45" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="13">
-        <f>D45*הגדרות!$B$4</f>
-        <v/>
+      <c r="E45" s="13" t="n">
+        <v>15.71</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -4234,9 +4152,8 @@
       <c r="D46" s="16" t="n">
         <v>20.79</v>
       </c>
-      <c r="E46" s="17">
-        <f>D46*הגדרות!$B$4</f>
-        <v/>
+      <c r="E46" s="17" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
@@ -4263,9 +4180,8 @@
       <c r="D47" s="12" t="n">
         <v>139.92</v>
       </c>
-      <c r="E47" s="13">
-        <f>D47*הגדרות!$B$4</f>
-        <v/>
+      <c r="E47" s="13" t="n">
+        <v>439.63</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -4292,9 +4208,8 @@
       <c r="D48" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="E48" s="17">
-        <f>D48*הגדרות!$B$4</f>
-        <v/>
+      <c r="E48" s="17" t="n">
+        <v>47.13</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
@@ -4321,9 +4236,8 @@
       <c r="D49" s="12" t="n">
         <v>19.43</v>
       </c>
-      <c r="E49" s="13">
-        <f>D49*הגדרות!$B$4</f>
-        <v/>
+      <c r="E49" s="13" t="n">
+        <v>61.05</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
@@ -4350,9 +4264,8 @@
       <c r="D50" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E50" s="17">
-        <f>D50*הגדרות!$B$4</f>
-        <v/>
+      <c r="E50" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
@@ -4379,9 +4292,8 @@
       <c r="D51" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E51" s="13">
-        <f>D51*הגדרות!$B$4</f>
-        <v/>
+      <c r="E51" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
@@ -4408,9 +4320,8 @@
       <c r="D52" s="16" t="n">
         <v>13.67</v>
       </c>
-      <c r="E52" s="17">
-        <f>D52*הגדרות!$B$4</f>
-        <v/>
+      <c r="E52" s="17" t="n">
+        <v>49.9</v>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
@@ -4437,9 +4348,8 @@
       <c r="D53" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E53" s="13">
-        <f>D53*הגדרות!$B$4</f>
-        <v/>
+      <c r="E53" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
@@ -4466,9 +4376,8 @@
       <c r="D54" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="E54" s="17">
-        <f>D54*הגדרות!$B$4</f>
-        <v/>
+      <c r="E54" s="17" t="n">
+        <v>122.54</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
@@ -4495,9 +4404,8 @@
       <c r="D55" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E55" s="13">
-        <f>D55*הגדרות!$B$4</f>
-        <v/>
+      <c r="E55" s="13" t="n">
+        <v>78.55</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
@@ -4524,9 +4432,8 @@
       <c r="D56" s="16" t="n">
         <v>43</v>
       </c>
-      <c r="E56" s="17">
-        <f>D56*הגדרות!$B$4</f>
-        <v/>
+      <c r="E56" s="17" t="n">
+        <v>135.11</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
@@ -4553,9 +4460,8 @@
       <c r="D57" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E57" s="13">
-        <f>D57*הגדרות!$B$4</f>
-        <v/>
+      <c r="E57" s="13" t="n">
+        <v>15.71</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
@@ -4582,9 +4488,8 @@
       <c r="D58" s="16" t="n">
         <v>14.5</v>
       </c>
-      <c r="E58" s="17">
-        <f>D58*הגדרות!$B$4</f>
-        <v/>
+      <c r="E58" s="17" t="n">
+        <v>45.56</v>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
@@ -4611,9 +4516,8 @@
       <c r="D59" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E59" s="13">
-        <f>D59*הגדרות!$B$4</f>
-        <v/>
+      <c r="E59" s="13" t="n">
+        <v>78.55</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
@@ -4640,9 +4544,8 @@
       <c r="D60" s="16" t="n">
         <v>20.79</v>
       </c>
-      <c r="E60" s="17">
-        <f>D60*הגדרות!$B$4</f>
-        <v/>
+      <c r="E60" s="17" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
@@ -4669,9 +4572,8 @@
       <c r="D61" s="12" t="n">
         <v>31.42</v>
       </c>
-      <c r="E61" s="13">
-        <f>D61*הגדרות!$B$4</f>
-        <v/>
+      <c r="E61" s="13" t="n">
+        <v>98.72</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
@@ -4698,9 +4600,8 @@
       <c r="D62" s="16" t="n">
         <v>13.67</v>
       </c>
-      <c r="E62" s="17">
-        <f>D62*הגדרות!$B$4</f>
-        <v/>
+      <c r="E62" s="17" t="n">
+        <v>49.9</v>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
@@ -4727,9 +4628,8 @@
       <c r="D63" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="E63" s="13">
-        <f>D63*הגדרות!$B$4</f>
-        <v/>
+      <c r="E63" s="13" t="n">
+        <v>147.67</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
@@ -4756,9 +4656,8 @@
       <c r="D64" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E64" s="17">
-        <f>D64*הגדרות!$B$4</f>
-        <v/>
+      <c r="E64" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
@@ -4785,9 +4684,8 @@
       <c r="D65" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E65" s="13">
-        <f>D65*הגדרות!$B$4</f>
-        <v/>
+      <c r="E65" s="13" t="n">
+        <v>15.71</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
@@ -4814,9 +4712,8 @@
       <c r="D66" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="17">
-        <f>D66*הגדרות!$B$4</f>
-        <v/>
+      <c r="E66" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -4843,9 +4740,8 @@
       <c r="D67" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E67" s="13">
-        <f>D67*הגדרות!$B$4</f>
-        <v/>
+      <c r="E67" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
@@ -4872,9 +4768,8 @@
       <c r="D68" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="E68" s="17">
-        <f>D68*הגדרות!$B$4</f>
-        <v/>
+      <c r="E68" s="17" t="n">
+        <v>157.1</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
@@ -4901,9 +4796,8 @@
       <c r="D69" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="E69" s="13">
-        <f>D69*הגדרות!$B$4</f>
-        <v/>
+      <c r="E69" s="13" t="n">
+        <v>160.24</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -4930,9 +4824,8 @@
       <c r="D70" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E70" s="17">
-        <f>D70*הגדרות!$B$4</f>
-        <v/>
+      <c r="E70" s="17" t="n">
+        <v>15.71</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -4959,9 +4852,8 @@
       <c r="D71" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E71" s="13">
-        <f>D71*הגדרות!$B$4</f>
-        <v/>
+      <c r="E71" s="13" t="n">
+        <v>31.42</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -4988,9 +4880,8 @@
       <c r="D72" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="E72" s="17">
-        <f>D72*הגדרות!$B$4</f>
-        <v/>
+      <c r="E72" s="17" t="n">
+        <v>31.42</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -5017,9 +4908,8 @@
       <c r="D73" s="12" t="n">
         <v>14.5</v>
       </c>
-      <c r="E73" s="13">
-        <f>D73*הגדרות!$B$4</f>
-        <v/>
+      <c r="E73" s="13" t="n">
+        <v>45.56</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -5046,9 +4936,8 @@
       <c r="D74" s="16" t="n">
         <v>20.79</v>
       </c>
-      <c r="E74" s="17">
-        <f>D74*הגדרות!$B$4</f>
-        <v/>
+      <c r="E74" s="17" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -5075,9 +4964,8 @@
       <c r="D75" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E75" s="13">
-        <f>D75*הגדרות!$B$4</f>
-        <v/>
+      <c r="E75" s="13" t="n">
+        <v>31.42</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -5104,9 +4992,8 @@
       <c r="D76" s="16" t="n">
         <v>40.11</v>
       </c>
-      <c r="E76" s="17">
-        <f>D76*הגדרות!$B$4</f>
-        <v/>
+      <c r="E76" s="17" t="n">
+        <v>126.03</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -5133,9 +5020,8 @@
       <c r="D77" s="12" t="n">
         <v>13.67</v>
       </c>
-      <c r="E77" s="13">
-        <f>D77*הגדרות!$B$4</f>
-        <v/>
+      <c r="E77" s="13" t="n">
+        <v>49.9</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -5162,9 +5048,8 @@
       <c r="D78" s="16" t="n">
         <v>51</v>
       </c>
-      <c r="E78" s="17">
-        <f>D78*הגדרות!$B$4</f>
-        <v/>
+      <c r="E78" s="17" t="n">
+        <v>160.24</v>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -5191,9 +5076,8 @@
       <c r="D79" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E79" s="13">
-        <f>D79*הגדרות!$B$4</f>
-        <v/>
+      <c r="E79" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -5220,9 +5104,8 @@
       <c r="D80" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E80" s="17">
-        <f>D80*הגדרות!$B$4</f>
-        <v/>
+      <c r="E80" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -5249,9 +5132,8 @@
       <c r="D81" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E81" s="13">
-        <f>D81*הגדרות!$B$4</f>
-        <v/>
+      <c r="E81" s="13" t="n">
+        <v>31.42</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -5278,9 +5160,8 @@
       <c r="D82" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="E82" s="17">
-        <f>D82*הגדרות!$B$4</f>
-        <v/>
+      <c r="E82" s="17" t="n">
+        <v>34.56</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -5307,9 +5188,8 @@
       <c r="D83" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="13">
-        <f>D83*הגדרות!$B$4</f>
-        <v/>
+      <c r="E83" s="13" t="n">
+        <v>15.71</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5336,9 +5216,8 @@
       <c r="D84" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E84" s="17">
-        <f>D84*הגדרות!$B$4</f>
-        <v/>
+      <c r="E84" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5365,9 +5244,8 @@
       <c r="D85" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E85" s="13">
-        <f>D85*הגדרות!$B$4</f>
-        <v/>
+      <c r="E85" s="13" t="n">
+        <v>15.71</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5394,9 +5272,8 @@
       <c r="D86" s="16" t="n">
         <v>20.79</v>
       </c>
-      <c r="E86" s="17">
-        <f>D86*הגדרות!$B$4</f>
-        <v/>
+      <c r="E86" s="17" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -5423,9 +5300,8 @@
       <c r="D87" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="E87" s="13">
-        <f>D87*הגדרות!$B$4</f>
-        <v/>
+      <c r="E87" s="13" t="n">
+        <v>160.24</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -5452,9 +5328,8 @@
       <c r="D88" s="16" t="n">
         <v>2.25</v>
       </c>
-      <c r="E88" s="17">
-        <f>D88*הגדרות!$B$4</f>
-        <v/>
+      <c r="E88" s="17" t="n">
+        <v>7.07</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5481,9 +5356,8 @@
       <c r="D89" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E89" s="13">
-        <f>D89*הגדרות!$B$4</f>
-        <v/>
+      <c r="E89" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5510,9 +5384,8 @@
       <c r="D90" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E90" s="17">
-        <f>D90*הגדרות!$B$4</f>
-        <v/>
+      <c r="E90" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5539,9 +5412,8 @@
       <c r="D91" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E91" s="13">
-        <f>D91*הגדרות!$B$4</f>
-        <v/>
+      <c r="E91" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5568,9 +5440,8 @@
       <c r="D92" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E92" s="17">
-        <f>D92*הגדרות!$B$4</f>
-        <v/>
+      <c r="E92" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5597,9 +5468,8 @@
       <c r="D93" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E93" s="13">
-        <f>D93*הגדרות!$B$4</f>
-        <v/>
+      <c r="E93" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -5626,9 +5496,8 @@
       <c r="D94" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E94" s="17">
-        <f>D94*הגדרות!$B$4</f>
-        <v/>
+      <c r="E94" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -5655,9 +5524,8 @@
       <c r="D95" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E95" s="13">
-        <f>D95*הגדרות!$B$4</f>
-        <v/>
+      <c r="E95" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5684,9 +5552,8 @@
       <c r="D96" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E96" s="17">
-        <f>D96*הגדרות!$B$4</f>
-        <v/>
+      <c r="E96" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5713,9 +5580,8 @@
       <c r="D97" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E97" s="13">
-        <f>D97*הגדרות!$B$4</f>
-        <v/>
+      <c r="E97" s="13" t="n">
+        <v>62.84</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5742,9 +5608,8 @@
       <c r="D98" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E98" s="17">
-        <f>D98*הגדרות!$B$4</f>
-        <v/>
+      <c r="E98" s="17" t="n">
+        <v>62.84</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5863,9 +5728,8 @@
       <c r="D4" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -6293,7 +6157,7 @@
         <v/>
       </c>
       <c r="C5" s="38">
-        <f>IF(B5&gt;0,B5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D5" s="37">
@@ -6301,7 +6165,7 @@
         <v/>
       </c>
       <c r="E5" s="38">
-        <f>IF(D5&gt;0,D5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F5" s="37">
@@ -6309,7 +6173,7 @@
         <v/>
       </c>
       <c r="G5" s="38">
-        <f>IF(F5&gt;0,F5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H5" s="37">
@@ -6317,7 +6181,7 @@
         <v/>
       </c>
       <c r="I5" s="38">
-        <f>IF(H5&gt;0,H5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J5" s="37">
@@ -6325,7 +6189,7 @@
         <v/>
       </c>
       <c r="K5" s="38">
-        <f>IF(J5&gt;0,J5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L5" s="37">
@@ -6333,7 +6197,7 @@
         <v/>
       </c>
       <c r="M5" s="38">
-        <f>IF(L5&gt;0,L5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N5" s="37">
@@ -6341,7 +6205,7 @@
         <v/>
       </c>
       <c r="O5" s="38">
-        <f>IF(N5&gt;0,N5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P5" s="37">
@@ -6349,7 +6213,7 @@
         <v/>
       </c>
       <c r="Q5" s="38">
-        <f>IF(P5&gt;0,P5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R5" s="37">
@@ -6357,7 +6221,7 @@
         <v/>
       </c>
       <c r="S5" s="38">
-        <f>IF(R5&gt;0,R5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T5" s="37">
@@ -6365,7 +6229,7 @@
         <v/>
       </c>
       <c r="U5" s="38">
-        <f>IF(T5&gt;0,T5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V5" s="37">
@@ -6373,7 +6237,7 @@
         <v/>
       </c>
       <c r="W5" s="38">
-        <f>IF(V5&gt;0,V5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X5" s="37">
@@ -6381,7 +6245,7 @@
         <v/>
       </c>
       <c r="Y5" s="38">
-        <f>IF(X5&gt;0,X5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z5" s="37">
@@ -6389,7 +6253,7 @@
         <v/>
       </c>
       <c r="AA5" s="38">
-        <f>IF(Z5&gt;0,Z5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB5" s="37">
@@ -6397,7 +6261,7 @@
         <v/>
       </c>
       <c r="AC5" s="38">
-        <f>IF(AB5&gt;0,AB5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD5" s="37">
@@ -6405,7 +6269,7 @@
         <v/>
       </c>
       <c r="AE5" s="38">
-        <f>IF(AD5&gt;0,AD5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF5" s="37">
@@ -6413,7 +6277,7 @@
         <v/>
       </c>
       <c r="AG5" s="38">
-        <f>IF(AF5&gt;0,AF5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH5" s="37">
@@ -6421,7 +6285,7 @@
         <v/>
       </c>
       <c r="AI5" s="38">
-        <f>IF(AH5&gt;0,AH5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ5" s="37">
@@ -6429,7 +6293,7 @@
         <v/>
       </c>
       <c r="AK5" s="38">
-        <f>IF(AJ5&gt;0,AJ5*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Anthropic",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL5" s="39">
@@ -6437,7 +6301,7 @@
         <v/>
       </c>
       <c r="AM5" s="40">
-        <f>IF(AL5&gt;0,AL5*הגדרות!$B$4,"")</f>
+        <f>SUM(C5,E5,G5,I5,K5,M5,O5,Q5,S5,U5,W5,Y5,AA5,AC5,AE5,AG5,AI5,AK5)</f>
         <v/>
       </c>
     </row>
@@ -6452,7 +6316,7 @@
         <v/>
       </c>
       <c r="C6" s="43">
-        <f>IF(B6&gt;0,B6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D6" s="42">
@@ -6460,7 +6324,7 @@
         <v/>
       </c>
       <c r="E6" s="43">
-        <f>IF(D6&gt;0,D6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F6" s="42">
@@ -6468,7 +6332,7 @@
         <v/>
       </c>
       <c r="G6" s="43">
-        <f>IF(F6&gt;0,F6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H6" s="42">
@@ -6476,7 +6340,7 @@
         <v/>
       </c>
       <c r="I6" s="43">
-        <f>IF(H6&gt;0,H6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J6" s="42">
@@ -6484,7 +6348,7 @@
         <v/>
       </c>
       <c r="K6" s="43">
-        <f>IF(J6&gt;0,J6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L6" s="42">
@@ -6492,7 +6356,7 @@
         <v/>
       </c>
       <c r="M6" s="43">
-        <f>IF(L6&gt;0,L6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N6" s="42">
@@ -6500,7 +6364,7 @@
         <v/>
       </c>
       <c r="O6" s="43">
-        <f>IF(N6&gt;0,N6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P6" s="42">
@@ -6508,7 +6372,7 @@
         <v/>
       </c>
       <c r="Q6" s="43">
-        <f>IF(P6&gt;0,P6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R6" s="42">
@@ -6516,7 +6380,7 @@
         <v/>
       </c>
       <c r="S6" s="43">
-        <f>IF(R6&gt;0,R6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T6" s="42">
@@ -6524,7 +6388,7 @@
         <v/>
       </c>
       <c r="U6" s="43">
-        <f>IF(T6&gt;0,T6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V6" s="42">
@@ -6532,7 +6396,7 @@
         <v/>
       </c>
       <c r="W6" s="43">
-        <f>IF(V6&gt;0,V6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X6" s="42">
@@ -6540,7 +6404,7 @@
         <v/>
       </c>
       <c r="Y6" s="43">
-        <f>IF(X6&gt;0,X6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z6" s="42">
@@ -6548,7 +6412,7 @@
         <v/>
       </c>
       <c r="AA6" s="43">
-        <f>IF(Z6&gt;0,Z6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB6" s="42">
@@ -6556,7 +6420,7 @@
         <v/>
       </c>
       <c r="AC6" s="43">
-        <f>IF(AB6&gt;0,AB6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD6" s="42">
@@ -6564,7 +6428,7 @@
         <v/>
       </c>
       <c r="AE6" s="43">
-        <f>IF(AD6&gt;0,AD6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF6" s="42">
@@ -6572,7 +6436,7 @@
         <v/>
       </c>
       <c r="AG6" s="43">
-        <f>IF(AF6&gt;0,AF6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH6" s="42">
@@ -6580,7 +6444,7 @@
         <v/>
       </c>
       <c r="AI6" s="43">
-        <f>IF(AH6&gt;0,AH6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ6" s="42">
@@ -6588,7 +6452,7 @@
         <v/>
       </c>
       <c r="AK6" s="43">
-        <f>IF(AJ6&gt;0,AJ6*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Astria",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL6" s="39">
@@ -6596,7 +6460,7 @@
         <v/>
       </c>
       <c r="AM6" s="40">
-        <f>IF(AL6&gt;0,AL6*הגדרות!$B$4,"")</f>
+        <f>SUM(C6,E6,G6,I6,K6,M6,O6,Q6,S6,U6,W6,Y6,AA6,AC6,AE6,AG6,AI6,AK6)</f>
         <v/>
       </c>
     </row>
@@ -6611,7 +6475,7 @@
         <v/>
       </c>
       <c r="C7" s="38">
-        <f>IF(B7&gt;0,B7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D7" s="37">
@@ -6619,7 +6483,7 @@
         <v/>
       </c>
       <c r="E7" s="38">
-        <f>IF(D7&gt;0,D7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F7" s="37">
@@ -6627,7 +6491,7 @@
         <v/>
       </c>
       <c r="G7" s="38">
-        <f>IF(F7&gt;0,F7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H7" s="37">
@@ -6635,7 +6499,7 @@
         <v/>
       </c>
       <c r="I7" s="38">
-        <f>IF(H7&gt;0,H7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J7" s="37">
@@ -6643,7 +6507,7 @@
         <v/>
       </c>
       <c r="K7" s="38">
-        <f>IF(J7&gt;0,J7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L7" s="37">
@@ -6651,7 +6515,7 @@
         <v/>
       </c>
       <c r="M7" s="38">
-        <f>IF(L7&gt;0,L7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N7" s="37">
@@ -6659,7 +6523,7 @@
         <v/>
       </c>
       <c r="O7" s="38">
-        <f>IF(N7&gt;0,N7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P7" s="37">
@@ -6667,7 +6531,7 @@
         <v/>
       </c>
       <c r="Q7" s="38">
-        <f>IF(P7&gt;0,P7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R7" s="37">
@@ -6675,7 +6539,7 @@
         <v/>
       </c>
       <c r="S7" s="38">
-        <f>IF(R7&gt;0,R7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T7" s="37">
@@ -6683,7 +6547,7 @@
         <v/>
       </c>
       <c r="U7" s="38">
-        <f>IF(T7&gt;0,T7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V7" s="37">
@@ -6691,7 +6555,7 @@
         <v/>
       </c>
       <c r="W7" s="38">
-        <f>IF(V7&gt;0,V7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X7" s="37">
@@ -6699,7 +6563,7 @@
         <v/>
       </c>
       <c r="Y7" s="38">
-        <f>IF(X7&gt;0,X7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z7" s="37">
@@ -6707,7 +6571,7 @@
         <v/>
       </c>
       <c r="AA7" s="38">
-        <f>IF(Z7&gt;0,Z7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB7" s="37">
@@ -6715,7 +6579,7 @@
         <v/>
       </c>
       <c r="AC7" s="38">
-        <f>IF(AB7&gt;0,AB7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD7" s="37">
@@ -6723,7 +6587,7 @@
         <v/>
       </c>
       <c r="AE7" s="38">
-        <f>IF(AD7&gt;0,AD7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF7" s="37">
@@ -6731,7 +6595,7 @@
         <v/>
       </c>
       <c r="AG7" s="38">
-        <f>IF(AF7&gt;0,AF7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH7" s="37">
@@ -6739,7 +6603,7 @@
         <v/>
       </c>
       <c r="AI7" s="38">
-        <f>IF(AH7&gt;0,AH7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ7" s="37">
@@ -6747,7 +6611,7 @@
         <v/>
       </c>
       <c r="AK7" s="38">
-        <f>IF(AJ7&gt;0,AJ7*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"CapCut",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL7" s="39">
@@ -6755,7 +6619,7 @@
         <v/>
       </c>
       <c r="AM7" s="40">
-        <f>IF(AL7&gt;0,AL7*הגדרות!$B$4,"")</f>
+        <f>SUM(C7,E7,G7,I7,K7,M7,O7,Q7,S7,U7,W7,Y7,AA7,AC7,AE7,AG7,AI7,AK7)</f>
         <v/>
       </c>
     </row>
@@ -6770,7 +6634,7 @@
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>IF(B8&gt;0,B8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D8" s="42">
@@ -6778,7 +6642,7 @@
         <v/>
       </c>
       <c r="E8" s="43">
-        <f>IF(D8&gt;0,D8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F8" s="42">
@@ -6786,7 +6650,7 @@
         <v/>
       </c>
       <c r="G8" s="43">
-        <f>IF(F8&gt;0,F8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H8" s="42">
@@ -6794,7 +6658,7 @@
         <v/>
       </c>
       <c r="I8" s="43">
-        <f>IF(H8&gt;0,H8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J8" s="42">
@@ -6802,7 +6666,7 @@
         <v/>
       </c>
       <c r="K8" s="43">
-        <f>IF(J8&gt;0,J8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L8" s="42">
@@ -6810,7 +6674,7 @@
         <v/>
       </c>
       <c r="M8" s="43">
-        <f>IF(L8&gt;0,L8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N8" s="42">
@@ -6818,7 +6682,7 @@
         <v/>
       </c>
       <c r="O8" s="43">
-        <f>IF(N8&gt;0,N8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P8" s="42">
@@ -6826,7 +6690,7 @@
         <v/>
       </c>
       <c r="Q8" s="43">
-        <f>IF(P8&gt;0,P8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R8" s="42">
@@ -6834,7 +6698,7 @@
         <v/>
       </c>
       <c r="S8" s="43">
-        <f>IF(R8&gt;0,R8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T8" s="42">
@@ -6842,7 +6706,7 @@
         <v/>
       </c>
       <c r="U8" s="43">
-        <f>IF(T8&gt;0,T8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V8" s="42">
@@ -6850,7 +6714,7 @@
         <v/>
       </c>
       <c r="W8" s="43">
-        <f>IF(V8&gt;0,V8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X8" s="42">
@@ -6858,7 +6722,7 @@
         <v/>
       </c>
       <c r="Y8" s="43">
-        <f>IF(X8&gt;0,X8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z8" s="42">
@@ -6866,7 +6730,7 @@
         <v/>
       </c>
       <c r="AA8" s="43">
-        <f>IF(Z8&gt;0,Z8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB8" s="42">
@@ -6874,7 +6738,7 @@
         <v/>
       </c>
       <c r="AC8" s="43">
-        <f>IF(AB8&gt;0,AB8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD8" s="42">
@@ -6882,7 +6746,7 @@
         <v/>
       </c>
       <c r="AE8" s="43">
-        <f>IF(AD8&gt;0,AD8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF8" s="42">
@@ -6890,7 +6754,7 @@
         <v/>
       </c>
       <c r="AG8" s="43">
-        <f>IF(AF8&gt;0,AF8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH8" s="42">
@@ -6898,7 +6762,7 @@
         <v/>
       </c>
       <c r="AI8" s="43">
-        <f>IF(AH8&gt;0,AH8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ8" s="42">
@@ -6906,7 +6770,7 @@
         <v/>
       </c>
       <c r="AK8" s="43">
-        <f>IF(AJ8&gt;0,AJ8*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL8" s="39">
@@ -6914,7 +6778,7 @@
         <v/>
       </c>
       <c r="AM8" s="40">
-        <f>IF(AL8&gt;0,AL8*הגדרות!$B$4,"")</f>
+        <f>SUM(C8,E8,G8,I8,K8,M8,O8,Q8,S8,U8,W8,Y8,AA8,AC8,AE8,AG8,AI8,AK8)</f>
         <v/>
       </c>
     </row>
@@ -6929,7 +6793,7 @@
         <v/>
       </c>
       <c r="C9" s="38">
-        <f>IF(B9&gt;0,B9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D9" s="37">
@@ -6937,7 +6801,7 @@
         <v/>
       </c>
       <c r="E9" s="38">
-        <f>IF(D9&gt;0,D9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F9" s="37">
@@ -6945,7 +6809,7 @@
         <v/>
       </c>
       <c r="G9" s="38">
-        <f>IF(F9&gt;0,F9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H9" s="37">
@@ -6953,7 +6817,7 @@
         <v/>
       </c>
       <c r="I9" s="38">
-        <f>IF(H9&gt;0,H9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J9" s="37">
@@ -6961,7 +6825,7 @@
         <v/>
       </c>
       <c r="K9" s="38">
-        <f>IF(J9&gt;0,J9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L9" s="37">
@@ -6969,7 +6833,7 @@
         <v/>
       </c>
       <c r="M9" s="38">
-        <f>IF(L9&gt;0,L9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N9" s="37">
@@ -6977,7 +6841,7 @@
         <v/>
       </c>
       <c r="O9" s="38">
-        <f>IF(N9&gt;0,N9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P9" s="37">
@@ -6985,7 +6849,7 @@
         <v/>
       </c>
       <c r="Q9" s="38">
-        <f>IF(P9&gt;0,P9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R9" s="37">
@@ -6993,7 +6857,7 @@
         <v/>
       </c>
       <c r="S9" s="38">
-        <f>IF(R9&gt;0,R9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T9" s="37">
@@ -7001,7 +6865,7 @@
         <v/>
       </c>
       <c r="U9" s="38">
-        <f>IF(T9&gt;0,T9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V9" s="37">
@@ -7009,7 +6873,7 @@
         <v/>
       </c>
       <c r="W9" s="38">
-        <f>IF(V9&gt;0,V9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X9" s="37">
@@ -7017,7 +6881,7 @@
         <v/>
       </c>
       <c r="Y9" s="38">
-        <f>IF(X9&gt;0,X9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z9" s="37">
@@ -7025,7 +6889,7 @@
         <v/>
       </c>
       <c r="AA9" s="38">
-        <f>IF(Z9&gt;0,Z9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB9" s="37">
@@ -7033,7 +6897,7 @@
         <v/>
       </c>
       <c r="AC9" s="38">
-        <f>IF(AB9&gt;0,AB9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD9" s="37">
@@ -7041,7 +6905,7 @@
         <v/>
       </c>
       <c r="AE9" s="38">
-        <f>IF(AD9&gt;0,AD9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF9" s="37">
@@ -7049,7 +6913,7 @@
         <v/>
       </c>
       <c r="AG9" s="38">
-        <f>IF(AF9&gt;0,AF9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH9" s="37">
@@ -7057,7 +6921,7 @@
         <v/>
       </c>
       <c r="AI9" s="38">
-        <f>IF(AH9&gt;0,AH9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ9" s="37">
@@ -7065,7 +6929,7 @@
         <v/>
       </c>
       <c r="AK9" s="38">
-        <f>IF(AJ9&gt;0,AJ9*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL9" s="39">
@@ -7073,7 +6937,7 @@
         <v/>
       </c>
       <c r="AM9" s="40">
-        <f>IF(AL9&gt;0,AL9*הגדרות!$B$4,"")</f>
+        <f>SUM(C9,E9,G9,I9,K9,M9,O9,Q9,S9,U9,W9,Y9,AA9,AC9,AE9,AG9,AI9,AK9)</f>
         <v/>
       </c>
     </row>
@@ -7088,7 +6952,7 @@
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>IF(B10&gt;0,B10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D10" s="42">
@@ -7096,7 +6960,7 @@
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>IF(D10&gt;0,D10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F10" s="42">
@@ -7104,7 +6968,7 @@
         <v/>
       </c>
       <c r="G10" s="43">
-        <f>IF(F10&gt;0,F10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H10" s="42">
@@ -7112,7 +6976,7 @@
         <v/>
       </c>
       <c r="I10" s="43">
-        <f>IF(H10&gt;0,H10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J10" s="42">
@@ -7120,7 +6984,7 @@
         <v/>
       </c>
       <c r="K10" s="43">
-        <f>IF(J10&gt;0,J10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L10" s="42">
@@ -7128,7 +6992,7 @@
         <v/>
       </c>
       <c r="M10" s="43">
-        <f>IF(L10&gt;0,L10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N10" s="42">
@@ -7136,7 +7000,7 @@
         <v/>
       </c>
       <c r="O10" s="43">
-        <f>IF(N10&gt;0,N10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P10" s="42">
@@ -7144,7 +7008,7 @@
         <v/>
       </c>
       <c r="Q10" s="43">
-        <f>IF(P10&gt;0,P10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R10" s="42">
@@ -7152,7 +7016,7 @@
         <v/>
       </c>
       <c r="S10" s="43">
-        <f>IF(R10&gt;0,R10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T10" s="42">
@@ -7160,7 +7024,7 @@
         <v/>
       </c>
       <c r="U10" s="43">
-        <f>IF(T10&gt;0,T10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V10" s="42">
@@ -7168,7 +7032,7 @@
         <v/>
       </c>
       <c r="W10" s="43">
-        <f>IF(V10&gt;0,V10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X10" s="42">
@@ -7176,7 +7040,7 @@
         <v/>
       </c>
       <c r="Y10" s="43">
-        <f>IF(X10&gt;0,X10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z10" s="42">
@@ -7184,7 +7048,7 @@
         <v/>
       </c>
       <c r="AA10" s="43">
-        <f>IF(Z10&gt;0,Z10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB10" s="42">
@@ -7192,7 +7056,7 @@
         <v/>
       </c>
       <c r="AC10" s="43">
-        <f>IF(AB10&gt;0,AB10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD10" s="42">
@@ -7200,7 +7064,7 @@
         <v/>
       </c>
       <c r="AE10" s="43">
-        <f>IF(AD10&gt;0,AD10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF10" s="42">
@@ -7208,7 +7072,7 @@
         <v/>
       </c>
       <c r="AG10" s="43">
-        <f>IF(AF10&gt;0,AF10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH10" s="42">
@@ -7216,7 +7080,7 @@
         <v/>
       </c>
       <c r="AI10" s="43">
-        <f>IF(AH10&gt;0,AH10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ10" s="42">
@@ -7224,7 +7088,7 @@
         <v/>
       </c>
       <c r="AK10" s="43">
-        <f>IF(AJ10&gt;0,AJ10*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL10" s="39">
@@ -7232,7 +7096,7 @@
         <v/>
       </c>
       <c r="AM10" s="40">
-        <f>IF(AL10&gt;0,AL10*הגדרות!$B$4,"")</f>
+        <f>SUM(C10,E10,G10,I10,K10,M10,O10,Q10,S10,U10,W10,Y10,AA10,AC10,AE10,AG10,AI10,AK10)</f>
         <v/>
       </c>
     </row>
@@ -7247,7 +7111,7 @@
         <v/>
       </c>
       <c r="C11" s="38">
-        <f>IF(B11&gt;0,B11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D11" s="37">
@@ -7255,7 +7119,7 @@
         <v/>
       </c>
       <c r="E11" s="38">
-        <f>IF(D11&gt;0,D11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F11" s="37">
@@ -7263,7 +7127,7 @@
         <v/>
       </c>
       <c r="G11" s="38">
-        <f>IF(F11&gt;0,F11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H11" s="37">
@@ -7271,7 +7135,7 @@
         <v/>
       </c>
       <c r="I11" s="38">
-        <f>IF(H11&gt;0,H11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J11" s="37">
@@ -7279,7 +7143,7 @@
         <v/>
       </c>
       <c r="K11" s="38">
-        <f>IF(J11&gt;0,J11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L11" s="37">
@@ -7287,7 +7151,7 @@
         <v/>
       </c>
       <c r="M11" s="38">
-        <f>IF(L11&gt;0,L11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N11" s="37">
@@ -7295,7 +7159,7 @@
         <v/>
       </c>
       <c r="O11" s="38">
-        <f>IF(N11&gt;0,N11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P11" s="37">
@@ -7303,7 +7167,7 @@
         <v/>
       </c>
       <c r="Q11" s="38">
-        <f>IF(P11&gt;0,P11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R11" s="37">
@@ -7311,7 +7175,7 @@
         <v/>
       </c>
       <c r="S11" s="38">
-        <f>IF(R11&gt;0,R11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T11" s="37">
@@ -7319,7 +7183,7 @@
         <v/>
       </c>
       <c r="U11" s="38">
-        <f>IF(T11&gt;0,T11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V11" s="37">
@@ -7327,7 +7191,7 @@
         <v/>
       </c>
       <c r="W11" s="38">
-        <f>IF(V11&gt;0,V11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X11" s="37">
@@ -7335,7 +7199,7 @@
         <v/>
       </c>
       <c r="Y11" s="38">
-        <f>IF(X11&gt;0,X11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z11" s="37">
@@ -7343,7 +7207,7 @@
         <v/>
       </c>
       <c r="AA11" s="38">
-        <f>IF(Z11&gt;0,Z11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB11" s="37">
@@ -7351,7 +7215,7 @@
         <v/>
       </c>
       <c r="AC11" s="38">
-        <f>IF(AB11&gt;0,AB11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD11" s="37">
@@ -7359,7 +7223,7 @@
         <v/>
       </c>
       <c r="AE11" s="38">
-        <f>IF(AD11&gt;0,AD11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF11" s="37">
@@ -7367,7 +7231,7 @@
         <v/>
       </c>
       <c r="AG11" s="38">
-        <f>IF(AF11&gt;0,AF11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH11" s="37">
@@ -7375,7 +7239,7 @@
         <v/>
       </c>
       <c r="AI11" s="38">
-        <f>IF(AH11&gt;0,AH11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ11" s="37">
@@ -7383,7 +7247,7 @@
         <v/>
       </c>
       <c r="AK11" s="38">
-        <f>IF(AJ11&gt;0,AJ11*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL11" s="39">
@@ -7391,7 +7255,7 @@
         <v/>
       </c>
       <c r="AM11" s="40">
-        <f>IF(AL11&gt;0,AL11*הגדרות!$B$4,"")</f>
+        <f>SUM(C11,E11,G11,I11,K11,M11,O11,Q11,S11,U11,W11,Y11,AA11,AC11,AE11,AG11,AI11,AK11)</f>
         <v/>
       </c>
     </row>
@@ -7406,7 +7270,7 @@
         <v/>
       </c>
       <c r="C12" s="43">
-        <f>IF(B12&gt;0,B12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D12" s="42">
@@ -7414,7 +7278,7 @@
         <v/>
       </c>
       <c r="E12" s="43">
-        <f>IF(D12&gt;0,D12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F12" s="42">
@@ -7422,7 +7286,7 @@
         <v/>
       </c>
       <c r="G12" s="43">
-        <f>IF(F12&gt;0,F12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H12" s="42">
@@ -7430,7 +7294,7 @@
         <v/>
       </c>
       <c r="I12" s="43">
-        <f>IF(H12&gt;0,H12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J12" s="42">
@@ -7438,7 +7302,7 @@
         <v/>
       </c>
       <c r="K12" s="43">
-        <f>IF(J12&gt;0,J12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L12" s="42">
@@ -7446,7 +7310,7 @@
         <v/>
       </c>
       <c r="M12" s="43">
-        <f>IF(L12&gt;0,L12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N12" s="42">
@@ -7454,7 +7318,7 @@
         <v/>
       </c>
       <c r="O12" s="43">
-        <f>IF(N12&gt;0,N12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P12" s="42">
@@ -7462,7 +7326,7 @@
         <v/>
       </c>
       <c r="Q12" s="43">
-        <f>IF(P12&gt;0,P12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R12" s="42">
@@ -7470,7 +7334,7 @@
         <v/>
       </c>
       <c r="S12" s="43">
-        <f>IF(R12&gt;0,R12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T12" s="42">
@@ -7478,7 +7342,7 @@
         <v/>
       </c>
       <c r="U12" s="43">
-        <f>IF(T12&gt;0,T12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V12" s="42">
@@ -7486,7 +7350,7 @@
         <v/>
       </c>
       <c r="W12" s="43">
-        <f>IF(V12&gt;0,V12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X12" s="42">
@@ -7494,7 +7358,7 @@
         <v/>
       </c>
       <c r="Y12" s="43">
-        <f>IF(X12&gt;0,X12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z12" s="42">
@@ -7502,7 +7366,7 @@
         <v/>
       </c>
       <c r="AA12" s="43">
-        <f>IF(Z12&gt;0,Z12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB12" s="42">
@@ -7510,7 +7374,7 @@
         <v/>
       </c>
       <c r="AC12" s="43">
-        <f>IF(AB12&gt;0,AB12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD12" s="42">
@@ -7518,7 +7382,7 @@
         <v/>
       </c>
       <c r="AE12" s="43">
-        <f>IF(AD12&gt;0,AD12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF12" s="42">
@@ -7526,7 +7390,7 @@
         <v/>
       </c>
       <c r="AG12" s="43">
-        <f>IF(AF12&gt;0,AF12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH12" s="42">
@@ -7534,7 +7398,7 @@
         <v/>
       </c>
       <c r="AI12" s="43">
-        <f>IF(AH12&gt;0,AH12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ12" s="42">
@@ -7542,7 +7406,7 @@
         <v/>
       </c>
       <c r="AK12" s="43">
-        <f>IF(AJ12&gt;0,AJ12*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL12" s="39">
@@ -7550,7 +7414,7 @@
         <v/>
       </c>
       <c r="AM12" s="40">
-        <f>IF(AL12&gt;0,AL12*הגדרות!$B$4,"")</f>
+        <f>SUM(C12,E12,G12,I12,K12,M12,O12,Q12,S12,U12,W12,Y12,AA12,AC12,AE12,AG12,AI12,AK12)</f>
         <v/>
       </c>
     </row>
@@ -7565,7 +7429,7 @@
         <v/>
       </c>
       <c r="C13" s="38">
-        <f>IF(B13&gt;0,B13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D13" s="37">
@@ -7573,7 +7437,7 @@
         <v/>
       </c>
       <c r="E13" s="38">
-        <f>IF(D13&gt;0,D13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F13" s="37">
@@ -7581,7 +7445,7 @@
         <v/>
       </c>
       <c r="G13" s="38">
-        <f>IF(F13&gt;0,F13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H13" s="37">
@@ -7589,7 +7453,7 @@
         <v/>
       </c>
       <c r="I13" s="38">
-        <f>IF(H13&gt;0,H13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J13" s="37">
@@ -7597,7 +7461,7 @@
         <v/>
       </c>
       <c r="K13" s="38">
-        <f>IF(J13&gt;0,J13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L13" s="37">
@@ -7605,7 +7469,7 @@
         <v/>
       </c>
       <c r="M13" s="38">
-        <f>IF(L13&gt;0,L13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N13" s="37">
@@ -7613,7 +7477,7 @@
         <v/>
       </c>
       <c r="O13" s="38">
-        <f>IF(N13&gt;0,N13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P13" s="37">
@@ -7621,7 +7485,7 @@
         <v/>
       </c>
       <c r="Q13" s="38">
-        <f>IF(P13&gt;0,P13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R13" s="37">
@@ -7629,7 +7493,7 @@
         <v/>
       </c>
       <c r="S13" s="38">
-        <f>IF(R13&gt;0,R13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T13" s="37">
@@ -7637,7 +7501,7 @@
         <v/>
       </c>
       <c r="U13" s="38">
-        <f>IF(T13&gt;0,T13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V13" s="37">
@@ -7645,7 +7509,7 @@
         <v/>
       </c>
       <c r="W13" s="38">
-        <f>IF(V13&gt;0,V13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X13" s="37">
@@ -7653,7 +7517,7 @@
         <v/>
       </c>
       <c r="Y13" s="38">
-        <f>IF(X13&gt;0,X13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z13" s="37">
@@ -7661,7 +7525,7 @@
         <v/>
       </c>
       <c r="AA13" s="38">
-        <f>IF(Z13&gt;0,Z13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB13" s="37">
@@ -7669,7 +7533,7 @@
         <v/>
       </c>
       <c r="AC13" s="38">
-        <f>IF(AB13&gt;0,AB13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD13" s="37">
@@ -7677,7 +7541,7 @@
         <v/>
       </c>
       <c r="AE13" s="38">
-        <f>IF(AD13&gt;0,AD13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF13" s="37">
@@ -7685,7 +7549,7 @@
         <v/>
       </c>
       <c r="AG13" s="38">
-        <f>IF(AF13&gt;0,AF13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH13" s="37">
@@ -7693,7 +7557,7 @@
         <v/>
       </c>
       <c r="AI13" s="38">
-        <f>IF(AH13&gt;0,AH13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ13" s="37">
@@ -7701,7 +7565,7 @@
         <v/>
       </c>
       <c r="AK13" s="38">
-        <f>IF(AJ13&gt;0,AJ13*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL13" s="39">
@@ -7709,7 +7573,7 @@
         <v/>
       </c>
       <c r="AM13" s="40">
-        <f>IF(AL13&gt;0,AL13*הגדרות!$B$4,"")</f>
+        <f>SUM(C13,E13,G13,I13,K13,M13,O13,Q13,S13,U13,W13,Y13,AA13,AC13,AE13,AG13,AI13,AK13)</f>
         <v/>
       </c>
     </row>
@@ -7724,7 +7588,7 @@
         <v/>
       </c>
       <c r="C14" s="43">
-        <f>IF(B14&gt;0,B14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D14" s="42">
@@ -7732,7 +7596,7 @@
         <v/>
       </c>
       <c r="E14" s="43">
-        <f>IF(D14&gt;0,D14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F14" s="42">
@@ -7740,7 +7604,7 @@
         <v/>
       </c>
       <c r="G14" s="43">
-        <f>IF(F14&gt;0,F14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H14" s="42">
@@ -7748,7 +7612,7 @@
         <v/>
       </c>
       <c r="I14" s="43">
-        <f>IF(H14&gt;0,H14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J14" s="42">
@@ -7756,7 +7620,7 @@
         <v/>
       </c>
       <c r="K14" s="43">
-        <f>IF(J14&gt;0,J14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L14" s="42">
@@ -7764,7 +7628,7 @@
         <v/>
       </c>
       <c r="M14" s="43">
-        <f>IF(L14&gt;0,L14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N14" s="42">
@@ -7772,7 +7636,7 @@
         <v/>
       </c>
       <c r="O14" s="43">
-        <f>IF(N14&gt;0,N14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P14" s="42">
@@ -7780,7 +7644,7 @@
         <v/>
       </c>
       <c r="Q14" s="43">
-        <f>IF(P14&gt;0,P14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R14" s="42">
@@ -7788,7 +7652,7 @@
         <v/>
       </c>
       <c r="S14" s="43">
-        <f>IF(R14&gt;0,R14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T14" s="42">
@@ -7796,7 +7660,7 @@
         <v/>
       </c>
       <c r="U14" s="43">
-        <f>IF(T14&gt;0,T14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V14" s="42">
@@ -7804,7 +7668,7 @@
         <v/>
       </c>
       <c r="W14" s="43">
-        <f>IF(V14&gt;0,V14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X14" s="42">
@@ -7812,7 +7676,7 @@
         <v/>
       </c>
       <c r="Y14" s="43">
-        <f>IF(X14&gt;0,X14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z14" s="42">
@@ -7820,7 +7684,7 @@
         <v/>
       </c>
       <c r="AA14" s="43">
-        <f>IF(Z14&gt;0,Z14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB14" s="42">
@@ -7828,7 +7692,7 @@
         <v/>
       </c>
       <c r="AC14" s="43">
-        <f>IF(AB14&gt;0,AB14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD14" s="42">
@@ -7836,7 +7700,7 @@
         <v/>
       </c>
       <c r="AE14" s="43">
-        <f>IF(AD14&gt;0,AD14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF14" s="42">
@@ -7844,7 +7708,7 @@
         <v/>
       </c>
       <c r="AG14" s="43">
-        <f>IF(AF14&gt;0,AF14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH14" s="42">
@@ -7852,7 +7716,7 @@
         <v/>
       </c>
       <c r="AI14" s="43">
-        <f>IF(AH14&gt;0,AH14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ14" s="42">
@@ -7860,7 +7724,7 @@
         <v/>
       </c>
       <c r="AK14" s="43">
-        <f>IF(AJ14&gt;0,AJ14*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL14" s="39">
@@ -7868,7 +7732,7 @@
         <v/>
       </c>
       <c r="AM14" s="40">
-        <f>IF(AL14&gt;0,AL14*הגדרות!$B$4,"")</f>
+        <f>SUM(C14,E14,G14,I14,K14,M14,O14,Q14,S14,U14,W14,Y14,AA14,AC14,AE14,AG14,AI14,AK14)</f>
         <v/>
       </c>
     </row>
@@ -7883,7 +7747,7 @@
         <v/>
       </c>
       <c r="C15" s="38">
-        <f>IF(B15&gt;0,B15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D15" s="37">
@@ -7891,7 +7755,7 @@
         <v/>
       </c>
       <c r="E15" s="38">
-        <f>IF(D15&gt;0,D15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F15" s="37">
@@ -7899,7 +7763,7 @@
         <v/>
       </c>
       <c r="G15" s="38">
-        <f>IF(F15&gt;0,F15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H15" s="37">
@@ -7907,7 +7771,7 @@
         <v/>
       </c>
       <c r="I15" s="38">
-        <f>IF(H15&gt;0,H15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J15" s="37">
@@ -7915,7 +7779,7 @@
         <v/>
       </c>
       <c r="K15" s="38">
-        <f>IF(J15&gt;0,J15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L15" s="37">
@@ -7923,7 +7787,7 @@
         <v/>
       </c>
       <c r="M15" s="38">
-        <f>IF(L15&gt;0,L15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N15" s="37">
@@ -7931,7 +7795,7 @@
         <v/>
       </c>
       <c r="O15" s="38">
-        <f>IF(N15&gt;0,N15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P15" s="37">
@@ -7939,7 +7803,7 @@
         <v/>
       </c>
       <c r="Q15" s="38">
-        <f>IF(P15&gt;0,P15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R15" s="37">
@@ -7947,7 +7811,7 @@
         <v/>
       </c>
       <c r="S15" s="38">
-        <f>IF(R15&gt;0,R15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T15" s="37">
@@ -7955,7 +7819,7 @@
         <v/>
       </c>
       <c r="U15" s="38">
-        <f>IF(T15&gt;0,T15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V15" s="37">
@@ -7963,7 +7827,7 @@
         <v/>
       </c>
       <c r="W15" s="38">
-        <f>IF(V15&gt;0,V15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X15" s="37">
@@ -7971,7 +7835,7 @@
         <v/>
       </c>
       <c r="Y15" s="38">
-        <f>IF(X15&gt;0,X15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z15" s="37">
@@ -7979,7 +7843,7 @@
         <v/>
       </c>
       <c r="AA15" s="38">
-        <f>IF(Z15&gt;0,Z15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB15" s="37">
@@ -7987,7 +7851,7 @@
         <v/>
       </c>
       <c r="AC15" s="38">
-        <f>IF(AB15&gt;0,AB15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD15" s="37">
@@ -7995,7 +7859,7 @@
         <v/>
       </c>
       <c r="AE15" s="38">
-        <f>IF(AD15&gt;0,AD15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF15" s="37">
@@ -8003,7 +7867,7 @@
         <v/>
       </c>
       <c r="AG15" s="38">
-        <f>IF(AF15&gt;0,AF15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH15" s="37">
@@ -8011,7 +7875,7 @@
         <v/>
       </c>
       <c r="AI15" s="38">
-        <f>IF(AH15&gt;0,AH15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ15" s="37">
@@ -8019,7 +7883,7 @@
         <v/>
       </c>
       <c r="AK15" s="38">
-        <f>IF(AJ15&gt;0,AJ15*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL15" s="39">
@@ -8027,7 +7891,7 @@
         <v/>
       </c>
       <c r="AM15" s="40">
-        <f>IF(AL15&gt;0,AL15*הגדרות!$B$4,"")</f>
+        <f>SUM(C15,E15,G15,I15,K15,M15,O15,Q15,S15,U15,W15,Y15,AA15,AC15,AE15,AG15,AI15,AK15)</f>
         <v/>
       </c>
     </row>
@@ -8042,7 +7906,7 @@
         <v/>
       </c>
       <c r="C16" s="43">
-        <f>IF(B16&gt;0,B16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D16" s="42">
@@ -8050,7 +7914,7 @@
         <v/>
       </c>
       <c r="E16" s="43">
-        <f>IF(D16&gt;0,D16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F16" s="42">
@@ -8058,7 +7922,7 @@
         <v/>
       </c>
       <c r="G16" s="43">
-        <f>IF(F16&gt;0,F16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H16" s="42">
@@ -8066,7 +7930,7 @@
         <v/>
       </c>
       <c r="I16" s="43">
-        <f>IF(H16&gt;0,H16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J16" s="42">
@@ -8074,7 +7938,7 @@
         <v/>
       </c>
       <c r="K16" s="43">
-        <f>IF(J16&gt;0,J16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L16" s="42">
@@ -8082,7 +7946,7 @@
         <v/>
       </c>
       <c r="M16" s="43">
-        <f>IF(L16&gt;0,L16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N16" s="42">
@@ -8090,7 +7954,7 @@
         <v/>
       </c>
       <c r="O16" s="43">
-        <f>IF(N16&gt;0,N16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P16" s="42">
@@ -8098,7 +7962,7 @@
         <v/>
       </c>
       <c r="Q16" s="43">
-        <f>IF(P16&gt;0,P16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R16" s="42">
@@ -8106,7 +7970,7 @@
         <v/>
       </c>
       <c r="S16" s="43">
-        <f>IF(R16&gt;0,R16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T16" s="42">
@@ -8114,7 +7978,7 @@
         <v/>
       </c>
       <c r="U16" s="43">
-        <f>IF(T16&gt;0,T16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V16" s="42">
@@ -8122,7 +7986,7 @@
         <v/>
       </c>
       <c r="W16" s="43">
-        <f>IF(V16&gt;0,V16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X16" s="42">
@@ -8130,7 +7994,7 @@
         <v/>
       </c>
       <c r="Y16" s="43">
-        <f>IF(X16&gt;0,X16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z16" s="42">
@@ -8138,7 +8002,7 @@
         <v/>
       </c>
       <c r="AA16" s="43">
-        <f>IF(Z16&gt;0,Z16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB16" s="42">
@@ -8146,7 +8010,7 @@
         <v/>
       </c>
       <c r="AC16" s="43">
-        <f>IF(AB16&gt;0,AB16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD16" s="42">
@@ -8154,7 +8018,7 @@
         <v/>
       </c>
       <c r="AE16" s="43">
-        <f>IF(AD16&gt;0,AD16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF16" s="42">
@@ -8162,7 +8026,7 @@
         <v/>
       </c>
       <c r="AG16" s="43">
-        <f>IF(AF16&gt;0,AF16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH16" s="42">
@@ -8170,7 +8034,7 @@
         <v/>
       </c>
       <c r="AI16" s="43">
-        <f>IF(AH16&gt;0,AH16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ16" s="42">
@@ -8178,7 +8042,7 @@
         <v/>
       </c>
       <c r="AK16" s="43">
-        <f>IF(AJ16&gt;0,AJ16*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL16" s="39">
@@ -8186,7 +8050,7 @@
         <v/>
       </c>
       <c r="AM16" s="40">
-        <f>IF(AL16&gt;0,AL16*הגדרות!$B$4,"")</f>
+        <f>SUM(C16,E16,G16,I16,K16,M16,O16,Q16,S16,U16,W16,Y16,AA16,AC16,AE16,AG16,AI16,AK16)</f>
         <v/>
       </c>
     </row>
@@ -8201,7 +8065,7 @@
         <v/>
       </c>
       <c r="C17" s="38">
-        <f>IF(B17&gt;0,B17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D17" s="37">
@@ -8209,7 +8073,7 @@
         <v/>
       </c>
       <c r="E17" s="38">
-        <f>IF(D17&gt;0,D17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F17" s="37">
@@ -8217,7 +8081,7 @@
         <v/>
       </c>
       <c r="G17" s="38">
-        <f>IF(F17&gt;0,F17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H17" s="37">
@@ -8225,7 +8089,7 @@
         <v/>
       </c>
       <c r="I17" s="38">
-        <f>IF(H17&gt;0,H17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J17" s="37">
@@ -8233,7 +8097,7 @@
         <v/>
       </c>
       <c r="K17" s="38">
-        <f>IF(J17&gt;0,J17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L17" s="37">
@@ -8241,7 +8105,7 @@
         <v/>
       </c>
       <c r="M17" s="38">
-        <f>IF(L17&gt;0,L17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N17" s="37">
@@ -8249,7 +8113,7 @@
         <v/>
       </c>
       <c r="O17" s="38">
-        <f>IF(N17&gt;0,N17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P17" s="37">
@@ -8257,7 +8121,7 @@
         <v/>
       </c>
       <c r="Q17" s="38">
-        <f>IF(P17&gt;0,P17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R17" s="37">
@@ -8265,7 +8129,7 @@
         <v/>
       </c>
       <c r="S17" s="38">
-        <f>IF(R17&gt;0,R17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T17" s="37">
@@ -8273,7 +8137,7 @@
         <v/>
       </c>
       <c r="U17" s="38">
-        <f>IF(T17&gt;0,T17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V17" s="37">
@@ -8281,7 +8145,7 @@
         <v/>
       </c>
       <c r="W17" s="38">
-        <f>IF(V17&gt;0,V17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X17" s="37">
@@ -8289,7 +8153,7 @@
         <v/>
       </c>
       <c r="Y17" s="38">
-        <f>IF(X17&gt;0,X17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z17" s="37">
@@ -8297,7 +8161,7 @@
         <v/>
       </c>
       <c r="AA17" s="38">
-        <f>IF(Z17&gt;0,Z17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB17" s="37">
@@ -8305,7 +8169,7 @@
         <v/>
       </c>
       <c r="AC17" s="38">
-        <f>IF(AB17&gt;0,AB17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD17" s="37">
@@ -8313,7 +8177,7 @@
         <v/>
       </c>
       <c r="AE17" s="38">
-        <f>IF(AD17&gt;0,AD17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF17" s="37">
@@ -8321,7 +8185,7 @@
         <v/>
       </c>
       <c r="AG17" s="38">
-        <f>IF(AF17&gt;0,AF17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH17" s="37">
@@ -8329,7 +8193,7 @@
         <v/>
       </c>
       <c r="AI17" s="38">
-        <f>IF(AH17&gt;0,AH17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ17" s="37">
@@ -8337,7 +8201,7 @@
         <v/>
       </c>
       <c r="AK17" s="38">
-        <f>IF(AJ17&gt;0,AJ17*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL17" s="39">
@@ -8345,7 +8209,7 @@
         <v/>
       </c>
       <c r="AM17" s="40">
-        <f>IF(AL17&gt;0,AL17*הגדרות!$B$4,"")</f>
+        <f>SUM(C17,E17,G17,I17,K17,M17,O17,Q17,S17,U17,W17,Y17,AA17,AC17,AE17,AG17,AI17,AK17)</f>
         <v/>
       </c>
     </row>
@@ -8360,7 +8224,7 @@
         <v/>
       </c>
       <c r="C18" s="43">
-        <f>IF(B18&gt;0,B18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D18" s="42">
@@ -8368,7 +8232,7 @@
         <v/>
       </c>
       <c r="E18" s="43">
-        <f>IF(D18&gt;0,D18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F18" s="42">
@@ -8376,7 +8240,7 @@
         <v/>
       </c>
       <c r="G18" s="43">
-        <f>IF(F18&gt;0,F18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H18" s="42">
@@ -8384,7 +8248,7 @@
         <v/>
       </c>
       <c r="I18" s="43">
-        <f>IF(H18&gt;0,H18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J18" s="42">
@@ -8392,7 +8256,7 @@
         <v/>
       </c>
       <c r="K18" s="43">
-        <f>IF(J18&gt;0,J18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L18" s="42">
@@ -8400,7 +8264,7 @@
         <v/>
       </c>
       <c r="M18" s="43">
-        <f>IF(L18&gt;0,L18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N18" s="42">
@@ -8408,7 +8272,7 @@
         <v/>
       </c>
       <c r="O18" s="43">
-        <f>IF(N18&gt;0,N18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P18" s="42">
@@ -8416,7 +8280,7 @@
         <v/>
       </c>
       <c r="Q18" s="43">
-        <f>IF(P18&gt;0,P18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R18" s="42">
@@ -8424,7 +8288,7 @@
         <v/>
       </c>
       <c r="S18" s="43">
-        <f>IF(R18&gt;0,R18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T18" s="42">
@@ -8432,7 +8296,7 @@
         <v/>
       </c>
       <c r="U18" s="43">
-        <f>IF(T18&gt;0,T18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V18" s="42">
@@ -8440,7 +8304,7 @@
         <v/>
       </c>
       <c r="W18" s="43">
-        <f>IF(V18&gt;0,V18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X18" s="42">
@@ -8448,7 +8312,7 @@
         <v/>
       </c>
       <c r="Y18" s="43">
-        <f>IF(X18&gt;0,X18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z18" s="42">
@@ -8456,7 +8320,7 @@
         <v/>
       </c>
       <c r="AA18" s="43">
-        <f>IF(Z18&gt;0,Z18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB18" s="42">
@@ -8464,7 +8328,7 @@
         <v/>
       </c>
       <c r="AC18" s="43">
-        <f>IF(AB18&gt;0,AB18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD18" s="42">
@@ -8472,7 +8336,7 @@
         <v/>
       </c>
       <c r="AE18" s="43">
-        <f>IF(AD18&gt;0,AD18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF18" s="42">
@@ -8480,7 +8344,7 @@
         <v/>
       </c>
       <c r="AG18" s="43">
-        <f>IF(AF18&gt;0,AF18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH18" s="42">
@@ -8488,7 +8352,7 @@
         <v/>
       </c>
       <c r="AI18" s="43">
-        <f>IF(AH18&gt;0,AH18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ18" s="42">
@@ -8496,7 +8360,7 @@
         <v/>
       </c>
       <c r="AK18" s="43">
-        <f>IF(AJ18&gt;0,AJ18*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL18" s="39">
@@ -8504,7 +8368,7 @@
         <v/>
       </c>
       <c r="AM18" s="40">
-        <f>IF(AL18&gt;0,AL18*הגדרות!$B$4,"")</f>
+        <f>SUM(C18,E18,G18,I18,K18,M18,O18,Q18,S18,U18,W18,Y18,AA18,AC18,AE18,AG18,AI18,AK18)</f>
         <v/>
       </c>
     </row>
@@ -8519,7 +8383,7 @@
         <v/>
       </c>
       <c r="C19" s="38">
-        <f>IF(B19&gt;0,B19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D19" s="37">
@@ -8527,7 +8391,7 @@
         <v/>
       </c>
       <c r="E19" s="38">
-        <f>IF(D19&gt;0,D19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F19" s="37">
@@ -8535,7 +8399,7 @@
         <v/>
       </c>
       <c r="G19" s="38">
-        <f>IF(F19&gt;0,F19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H19" s="37">
@@ -8543,7 +8407,7 @@
         <v/>
       </c>
       <c r="I19" s="38">
-        <f>IF(H19&gt;0,H19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J19" s="37">
@@ -8551,7 +8415,7 @@
         <v/>
       </c>
       <c r="K19" s="38">
-        <f>IF(J19&gt;0,J19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L19" s="37">
@@ -8559,7 +8423,7 @@
         <v/>
       </c>
       <c r="M19" s="38">
-        <f>IF(L19&gt;0,L19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N19" s="37">
@@ -8567,7 +8431,7 @@
         <v/>
       </c>
       <c r="O19" s="38">
-        <f>IF(N19&gt;0,N19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P19" s="37">
@@ -8575,7 +8439,7 @@
         <v/>
       </c>
       <c r="Q19" s="38">
-        <f>IF(P19&gt;0,P19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R19" s="37">
@@ -8583,7 +8447,7 @@
         <v/>
       </c>
       <c r="S19" s="38">
-        <f>IF(R19&gt;0,R19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T19" s="37">
@@ -8591,7 +8455,7 @@
         <v/>
       </c>
       <c r="U19" s="38">
-        <f>IF(T19&gt;0,T19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V19" s="37">
@@ -8599,7 +8463,7 @@
         <v/>
       </c>
       <c r="W19" s="38">
-        <f>IF(V19&gt;0,V19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X19" s="37">
@@ -8607,7 +8471,7 @@
         <v/>
       </c>
       <c r="Y19" s="38">
-        <f>IF(X19&gt;0,X19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z19" s="37">
@@ -8615,7 +8479,7 @@
         <v/>
       </c>
       <c r="AA19" s="38">
-        <f>IF(Z19&gt;0,Z19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB19" s="37">
@@ -8623,7 +8487,7 @@
         <v/>
       </c>
       <c r="AC19" s="38">
-        <f>IF(AB19&gt;0,AB19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD19" s="37">
@@ -8631,7 +8495,7 @@
         <v/>
       </c>
       <c r="AE19" s="38">
-        <f>IF(AD19&gt;0,AD19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF19" s="37">
@@ -8639,7 +8503,7 @@
         <v/>
       </c>
       <c r="AG19" s="38">
-        <f>IF(AF19&gt;0,AF19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH19" s="37">
@@ -8647,7 +8511,7 @@
         <v/>
       </c>
       <c r="AI19" s="38">
-        <f>IF(AH19&gt;0,AH19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ19" s="37">
@@ -8655,7 +8519,7 @@
         <v/>
       </c>
       <c r="AK19" s="38">
-        <f>IF(AJ19&gt;0,AJ19*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL19" s="39">
@@ -8663,7 +8527,7 @@
         <v/>
       </c>
       <c r="AM19" s="40">
-        <f>IF(AL19&gt;0,AL19*הגדרות!$B$4,"")</f>
+        <f>SUM(C19,E19,G19,I19,K19,M19,O19,Q19,S19,U19,W19,Y19,AA19,AC19,AE19,AG19,AI19,AK19)</f>
         <v/>
       </c>
     </row>
@@ -8678,7 +8542,7 @@
         <v/>
       </c>
       <c r="C20" s="43">
-        <f>IF(B20&gt;0,B20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D20" s="42">
@@ -8686,7 +8550,7 @@
         <v/>
       </c>
       <c r="E20" s="43">
-        <f>IF(D20&gt;0,D20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F20" s="42">
@@ -8694,7 +8558,7 @@
         <v/>
       </c>
       <c r="G20" s="43">
-        <f>IF(F20&gt;0,F20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H20" s="42">
@@ -8702,7 +8566,7 @@
         <v/>
       </c>
       <c r="I20" s="43">
-        <f>IF(H20&gt;0,H20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J20" s="42">
@@ -8710,7 +8574,7 @@
         <v/>
       </c>
       <c r="K20" s="43">
-        <f>IF(J20&gt;0,J20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L20" s="42">
@@ -8718,7 +8582,7 @@
         <v/>
       </c>
       <c r="M20" s="43">
-        <f>IF(L20&gt;0,L20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N20" s="42">
@@ -8726,7 +8590,7 @@
         <v/>
       </c>
       <c r="O20" s="43">
-        <f>IF(N20&gt;0,N20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P20" s="42">
@@ -8734,7 +8598,7 @@
         <v/>
       </c>
       <c r="Q20" s="43">
-        <f>IF(P20&gt;0,P20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R20" s="42">
@@ -8742,7 +8606,7 @@
         <v/>
       </c>
       <c r="S20" s="43">
-        <f>IF(R20&gt;0,R20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T20" s="42">
@@ -8750,7 +8614,7 @@
         <v/>
       </c>
       <c r="U20" s="43">
-        <f>IF(T20&gt;0,T20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V20" s="42">
@@ -8758,7 +8622,7 @@
         <v/>
       </c>
       <c r="W20" s="43">
-        <f>IF(V20&gt;0,V20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X20" s="42">
@@ -8766,7 +8630,7 @@
         <v/>
       </c>
       <c r="Y20" s="43">
-        <f>IF(X20&gt;0,X20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z20" s="42">
@@ -8774,7 +8638,7 @@
         <v/>
       </c>
       <c r="AA20" s="43">
-        <f>IF(Z20&gt;0,Z20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB20" s="42">
@@ -8782,7 +8646,7 @@
         <v/>
       </c>
       <c r="AC20" s="43">
-        <f>IF(AB20&gt;0,AB20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD20" s="42">
@@ -8790,7 +8654,7 @@
         <v/>
       </c>
       <c r="AE20" s="43">
-        <f>IF(AD20&gt;0,AD20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF20" s="42">
@@ -8798,7 +8662,7 @@
         <v/>
       </c>
       <c r="AG20" s="43">
-        <f>IF(AF20&gt;0,AF20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH20" s="42">
@@ -8806,7 +8670,7 @@
         <v/>
       </c>
       <c r="AI20" s="43">
-        <f>IF(AH20&gt;0,AH20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ20" s="42">
@@ -8814,7 +8678,7 @@
         <v/>
       </c>
       <c r="AK20" s="43">
-        <f>IF(AJ20&gt;0,AJ20*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL20" s="39">
@@ -8822,7 +8686,7 @@
         <v/>
       </c>
       <c r="AM20" s="40">
-        <f>IF(AL20&gt;0,AL20*הגדרות!$B$4,"")</f>
+        <f>SUM(C20,E20,G20,I20,K20,M20,O20,Q20,S20,U20,W20,Y20,AA20,AC20,AE20,AG20,AI20,AK20)</f>
         <v/>
       </c>
     </row>
@@ -8837,7 +8701,7 @@
         <v/>
       </c>
       <c r="C21" s="38">
-        <f>IF(B21&gt;0,B21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D21" s="37">
@@ -8845,7 +8709,7 @@
         <v/>
       </c>
       <c r="E21" s="38">
-        <f>IF(D21&gt;0,D21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F21" s="37">
@@ -8853,7 +8717,7 @@
         <v/>
       </c>
       <c r="G21" s="38">
-        <f>IF(F21&gt;0,F21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H21" s="37">
@@ -8861,7 +8725,7 @@
         <v/>
       </c>
       <c r="I21" s="38">
-        <f>IF(H21&gt;0,H21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J21" s="37">
@@ -8869,7 +8733,7 @@
         <v/>
       </c>
       <c r="K21" s="38">
-        <f>IF(J21&gt;0,J21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L21" s="37">
@@ -8877,7 +8741,7 @@
         <v/>
       </c>
       <c r="M21" s="38">
-        <f>IF(L21&gt;0,L21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N21" s="37">
@@ -8885,7 +8749,7 @@
         <v/>
       </c>
       <c r="O21" s="38">
-        <f>IF(N21&gt;0,N21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P21" s="37">
@@ -8893,7 +8757,7 @@
         <v/>
       </c>
       <c r="Q21" s="38">
-        <f>IF(P21&gt;0,P21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R21" s="37">
@@ -8901,7 +8765,7 @@
         <v/>
       </c>
       <c r="S21" s="38">
-        <f>IF(R21&gt;0,R21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T21" s="37">
@@ -8909,7 +8773,7 @@
         <v/>
       </c>
       <c r="U21" s="38">
-        <f>IF(T21&gt;0,T21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V21" s="37">
@@ -8917,7 +8781,7 @@
         <v/>
       </c>
       <c r="W21" s="38">
-        <f>IF(V21&gt;0,V21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X21" s="37">
@@ -8925,7 +8789,7 @@
         <v/>
       </c>
       <c r="Y21" s="38">
-        <f>IF(X21&gt;0,X21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z21" s="37">
@@ -8933,7 +8797,7 @@
         <v/>
       </c>
       <c r="AA21" s="38">
-        <f>IF(Z21&gt;0,Z21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB21" s="37">
@@ -8941,7 +8805,7 @@
         <v/>
       </c>
       <c r="AC21" s="38">
-        <f>IF(AB21&gt;0,AB21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD21" s="37">
@@ -8949,7 +8813,7 @@
         <v/>
       </c>
       <c r="AE21" s="38">
-        <f>IF(AD21&gt;0,AD21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF21" s="37">
@@ -8957,7 +8821,7 @@
         <v/>
       </c>
       <c r="AG21" s="38">
-        <f>IF(AF21&gt;0,AF21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH21" s="37">
@@ -8965,7 +8829,7 @@
         <v/>
       </c>
       <c r="AI21" s="38">
-        <f>IF(AH21&gt;0,AH21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ21" s="37">
@@ -8973,7 +8837,7 @@
         <v/>
       </c>
       <c r="AK21" s="38">
-        <f>IF(AJ21&gt;0,AJ21*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL21" s="39">
@@ -8981,7 +8845,7 @@
         <v/>
       </c>
       <c r="AM21" s="40">
-        <f>IF(AL21&gt;0,AL21*הגדרות!$B$4,"")</f>
+        <f>SUM(C21,E21,G21,I21,K21,M21,O21,Q21,S21,U21,W21,Y21,AA21,AC21,AE21,AG21,AI21,AK21)</f>
         <v/>
       </c>
     </row>
@@ -8996,7 +8860,7 @@
         <v/>
       </c>
       <c r="C22" s="43">
-        <f>IF(B22&gt;0,B22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D22" s="42">
@@ -9004,7 +8868,7 @@
         <v/>
       </c>
       <c r="E22" s="43">
-        <f>IF(D22&gt;0,D22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F22" s="42">
@@ -9012,7 +8876,7 @@
         <v/>
       </c>
       <c r="G22" s="43">
-        <f>IF(F22&gt;0,F22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H22" s="42">
@@ -9020,7 +8884,7 @@
         <v/>
       </c>
       <c r="I22" s="43">
-        <f>IF(H22&gt;0,H22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J22" s="42">
@@ -9028,7 +8892,7 @@
         <v/>
       </c>
       <c r="K22" s="43">
-        <f>IF(J22&gt;0,J22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L22" s="42">
@@ -9036,7 +8900,7 @@
         <v/>
       </c>
       <c r="M22" s="43">
-        <f>IF(L22&gt;0,L22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N22" s="42">
@@ -9044,7 +8908,7 @@
         <v/>
       </c>
       <c r="O22" s="43">
-        <f>IF(N22&gt;0,N22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P22" s="42">
@@ -9052,7 +8916,7 @@
         <v/>
       </c>
       <c r="Q22" s="43">
-        <f>IF(P22&gt;0,P22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R22" s="42">
@@ -9060,7 +8924,7 @@
         <v/>
       </c>
       <c r="S22" s="43">
-        <f>IF(R22&gt;0,R22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T22" s="42">
@@ -9068,7 +8932,7 @@
         <v/>
       </c>
       <c r="U22" s="43">
-        <f>IF(T22&gt;0,T22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V22" s="42">
@@ -9076,7 +8940,7 @@
         <v/>
       </c>
       <c r="W22" s="43">
-        <f>IF(V22&gt;0,V22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X22" s="42">
@@ -9084,7 +8948,7 @@
         <v/>
       </c>
       <c r="Y22" s="43">
-        <f>IF(X22&gt;0,X22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z22" s="42">
@@ -9092,7 +8956,7 @@
         <v/>
       </c>
       <c r="AA22" s="43">
-        <f>IF(Z22&gt;0,Z22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB22" s="42">
@@ -9100,7 +8964,7 @@
         <v/>
       </c>
       <c r="AC22" s="43">
-        <f>IF(AB22&gt;0,AB22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD22" s="42">
@@ -9108,7 +8972,7 @@
         <v/>
       </c>
       <c r="AE22" s="43">
-        <f>IF(AD22&gt;0,AD22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF22" s="42">
@@ -9116,7 +8980,7 @@
         <v/>
       </c>
       <c r="AG22" s="43">
-        <f>IF(AF22&gt;0,AF22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH22" s="42">
@@ -9124,7 +8988,7 @@
         <v/>
       </c>
       <c r="AI22" s="43">
-        <f>IF(AH22&gt;0,AH22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ22" s="42">
@@ -9132,7 +8996,7 @@
         <v/>
       </c>
       <c r="AK22" s="43">
-        <f>IF(AJ22&gt;0,AJ22*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL22" s="39">
@@ -9140,7 +9004,7 @@
         <v/>
       </c>
       <c r="AM22" s="40">
-        <f>IF(AL22&gt;0,AL22*הגדרות!$B$4,"")</f>
+        <f>SUM(C22,E22,G22,I22,K22,M22,O22,Q22,S22,U22,W22,Y22,AA22,AC22,AE22,AG22,AI22,AK22)</f>
         <v/>
       </c>
     </row>
@@ -9155,7 +9019,7 @@
         <v/>
       </c>
       <c r="C23" s="38">
-        <f>IF(B23&gt;0,B23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D23" s="37">
@@ -9163,7 +9027,7 @@
         <v/>
       </c>
       <c r="E23" s="38">
-        <f>IF(D23&gt;0,D23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F23" s="37">
@@ -9171,7 +9035,7 @@
         <v/>
       </c>
       <c r="G23" s="38">
-        <f>IF(F23&gt;0,F23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H23" s="37">
@@ -9179,7 +9043,7 @@
         <v/>
       </c>
       <c r="I23" s="38">
-        <f>IF(H23&gt;0,H23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J23" s="37">
@@ -9187,7 +9051,7 @@
         <v/>
       </c>
       <c r="K23" s="38">
-        <f>IF(J23&gt;0,J23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L23" s="37">
@@ -9195,7 +9059,7 @@
         <v/>
       </c>
       <c r="M23" s="38">
-        <f>IF(L23&gt;0,L23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N23" s="37">
@@ -9203,7 +9067,7 @@
         <v/>
       </c>
       <c r="O23" s="38">
-        <f>IF(N23&gt;0,N23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P23" s="37">
@@ -9211,7 +9075,7 @@
         <v/>
       </c>
       <c r="Q23" s="38">
-        <f>IF(P23&gt;0,P23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R23" s="37">
@@ -9219,7 +9083,7 @@
         <v/>
       </c>
       <c r="S23" s="38">
-        <f>IF(R23&gt;0,R23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T23" s="37">
@@ -9227,7 +9091,7 @@
         <v/>
       </c>
       <c r="U23" s="38">
-        <f>IF(T23&gt;0,T23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V23" s="37">
@@ -9235,7 +9099,7 @@
         <v/>
       </c>
       <c r="W23" s="38">
-        <f>IF(V23&gt;0,V23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X23" s="37">
@@ -9243,7 +9107,7 @@
         <v/>
       </c>
       <c r="Y23" s="38">
-        <f>IF(X23&gt;0,X23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z23" s="37">
@@ -9251,7 +9115,7 @@
         <v/>
       </c>
       <c r="AA23" s="38">
-        <f>IF(Z23&gt;0,Z23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB23" s="37">
@@ -9259,7 +9123,7 @@
         <v/>
       </c>
       <c r="AC23" s="38">
-        <f>IF(AB23&gt;0,AB23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD23" s="37">
@@ -9267,7 +9131,7 @@
         <v/>
       </c>
       <c r="AE23" s="38">
-        <f>IF(AD23&gt;0,AD23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF23" s="37">
@@ -9275,7 +9139,7 @@
         <v/>
       </c>
       <c r="AG23" s="38">
-        <f>IF(AF23&gt;0,AF23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH23" s="37">
@@ -9283,7 +9147,7 @@
         <v/>
       </c>
       <c r="AI23" s="38">
-        <f>IF(AH23&gt;0,AH23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ23" s="37">
@@ -9291,7 +9155,7 @@
         <v/>
       </c>
       <c r="AK23" s="38">
-        <f>IF(AJ23&gt;0,AJ23*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL23" s="39">
@@ -9299,7 +9163,7 @@
         <v/>
       </c>
       <c r="AM23" s="40">
-        <f>IF(AL23&gt;0,AL23*הגדרות!$B$4,"")</f>
+        <f>SUM(C23,E23,G23,I23,K23,M23,O23,Q23,S23,U23,W23,Y23,AA23,AC23,AE23,AG23,AI23,AK23)</f>
         <v/>
       </c>
     </row>
@@ -9314,7 +9178,7 @@
         <v/>
       </c>
       <c r="C24" s="43">
-        <f>IF(B24&gt;0,B24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D24" s="42">
@@ -9322,7 +9186,7 @@
         <v/>
       </c>
       <c r="E24" s="43">
-        <f>IF(D24&gt;0,D24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F24" s="42">
@@ -9330,7 +9194,7 @@
         <v/>
       </c>
       <c r="G24" s="43">
-        <f>IF(F24&gt;0,F24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H24" s="42">
@@ -9338,7 +9202,7 @@
         <v/>
       </c>
       <c r="I24" s="43">
-        <f>IF(H24&gt;0,H24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J24" s="42">
@@ -9346,7 +9210,7 @@
         <v/>
       </c>
       <c r="K24" s="43">
-        <f>IF(J24&gt;0,J24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L24" s="42">
@@ -9354,7 +9218,7 @@
         <v/>
       </c>
       <c r="M24" s="43">
-        <f>IF(L24&gt;0,L24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N24" s="42">
@@ -9362,7 +9226,7 @@
         <v/>
       </c>
       <c r="O24" s="43">
-        <f>IF(N24&gt;0,N24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P24" s="42">
@@ -9370,7 +9234,7 @@
         <v/>
       </c>
       <c r="Q24" s="43">
-        <f>IF(P24&gt;0,P24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R24" s="42">
@@ -9378,7 +9242,7 @@
         <v/>
       </c>
       <c r="S24" s="43">
-        <f>IF(R24&gt;0,R24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T24" s="42">
@@ -9386,7 +9250,7 @@
         <v/>
       </c>
       <c r="U24" s="43">
-        <f>IF(T24&gt;0,T24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V24" s="42">
@@ -9394,7 +9258,7 @@
         <v/>
       </c>
       <c r="W24" s="43">
-        <f>IF(V24&gt;0,V24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X24" s="42">
@@ -9402,7 +9266,7 @@
         <v/>
       </c>
       <c r="Y24" s="43">
-        <f>IF(X24&gt;0,X24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z24" s="42">
@@ -9410,7 +9274,7 @@
         <v/>
       </c>
       <c r="AA24" s="43">
-        <f>IF(Z24&gt;0,Z24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB24" s="42">
@@ -9418,7 +9282,7 @@
         <v/>
       </c>
       <c r="AC24" s="43">
-        <f>IF(AB24&gt;0,AB24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD24" s="42">
@@ -9426,7 +9290,7 @@
         <v/>
       </c>
       <c r="AE24" s="43">
-        <f>IF(AD24&gt;0,AD24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF24" s="42">
@@ -9434,7 +9298,7 @@
         <v/>
       </c>
       <c r="AG24" s="43">
-        <f>IF(AF24&gt;0,AF24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH24" s="42">
@@ -9442,7 +9306,7 @@
         <v/>
       </c>
       <c r="AI24" s="43">
-        <f>IF(AH24&gt;0,AH24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ24" s="42">
@@ -9450,7 +9314,7 @@
         <v/>
       </c>
       <c r="AK24" s="43">
-        <f>IF(AJ24&gt;0,AJ24*הגדרות!$B$4,"")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL24" s="39">
@@ -9458,7 +9322,7 @@
         <v/>
       </c>
       <c r="AM24" s="40">
-        <f>IF(AL24&gt;0,AL24*הגדרות!$B$4,"")</f>
+        <f>SUM(C24,E24,G24,I24,K24,M24,O24,Q24,S24,U24,W24,Y24,AA24,AC24,AE24,AG24,AI24,AK24)</f>
         <v/>
       </c>
     </row>
@@ -9748,7 +9612,7 @@
         <v/>
       </c>
       <c r="D4" s="49">
-        <f>C4*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"יולי 2025",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E4" s="50">
@@ -9773,7 +9637,7 @@
         <v/>
       </c>
       <c r="D5" s="53">
-        <f>C5*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"אוגוסט 2025",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E5" s="54">
@@ -9798,7 +9662,7 @@
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>C6*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"ספטמבר 2025",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E6" s="50">
@@ -9823,7 +9687,7 @@
         <v/>
       </c>
       <c r="D7" s="53">
-        <f>C7*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"אוקטובר 2025",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E7" s="54">
@@ -9848,7 +9712,7 @@
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>C8*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"נובמבר 2025",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E8" s="50">
@@ -9873,7 +9737,7 @@
         <v/>
       </c>
       <c r="D9" s="53">
-        <f>C9*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"דצמבר 2025",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E9" s="54">
@@ -9898,7 +9762,7 @@
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>C10*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"ינואר 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E10" s="50">
@@ -9923,7 +9787,7 @@
         <v/>
       </c>
       <c r="D11" s="53">
-        <f>C11*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"פברואר 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E11" s="54">
@@ -9948,7 +9812,7 @@
         <v/>
       </c>
       <c r="D12" s="49">
-        <f>C12*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"מרץ 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E12" s="50">
@@ -9973,7 +9837,7 @@
         <v/>
       </c>
       <c r="D13" s="53">
-        <f>C13*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"אפריל 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E13" s="54">
@@ -9998,7 +9862,7 @@
         <v/>
       </c>
       <c r="D14" s="49">
-        <f>C14*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"מאי 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E14" s="50">
@@ -10023,7 +9887,7 @@
         <v/>
       </c>
       <c r="D15" s="53">
-        <f>C15*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"יוני 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E15" s="54">
@@ -10048,7 +9912,7 @@
         <v/>
       </c>
       <c r="D16" s="49">
-        <f>C16*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"יולי 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E16" s="50">
@@ -10073,7 +9937,7 @@
         <v/>
       </c>
       <c r="D17" s="53">
-        <f>C17*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"אוגוסט 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E17" s="54">
@@ -10098,7 +9962,7 @@
         <v/>
       </c>
       <c r="D18" s="49">
-        <f>C18*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"ספטמבר 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E18" s="50">
@@ -10123,7 +9987,7 @@
         <v/>
       </c>
       <c r="D19" s="53">
-        <f>C19*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"אוקטובר 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E19" s="54">
@@ -10148,7 +10012,7 @@
         <v/>
       </c>
       <c r="D20" s="49">
-        <f>C20*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"נובמבר 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E20" s="50">
@@ -10173,7 +10037,7 @@
         <v/>
       </c>
       <c r="D21" s="53">
-        <f>C21*הגדרות!$B$4</f>
+        <f>SUMIF('כל ההוצאות'!$F:$F,"דצמבר 2026",'כל ההוצאות'!$E:$E)</f>
         <v/>
       </c>
       <c r="E21" s="54">
@@ -10202,7 +10066,7 @@
         <v/>
       </c>
       <c r="D23" s="57">
-        <f>C23*הגדרות!$B$4</f>
+        <f>SUM(D4:D21)</f>
         <v/>
       </c>
       <c r="E23" s="58" t="inlineStr">
@@ -10346,9 +10210,8 @@
       <c r="D4" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>3.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10371,9 +10234,8 @@
       <c r="D5" s="27" t="n">
         <v>72</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>226.22</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -10396,9 +10258,8 @@
       <c r="D6" s="25" t="n">
         <v>10.59</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>33.27</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -10421,9 +10282,8 @@
       <c r="D7" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -10446,9 +10306,8 @@
       <c r="D8" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -10471,9 +10330,8 @@
       <c r="D9" s="27" t="n">
         <v>13.5</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>42.42</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -10496,9 +10354,8 @@
       <c r="D10" s="25" t="n">
         <v>113.14</v>
       </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="26" t="n">
+        <v>355.49</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -10521,9 +10378,8 @@
       <c r="D11" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="28">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
+      <c r="E11" s="28" t="n">
+        <v>31.42</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -10641,9 +10497,8 @@
       <c r="D4" s="25" t="n">
         <v>15.6</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>56.93</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10666,9 +10521,8 @@
       <c r="D5" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>47.13</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -10691,9 +10545,8 @@
       <c r="D6" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>37.7</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -10716,9 +10569,8 @@
       <c r="D7" s="27" t="n">
         <v>0.9</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>2.83</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -10741,9 +10593,8 @@
       <c r="D8" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>59.7</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -10766,9 +10617,8 @@
       <c r="D9" s="27" t="n">
         <v>10.59</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>33.27</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -10791,9 +10641,8 @@
       <c r="D10" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -10816,9 +10665,8 @@
       <c r="D11" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E11" s="28">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
+      <c r="E11" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -10841,9 +10689,8 @@
       <c r="D12" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="26">
-        <f>D12*הגדרות!$B$4</f>
-        <v/>
+      <c r="E12" s="26" t="n">
+        <v>15.71</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -10866,9 +10713,8 @@
       <c r="D13" s="27" t="n">
         <v>11.25</v>
       </c>
-      <c r="E13" s="28">
-        <f>D13*הגדרות!$B$4</f>
-        <v/>
+      <c r="E13" s="28" t="n">
+        <v>35.35</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -10986,9 +10832,8 @@
       <c r="D4" s="25" t="n">
         <v>15.6</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>56.93</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11011,9 +10856,8 @@
       <c r="D5" s="27" t="n">
         <v>2.79</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>8.77</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11036,9 +10880,8 @@
       <c r="D6" s="25" t="n">
         <v>10.59</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>33.27</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11061,9 +10904,8 @@
       <c r="D7" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11086,9 +10928,8 @@
       <c r="D8" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11111,9 +10952,8 @@
       <c r="D9" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>15.71</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11231,9 +11071,8 @@
       <c r="D4" s="25" t="n">
         <v>15.6</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>56.93</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11256,9 +11095,8 @@
       <c r="D5" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11281,9 +11119,8 @@
       <c r="D6" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11306,9 +11143,8 @@
       <c r="D7" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>15.71</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11426,9 +11262,8 @@
       <c r="D4" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>37.7</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11451,9 +11286,8 @@
       <c r="D5" s="27" t="n">
         <v>11.8</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>37.08</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11476,9 +11310,8 @@
       <c r="D6" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>47.13</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11501,9 +11334,8 @@
       <c r="D7" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>31.42</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11526,9 +11358,8 @@
       <c r="D8" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11551,9 +11382,8 @@
       <c r="D9" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11576,9 +11406,8 @@
       <c r="D10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="26" t="n">
+        <v>15.71</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -11696,9 +11525,8 @@
       <c r="D4" s="25" t="n">
         <v>20.79</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11721,9 +11549,8 @@
       <c r="D5" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>47.13</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11746,9 +11573,8 @@
       <c r="D6" s="25" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>30.54</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11771,9 +11597,8 @@
       <c r="D7" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>94.26000000000001</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11796,9 +11621,8 @@
       <c r="D8" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>103.69</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11821,9 +11645,8 @@
       <c r="D9" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11846,9 +11669,8 @@
       <c r="D10" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="26" t="n">
+        <v>113.11</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -11871,9 +11693,8 @@
       <c r="D11" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="28">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
+      <c r="E11" s="28" t="n">
+        <v>15.71</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -11991,9 +11812,8 @@
       <c r="D4" s="25" t="n">
         <v>20.79</v>
       </c>
-      <c r="E4" s="26">
-        <f>D4*הגדרות!$B$4</f>
-        <v/>
+      <c r="E4" s="26" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -12016,9 +11836,8 @@
       <c r="D5" s="27" t="n">
         <v>139.92</v>
       </c>
-      <c r="E5" s="28">
-        <f>D5*הגדרות!$B$4</f>
-        <v/>
+      <c r="E5" s="28" t="n">
+        <v>439.63</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -12041,9 +11860,8 @@
       <c r="D6" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="26">
-        <f>D6*הגדרות!$B$4</f>
-        <v/>
+      <c r="E6" s="26" t="n">
+        <v>47.13</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -12066,9 +11884,8 @@
       <c r="D7" s="27" t="n">
         <v>19.43</v>
       </c>
-      <c r="E7" s="28">
-        <f>D7*הגדרות!$B$4</f>
-        <v/>
+      <c r="E7" s="28" t="n">
+        <v>61.05</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -12091,9 +11908,8 @@
       <c r="D8" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="26">
-        <f>D8*הגדרות!$B$4</f>
-        <v/>
+      <c r="E8" s="26" t="n">
+        <v>62.84</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -12116,9 +11932,8 @@
       <c r="D9" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="28">
-        <f>D9*הגדרות!$B$4</f>
-        <v/>
+      <c r="E9" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -12141,9 +11956,8 @@
       <c r="D10" s="25" t="n">
         <v>13.67</v>
       </c>
-      <c r="E10" s="26">
-        <f>D10*הגדרות!$B$4</f>
-        <v/>
+      <c r="E10" s="26" t="n">
+        <v>49.9</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -12166,9 +11980,8 @@
       <c r="D11" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E11" s="28">
-        <f>D11*הגדרות!$B$4</f>
-        <v/>
+      <c r="E11" s="28" t="n">
+        <v>62.84</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -12191,9 +12004,8 @@
       <c r="D12" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="E12" s="26">
-        <f>D12*הגדרות!$B$4</f>
-        <v/>
+      <c r="E12" s="26" t="n">
+        <v>122.54</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -12216,9 +12028,8 @@
       <c r="D13" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="E13" s="28">
-        <f>D13*הגדרות!$B$4</f>
-        <v/>
+      <c r="E13" s="28" t="n">
+        <v>78.55</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -12241,9 +12052,8 @@
       <c r="D14" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="E14" s="26">
-        <f>D14*הגדרות!$B$4</f>
-        <v/>
+      <c r="E14" s="26" t="n">
+        <v>135.11</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -12266,9 +12076,8 @@
       <c r="D15" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="28">
-        <f>D15*הגדרות!$B$4</f>
-        <v/>
+      <c r="E15" s="28" t="n">
+        <v>15.71</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -12291,9 +12100,8 @@
       <c r="D16" s="25" t="n">
         <v>14.5</v>
       </c>
-      <c r="E16" s="26">
-        <f>D16*הגדרות!$B$4</f>
-        <v/>
+      <c r="E16" s="26" t="n">
+        <v>45.56</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.142</v>
+        <v>3.087</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-07</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>78.55</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1119,7 +1119,7 @@
         <v>31.42</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>98.72</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -1167,7 +1167,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>147.67</v>
+        <v>145.09</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -1191,7 +1191,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -1215,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -1239,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -1263,7 +1263,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1287,7 +1287,7 @@
         <v>50</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>157.1</v>
+        <v>154.35</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1311,7 +1311,7 @@
         <v>51</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>160.24</v>
+        <v>157.44</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1335,7 +1335,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1359,7 +1359,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -1478,7 +1478,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1502,7 +1502,7 @@
         <v>14.5</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>45.56</v>
+        <v>44.76</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1550,7 +1550,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -1574,7 +1574,7 @@
         <v>40.11</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>126.03</v>
+        <v>123.82</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -1622,7 +1622,7 @@
         <v>51</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>160.24</v>
+        <v>157.44</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -1646,7 +1646,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -1670,7 +1670,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1718,7 +1718,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>34.56</v>
+        <v>33.96</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1861,7 +1861,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1885,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1933,7 +1933,7 @@
         <v>51</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>160.24</v>
+        <v>157.44</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -1957,7 +1957,7 @@
         <v>2.25</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>7.07</v>
+        <v>6.95</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -1981,7 +1981,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -2005,7 +2005,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -2124,7 +2124,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2243,7 +2243,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2362,7 +2362,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2481,7 +2481,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2600,7 +2600,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2719,7 +2719,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2838,7 +2838,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2949,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>72</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>226.22</v>
+        <v>222.26</v>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>10.59</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>33.27</v>
+        <v>32.69</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>13.5</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>42.42</v>
+        <v>41.67</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>113.14</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>355.49</v>
+        <v>349.26</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>15</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>47.13</v>
+        <v>46.3</v>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>37.7</v>
+        <v>37.04</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>0.9</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>59.7</v>
+        <v>58.65</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>10.59</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>33.27</v>
+        <v>32.69</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>11.25</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>35.35</v>
+        <v>34.73</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>2.79</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>8.77</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>10.59</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>33.27</v>
+        <v>32.69</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>5</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>37.7</v>
+        <v>37.04</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>11.8</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>37.08</v>
+        <v>36.43</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>47.13</v>
+        <v>46.3</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>10</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>47.13</v>
+        <v>46.3</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>30.54</v>
+        <v>30.01</v>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>30</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>94.26000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>33</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>103.69</v>
+        <v>101.87</v>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>36</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>113.11</v>
+        <v>111.13</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>5</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>139.92</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>439.63</v>
+        <v>431.93</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>15</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>47.13</v>
+        <v>46.3</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>19.43</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>61.05</v>
+        <v>59.98</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>39</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>122.54</v>
+        <v>120.39</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>25</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>78.55</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>43</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>135.11</v>
+        <v>132.74</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>5</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>14.5</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>45.56</v>
+        <v>44.76</v>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>25</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>78.55</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>31.42</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>98.72</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>47</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>147.67</v>
+        <v>145.09</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>20</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>20</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>50</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>157.1</v>
+        <v>154.35</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>51</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>160.24</v>
+        <v>157.44</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>5</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>10</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>14.5</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>45.56</v>
+        <v>44.76</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>10</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>40.11</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>126.03</v>
+        <v>123.82</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>51</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>160.24</v>
+        <v>157.44</v>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>20</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>10</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>11</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>34.56</v>
+        <v>33.96</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>5</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>20</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>5</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>51</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>160.24</v>
+        <v>157.44</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>2.25</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>7.07</v>
+        <v>6.95</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>20</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>20</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>20</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>20</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>20</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10211,7 +10211,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10235,7 +10235,7 @@
         <v>72</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>226.22</v>
+        <v>222.26</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -10259,7 +10259,7 @@
         <v>10.59</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>33.27</v>
+        <v>32.69</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -10283,7 +10283,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -10307,7 +10307,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -10331,7 +10331,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>42.42</v>
+        <v>41.67</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -10355,7 +10355,7 @@
         <v>113.14</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>355.49</v>
+        <v>349.26</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -10379,7 +10379,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -10522,7 +10522,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>47.13</v>
+        <v>46.3</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -10546,7 +10546,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>37.7</v>
+        <v>37.04</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -10570,7 +10570,7 @@
         <v>0.9</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -10594,7 +10594,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>59.7</v>
+        <v>58.65</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -10618,7 +10618,7 @@
         <v>10.59</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>33.27</v>
+        <v>32.69</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -10642,7 +10642,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -10666,7 +10666,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -10690,7 +10690,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -10714,7 +10714,7 @@
         <v>11.25</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>35.35</v>
+        <v>34.73</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -10857,7 +10857,7 @@
         <v>2.79</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>8.77</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -10881,7 +10881,7 @@
         <v>10.59</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>33.27</v>
+        <v>32.69</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -10905,7 +10905,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -10929,7 +10929,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -10953,7 +10953,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11096,7 +11096,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11120,7 +11120,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11144,7 +11144,7 @@
         <v>5</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11263,7 +11263,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>37.7</v>
+        <v>37.04</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11287,7 +11287,7 @@
         <v>11.8</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>37.08</v>
+        <v>36.43</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11311,7 +11311,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>47.13</v>
+        <v>46.3</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11335,7 +11335,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>31.42</v>
+        <v>30.87</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11359,7 +11359,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11383,7 +11383,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11407,7 +11407,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -11550,7 +11550,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>47.13</v>
+        <v>46.3</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11574,7 +11574,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>30.54</v>
+        <v>30.01</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11598,7 +11598,7 @@
         <v>30</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>94.26000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11622,7 +11622,7 @@
         <v>33</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>103.69</v>
+        <v>101.87</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11646,7 +11646,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11670,7 +11670,7 @@
         <v>36</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>113.11</v>
+        <v>111.13</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -11694,7 +11694,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -11837,7 +11837,7 @@
         <v>139.92</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>439.63</v>
+        <v>431.93</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11861,7 +11861,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>47.13</v>
+        <v>46.3</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11885,7 +11885,7 @@
         <v>19.43</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>61.05</v>
+        <v>59.98</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11909,7 +11909,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11933,7 +11933,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11981,7 +11981,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>62.84</v>
+        <v>61.74</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -12005,7 +12005,7 @@
         <v>39</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>122.54</v>
+        <v>120.39</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -12029,7 +12029,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>78.55</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -12053,7 +12053,7 @@
         <v>43</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>135.11</v>
+        <v>132.74</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -12077,7 +12077,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.71</v>
+        <v>15.44</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -12101,7 +12101,7 @@
         <v>14.5</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>45.56</v>
+        <v>44.76</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1783,7 +1783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1940,65 +1940,65 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>2.25</v>
+        <v>18</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>6.95</v>
+        <v>55.57</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.74</v>
+        <v>6.95</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
@@ -2009,28 +2009,52 @@
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="F11" s="29" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="20">
-        <f>SUM(D4:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="21">
-        <f>SUM(E4:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="31" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="20">
+        <f>SUM(D4:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>SUM(E4:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -2879,7 +2903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5312,24 +5336,24 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>2.25</v>
+        <v>18</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>6.95</v>
+        <v>55.57</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5340,24 +5364,24 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>61.74</v>
+        <v>6.95</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5368,17 +5392,17 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D90" s="16" t="n">
@@ -5396,7 +5420,7 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -5417,14 +5441,14 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
@@ -5445,14 +5469,14 @@
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -5473,14 +5497,14 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -5501,14 +5525,14 @@
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -5529,14 +5553,14 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5557,14 +5581,14 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5585,14 +5609,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5613,31 +5637,59 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="18" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B99" s="19" t="n"/>
-      <c r="C99" s="19" t="n"/>
-      <c r="D99" s="20">
-        <f>SUM(D3:D98)</f>
-        <v/>
-      </c>
-      <c r="E99" s="21">
-        <f>SUM(E3:E98)</f>
-        <v/>
-      </c>
-      <c r="F99" s="19" t="n"/>
+      <c r="B100" s="19" t="n"/>
+      <c r="C100" s="19" t="n"/>
+      <c r="D100" s="20">
+        <f>SUM(D3:D99)</f>
+        <v/>
+      </c>
+      <c r="E100" s="21">
+        <f>SUM(E3:E99)</f>
+        <v/>
+      </c>
+      <c r="F100" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A100:C100"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5770,7 +5822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM25"/>
+  <dimension ref="A1:AM26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6626,151 +6678,151 @@
     <row r="8">
       <c r="A8" s="41" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="B8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ8" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK8" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Dzine",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL8" s="39">
@@ -6785,151 +6837,151 @@
     <row r="9">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>Genspark</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="B9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ9" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK9" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Eleven Labs",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL9" s="39">
@@ -6944,151 +6996,151 @@
     <row r="10">
       <c r="A10" s="41" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Genspark</t>
         </is>
       </c>
       <c r="B10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ10" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK10" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Genspark",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL10" s="39">
@@ -7103,151 +7155,151 @@
     <row r="11">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>Hedra</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="B11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ11" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK11" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Google Workspace",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL11" s="39">
@@ -7262,151 +7314,151 @@
     <row r="12">
       <c r="A12" s="41" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>Hedra</t>
         </is>
       </c>
       <c r="B12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ12" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK12" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Hedra",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL12" s="39">
@@ -7421,151 +7473,151 @@
     <row r="13">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="B13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ13" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK13" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Higgsfield",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL13" s="39">
@@ -7580,151 +7632,151 @@
     <row r="14">
       <c r="A14" s="41" t="inlineStr">
         <is>
-          <t>Ideogram AI</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="B14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ14" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK14" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"IONOS",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL14" s="39">
@@ -7739,151 +7791,151 @@
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Ideogram AI</t>
         </is>
       </c>
       <c r="B15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ15" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK15" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Ideogram AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL15" s="39">
@@ -7898,151 +7950,151 @@
     <row r="16">
       <c r="A16" s="41" t="inlineStr">
         <is>
-          <t>Make</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="B16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ16" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK16" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Lovable",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL16" s="39">
@@ -8057,151 +8109,151 @@
     <row r="17">
       <c r="A17" s="36" t="inlineStr">
         <is>
-          <t>Manus AI</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="B17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ17" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK17" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Make",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL17" s="39">
@@ -8216,151 +8268,151 @@
     <row r="18">
       <c r="A18" s="41" t="inlineStr">
         <is>
-          <t>Manychat</t>
+          <t>Manus AI</t>
         </is>
       </c>
       <c r="B18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ18" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK18" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manus AI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL18" s="39">
@@ -8375,151 +8427,151 @@
     <row r="19">
       <c r="A19" s="36" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Manychat</t>
         </is>
       </c>
       <c r="B19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ19" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK19" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Manychat",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL19" s="39">
@@ -8534,151 +8586,151 @@
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="B20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ20" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK20" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Meta (Ads)",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL20" s="39">
@@ -8693,151 +8745,151 @@
     <row r="21">
       <c r="A21" s="36" t="inlineStr">
         <is>
-          <t>Recraft</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ21" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK21" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"OpenAI",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL21" s="39">
@@ -8852,151 +8904,151 @@
     <row r="22">
       <c r="A22" s="41" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Recraft</t>
         </is>
       </c>
       <c r="B22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ22" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK22" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Recraft",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL22" s="39">
@@ -9011,151 +9063,151 @@
     <row r="23">
       <c r="A23" s="36" t="inlineStr">
         <is>
-          <t>Runway ML</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="B23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ23" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK23" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Replicate",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL23" s="39">
@@ -9170,151 +9222,151 @@
     <row r="24">
       <c r="A24" s="41" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Runway ML</t>
         </is>
       </c>
       <c r="B24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ24" s="42">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK24" s="43">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Runway ML",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL24" s="39">
@@ -9326,162 +9378,321 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>Timeless</t>
+        </is>
+      </c>
+      <c r="B25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <v/>
+      </c>
+      <c r="C25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <v/>
+      </c>
+      <c r="D25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <v/>
+      </c>
+      <c r="E25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <v/>
+      </c>
+      <c r="F25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="G25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="H25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <v/>
+      </c>
+      <c r="I25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <v/>
+      </c>
+      <c r="J25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="K25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="L25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="M25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="N25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <v/>
+      </c>
+      <c r="O25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <v/>
+      </c>
+      <c r="P25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <v/>
+      </c>
+      <c r="R25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <v/>
+      </c>
+      <c r="S25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <v/>
+      </c>
+      <c r="T25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <v/>
+      </c>
+      <c r="U25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <v/>
+      </c>
+      <c r="V25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="X25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Z25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AB25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AD25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AF25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AH25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="37">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK25" s="38">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AL25" s="39">
+        <f>SUM(B25,D25,F25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25,AB25,AD25,AF25,AH25,AJ25)</f>
+        <v/>
+      </c>
+      <c r="AM25" s="40">
+        <f>SUM(C25,E25,G25,I25,K25,M25,O25,Q25,S25,U25,W25,Y25,AA25,AC25,AE25,AG25,AI25,AK25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודשי</t>
         </is>
       </c>
-      <c r="B25" s="20">
-        <f>SUM(B5:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="21">
-        <f>SUM(C5:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="20">
-        <f>SUM(D5:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="21">
-        <f>SUM(E5:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="20">
-        <f>SUM(F5:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="21">
-        <f>SUM(G5:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="20">
-        <f>SUM(H5:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="21">
-        <f>SUM(I5:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="20">
-        <f>SUM(J5:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="21">
-        <f>SUM(K5:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="20">
-        <f>SUM(L5:L24)</f>
-        <v/>
-      </c>
-      <c r="M25" s="21">
-        <f>SUM(M5:M24)</f>
-        <v/>
-      </c>
-      <c r="N25" s="20">
-        <f>SUM(N5:N24)</f>
-        <v/>
-      </c>
-      <c r="O25" s="21">
-        <f>SUM(O5:O24)</f>
-        <v/>
-      </c>
-      <c r="P25" s="20">
-        <f>SUM(P5:P24)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="21">
-        <f>SUM(Q5:Q24)</f>
-        <v/>
-      </c>
-      <c r="R25" s="20">
-        <f>SUM(R5:R24)</f>
-        <v/>
-      </c>
-      <c r="S25" s="21">
-        <f>SUM(S5:S24)</f>
-        <v/>
-      </c>
-      <c r="T25" s="20">
-        <f>SUM(T5:T24)</f>
-        <v/>
-      </c>
-      <c r="U25" s="21">
-        <f>SUM(U5:U24)</f>
-        <v/>
-      </c>
-      <c r="V25" s="20">
-        <f>SUM(V5:V24)</f>
-        <v/>
-      </c>
-      <c r="W25" s="21">
-        <f>SUM(W5:W24)</f>
-        <v/>
-      </c>
-      <c r="X25" s="20">
-        <f>SUM(X5:X24)</f>
-        <v/>
-      </c>
-      <c r="Y25" s="21">
-        <f>SUM(Y5:Y24)</f>
-        <v/>
-      </c>
-      <c r="Z25" s="20">
-        <f>SUM(Z5:Z24)</f>
-        <v/>
-      </c>
-      <c r="AA25" s="21">
-        <f>SUM(AA5:AA24)</f>
-        <v/>
-      </c>
-      <c r="AB25" s="20">
-        <f>SUM(AB5:AB24)</f>
-        <v/>
-      </c>
-      <c r="AC25" s="21">
-        <f>SUM(AC5:AC24)</f>
-        <v/>
-      </c>
-      <c r="AD25" s="20">
-        <f>SUM(AD5:AD24)</f>
-        <v/>
-      </c>
-      <c r="AE25" s="21">
-        <f>SUM(AE5:AE24)</f>
-        <v/>
-      </c>
-      <c r="AF25" s="20">
-        <f>SUM(AF5:AF24)</f>
-        <v/>
-      </c>
-      <c r="AG25" s="21">
-        <f>SUM(AG5:AG24)</f>
-        <v/>
-      </c>
-      <c r="AH25" s="20">
-        <f>SUM(AH5:AH24)</f>
-        <v/>
-      </c>
-      <c r="AI25" s="21">
-        <f>SUM(AI5:AI24)</f>
-        <v/>
-      </c>
-      <c r="AJ25" s="20">
-        <f>SUM(AJ5:AJ24)</f>
-        <v/>
-      </c>
-      <c r="AK25" s="21">
-        <f>SUM(AK5:AK24)</f>
-        <v/>
-      </c>
-      <c r="AL25" s="44">
-        <f>SUM(AL5:AL24)</f>
-        <v/>
-      </c>
-      <c r="AM25" s="45">
-        <f>SUM(AM5:AM24)</f>
+      <c r="B26" s="20">
+        <f>SUM(B5:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="21">
+        <f>SUM(C5:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="20">
+        <f>SUM(D5:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>SUM(E5:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="20">
+        <f>SUM(F5:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="21">
+        <f>SUM(G5:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="20">
+        <f>SUM(H5:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="21">
+        <f>SUM(I5:I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="20">
+        <f>SUM(J5:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="21">
+        <f>SUM(K5:K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="20">
+        <f>SUM(L5:L25)</f>
+        <v/>
+      </c>
+      <c r="M26" s="21">
+        <f>SUM(M5:M25)</f>
+        <v/>
+      </c>
+      <c r="N26" s="20">
+        <f>SUM(N5:N25)</f>
+        <v/>
+      </c>
+      <c r="O26" s="21">
+        <f>SUM(O5:O25)</f>
+        <v/>
+      </c>
+      <c r="P26" s="20">
+        <f>SUM(P5:P25)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="21">
+        <f>SUM(Q5:Q25)</f>
+        <v/>
+      </c>
+      <c r="R26" s="20">
+        <f>SUM(R5:R25)</f>
+        <v/>
+      </c>
+      <c r="S26" s="21">
+        <f>SUM(S5:S25)</f>
+        <v/>
+      </c>
+      <c r="T26" s="20">
+        <f>SUM(T5:T25)</f>
+        <v/>
+      </c>
+      <c r="U26" s="21">
+        <f>SUM(U5:U25)</f>
+        <v/>
+      </c>
+      <c r="V26" s="20">
+        <f>SUM(V5:V25)</f>
+        <v/>
+      </c>
+      <c r="W26" s="21">
+        <f>SUM(W5:W25)</f>
+        <v/>
+      </c>
+      <c r="X26" s="20">
+        <f>SUM(X5:X25)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="21">
+        <f>SUM(Y5:Y25)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="20">
+        <f>SUM(Z5:Z25)</f>
+        <v/>
+      </c>
+      <c r="AA26" s="21">
+        <f>SUM(AA5:AA25)</f>
+        <v/>
+      </c>
+      <c r="AB26" s="20">
+        <f>SUM(AB5:AB25)</f>
+        <v/>
+      </c>
+      <c r="AC26" s="21">
+        <f>SUM(AC5:AC25)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="20">
+        <f>SUM(AD5:AD25)</f>
+        <v/>
+      </c>
+      <c r="AE26" s="21">
+        <f>SUM(AE5:AE25)</f>
+        <v/>
+      </c>
+      <c r="AF26" s="20">
+        <f>SUM(AF5:AF25)</f>
+        <v/>
+      </c>
+      <c r="AG26" s="21">
+        <f>SUM(AG5:AG25)</f>
+        <v/>
+      </c>
+      <c r="AH26" s="20">
+        <f>SUM(AH5:AH25)</f>
+        <v/>
+      </c>
+      <c r="AI26" s="21">
+        <f>SUM(AI5:AI25)</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="20">
+        <f>SUM(AJ5:AJ25)</f>
+        <v/>
+      </c>
+      <c r="AK26" s="21">
+        <f>SUM(AK5:AK25)</f>
+        <v/>
+      </c>
+      <c r="AL26" s="44">
+        <f>SUM(AL5:AL25)</f>
+        <v/>
+      </c>
+      <c r="AM26" s="45">
+        <f>SUM(AM5:AM25)</f>
         <v/>
       </c>
     </row>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1400,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1746,28 +1746,52 @@
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Dzine</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Video Top-Up</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="20">
-        <f>SUM(D4:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>SUM(E4:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="20">
+        <f>SUM(D4:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>SUM(E4:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -2903,7 +2927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5224,17 +5248,17 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
@@ -5245,7 +5269,7 @@
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מרץ 2026</t>
         </is>
       </c>
     </row>
@@ -5262,14 +5286,14 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>15.44</v>
+        <v>61.74</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5285,19 +5309,19 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>20.79</v>
+        <v>5</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>75.90000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -5313,19 +5337,19 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>51</v>
+        <v>20.79</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>157.44</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -5336,24 +5360,24 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>55.57</v>
+        <v>157.44</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5364,24 +5388,24 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>2.25</v>
+        <v>18</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>6.95</v>
+        <v>55.57</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5392,24 +5416,24 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>61.74</v>
+        <v>6.95</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5420,17 +5444,17 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
@@ -5448,7 +5472,7 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
@@ -5469,14 +5493,14 @@
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -5497,14 +5521,14 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -5525,14 +5549,14 @@
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -5553,14 +5577,14 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5581,14 +5605,14 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5609,14 +5633,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5637,14 +5661,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5665,32 +5689,60 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="18" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B100" s="19" t="n"/>
-      <c r="C100" s="19" t="n"/>
-      <c r="D100" s="20">
-        <f>SUM(D3:D99)</f>
-        <v/>
-      </c>
-      <c r="E100" s="21">
-        <f>SUM(E3:E99)</f>
-        <v/>
-      </c>
-      <c r="F100" s="19" t="n"/>
+      <c r="B101" s="19" t="n"/>
+      <c r="C101" s="19" t="n"/>
+      <c r="D101" s="20">
+        <f>SUM(D3:D100)</f>
+        <v/>
+      </c>
+      <c r="E101" s="21">
+        <f>SUM(E3:E100)</f>
+        <v/>
+      </c>
+      <c r="F101" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A100:C100"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A101:C101"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1400,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1725,72 +1725,96 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.44</v>
+        <v>27.78</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Lite plan</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Dzine</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Video Top-Up</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D17" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E17" s="28" t="n">
         <v>61.74</v>
       </c>
-      <c r="F16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="F17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="20">
-        <f>SUM(D4:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>SUM(E4:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="31" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="20">
+        <f>SUM(D4:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>SUM(E4:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -2927,7 +2951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5220,24 +5244,24 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>15.44</v>
+        <v>27.78</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5248,24 +5272,24 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>61.74</v>
+        <v>15.44</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5276,17 +5300,17 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
@@ -5297,7 +5321,7 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מרץ 2026</t>
         </is>
       </c>
     </row>
@@ -5314,14 +5338,14 @@
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>15.44</v>
+        <v>61.74</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -5337,19 +5361,19 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.79</v>
+        <v>5</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -5365,19 +5389,19 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>51</v>
+        <v>20.79</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>157.44</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5388,24 +5412,24 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>55.57</v>
+        <v>157.44</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5416,24 +5440,24 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>2.25</v>
+        <v>18</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>6.95</v>
+        <v>55.57</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5444,24 +5468,24 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>61.74</v>
+        <v>6.95</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5472,17 +5496,17 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D92" s="16" t="n">
@@ -5500,7 +5524,7 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -5521,14 +5545,14 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -5549,14 +5573,14 @@
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -5577,14 +5601,14 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5605,14 +5629,14 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5633,14 +5657,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5661,14 +5685,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5689,14 +5713,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5717,32 +5741,60 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="18" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B101" s="19" t="n"/>
-      <c r="C101" s="19" t="n"/>
-      <c r="D101" s="20">
-        <f>SUM(D3:D100)</f>
-        <v/>
-      </c>
-      <c r="E101" s="21">
-        <f>SUM(E3:E100)</f>
-        <v/>
-      </c>
-      <c r="F101" s="19" t="n"/>
+      <c r="B102" s="19" t="n"/>
+      <c r="C102" s="19" t="n"/>
+      <c r="D102" s="20">
+        <f>SUM(D3:D101)</f>
+        <v/>
+      </c>
+      <c r="E102" s="21">
+        <f>SUM(E3:E101)</f>
+        <v/>
+      </c>
+      <c r="F102" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A102:C102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.087</v>
+        <v>3.057</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-09</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-10</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>77.18000000000001</v>
+        <v>76.42</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1119,7 +1119,7 @@
         <v>31.42</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>96.98999999999999</v>
+        <v>96.05</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -1167,7 +1167,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>145.09</v>
+        <v>143.68</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -1191,7 +1191,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -1215,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -1239,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -1263,7 +1263,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1287,7 +1287,7 @@
         <v>50</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>154.35</v>
+        <v>152.85</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1311,7 +1311,7 @@
         <v>51</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>157.44</v>
+        <v>155.91</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1335,7 +1335,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1359,7 +1359,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -1478,7 +1478,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1502,7 +1502,7 @@
         <v>14.5</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>44.76</v>
+        <v>44.33</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1550,7 +1550,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -1574,7 +1574,7 @@
         <v>40.11</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>123.82</v>
+        <v>122.62</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -1622,7 +1622,7 @@
         <v>51</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>157.44</v>
+        <v>155.91</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -1646,7 +1646,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -1670,7 +1670,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1718,7 +1718,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>33.96</v>
+        <v>33.63</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>27.78</v>
+        <v>27.51</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1766,7 +1766,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -1790,7 +1790,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
@@ -1831,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1909,7 +1909,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1933,7 +1933,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1981,7 +1981,7 @@
         <v>51</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>157.44</v>
+        <v>155.91</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -2005,7 +2005,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>55.57</v>
+        <v>55.03</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -2029,7 +2029,7 @@
         <v>2.25</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>6.95</v>
+        <v>6.88</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -2053,55 +2053,79 @@
         <v>20</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>capcut_pro_discount1</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>16.323193</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F11" s="29" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>ChatGPT Plus</t>
         </is>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D12" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E11" s="28" t="n">
-        <v>61.74</v>
-      </c>
-      <c r="F11" s="29" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="E12" s="26" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="F12" s="24" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="20">
-        <f>SUM(D4:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="21">
-        <f>SUM(E4:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="31" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="20">
+        <f>SUM(D4:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>SUM(E4:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -2196,7 +2220,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2315,7 +2339,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2434,7 +2458,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2553,7 +2577,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2672,7 +2696,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2791,7 +2815,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2910,7 +2934,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2951,7 +2975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3021,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
@@ -3049,7 +3073,7 @@
         <v>72</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>222.26</v>
+        <v>220.1</v>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
@@ -3077,7 +3101,7 @@
         <v>10.59</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>32.69</v>
+        <v>32.37</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -3105,7 +3129,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
@@ -3133,7 +3157,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -3161,7 +3185,7 @@
         <v>13.5</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>41.67</v>
+        <v>41.27</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
@@ -3189,7 +3213,7 @@
         <v>113.14</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>349.26</v>
+        <v>345.87</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -3217,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
@@ -3273,7 +3297,7 @@
         <v>15</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>46.3</v>
+        <v>45.85</v>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
@@ -3301,7 +3325,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>37.04</v>
+        <v>36.68</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -3329,7 +3353,7 @@
         <v>0.9</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
@@ -3357,7 +3381,7 @@
         <v>19</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>58.65</v>
+        <v>58.08</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -3385,7 +3409,7 @@
         <v>10.59</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>32.69</v>
+        <v>32.37</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
@@ -3413,7 +3437,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -3441,7 +3465,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
@@ -3469,7 +3493,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -3497,7 +3521,7 @@
         <v>11.25</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>34.73</v>
+        <v>34.39</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
@@ -3553,7 +3577,7 @@
         <v>2.79</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>8.609999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
@@ -3581,7 +3605,7 @@
         <v>10.59</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>32.69</v>
+        <v>32.37</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -3609,7 +3633,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -3637,7 +3661,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -3665,7 +3689,7 @@
         <v>5</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
@@ -3721,7 +3745,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
@@ -3749,7 +3773,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -3777,7 +3801,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
@@ -3805,7 +3829,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>37.04</v>
+        <v>36.68</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -3833,7 +3857,7 @@
         <v>11.8</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>36.43</v>
+        <v>36.07</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -3861,7 +3885,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>46.3</v>
+        <v>45.85</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -3889,7 +3913,7 @@
         <v>10</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
@@ -3917,7 +3941,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -3945,7 +3969,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
@@ -3973,7 +3997,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -4029,7 +4053,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>46.3</v>
+        <v>45.85</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -4057,7 +4081,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>30.01</v>
+        <v>29.71</v>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
@@ -4085,7 +4109,7 @@
         <v>30</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>92.61</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -4113,7 +4137,7 @@
         <v>33</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>101.87</v>
+        <v>100.88</v>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
@@ -4141,7 +4165,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -4169,7 +4193,7 @@
         <v>36</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>111.13</v>
+        <v>110.05</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
@@ -4197,7 +4221,7 @@
         <v>5</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -4253,7 +4277,7 @@
         <v>139.92</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>431.93</v>
+        <v>427.74</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -4281,7 +4305,7 @@
         <v>15</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>46.3</v>
+        <v>45.85</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
@@ -4309,7 +4333,7 @@
         <v>19.43</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>59.98</v>
+        <v>59.4</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
@@ -4337,7 +4361,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
@@ -4365,7 +4389,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
@@ -4421,7 +4445,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
@@ -4449,7 +4473,7 @@
         <v>39</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>120.39</v>
+        <v>119.22</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
@@ -4477,7 +4501,7 @@
         <v>25</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>77.18000000000001</v>
+        <v>76.42</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
@@ -4505,7 +4529,7 @@
         <v>43</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>132.74</v>
+        <v>131.45</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
@@ -4533,7 +4557,7 @@
         <v>5</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
@@ -4561,7 +4585,7 @@
         <v>14.5</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>44.76</v>
+        <v>44.33</v>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
@@ -4589,7 +4613,7 @@
         <v>25</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>77.18000000000001</v>
+        <v>76.42</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
@@ -4645,7 +4669,7 @@
         <v>31.42</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>96.98999999999999</v>
+        <v>96.05</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
@@ -4701,7 +4725,7 @@
         <v>47</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>145.09</v>
+        <v>143.68</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
@@ -4729,7 +4753,7 @@
         <v>20</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
@@ -4757,7 +4781,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
@@ -4785,7 +4809,7 @@
         <v>20</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -4813,7 +4837,7 @@
         <v>20</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
@@ -4841,7 +4865,7 @@
         <v>50</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>154.35</v>
+        <v>152.85</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
@@ -4869,7 +4893,7 @@
         <v>51</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>157.44</v>
+        <v>155.91</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -4897,7 +4921,7 @@
         <v>5</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -4925,7 +4949,7 @@
         <v>10</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -4953,7 +4977,7 @@
         <v>10</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -4981,7 +5005,7 @@
         <v>14.5</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>44.76</v>
+        <v>44.33</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -5037,7 +5061,7 @@
         <v>10</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -5065,7 +5089,7 @@
         <v>40.11</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>123.82</v>
+        <v>122.62</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -5121,7 +5145,7 @@
         <v>51</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>157.44</v>
+        <v>155.91</v>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -5149,7 +5173,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -5177,7 +5201,7 @@
         <v>20</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -5205,7 +5229,7 @@
         <v>10</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -5233,7 +5257,7 @@
         <v>11</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>33.96</v>
+        <v>33.63</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -5261,7 +5285,7 @@
         <v>9</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>27.78</v>
+        <v>27.51</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5289,7 +5313,7 @@
         <v>5</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5317,7 +5341,7 @@
         <v>20</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5345,7 +5369,7 @@
         <v>20</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -5373,7 +5397,7 @@
         <v>5</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -5429,7 +5453,7 @@
         <v>51</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>157.44</v>
+        <v>155.91</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5457,7 +5481,7 @@
         <v>18</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>55.57</v>
+        <v>55.03</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5485,7 +5509,7 @@
         <v>2.25</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>6.95</v>
+        <v>6.88</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5513,7 +5537,7 @@
         <v>20</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5524,24 +5548,24 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>61.74</v>
+        <v>49.9</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -5552,7 +5576,7 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -5569,18 +5593,18 @@
         <v>20</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -5597,18 +5621,18 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5625,18 +5649,18 @@
         <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5653,18 +5677,18 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5681,18 +5705,18 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5709,18 +5733,18 @@
         <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5737,18 +5761,18 @@
         <v>20</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5765,36 +5789,64 @@
         <v>20</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D102" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="18" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B102" s="19" t="n"/>
-      <c r="C102" s="19" t="n"/>
-      <c r="D102" s="20">
-        <f>SUM(D3:D101)</f>
-        <v/>
-      </c>
-      <c r="E102" s="21">
-        <f>SUM(E3:E101)</f>
-        <v/>
-      </c>
-      <c r="F102" s="19" t="n"/>
+      <c r="B103" s="19" t="n"/>
+      <c r="C103" s="19" t="n"/>
+      <c r="D103" s="20">
+        <f>SUM(D3:D102)</f>
+        <v/>
+      </c>
+      <c r="E103" s="21">
+        <f>SUM(E3:E102)</f>
+        <v/>
+      </c>
+      <c r="F103" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A103:C103"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A102:C102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5885,7 +5937,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10526,7 +10578,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10550,7 +10602,7 @@
         <v>72</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>222.26</v>
+        <v>220.1</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -10574,7 +10626,7 @@
         <v>10.59</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>32.69</v>
+        <v>32.37</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -10598,7 +10650,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -10622,7 +10674,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -10646,7 +10698,7 @@
         <v>13.5</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>41.67</v>
+        <v>41.27</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -10670,7 +10722,7 @@
         <v>113.14</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>349.26</v>
+        <v>345.87</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -10694,7 +10746,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -10837,7 +10889,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>46.3</v>
+        <v>45.85</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -10861,7 +10913,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>37.04</v>
+        <v>36.68</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -10885,7 +10937,7 @@
         <v>0.9</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -10909,7 +10961,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>58.65</v>
+        <v>58.08</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -10933,7 +10985,7 @@
         <v>10.59</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>32.69</v>
+        <v>32.37</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -10957,7 +11009,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -10981,7 +11033,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -11005,7 +11057,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -11029,7 +11081,7 @@
         <v>11.25</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>34.73</v>
+        <v>34.39</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -11172,7 +11224,7 @@
         <v>2.79</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>8.609999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11196,7 +11248,7 @@
         <v>10.59</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>32.69</v>
+        <v>32.37</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11220,7 +11272,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11244,7 +11296,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11268,7 +11320,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11411,7 +11463,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11435,7 +11487,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11459,7 +11511,7 @@
         <v>5</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11578,7 +11630,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>37.04</v>
+        <v>36.68</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11602,7 +11654,7 @@
         <v>11.8</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>36.43</v>
+        <v>36.07</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11626,7 +11678,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>46.3</v>
+        <v>45.85</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11650,7 +11702,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>30.87</v>
+        <v>30.57</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11674,7 +11726,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11698,7 +11750,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11722,7 +11774,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -11865,7 +11917,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>46.3</v>
+        <v>45.85</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11889,7 +11941,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>30.01</v>
+        <v>29.71</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11913,7 +11965,7 @@
         <v>30</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>92.61</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11937,7 +11989,7 @@
         <v>33</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>101.87</v>
+        <v>100.88</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11961,7 +12013,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11985,7 +12037,7 @@
         <v>36</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>111.13</v>
+        <v>110.05</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -12009,7 +12061,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -12152,7 +12204,7 @@
         <v>139.92</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>431.93</v>
+        <v>427.74</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -12176,7 +12228,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>46.3</v>
+        <v>45.85</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -12200,7 +12252,7 @@
         <v>19.43</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>59.98</v>
+        <v>59.4</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -12224,7 +12276,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -12248,7 +12300,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -12296,7 +12348,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.74</v>
+        <v>61.14</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -12320,7 +12372,7 @@
         <v>39</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>120.39</v>
+        <v>119.22</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -12344,7 +12396,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>77.18000000000001</v>
+        <v>76.42</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -12368,7 +12420,7 @@
         <v>43</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>132.74</v>
+        <v>131.45</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -12392,7 +12444,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.44</v>
+        <v>15.29</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -12416,7 +12468,7 @@
         <v>14.5</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>44.76</v>
+        <v>44.33</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1400,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1605,65 +1605,65 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>51</v>
+        <v>16.323193</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>155.91</v>
+        <v>49.9</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.14</v>
+        <v>155.91</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -1677,24 +1677,24 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>30.57</v>
+        <v>61.14</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1706,115 +1706,139 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>33.63</v>
+        <v>30.57</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>27.51</v>
+        <v>33.63</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>15.29</v>
+        <v>27.51</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Lite plan</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="F17" s="29" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Dzine</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Video Top-Up</t>
         </is>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D18" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E17" s="28" t="n">
+      <c r="E18" s="26" t="n">
         <v>61.14</v>
       </c>
-      <c r="F17" s="29" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="F18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="20">
-        <f>SUM(D4:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="21">
-        <f>SUM(E4:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="31" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="20">
+        <f>SUM(D4:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>SUM(E4:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -2975,7 +2999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5128,24 +5152,24 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>51</v>
+        <v>16.323193</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>155.91</v>
+        <v>49.9</v>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -5156,24 +5180,24 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>61.14</v>
+        <v>155.91</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -5184,17 +5208,17 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D80" s="16" t="n">
@@ -5212,24 +5236,24 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>30.57</v>
+        <v>61.14</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -5245,19 +5269,19 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>33.63</v>
+        <v>30.57</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -5268,24 +5292,24 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>27.51</v>
+        <v>33.63</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5296,24 +5320,24 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>15.29</v>
+        <v>27.51</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5324,24 +5348,24 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5352,17 +5376,17 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
@@ -5373,7 +5397,7 @@
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מרץ 2026</t>
         </is>
       </c>
     </row>
@@ -5390,14 +5414,14 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -5413,19 +5437,19 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>20.79</v>
+        <v>5</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>75.90000000000001</v>
+        <v>15.29</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5441,19 +5465,19 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>51</v>
+        <v>20.79</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>155.91</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5464,24 +5488,24 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>55.03</v>
+        <v>155.91</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5492,24 +5516,24 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>2.25</v>
+        <v>18</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>6.88</v>
+        <v>55.03</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5520,24 +5544,24 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>61.14</v>
+        <v>6.88</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5548,24 +5572,24 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -5576,24 +5600,24 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>61.14</v>
+        <v>49.9</v>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -5604,7 +5628,7 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -5625,14 +5649,14 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5653,14 +5677,14 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5681,14 +5705,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5709,14 +5733,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5737,14 +5761,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5765,14 +5789,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5793,14 +5817,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5821,32 +5845,60 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="18" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B103" s="19" t="n"/>
-      <c r="C103" s="19" t="n"/>
-      <c r="D103" s="20">
-        <f>SUM(D3:D102)</f>
-        <v/>
-      </c>
-      <c r="E103" s="21">
-        <f>SUM(E3:E102)</f>
-        <v/>
-      </c>
-      <c r="F103" s="19" t="n"/>
+      <c r="B104" s="19" t="n"/>
+      <c r="C104" s="19" t="n"/>
+      <c r="D104" s="20">
+        <f>SUM(D3:D103)</f>
+        <v/>
+      </c>
+      <c r="E104" s="21">
+        <f>SUM(E3:E103)</f>
+        <v/>
+      </c>
+      <c r="F104" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A103:C103"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A104:C104"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -993,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1150,55 +1150,55 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>47</v>
+        <v>16.323193</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>143.68</v>
+        <v>49.9</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.14</v>
+        <v>143.68</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -1208,14 +1208,14 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -1227,36 +1227,36 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -1270,24 +1270,24 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>On-Demand credits 500</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>152.85</v>
+        <v>61.14</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1299,43 +1299,43 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro2 monthly</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>155.91</v>
+        <v>152.85</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.29</v>
+        <v>155.91</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1347,43 +1347,67 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
           <t>Lovable</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D17" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E17" s="28" t="n">
         <v>30.57</v>
       </c>
-      <c r="F16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="F17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="20">
-        <f>SUM(D4:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>SUM(E4:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="31" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="20">
+        <f>SUM(D4:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>SUM(E4:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -2999,7 +3023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4732,24 +4756,24 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>47</v>
+        <v>16.323193</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>143.68</v>
+        <v>49.9</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
@@ -4760,24 +4784,24 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>61.14</v>
+        <v>143.68</v>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
@@ -4788,7 +4812,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -4798,14 +4822,14 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
@@ -4821,19 +4845,19 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D66" s="16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -4844,17 +4868,17 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D67" s="12" t="n">
@@ -4872,24 +4896,24 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>On-Demand credits 500</t>
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>152.85</v>
+        <v>61.14</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
@@ -4905,19 +4929,19 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro2 monthly</t>
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>155.91</v>
+        <v>152.85</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -4928,24 +4952,24 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>15.29</v>
+        <v>155.91</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -4961,19 +4985,19 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>30.57</v>
+        <v>15.29</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -4984,7 +5008,7 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
@@ -5005,7 +5029,7 @@
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
@@ -5017,19 +5041,19 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>44.33</v>
+        <v>30.57</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -5040,24 +5064,24 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Timeless</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Feb 2026 (₪75.90)</t>
+          <t>Pro monthly (50% off)</t>
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>20.79</v>
+        <v>14.5</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>75.90000000000001</v>
+        <v>44.33</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -5073,19 +5097,19 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Business Plus – Feb 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>10</v>
+        <v>20.79</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>30.57</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -5096,24 +5120,24 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>40.11</v>
+        <v>10</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>122.62</v>
+        <v>30.57</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -5124,24 +5148,24 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Pro – Mar 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>13.67</v>
+        <v>40.11</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>49.9</v>
+        <v>122.62</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -5162,11 +5186,11 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Pro – Mar 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.323193</v>
+        <v>13.67</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5180,24 +5204,24 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>51</v>
+        <v>16.323193</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>155.91</v>
+        <v>49.9</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -5208,24 +5232,24 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>61.14</v>
+        <v>155.91</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -5236,17 +5260,17 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D81" s="12" t="n">
@@ -5264,24 +5288,24 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>30.57</v>
+        <v>61.14</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -5297,19 +5321,19 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>33.63</v>
+        <v>30.57</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5320,24 +5344,24 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>27.51</v>
+        <v>33.63</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5348,24 +5372,24 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>15.29</v>
+        <v>27.51</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5376,24 +5400,24 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -5404,17 +5428,17 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
@@ -5425,7 +5449,7 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מרץ 2026</t>
         </is>
       </c>
     </row>
@@ -5442,14 +5466,14 @@
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5465,19 +5489,19 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>20.79</v>
+        <v>5</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>15.29</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5493,19 +5517,19 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>51</v>
+        <v>20.79</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>155.91</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5516,24 +5540,24 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>55.03</v>
+        <v>155.91</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5544,24 +5568,24 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.25</v>
+        <v>18</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>6.88</v>
+        <v>55.03</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5572,24 +5596,24 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>61.14</v>
+        <v>6.88</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -5600,24 +5624,24 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -5628,24 +5652,24 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>61.14</v>
+        <v>49.9</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5656,7 +5680,7 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5677,14 +5701,14 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5705,14 +5729,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5733,14 +5757,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5761,14 +5785,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5789,14 +5813,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5817,14 +5841,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5845,14 +5869,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5873,32 +5897,60 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="18" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B104" s="19" t="n"/>
-      <c r="C104" s="19" t="n"/>
-      <c r="D104" s="20">
-        <f>SUM(D3:D103)</f>
-        <v/>
-      </c>
-      <c r="E104" s="21">
-        <f>SUM(E3:E103)</f>
-        <v/>
-      </c>
-      <c r="F104" s="19" t="n"/>
+      <c r="B105" s="19" t="n"/>
+      <c r="C105" s="19" t="n"/>
+      <c r="D105" s="20">
+        <f>SUM(D3:D104)</f>
+        <v/>
+      </c>
+      <c r="E105" s="21">
+        <f>SUM(E3:E104)</f>
+        <v/>
+      </c>
+      <c r="F105" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A105:C105"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -3023,7 +3023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4476,24 +4476,24 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>61.14</v>
+        <v>49.9</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
@@ -4504,24 +4504,24 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>119.22</v>
+        <v>61.14</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
@@ -4532,24 +4532,24 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Pro 1 monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>76.42</v>
+        <v>119.22</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
@@ -4560,24 +4560,24 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro 1 monthly</t>
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>131.45</v>
+        <v>76.42</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
@@ -4588,24 +4588,24 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>15.29</v>
+        <v>131.45</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
@@ -4621,19 +4621,19 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.5</v>
+        <v>5</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>44.33</v>
+        <v>15.29</v>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
@@ -4644,52 +4644,52 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Timeless</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Upgrade Pro1 -&gt; Pro2 (prorated)</t>
+          <t>Pro monthly (50% off)</t>
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>76.42</v>
+        <v>44.33</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>ינואר 2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Jan 2026 (₪75.90)</t>
+          <t>Upgrade Pro1 -&gt; Pro2 (prorated)</t>
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>20.79</v>
+        <v>25</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>75.90000000000001</v>
+        <v>76.42</v>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
@@ -4700,24 +4700,24 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Business Plus – Jan 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>31.42</v>
+        <v>20.79</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>96.05</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
@@ -4728,24 +4728,24 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Pro – Feb 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>13.67</v>
+        <v>31.42</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>49.9</v>
+        <v>96.05</v>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
@@ -4766,11 +4766,11 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Pro – Feb 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>16.323193</v>
+        <v>13.67</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>49.9</v>
@@ -4784,24 +4784,24 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>47</v>
+        <v>16.323193</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>143.68</v>
+        <v>49.9</v>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
@@ -4812,24 +4812,24 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>61.14</v>
+        <v>143.68</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
@@ -4850,14 +4850,14 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D66" s="16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -4873,19 +4873,19 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
@@ -4896,17 +4896,17 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D68" s="16" t="n">
@@ -4924,24 +4924,24 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>On-Demand credits 500</t>
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>152.85</v>
+        <v>61.14</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -4957,19 +4957,19 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro2 monthly</t>
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>155.91</v>
+        <v>152.85</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -4980,24 +4980,24 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>15.29</v>
+        <v>155.91</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -5013,19 +5013,19 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>30.57</v>
+        <v>15.29</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>פברואר 2026</t>
         </is>
       </c>
     </row>
@@ -5069,19 +5069,19 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>44.33</v>
+        <v>30.57</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -5092,24 +5092,24 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Timeless</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Feb 2026 (₪75.90)</t>
+          <t>Pro monthly (50% off)</t>
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>20.79</v>
+        <v>14.5</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>44.33</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -5125,19 +5125,19 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Business Plus – Feb 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10</v>
+        <v>20.79</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>30.57</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -5148,24 +5148,24 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>40.11</v>
+        <v>10</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>122.62</v>
+        <v>30.57</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -5176,24 +5176,24 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Pro – Mar 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>13.67</v>
+        <v>40.11</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>49.9</v>
+        <v>122.62</v>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -5214,11 +5214,11 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Pro – Mar 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>16.323193</v>
+        <v>13.67</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>49.9</v>
@@ -5232,24 +5232,24 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>51</v>
+        <v>16.323193</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>155.91</v>
+        <v>49.9</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -5260,24 +5260,24 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>61.14</v>
+        <v>155.91</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -5288,17 +5288,17 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D82" s="16" t="n">
@@ -5316,24 +5316,24 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>30.57</v>
+        <v>61.14</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5349,19 +5349,19 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>33.63</v>
+        <v>30.57</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5372,24 +5372,24 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>27.51</v>
+        <v>33.63</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5400,24 +5400,24 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>15.29</v>
+        <v>27.51</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -5428,24 +5428,24 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -5456,17 +5456,17 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מרץ 2026</t>
         </is>
       </c>
     </row>
@@ -5494,14 +5494,14 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5517,19 +5517,19 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>20.79</v>
+        <v>5</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>75.90000000000001</v>
+        <v>15.29</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5545,19 +5545,19 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>51</v>
+        <v>20.79</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>155.91</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5568,24 +5568,24 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>55.03</v>
+        <v>155.91</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5596,24 +5596,24 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>2.25</v>
+        <v>18</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>6.88</v>
+        <v>55.03</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -5624,24 +5624,24 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>61.14</v>
+        <v>6.88</v>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -5652,24 +5652,24 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5680,24 +5680,24 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>61.14</v>
+        <v>49.9</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5729,14 +5729,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5813,14 +5813,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5841,14 +5841,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5869,14 +5869,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5925,32 +5925,60 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="18" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B105" s="19" t="n"/>
-      <c r="C105" s="19" t="n"/>
-      <c r="D105" s="20">
-        <f>SUM(D3:D104)</f>
-        <v/>
-      </c>
-      <c r="E105" s="21">
-        <f>SUM(E3:E104)</f>
-        <v/>
-      </c>
-      <c r="F105" s="19" t="n"/>
+      <c r="B106" s="19" t="n"/>
+      <c r="C106" s="19" t="n"/>
+      <c r="D106" s="20">
+        <f>SUM(D3:D105)</f>
+        <v/>
+      </c>
+      <c r="E106" s="21">
+        <f>SUM(E3:E105)</f>
+        <v/>
+      </c>
+      <c r="F106" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A105:C105"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12206,7 +12234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12435,120 +12463,120 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.14</v>
+        <v>49.9</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>119.22</v>
+        <v>61.14</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Pro 1 monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>76.42</v>
+        <v>119.22</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro 1 monthly</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>131.45</v>
+        <v>76.42</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.29</v>
+        <v>131.45</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -12560,43 +12588,67 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Starter monthly</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
           <t>Timeless</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Pro monthly (50% off)</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D17" s="27" t="n">
         <v>14.5</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E17" s="28" t="n">
         <v>44.33</v>
       </c>
-      <c r="F16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="F17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="20">
-        <f>SUM(D4:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>SUM(E4:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="31" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="20">
+        <f>SUM(D4:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>SUM(E4:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1159,55 +1159,55 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>16.323193</v>
+        <v>47</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>49.9</v>
+        <v>143.68</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>143.68</v>
+        <v>61.14</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -1217,62 +1217,62 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>On-Demand credits 500</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>Pro2 monthly</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.14</v>
+        <v>152.85</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1284,43 +1284,43 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>152.85</v>
+        <v>155.91</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>155.91</v>
+        <v>15.29</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1332,68 +1332,44 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.29</v>
+        <v>30.57</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="F16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="20">
-        <f>SUM(D4:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>SUM(E4:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="31" t="n"/>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="20">
+        <f>SUM(D4:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>SUM(E4:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -2715,7 +2691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4252,24 +4228,24 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>16.323193</v>
+        <v>47</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>49.9</v>
+        <v>143.68</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
@@ -4280,24 +4256,24 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>143.68</v>
+        <v>61.14</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
@@ -4308,7 +4284,7 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
@@ -4318,14 +4294,14 @@
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
@@ -4336,24 +4312,24 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>On-Demand credits 500</t>
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
@@ -4364,24 +4340,24 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>Pro2 monthly</t>
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>61.14</v>
+        <v>152.85</v>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
@@ -4397,19 +4373,19 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>152.85</v>
+        <v>155.91</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
@@ -4420,24 +4396,24 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>155.91</v>
+        <v>15.29</v>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
@@ -4453,19 +4429,19 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>15.29</v>
+        <v>30.57</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
@@ -4476,7 +4452,7 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
@@ -4497,7 +4473,7 @@
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>מרץ 2026</t>
         </is>
       </c>
     </row>
@@ -4509,19 +4485,19 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Timeless</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Pro monthly (50% off)</t>
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>30.57</v>
+        <v>44.33</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
@@ -4532,24 +4508,24 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>Business Plus – Feb 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D66" s="16" t="n">
-        <v>14.5</v>
+        <v>20.79</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>44.33</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -4565,19 +4541,19 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Feb 2026 (₪75.90)</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.79</v>
+        <v>10</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>30.57</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
@@ -4588,24 +4564,24 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>10</v>
+        <v>40.11</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>30.57</v>
+        <v>122.62</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
@@ -4616,24 +4592,24 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro – Mar 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>40.11</v>
+        <v>13.67</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>122.62</v>
+        <v>49.9</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -4654,11 +4630,11 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Pro – Mar 2026 (₪49.90)</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>13.67</v>
+        <v>16.323193</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>49.9</v>
@@ -4672,24 +4648,24 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>16.323193</v>
+        <v>51</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>49.9</v>
+        <v>155.91</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -4700,24 +4676,24 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>155.91</v>
+        <v>61.14</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -4728,7 +4704,7 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -4738,14 +4714,14 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>61.14</v>
+        <v>30.57</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -4761,19 +4737,19 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>30.57</v>
+        <v>33.63</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -4784,24 +4760,24 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>33.63</v>
+        <v>27.51</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -4812,24 +4788,24 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>27.51</v>
+        <v>15.29</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -4840,24 +4816,24 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -4868,17 +4844,17 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D78" s="16" t="n">
@@ -4889,7 +4865,7 @@
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
@@ -4906,14 +4882,14 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -4929,19 +4905,19 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>5</v>
+        <v>20.79</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>15.29</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -4957,19 +4933,19 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>20.79</v>
+        <v>51</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>155.91</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -4980,24 +4956,24 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>155.91</v>
+        <v>55.03</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -5008,24 +4984,24 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>18</v>
+        <v>2.25</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>55.03</v>
+        <v>6.88</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5036,24 +5012,24 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>2.25</v>
+        <v>20</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>6.88</v>
+        <v>61.14</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5064,24 +5040,24 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>61.14</v>
+        <v>49.9</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5090,55 +5066,27 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B86" s="15" t="inlineStr">
-        <is>
-          <t>CapCut</t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="inlineStr">
-        <is>
-          <t>capcut_pro_discount1</t>
-        </is>
-      </c>
-      <c r="D86" s="16" t="n">
-        <v>16.323193</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="F86" s="14" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="18" t="inlineStr">
+      <c r="A86" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B87" s="19" t="n"/>
-      <c r="C87" s="19" t="n"/>
-      <c r="D87" s="20">
-        <f>SUM(D3:D86)</f>
-        <v/>
-      </c>
-      <c r="E87" s="21">
-        <f>SUM(E3:E86)</f>
-        <v/>
-      </c>
-      <c r="F87" s="19" t="n"/>
+      <c r="B86" s="19" t="n"/>
+      <c r="C86" s="19" t="n"/>
+      <c r="D86" s="20">
+        <f>SUM(D3:D85)</f>
+        <v/>
+      </c>
+      <c r="E86" s="21">
+        <f>SUM(E3:E85)</f>
+        <v/>
+      </c>
+      <c r="F86" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A87:C87"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A86:C86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1385,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1590,55 +1590,55 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.323193</v>
+        <v>51</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>49.9</v>
+        <v>155.91</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>155.91</v>
+        <v>61.14</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -1648,14 +1648,14 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.14</v>
+        <v>30.57</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1667,139 +1667,115 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>30.57</v>
+        <v>33.63</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>33.63</v>
+        <v>27.51</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>27.51</v>
+        <v>15.29</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Dzine</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Video Top-Up</t>
-        </is>
-      </c>
-      <c r="D17" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="E17" s="28" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F17" s="29" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="20">
-        <f>SUM(D4:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="21">
-        <f>SUM(E4:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="20">
+        <f>SUM(D4:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>SUM(E4:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -2691,7 +2667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4620,24 +4596,24 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>16.323193</v>
+        <v>51</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>49.9</v>
+        <v>155.91</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -4648,24 +4624,24 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>155.91</v>
+        <v>61.14</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -4676,7 +4652,7 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
@@ -4686,14 +4662,14 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>61.14</v>
+        <v>30.57</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -4709,19 +4685,19 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>30.57</v>
+        <v>33.63</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -4732,24 +4708,24 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>33.63</v>
+        <v>27.51</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -4760,24 +4736,24 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>27.51</v>
+        <v>15.29</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -4788,24 +4764,24 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>15.29</v>
+        <v>61.14</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -4816,17 +4792,17 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D77" s="12" t="n">
@@ -4837,7 +4813,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
@@ -4854,14 +4830,14 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>61.14</v>
+        <v>15.29</v>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -4877,19 +4853,19 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>5</v>
+        <v>20.79</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>15.29</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -4905,19 +4881,19 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.79</v>
+        <v>51</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>75.90000000000001</v>
+        <v>155.91</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -4928,24 +4904,24 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>155.91</v>
+        <v>55.03</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -4956,24 +4932,24 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>18</v>
+        <v>2.25</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>55.03</v>
+        <v>6.88</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -4984,24 +4960,24 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>2.25</v>
+        <v>20</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>6.88</v>
+        <v>61.14</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5012,24 +4988,24 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>61.14</v>
+        <v>49.9</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5038,55 +5014,27 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>CapCut</t>
-        </is>
-      </c>
-      <c r="C85" s="11" t="inlineStr">
-        <is>
-          <t>capcut_pro_discount1</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="n">
-        <v>16.323193</v>
-      </c>
-      <c r="E85" s="13" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>אפריל 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="18" t="inlineStr">
+      <c r="A85" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B86" s="19" t="n"/>
-      <c r="C86" s="19" t="n"/>
-      <c r="D86" s="20">
-        <f>SUM(D3:D85)</f>
-        <v/>
-      </c>
-      <c r="E86" s="21">
-        <f>SUM(E3:E85)</f>
-        <v/>
-      </c>
-      <c r="F86" s="19" t="n"/>
+      <c r="B85" s="19" t="n"/>
+      <c r="C85" s="19" t="n"/>
+      <c r="D85" s="20">
+        <f>SUM(D3:D84)</f>
+        <v/>
+      </c>
+      <c r="E85" s="21">
+        <f>SUM(E3:E84)</f>
+        <v/>
+      </c>
+      <c r="F85" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A85:C85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>51</v>
+        <v>54.409552</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>155.91</v>
+        <v>166.33</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -2146,107 +2146,83 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>51</v>
+        <v>40.11</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>155.91</v>
+        <v>122.62</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>40.11</v>
+        <v>16.323193</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>122.62</v>
+        <v>49.9</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F15" s="29" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="20">
-        <f>SUM(D4:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>SUM(E4:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="31" t="n"/>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="20">
+        <f>SUM(D4:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>SUM(E4:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -3095,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5654,10 +5630,10 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>51</v>
+        <v>54.409552</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>155.91</v>
+        <v>166.33</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5766,10 +5742,10 @@
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>51</v>
+        <v>40.11</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>155.91</v>
+        <v>122.62</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5780,24 +5756,24 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>40.11</v>
+        <v>16.323193</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>122.62</v>
+        <v>49.9</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5808,24 +5784,24 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5836,7 +5812,7 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5857,14 +5833,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5885,14 +5861,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5913,14 +5889,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5941,14 +5917,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5969,14 +5945,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5997,14 +5973,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6025,14 +6001,14 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>נובמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6053,60 +6029,32 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C107" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E107" s="13" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="18" t="inlineStr">
+      <c r="A107" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B108" s="19" t="n"/>
-      <c r="C108" s="19" t="n"/>
-      <c r="D108" s="20">
-        <f>SUM(D3:D107)</f>
-        <v/>
-      </c>
-      <c r="E108" s="21">
-        <f>SUM(E3:E107)</f>
-        <v/>
-      </c>
-      <c r="F108" s="19" t="n"/>
+      <c r="B107" s="19" t="n"/>
+      <c r="C107" s="19" t="n"/>
+      <c r="D107" s="20">
+        <f>SUM(D3:D106)</f>
+        <v/>
+      </c>
+      <c r="E107" s="21">
+        <f>SUM(E3:E106)</f>
+        <v/>
+      </c>
+      <c r="F107" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A107:C107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2132,96 +2132,72 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.11</v>
+        <v>16.323193</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>122.62</v>
+        <v>49.9</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F14" s="24" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="31" t="n"/>
-      <c r="D15" s="20">
-        <f>SUM(D4:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="21">
-        <f>SUM(E4:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="31" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="20">
+        <f>SUM(D4:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>SUM(E4:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3071,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5728,24 +5704,24 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>40.11</v>
+        <v>16.323193</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>122.62</v>
+        <v>49.9</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5756,24 +5732,24 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5784,7 +5760,7 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5805,14 +5781,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5833,14 +5809,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5861,14 +5837,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5889,14 +5865,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5917,14 +5893,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5945,14 +5921,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5973,14 +5949,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>נובמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6001,60 +5977,32 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="14" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="B106" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C106" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D106" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F106" s="14" t="inlineStr">
-        <is>
-          <t>דצמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="18" t="inlineStr">
+      <c r="A106" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B107" s="19" t="n"/>
-      <c r="C107" s="19" t="n"/>
-      <c r="D107" s="20">
-        <f>SUM(D3:D106)</f>
-        <v/>
-      </c>
-      <c r="E107" s="21">
-        <f>SUM(E3:E106)</f>
-        <v/>
-      </c>
-      <c r="F107" s="19" t="n"/>
+      <c r="B106" s="19" t="n"/>
+      <c r="C106" s="19" t="n"/>
+      <c r="D106" s="20">
+        <f>SUM(D3:D105)</f>
+        <v/>
+      </c>
+      <c r="E106" s="21">
+        <f>SUM(E3:E105)</f>
+        <v/>
+      </c>
+      <c r="F106" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A107:C107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -993,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25</v>
+        <v>25.371279</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>76.42</v>
+        <v>77.56</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>20.79</v>
+        <v>24.828263</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1102,103 +1102,103 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace (₪75.9)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>24.828263</v>
+        <v>31.851488</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>75.90000000000001</v>
+        <v>97.37</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro – Feb 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>31.42</v>
+        <v>16.323193</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>96.05</v>
+        <v>49.9</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Pro – Feb 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>13.67</v>
+        <v>47.307818</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>49.9</v>
+        <v>144.62</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>47</v>
+        <v>20.193</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>143.68</v>
+        <v>61.73</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -1208,14 +1208,14 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20</v>
+        <v>5.050703</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>61.14</v>
+        <v>15.44</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -1227,67 +1227,67 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>15.29</v>
+        <v>61.77</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>On-Demand credits 500</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20</v>
+        <v>20.464508</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.14</v>
+        <v>62.56</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>Pro2 monthly</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>20</v>
+        <v>50.690219</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>61.14</v>
+        <v>154.96</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1299,43 +1299,43 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>50</v>
+        <v>51.704285</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>152.85</v>
+        <v>158.06</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>51</v>
+        <v>5.129212</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>155.91</v>
+        <v>15.68</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1347,67 +1347,43 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>5</v>
+        <v>10.255152</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>15.29</v>
+        <v>31.35</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
-        </is>
-      </c>
-      <c r="D17" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="28" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="F17" s="29" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="20">
-        <f>SUM(D4:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="21">
-        <f>SUM(E4:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="20">
+        <f>SUM(D4:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>SUM(E4:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -1523,10 +1499,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10</v>
+        <v>10.232254</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>30.57</v>
+        <v>31.28</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1547,10 +1523,10 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.5</v>
+        <v>14.838077</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>44.33</v>
+        <v>45.36</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -1571,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.79</v>
+        <v>24.828263</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1595,10 +1571,10 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10</v>
+        <v>10.206084</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>30.57</v>
+        <v>31.2</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -1619,10 +1595,10 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>40.11</v>
+        <v>40.376186</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>122.62</v>
+        <v>123.43</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -1643,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>13.67</v>
+        <v>16.323193</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1667,10 +1643,10 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>51</v>
+        <v>52.230945</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>155.91</v>
+        <v>159.67</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -1691,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20</v>
+        <v>20.565914</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.14</v>
+        <v>62.87</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -1718,7 +1694,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>61.14</v>
+        <v>62.87</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -1739,10 +1715,10 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10</v>
+        <v>10.176644</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>30.57</v>
+        <v>31.11</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1763,10 +1739,10 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11</v>
+        <v>11.193981</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>33.63</v>
+        <v>34.22</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -1790,7 +1766,7 @@
         <v>9</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>27.51</v>
+        <v>28.06</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -1811,10 +1787,10 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5</v>
+        <v>5.109585</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>15.29</v>
+        <v>15.62</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
@@ -1838,7 +1814,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>61.14</v>
+        <v>62.37</v>
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
@@ -1879,7 +1855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1954,10 +1930,10 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20</v>
+        <v>20.565914</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>62.87</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1978,10 +1954,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5</v>
+        <v>5.142296</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>15.29</v>
+        <v>15.72</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -2002,7 +1978,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>20.79</v>
+        <v>24.828263</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>75.90000000000001</v>
@@ -2017,187 +1993,163 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace (₪75.9)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>24.828263</v>
+        <v>54.409552</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>75.90000000000001</v>
+        <v>166.33</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>54.409552</v>
+        <v>18</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>166.33</v>
+        <v>56.49</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>18</v>
+        <v>2.306183</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>55.03</v>
+        <v>7.05</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>2.25</v>
+        <v>20.55283</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>6.88</v>
+        <v>62.83</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>20</v>
+        <v>16.323193</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.14</v>
+        <v>49.9</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F13" s="29" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="20">
-        <f>SUM(D4:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="21">
-        <f>SUM(E4:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="31" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="20">
+        <f>SUM(D4:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>SUM(E4:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3047,7 +2999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3114,10 +3066,10 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1</v>
+        <v>1.092574</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>3.06</v>
+        <v>3.34</v>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
@@ -3142,10 +3094,10 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>72</v>
+        <v>78.86162899999999</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>220.1</v>
+        <v>241.08</v>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
@@ -3170,10 +3122,10 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>10.59</v>
+        <v>11.462218</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>32.37</v>
+        <v>35.04</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -3198,10 +3150,10 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>20</v>
+        <v>21.687929</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>61.14</v>
+        <v>66.3</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
@@ -3229,7 +3181,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>61.14</v>
+        <v>67.31</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -3254,10 +3206,10 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>13.5</v>
+        <v>14.828263</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>41.27</v>
+        <v>45.33</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
@@ -3282,10 +3234,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>113.14</v>
+        <v>124.586196</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>345.87</v>
+        <v>380.86</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -3310,10 +3262,10 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>10</v>
+        <v>11.010795</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>30.57</v>
+        <v>33.66</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
@@ -3338,7 +3290,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>15.6</v>
+        <v>18.622833</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3366,10 +3318,10 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>15</v>
+        <v>16.745175</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>45.85</v>
+        <v>51.19</v>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
@@ -3394,10 +3346,10 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>12</v>
+        <v>13.385672</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>36.68</v>
+        <v>40.92</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -3422,10 +3374,10 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.9</v>
+        <v>1.007524</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
@@ -3450,10 +3402,10 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>19</v>
+        <v>21.341184</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>58.08</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -3478,10 +3430,10 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>10.59</v>
+        <v>11.894014</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>32.37</v>
+        <v>36.36</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
@@ -3506,10 +3458,10 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>20</v>
+        <v>22.384691</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>61.14</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -3537,7 +3489,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>61.14</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
@@ -3562,10 +3514,10 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5</v>
+        <v>5.466143</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>15.29</v>
+        <v>16.71</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -3590,10 +3542,10 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>11.25</v>
+        <v>12.29964</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>34.39</v>
+        <v>37.6</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
@@ -3618,7 +3570,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>15.6</v>
+        <v>18.622833</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3646,10 +3598,10 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>2.79</v>
+        <v>3.055283</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>8.529999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
@@ -3674,10 +3626,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>10.59</v>
+        <v>11.583252</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>32.37</v>
+        <v>35.41</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -3705,7 +3657,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>61.14</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -3730,10 +3682,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>20</v>
+        <v>21.871115</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>61.14</v>
+        <v>66.86</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -3758,10 +3710,10 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5</v>
+        <v>5.40072</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>15.29</v>
+        <v>16.51</v>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
@@ -3786,7 +3738,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>15.6</v>
+        <v>18.622833</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3817,7 +3769,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>61.14</v>
+        <v>65.72</v>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
@@ -3842,10 +3794,10 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>20</v>
+        <v>21.52437</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>61.14</v>
+        <v>65.8</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -3870,10 +3822,10 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5</v>
+        <v>5.322211</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>15.29</v>
+        <v>16.27</v>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
@@ -3898,10 +3850,10 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>12</v>
+        <v>12.79686</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>36.68</v>
+        <v>39.12</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -3926,10 +3878,10 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>11.8</v>
+        <v>12.463199</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>36.07</v>
+        <v>38.1</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -3954,10 +3906,10 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>15</v>
+        <v>15.8456</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>45.85</v>
+        <v>48.44</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -3982,10 +3934,10 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10</v>
+        <v>10.451423</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>30.57</v>
+        <v>31.95</v>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
@@ -4013,7 +3965,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>61.14</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -4038,10 +3990,10 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>20</v>
+        <v>21.432777</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>61.14</v>
+        <v>65.52</v>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
@@ -4066,10 +4018,10 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5</v>
+        <v>5.335296</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>15.29</v>
+        <v>16.31</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -4094,7 +4046,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>20.79</v>
+        <v>24.828263</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4122,10 +4074,10 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>15</v>
+        <v>15.95682</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>45.85</v>
+        <v>48.78</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -4150,10 +4102,10 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>9.720000000000001</v>
+        <v>10.340203</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>29.71</v>
+        <v>31.61</v>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
@@ -4178,10 +4130,10 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>30</v>
+        <v>31.71737</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>91.70999999999999</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -4206,10 +4158,10 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>33</v>
+        <v>34.684331</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>100.88</v>
+        <v>106.03</v>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
@@ -4237,7 +4189,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>61.14</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -4262,10 +4214,10 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>36</v>
+        <v>37.556428</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>110.05</v>
+        <v>114.81</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
@@ -4290,10 +4242,10 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5</v>
+        <v>5.210991</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>15.29</v>
+        <v>15.93</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -4318,7 +4270,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>20.79</v>
+        <v>24.828263</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4346,10 +4298,10 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>139.92</v>
+        <v>145.806346</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>427.74</v>
+        <v>445.73</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -4374,10 +4326,10 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15</v>
+        <v>15.629702</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>45.85</v>
+        <v>47.78</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
@@ -4402,10 +4354,10 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>19.43</v>
+        <v>20.24861</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>59.4</v>
+        <v>61.9</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
@@ -4430,10 +4382,10 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>20</v>
+        <v>20.77527</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>61.14</v>
+        <v>63.51</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
@@ -4458,10 +4410,10 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>20</v>
+        <v>20.716389</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>61.14</v>
+        <v>63.33</v>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
@@ -4486,7 +4438,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>13.67</v>
+        <v>16.323193</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4517,7 +4469,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>61.14</v>
+        <v>62.81</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
@@ -4542,10 +4494,10 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>39</v>
+        <v>40.170101</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>119.22</v>
+        <v>122.8</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
@@ -4570,10 +4522,10 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>25</v>
+        <v>25.583906</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>76.42</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
@@ -4598,10 +4550,10 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>43</v>
+        <v>43.833824</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>131.45</v>
+        <v>134</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
@@ -4626,10 +4578,10 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5</v>
+        <v>5.047432</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>15.29</v>
+        <v>15.43</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
@@ -4654,10 +4606,10 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.5</v>
+        <v>14.635263</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>44.33</v>
+        <v>44.74</v>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
@@ -4682,10 +4634,10 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25</v>
+        <v>25.371279</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>76.42</v>
+        <v>77.56</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
@@ -4710,7 +4662,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>20.79</v>
+        <v>24.828263</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4724,24 +4676,24 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace (₪75.9)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>24.828263</v>
+        <v>31.851488</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>97.37</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
@@ -4752,24 +4704,24 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro – Feb 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>31.42</v>
+        <v>16.323193</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>96.05</v>
+        <v>49.9</v>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
@@ -4780,24 +4732,24 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Pro – Feb 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>13.67</v>
+        <v>47.307818</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>49.9</v>
+        <v>144.62</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
@@ -4808,24 +4760,24 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>47</v>
+        <v>20.193</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>143.68</v>
+        <v>61.73</v>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
@@ -4836,7 +4788,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -4846,14 +4798,14 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>20</v>
+        <v>5.050703</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>61.14</v>
+        <v>15.44</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
@@ -4869,19 +4821,19 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D66" s="16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>15.29</v>
+        <v>61.77</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -4892,24 +4844,24 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>On-Demand credits 500</t>
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20</v>
+        <v>20.464508</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>61.14</v>
+        <v>62.56</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
@@ -4920,24 +4872,24 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>On-Demand credits 500</t>
+          <t>Pro2 monthly</t>
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>20</v>
+        <v>50.690219</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>61.14</v>
+        <v>154.96</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
@@ -4953,19 +4905,19 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Pro2 monthly</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>50</v>
+        <v>51.704285</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>152.85</v>
+        <v>158.06</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -4976,24 +4928,24 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Starter monthly</t>
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>51</v>
+        <v>5.129212</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>155.91</v>
+        <v>15.68</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -5009,19 +4961,19 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Starter monthly</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>5</v>
+        <v>10.255152</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>15.29</v>
+        <v>31.35</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -5032,28 +4984,28 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Google Workspace (₪75.9)</t>
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>10</v>
+        <v>24.828263</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>30.57</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>פברואר 2026</t>
+          <t>מרץ 2026</t>
         </is>
       </c>
     </row>
@@ -5065,19 +5017,19 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace (₪75.9)</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>24.828263</v>
+        <v>10.232254</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>31.28</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -5093,19 +5045,19 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Timeless</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Pro monthly (50% off)</t>
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>10</v>
+        <v>14.838077</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>30.57</v>
+        <v>45.36</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -5116,24 +5068,24 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Pro monthly (50% off)</t>
+          <t>Business Plus – Feb 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>14.5</v>
+        <v>24.828263</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>44.33</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -5149,19 +5101,19 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Feb 2026 (₪75.90)</t>
+          <t>Cloud &amp; AI Balance Top-up</t>
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>20.79</v>
+        <v>10.206084</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>75.90000000000001</v>
+        <v>31.2</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -5172,24 +5124,24 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Balance Top-up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>10</v>
+        <v>40.376186</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>30.57</v>
+        <v>123.43</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -5200,24 +5152,24 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Pro – Mar 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>40.11</v>
+        <v>16.323193</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>122.62</v>
+        <v>49.9</v>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -5228,24 +5180,24 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Pro – Mar 2026 (₪49.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>13.67</v>
+        <v>52.230945</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>49.9</v>
+        <v>159.67</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -5256,24 +5208,24 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>51</v>
+        <v>20.565914</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>155.91</v>
+        <v>62.87</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -5284,24 +5236,24 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D81" s="12" t="n">
         <v>20</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>61.14</v>
+        <v>62.87</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -5312,24 +5264,24 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>20</v>
+        <v>10.176644</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>61.14</v>
+        <v>31.11</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -5345,19 +5297,19 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>10</v>
+        <v>11.193981</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>30.57</v>
+        <v>34.22</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5368,24 +5320,24 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>33.63</v>
+        <v>28.06</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5396,24 +5348,24 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>9</v>
+        <v>5.109585</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>27.51</v>
+        <v>15.62</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5424,24 +5376,24 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>15.29</v>
+        <v>62.37</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -5452,28 +5404,28 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20</v>
+        <v>20.565914</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>61.14</v>
+        <v>62.87</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>מרץ 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
@@ -5490,14 +5442,14 @@
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>20</v>
+        <v>5.142296</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>61.14</v>
+        <v>15.72</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5513,19 +5465,19 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>5</v>
+        <v>24.828263</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>15.29</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5541,19 +5493,19 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>20.79</v>
+        <v>54.409552</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>75.90000000000001</v>
+        <v>166.33</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5564,24 +5516,24 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace (₪75.9)</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>24.828263</v>
+        <v>18</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>56.49</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5592,7 +5544,7 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
@@ -5606,10 +5558,10 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>54.409552</v>
+        <v>2.306183</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>166.33</v>
+        <v>7.05</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5620,24 +5572,24 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>18</v>
+        <v>20.55283</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>55.03</v>
+        <v>62.83</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -5648,24 +5600,24 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>2.25</v>
+        <v>16.323193</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>6.88</v>
+        <v>49.9</v>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -5676,17 +5628,17 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
@@ -5704,35 +5656,35 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>16.323193</v>
+        <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>49.9</v>
+        <v>61.14</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5753,14 +5705,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5781,14 +5733,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5809,14 +5761,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5837,14 +5789,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5865,14 +5817,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5893,14 +5845,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>נובמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5921,88 +5873,32 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="14" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="B104" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C104" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D104" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F104" s="14" t="inlineStr">
-        <is>
-          <t>נובמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D105" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E105" s="13" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="18" t="inlineStr">
+      <c r="A104" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B106" s="19" t="n"/>
-      <c r="C106" s="19" t="n"/>
-      <c r="D106" s="20">
-        <f>SUM(D3:D105)</f>
-        <v/>
-      </c>
-      <c r="E106" s="21">
-        <f>SUM(E3:E105)</f>
-        <v/>
-      </c>
-      <c r="F106" s="19" t="n"/>
+      <c r="B104" s="19" t="n"/>
+      <c r="C104" s="19" t="n"/>
+      <c r="D104" s="20">
+        <f>SUM(D3:D103)</f>
+        <v/>
+      </c>
+      <c r="E104" s="21">
+        <f>SUM(E3:E103)</f>
+        <v/>
+      </c>
+      <c r="F104" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A104:C104"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10731,10 +10627,10 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1</v>
+        <v>1.092574</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>3.06</v>
+        <v>3.34</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10755,10 +10651,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>72</v>
+        <v>78.86162899999999</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>220.1</v>
+        <v>241.08</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -10779,10 +10675,10 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.59</v>
+        <v>11.462218</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>32.37</v>
+        <v>35.04</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -10803,10 +10699,10 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20</v>
+        <v>21.687929</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>61.14</v>
+        <v>66.3</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -10830,7 +10726,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>61.14</v>
+        <v>67.31</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -10851,10 +10747,10 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>13.5</v>
+        <v>14.828263</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>41.27</v>
+        <v>45.33</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -10875,10 +10771,10 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>113.14</v>
+        <v>124.586196</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>345.87</v>
+        <v>380.86</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -10899,10 +10795,10 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>10</v>
+        <v>11.010795</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>30.57</v>
+        <v>33.66</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -11018,7 +10914,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>15.6</v>
+        <v>18.622833</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11042,10 +10938,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>15</v>
+        <v>16.745175</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>45.85</v>
+        <v>51.19</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11066,10 +10962,10 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>12</v>
+        <v>13.385672</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>36.68</v>
+        <v>40.92</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11090,10 +10986,10 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>0.9</v>
+        <v>1.007524</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11114,10 +11010,10 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>19</v>
+        <v>21.341184</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>58.08</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11138,10 +11034,10 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>10.59</v>
+        <v>11.894014</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>32.37</v>
+        <v>36.36</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11162,10 +11058,10 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20</v>
+        <v>22.384691</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>61.14</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -11189,7 +11085,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.14</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -11210,10 +11106,10 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5</v>
+        <v>5.466143</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>15.29</v>
+        <v>16.71</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -11234,10 +11130,10 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>11.25</v>
+        <v>12.29964</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>34.39</v>
+        <v>37.6</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -11353,7 +11249,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>15.6</v>
+        <v>18.622833</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11377,10 +11273,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>2.79</v>
+        <v>3.055283</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>8.529999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11401,10 +11297,10 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.59</v>
+        <v>11.583252</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>32.37</v>
+        <v>35.41</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11428,7 +11324,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>61.14</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11449,10 +11345,10 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>20</v>
+        <v>21.871115</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>61.14</v>
+        <v>66.86</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11473,10 +11369,10 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5</v>
+        <v>5.40072</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>15.29</v>
+        <v>16.51</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11592,7 +11488,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>15.6</v>
+        <v>18.622833</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11619,7 +11515,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>61.14</v>
+        <v>65.72</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11640,10 +11536,10 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>20</v>
+        <v>21.52437</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>61.14</v>
+        <v>65.8</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11664,10 +11560,10 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5</v>
+        <v>5.322211</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>15.29</v>
+        <v>16.27</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11783,10 +11679,10 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>12</v>
+        <v>12.79686</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>36.68</v>
+        <v>39.12</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11807,10 +11703,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>11.8</v>
+        <v>12.463199</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>36.07</v>
+        <v>38.1</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -11831,10 +11727,10 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15</v>
+        <v>15.8456</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>45.85</v>
+        <v>48.44</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -11855,10 +11751,10 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10</v>
+        <v>10.451423</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>30.57</v>
+        <v>31.95</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -11882,7 +11778,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>61.14</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -11903,10 +11799,10 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20</v>
+        <v>21.432777</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.14</v>
+        <v>65.52</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -11927,10 +11823,10 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5</v>
+        <v>5.335296</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>15.29</v>
+        <v>16.31</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -12046,7 +11942,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.79</v>
+        <v>24.828263</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12070,10 +11966,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>15</v>
+        <v>15.95682</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>45.85</v>
+        <v>48.78</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -12094,10 +11990,10 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>9.720000000000001</v>
+        <v>10.340203</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>29.71</v>
+        <v>31.61</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -12118,10 +12014,10 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>30</v>
+        <v>31.71737</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>91.70999999999999</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -12142,10 +12038,10 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>33</v>
+        <v>34.684331</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>100.88</v>
+        <v>106.03</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -12169,7 +12065,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.14</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -12190,10 +12086,10 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>36</v>
+        <v>37.556428</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>110.05</v>
+        <v>114.81</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
@@ -12214,10 +12110,10 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5</v>
+        <v>5.210991</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>15.29</v>
+        <v>15.93</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -12333,7 +12229,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.79</v>
+        <v>24.828263</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12357,10 +12253,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>139.92</v>
+        <v>145.806346</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>427.74</v>
+        <v>445.73</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -12381,10 +12277,10 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15</v>
+        <v>15.629702</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>45.85</v>
+        <v>47.78</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
@@ -12405,10 +12301,10 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>19.43</v>
+        <v>20.24861</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>59.4</v>
+        <v>61.9</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
@@ -12429,10 +12325,10 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>20</v>
+        <v>20.77527</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>61.14</v>
+        <v>63.51</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
@@ -12453,10 +12349,10 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20</v>
+        <v>20.716389</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>61.14</v>
+        <v>63.33</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
@@ -12477,7 +12373,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>13.67</v>
+        <v>16.323193</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12504,7 +12400,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>61.14</v>
+        <v>62.81</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -12525,10 +12421,10 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>39</v>
+        <v>40.170101</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>119.22</v>
+        <v>122.8</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -12549,10 +12445,10 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>25</v>
+        <v>25.583906</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>76.42</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -12573,10 +12469,10 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43</v>
+        <v>43.833824</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>131.45</v>
+        <v>134</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -12597,10 +12493,10 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5</v>
+        <v>5.047432</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.29</v>
+        <v>15.43</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -12621,10 +12517,10 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.5</v>
+        <v>14.635263</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>44.33</v>
+        <v>44.74</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.057</v>
+        <v>3.058</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-10</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.371279</v>
+        <v>25.362982</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>31.851488</v>
+        <v>31.841073</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.323193</v>
+        <v>16.317855</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>47.307818</v>
+        <v>47.292348</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.193</v>
+        <v>20.186396</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.050703</v>
+        <v>5.049052</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.464508</v>
+        <v>20.457816</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>50.690219</v>
+        <v>50.673643</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>51.704285</v>
+        <v>51.687377</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.129212</v>
+        <v>5.127534</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.255152</v>
+        <v>10.251799</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.232254</v>
+        <v>10.228908</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.838077</v>
+        <v>14.833224</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.206084</v>
+        <v>10.202747</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>40.376186</v>
+        <v>40.362982</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.323193</v>
+        <v>16.317855</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>52.230945</v>
+        <v>52.213865</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.565914</v>
+        <v>20.559189</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10.176644</v>
+        <v>10.173316</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>31.11</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11.193981</v>
+        <v>11.19032</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>34.22</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5.109585</v>
+        <v>5.107914</v>
       </c>
       <c r="E17" s="28" t="n">
         <v>15.62</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.565914</v>
+        <v>20.559189</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>62.87</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5.142296</v>
+        <v>5.140615</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>15.72</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>54.409552</v>
+        <v>54.391759</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2.306183</v>
+        <v>2.305428</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20.55283</v>
+        <v>20.546109</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.323193</v>
+        <v>16.317855</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2363,7 +2363,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2482,7 +2482,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2720,7 +2720,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2839,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2958,7 +2958,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.092574</v>
+        <v>1.092217</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>78.86162899999999</v>
+        <v>78.83584</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.462218</v>
+        <v>11.45847</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>21.687929</v>
+        <v>21.680837</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>14.828263</v>
+        <v>14.823414</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>124.586196</v>
+        <v>124.545455</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.010795</v>
+        <v>11.007194</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.622833</v>
+        <v>18.616743</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>16.745175</v>
+        <v>16.739699</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.385672</v>
+        <v>13.381295</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.007524</v>
+        <v>1.007194</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.341184</v>
+        <v>21.334205</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>11.894014</v>
+        <v>11.890124</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.384691</v>
+        <v>22.377371</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.466143</v>
+        <v>5.464356</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.29964</v>
+        <v>12.295618</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.622833</v>
+        <v>18.616743</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.055283</v>
+        <v>3.054284</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.583252</v>
+        <v>11.579464</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>21.871115</v>
+        <v>21.863963</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.40072</v>
+        <v>5.398954</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.622833</v>
+        <v>18.616743</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.52437</v>
+        <v>21.517332</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.322211</v>
+        <v>5.320471</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>12.79686</v>
+        <v>12.792675</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.463199</v>
+        <v>12.459124</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>15.8456</v>
+        <v>15.840419</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.451423</v>
+        <v>10.448005</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.432777</v>
+        <v>21.425768</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.335296</v>
+        <v>5.333551</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>15.95682</v>
+        <v>15.951602</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.340203</v>
+        <v>10.336821</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>31.71737</v>
+        <v>31.706998</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>34.684331</v>
+        <v>34.672989</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>37.556428</v>
+        <v>37.544147</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.210991</v>
+        <v>5.209287</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>145.806346</v>
+        <v>145.758666</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.629702</v>
+        <v>15.624591</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.24861</v>
+        <v>20.241988</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>20.77527</v>
+        <v>20.768476</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>20.716389</v>
+        <v>20.709614</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.323193</v>
+        <v>16.317855</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.170101</v>
+        <v>40.156965</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>25.583906</v>
+        <v>25.57554</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>43.833824</v>
+        <v>43.81949</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.047432</v>
+        <v>5.045782</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.635263</v>
+        <v>14.630477</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.371279</v>
+        <v>25.362982</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>31.851488</v>
+        <v>31.841073</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.323193</v>
+        <v>16.317855</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>47.307818</v>
+        <v>47.292348</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.193</v>
+        <v>20.186396</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.050703</v>
+        <v>5.049052</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.464508</v>
+        <v>20.457816</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>50.690219</v>
+        <v>50.673643</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>51.704285</v>
+        <v>51.687377</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.129212</v>
+        <v>5.127534</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.255152</v>
+        <v>10.251799</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.232254</v>
+        <v>10.228908</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>14.838077</v>
+        <v>14.833224</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.206084</v>
+        <v>10.202747</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>40.376186</v>
+        <v>40.362982</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.323193</v>
+        <v>16.317855</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>52.230945</v>
+        <v>52.213865</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.565914</v>
+        <v>20.559189</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.176644</v>
+        <v>10.173316</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>31.11</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11.193981</v>
+        <v>11.19032</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>34.22</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5.109585</v>
+        <v>5.107914</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>15.62</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.565914</v>
+        <v>20.559189</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>62.87</v>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5.142296</v>
+        <v>5.140615</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>15.72</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>54.409552</v>
+        <v>54.391759</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.306183</v>
+        <v>2.305428</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.55283</v>
+        <v>20.546109</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.323193</v>
+        <v>16.317855</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5645,7 +5645,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.14</v>
+        <v>61.16</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.092574</v>
+        <v>1.092217</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>78.86162899999999</v>
+        <v>78.83584</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.462218</v>
+        <v>11.45847</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>21.687929</v>
+        <v>21.680837</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>14.828263</v>
+        <v>14.823414</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>124.586196</v>
+        <v>124.545455</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.010795</v>
+        <v>11.007194</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -10914,7 +10914,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.622833</v>
+        <v>18.616743</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -10938,7 +10938,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.745175</v>
+        <v>16.739699</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.385672</v>
+        <v>13.381295</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -10986,7 +10986,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.007524</v>
+        <v>1.007194</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.341184</v>
+        <v>21.334205</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11034,7 +11034,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>11.894014</v>
+        <v>11.890124</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.384691</v>
+        <v>22.377371</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.466143</v>
+        <v>5.464356</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.29964</v>
+        <v>12.295618</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.622833</v>
+        <v>18.616743</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.055283</v>
+        <v>3.054284</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.583252</v>
+        <v>11.579464</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.871115</v>
+        <v>21.863963</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.40072</v>
+        <v>5.398954</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.622833</v>
+        <v>18.616743</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11536,7 +11536,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.52437</v>
+        <v>21.517332</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.322211</v>
+        <v>5.320471</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>12.79686</v>
+        <v>12.792675</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.463199</v>
+        <v>12.459124</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -11727,7 +11727,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.8456</v>
+        <v>15.840419</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.451423</v>
+        <v>10.448005</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.432777</v>
+        <v>21.425768</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -11823,7 +11823,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.335296</v>
+        <v>5.333551</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -11942,7 +11942,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>15.95682</v>
+        <v>15.951602</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.340203</v>
+        <v>10.336821</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>31.71737</v>
+        <v>31.706998</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>34.684331</v>
+        <v>34.672989</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>37.556428</v>
+        <v>37.544147</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.210991</v>
+        <v>5.209287</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12229,7 +12229,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.828263</v>
+        <v>24.820144</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>145.806346</v>
+        <v>145.758666</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.629702</v>
+        <v>15.624591</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.24861</v>
+        <v>20.241988</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12325,7 +12325,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>20.77527</v>
+        <v>20.768476</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12349,7 +12349,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.716389</v>
+        <v>20.709614</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.323193</v>
+        <v>16.317855</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.170101</v>
+        <v>40.156965</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>25.583906</v>
+        <v>25.57554</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43.833824</v>
+        <v>43.81949</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.047432</v>
+        <v>5.045782</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.635263</v>
+        <v>14.630477</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.058</v>
+        <v>3.057</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-13</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-10</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.362982</v>
+        <v>25.371279</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>31.841073</v>
+        <v>31.851488</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.317855</v>
+        <v>16.323193</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>47.292348</v>
+        <v>47.307818</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.186396</v>
+        <v>20.193</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.049052</v>
+        <v>5.050703</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.457816</v>
+        <v>20.464508</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>50.673643</v>
+        <v>50.690219</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>51.687377</v>
+        <v>51.704285</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.127534</v>
+        <v>5.129212</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.251799</v>
+        <v>10.255152</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.228908</v>
+        <v>10.232254</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.833224</v>
+        <v>14.838077</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.202747</v>
+        <v>10.206084</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>40.362982</v>
+        <v>40.376186</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.317855</v>
+        <v>16.323193</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>52.213865</v>
+        <v>52.230945</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.559189</v>
+        <v>20.565914</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10.173316</v>
+        <v>10.176644</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>31.11</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11.19032</v>
+        <v>11.193981</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>34.22</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5.107914</v>
+        <v>5.109585</v>
       </c>
       <c r="E17" s="28" t="n">
         <v>15.62</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.559189</v>
+        <v>20.565914</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>62.87</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5.140615</v>
+        <v>5.142296</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>15.72</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>54.391759</v>
+        <v>54.409552</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2.305428</v>
+        <v>2.306183</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20.546109</v>
+        <v>20.55283</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.317855</v>
+        <v>16.323193</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2363,7 +2363,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2482,7 +2482,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2720,7 +2720,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2839,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2958,7 +2958,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.092217</v>
+        <v>1.092574</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>78.83584</v>
+        <v>78.86162899999999</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.45847</v>
+        <v>11.462218</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>21.680837</v>
+        <v>21.687929</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>14.823414</v>
+        <v>14.828263</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>124.545455</v>
+        <v>124.586196</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.007194</v>
+        <v>11.010795</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.616743</v>
+        <v>18.622833</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>16.739699</v>
+        <v>16.745175</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.381295</v>
+        <v>13.385672</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.007194</v>
+        <v>1.007524</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.334205</v>
+        <v>21.341184</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>11.890124</v>
+        <v>11.894014</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.377371</v>
+        <v>22.384691</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.464356</v>
+        <v>5.466143</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.295618</v>
+        <v>12.29964</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.616743</v>
+        <v>18.622833</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.054284</v>
+        <v>3.055283</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.579464</v>
+        <v>11.583252</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>21.863963</v>
+        <v>21.871115</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.398954</v>
+        <v>5.40072</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.616743</v>
+        <v>18.622833</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.517332</v>
+        <v>21.52437</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.320471</v>
+        <v>5.322211</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>12.792675</v>
+        <v>12.79686</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.459124</v>
+        <v>12.463199</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>15.840419</v>
+        <v>15.8456</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.448005</v>
+        <v>10.451423</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.425768</v>
+        <v>21.432777</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.333551</v>
+        <v>5.335296</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>15.951602</v>
+        <v>15.95682</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.336821</v>
+        <v>10.340203</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>31.706998</v>
+        <v>31.71737</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>34.672989</v>
+        <v>34.684331</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>37.544147</v>
+        <v>37.556428</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.209287</v>
+        <v>5.210991</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>145.758666</v>
+        <v>145.806346</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.624591</v>
+        <v>15.629702</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.241988</v>
+        <v>20.24861</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>20.768476</v>
+        <v>20.77527</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>20.709614</v>
+        <v>20.716389</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.317855</v>
+        <v>16.323193</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.156965</v>
+        <v>40.170101</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>25.57554</v>
+        <v>25.583906</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>43.81949</v>
+        <v>43.833824</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.045782</v>
+        <v>5.047432</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.630477</v>
+        <v>14.635263</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.362982</v>
+        <v>25.371279</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>31.841073</v>
+        <v>31.851488</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.317855</v>
+        <v>16.323193</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>47.292348</v>
+        <v>47.307818</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.186396</v>
+        <v>20.193</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.049052</v>
+        <v>5.050703</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.457816</v>
+        <v>20.464508</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>50.673643</v>
+        <v>50.690219</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>51.687377</v>
+        <v>51.704285</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.127534</v>
+        <v>5.129212</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.251799</v>
+        <v>10.255152</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.228908</v>
+        <v>10.232254</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>14.833224</v>
+        <v>14.838077</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.202747</v>
+        <v>10.206084</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>40.362982</v>
+        <v>40.376186</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.317855</v>
+        <v>16.323193</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>52.213865</v>
+        <v>52.230945</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.559189</v>
+        <v>20.565914</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.173316</v>
+        <v>10.176644</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>31.11</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11.19032</v>
+        <v>11.193981</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>34.22</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5.107914</v>
+        <v>5.109585</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>15.62</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.559189</v>
+        <v>20.565914</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>62.87</v>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5.140615</v>
+        <v>5.142296</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>15.72</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>54.391759</v>
+        <v>54.409552</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.305428</v>
+        <v>2.306183</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.546109</v>
+        <v>20.55283</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.317855</v>
+        <v>16.323193</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5645,7 +5645,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>61.14</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.092217</v>
+        <v>1.092574</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>78.83584</v>
+        <v>78.86162899999999</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.45847</v>
+        <v>11.462218</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>21.680837</v>
+        <v>21.687929</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>14.823414</v>
+        <v>14.828263</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>124.545455</v>
+        <v>124.586196</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.007194</v>
+        <v>11.010795</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -10914,7 +10914,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.616743</v>
+        <v>18.622833</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -10938,7 +10938,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.739699</v>
+        <v>16.745175</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.381295</v>
+        <v>13.385672</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -10986,7 +10986,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.007194</v>
+        <v>1.007524</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.334205</v>
+        <v>21.341184</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11034,7 +11034,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>11.890124</v>
+        <v>11.894014</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.377371</v>
+        <v>22.384691</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.464356</v>
+        <v>5.466143</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.295618</v>
+        <v>12.29964</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.616743</v>
+        <v>18.622833</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.054284</v>
+        <v>3.055283</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.579464</v>
+        <v>11.583252</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.863963</v>
+        <v>21.871115</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.398954</v>
+        <v>5.40072</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.616743</v>
+        <v>18.622833</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11536,7 +11536,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.517332</v>
+        <v>21.52437</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.320471</v>
+        <v>5.322211</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>12.792675</v>
+        <v>12.79686</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.459124</v>
+        <v>12.463199</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -11727,7 +11727,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.840419</v>
+        <v>15.8456</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.448005</v>
+        <v>10.451423</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.425768</v>
+        <v>21.432777</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -11823,7 +11823,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.333551</v>
+        <v>5.335296</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -11942,7 +11942,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>15.951602</v>
+        <v>15.95682</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.336821</v>
+        <v>10.340203</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>31.706998</v>
+        <v>31.71737</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>34.672989</v>
+        <v>34.684331</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>37.544147</v>
+        <v>37.556428</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.209287</v>
+        <v>5.210991</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12229,7 +12229,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.820144</v>
+        <v>24.828263</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>145.758666</v>
+        <v>145.806346</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.624591</v>
+        <v>15.629702</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.241988</v>
+        <v>20.24861</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12325,7 +12325,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>20.768476</v>
+        <v>20.77527</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12349,7 +12349,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.709614</v>
+        <v>20.716389</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.317855</v>
+        <v>16.323193</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.156965</v>
+        <v>40.170101</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>25.57554</v>
+        <v>25.583906</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43.81949</v>
+        <v>43.833824</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.045782</v>
+        <v>5.047432</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.630477</v>
+        <v>14.635263</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.058</v>
+        <v>3.019</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-13</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-14</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.362982</v>
+        <v>25.690626</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>31.841073</v>
+        <v>32.252401</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.317855</v>
+        <v>16.528652</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>47.292348</v>
+        <v>47.903279</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.186396</v>
+        <v>20.447168</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.049052</v>
+        <v>5.114276</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.457816</v>
+        <v>20.722093</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>50.673643</v>
+        <v>51.328254</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>51.687377</v>
+        <v>52.355084</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.127534</v>
+        <v>5.193773</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.251799</v>
+        <v>10.384233</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.228908</v>
+        <v>10.361047</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.833224</v>
+        <v>15.024843</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.202747</v>
+        <v>10.334548</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>40.362982</v>
+        <v>40.884399</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.317855</v>
+        <v>16.528652</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>52.213865</v>
+        <v>52.888374</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.559189</v>
+        <v>20.824776</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10.173316</v>
+        <v>10.304737</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>31.11</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11.19032</v>
+        <v>11.334879</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>34.22</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5.107914</v>
+        <v>5.173899</v>
       </c>
       <c r="E17" s="28" t="n">
         <v>15.62</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.559189</v>
+        <v>20.824776</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>62.87</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5.140615</v>
+        <v>5.207022</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>15.72</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>54.391759</v>
+        <v>55.094402</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2.305428</v>
+        <v>2.33521</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20.546109</v>
+        <v>20.811527</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.317855</v>
+        <v>16.528652</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2363,7 +2363,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2482,7 +2482,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2720,7 +2720,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2839,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2958,7 +2958,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.092217</v>
+        <v>1.106327</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>78.83584</v>
+        <v>79.85425600000001</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.45847</v>
+        <v>11.606492</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>21.680837</v>
+        <v>21.960914</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>14.823414</v>
+        <v>15.014906</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>124.545455</v>
+        <v>126.154356</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.007194</v>
+        <v>11.149387</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.616743</v>
+        <v>18.857237</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>16.739699</v>
+        <v>16.955946</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.381295</v>
+        <v>13.554157</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.007194</v>
+        <v>1.020205</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.334205</v>
+        <v>21.609805</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>11.890124</v>
+        <v>12.043723</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.377371</v>
+        <v>22.666446</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.464356</v>
+        <v>5.534945</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.295618</v>
+        <v>12.454455</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.616743</v>
+        <v>18.857237</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.054284</v>
+        <v>3.09374</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.579464</v>
+        <v>11.729049</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>21.863963</v>
+        <v>22.146406</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.398954</v>
+        <v>5.468698</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.616743</v>
+        <v>18.857237</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.517332</v>
+        <v>21.795296</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.320471</v>
+        <v>5.389202</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>12.792675</v>
+        <v>12.957933</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.459124</v>
+        <v>12.620073</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>15.840419</v>
+        <v>16.045048</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.448005</v>
+        <v>10.582974</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.425768</v>
+        <v>21.702551</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.333551</v>
+        <v>5.402451</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>15.951602</v>
+        <v>16.157668</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.336821</v>
+        <v>10.470354</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>31.706998</v>
+        <v>32.116595</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>34.672989</v>
+        <v>35.120901</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>37.544147</v>
+        <v>38.029149</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.209287</v>
+        <v>5.276582</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>145.758666</v>
+        <v>147.641603</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.624591</v>
+        <v>15.826433</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.241988</v>
+        <v>20.503478</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>20.768476</v>
+        <v>21.036767</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>20.709614</v>
+        <v>20.977145</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.317855</v>
+        <v>16.528652</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.156965</v>
+        <v>40.67572</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>25.57554</v>
+        <v>25.905929</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>43.81949</v>
+        <v>44.385558</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.045782</v>
+        <v>5.110964</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.630477</v>
+        <v>14.819477</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.362982</v>
+        <v>25.690626</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>31.841073</v>
+        <v>32.252401</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.317855</v>
+        <v>16.528652</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>47.292348</v>
+        <v>47.903279</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.186396</v>
+        <v>20.447168</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.049052</v>
+        <v>5.114276</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.457816</v>
+        <v>20.722093</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>50.673643</v>
+        <v>51.328254</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>51.687377</v>
+        <v>52.355084</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.127534</v>
+        <v>5.193773</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.251799</v>
+        <v>10.384233</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.228908</v>
+        <v>10.361047</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>14.833224</v>
+        <v>15.024843</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.202747</v>
+        <v>10.334548</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>40.362982</v>
+        <v>40.884399</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.317855</v>
+        <v>16.528652</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>52.213865</v>
+        <v>52.888374</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.559189</v>
+        <v>20.824776</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.173316</v>
+        <v>10.304737</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>31.11</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11.19032</v>
+        <v>11.334879</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>34.22</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5.107914</v>
+        <v>5.173899</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>15.62</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.559189</v>
+        <v>20.824776</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>62.87</v>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5.140615</v>
+        <v>5.207022</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>15.72</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>54.391759</v>
+        <v>55.094402</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.305428</v>
+        <v>2.33521</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.546109</v>
+        <v>20.811527</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.317855</v>
+        <v>16.528652</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5645,7 +5645,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>61.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.092217</v>
+        <v>1.106327</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>78.83584</v>
+        <v>79.85425600000001</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.45847</v>
+        <v>11.606492</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>21.680837</v>
+        <v>21.960914</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>14.823414</v>
+        <v>15.014906</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>124.545455</v>
+        <v>126.154356</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.007194</v>
+        <v>11.149387</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -10914,7 +10914,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.616743</v>
+        <v>18.857237</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -10938,7 +10938,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.739699</v>
+        <v>16.955946</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.381295</v>
+        <v>13.554157</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -10986,7 +10986,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.007194</v>
+        <v>1.020205</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.334205</v>
+        <v>21.609805</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11034,7 +11034,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>11.890124</v>
+        <v>12.043723</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.377371</v>
+        <v>22.666446</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.464356</v>
+        <v>5.534945</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.295618</v>
+        <v>12.454455</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.616743</v>
+        <v>18.857237</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.054284</v>
+        <v>3.09374</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.579464</v>
+        <v>11.729049</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.863963</v>
+        <v>22.146406</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.398954</v>
+        <v>5.468698</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.616743</v>
+        <v>18.857237</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11536,7 +11536,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.517332</v>
+        <v>21.795296</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.320471</v>
+        <v>5.389202</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>12.792675</v>
+        <v>12.957933</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.459124</v>
+        <v>12.620073</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -11727,7 +11727,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.840419</v>
+        <v>16.045048</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.448005</v>
+        <v>10.582974</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.425768</v>
+        <v>21.702551</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -11823,7 +11823,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.333551</v>
+        <v>5.402451</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -11942,7 +11942,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>15.951602</v>
+        <v>16.157668</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.336821</v>
+        <v>10.470354</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>31.706998</v>
+        <v>32.116595</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>34.672989</v>
+        <v>35.120901</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>37.544147</v>
+        <v>38.029149</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.209287</v>
+        <v>5.276582</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12229,7 +12229,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24.820144</v>
+        <v>25.140775</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>145.758666</v>
+        <v>147.641603</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.624591</v>
+        <v>15.826433</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.241988</v>
+        <v>20.503478</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12325,7 +12325,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>20.768476</v>
+        <v>21.036767</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12349,7 +12349,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.709614</v>
+        <v>20.977145</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.317855</v>
+        <v>16.528652</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.156965</v>
+        <v>40.67572</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>25.57554</v>
+        <v>25.905929</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43.81949</v>
+        <v>44.385558</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.045782</v>
+        <v>5.110964</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.630477</v>
+        <v>14.819477</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.019</v>
+        <v>3.014</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-14</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.690626</v>
+        <v>25.733245</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.252401</v>
+        <v>32.305906</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.528652</v>
+        <v>16.556072</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>47.903279</v>
+        <v>47.982747</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.447168</v>
+        <v>20.481088</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.114276</v>
+        <v>5.12276</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.722093</v>
+        <v>20.75647</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.328254</v>
+        <v>51.413404</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.355084</v>
+        <v>52.441938</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.193773</v>
+        <v>5.202389</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.384233</v>
+        <v>10.40146</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.361047</v>
+        <v>10.378235</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.024843</v>
+        <v>15.049768</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.334548</v>
+        <v>10.351692</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>40.884399</v>
+        <v>40.952223</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.528652</v>
+        <v>16.556072</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>52.888374</v>
+        <v>52.976111</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.824776</v>
+        <v>20.859323</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10.304737</v>
+        <v>10.321831</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>31.11</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11.334879</v>
+        <v>11.353683</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>34.22</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5.173899</v>
+        <v>5.182482</v>
       </c>
       <c r="E17" s="28" t="n">
         <v>15.62</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.824776</v>
+        <v>20.859323</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>62.87</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5.207022</v>
+        <v>5.21566</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>15.72</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>55.094402</v>
+        <v>55.1858</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2.33521</v>
+        <v>2.339084</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20.811527</v>
+        <v>20.846052</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.528652</v>
+        <v>16.556072</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2363,7 +2363,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2482,7 +2482,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2720,7 +2720,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2839,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2958,7 +2958,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.106327</v>
+        <v>1.108162</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>79.85425600000001</v>
+        <v>79.986729</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.606492</v>
+        <v>11.625747</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>21.960914</v>
+        <v>21.997346</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.014906</v>
+        <v>15.039814</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>126.154356</v>
+        <v>126.363636</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.149387</v>
+        <v>11.167883</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.857237</v>
+        <v>18.88852</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>16.955946</v>
+        <v>16.984074</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.554157</v>
+        <v>13.576642</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.020205</v>
+        <v>1.021898</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.609805</v>
+        <v>21.645654</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.043723</v>
+        <v>12.063703</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.666446</v>
+        <v>22.704048</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.534945</v>
+        <v>5.544127</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.454455</v>
+        <v>12.475116</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.857237</v>
+        <v>18.88852</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.09374</v>
+        <v>3.098872</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.729049</v>
+        <v>11.748507</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.146406</v>
+        <v>22.183145</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.468698</v>
+        <v>5.47777</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.857237</v>
+        <v>18.88852</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.795296</v>
+        <v>21.831453</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.389202</v>
+        <v>5.398142</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>12.957933</v>
+        <v>12.979429</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.620073</v>
+        <v>12.641009</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.045048</v>
+        <v>16.071666</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.582974</v>
+        <v>10.600531</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.702551</v>
+        <v>21.738553</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.402451</v>
+        <v>5.411413</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.157668</v>
+        <v>16.184472</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.470354</v>
+        <v>10.487724</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.116595</v>
+        <v>32.169874</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.120901</v>
+        <v>35.179164</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.029149</v>
+        <v>38.092236</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.276582</v>
+        <v>5.285335</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>147.641603</v>
+        <v>147.88653</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.826433</v>
+        <v>15.852687</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.503478</v>
+        <v>20.537492</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.036767</v>
+        <v>21.071666</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>20.977145</v>
+        <v>21.011944</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.528652</v>
+        <v>16.556072</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.67572</v>
+        <v>40.743198</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>25.905929</v>
+        <v>25.948905</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.385558</v>
+        <v>44.45919</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.110964</v>
+        <v>5.119443</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.819477</v>
+        <v>14.844061</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.690626</v>
+        <v>25.733245</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.252401</v>
+        <v>32.305906</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.528652</v>
+        <v>16.556072</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>47.903279</v>
+        <v>47.982747</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.447168</v>
+        <v>20.481088</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.114276</v>
+        <v>5.12276</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.722093</v>
+        <v>20.75647</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.328254</v>
+        <v>51.413404</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.355084</v>
+        <v>52.441938</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.193773</v>
+        <v>5.202389</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.384233</v>
+        <v>10.40146</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.361047</v>
+        <v>10.378235</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.024843</v>
+        <v>15.049768</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.334548</v>
+        <v>10.351692</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>40.884399</v>
+        <v>40.952223</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.528652</v>
+        <v>16.556072</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>52.888374</v>
+        <v>52.976111</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.824776</v>
+        <v>20.859323</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.304737</v>
+        <v>10.321831</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>31.11</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11.334879</v>
+        <v>11.353683</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>34.22</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5.173899</v>
+        <v>5.182482</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>15.62</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.824776</v>
+        <v>20.859323</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>62.87</v>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5.207022</v>
+        <v>5.21566</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>15.72</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.094402</v>
+        <v>55.1858</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.33521</v>
+        <v>2.339084</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.811527</v>
+        <v>20.846052</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.528652</v>
+        <v>16.556072</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5645,7 +5645,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.38</v>
+        <v>60.28</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.106327</v>
+        <v>1.108162</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>79.85425600000001</v>
+        <v>79.986729</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.606492</v>
+        <v>11.625747</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>21.960914</v>
+        <v>21.997346</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.014906</v>
+        <v>15.039814</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>126.154356</v>
+        <v>126.363636</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.149387</v>
+        <v>11.167883</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -10914,7 +10914,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.857237</v>
+        <v>18.88852</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -10938,7 +10938,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.955946</v>
+        <v>16.984074</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.554157</v>
+        <v>13.576642</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -10986,7 +10986,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.020205</v>
+        <v>1.021898</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.609805</v>
+        <v>21.645654</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11034,7 +11034,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.043723</v>
+        <v>12.063703</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.666446</v>
+        <v>22.704048</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.534945</v>
+        <v>5.544127</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.454455</v>
+        <v>12.475116</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.857237</v>
+        <v>18.88852</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.09374</v>
+        <v>3.098872</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.729049</v>
+        <v>11.748507</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.146406</v>
+        <v>22.183145</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.468698</v>
+        <v>5.47777</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.857237</v>
+        <v>18.88852</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11536,7 +11536,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.795296</v>
+        <v>21.831453</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.389202</v>
+        <v>5.398142</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>12.957933</v>
+        <v>12.979429</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.620073</v>
+        <v>12.641009</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -11727,7 +11727,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.045048</v>
+        <v>16.071666</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.582974</v>
+        <v>10.600531</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.702551</v>
+        <v>21.738553</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -11823,7 +11823,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.402451</v>
+        <v>5.411413</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -11942,7 +11942,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.157668</v>
+        <v>16.184472</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.470354</v>
+        <v>10.487724</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.116595</v>
+        <v>32.169874</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.120901</v>
+        <v>35.179164</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.029149</v>
+        <v>38.092236</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.276582</v>
+        <v>5.285335</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12229,7 +12229,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.140775</v>
+        <v>25.182482</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>147.641603</v>
+        <v>147.88653</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.826433</v>
+        <v>15.852687</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.503478</v>
+        <v>20.537492</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12325,7 +12325,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.036767</v>
+        <v>21.071666</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12349,7 +12349,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.977145</v>
+        <v>21.011944</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.528652</v>
+        <v>16.556072</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.67572</v>
+        <v>40.743198</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>25.905929</v>
+        <v>25.948905</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.385558</v>
+        <v>44.45919</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.110964</v>
+        <v>5.119443</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.819477</v>
+        <v>14.844061</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1855,7 +1855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2108,17 +2108,17 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -2129,27 +2129,51 @@
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="F13" s="29" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="20">
-        <f>SUM(D4:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="21">
-        <f>SUM(E4:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="31" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="20">
+        <f>SUM(D4:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>SUM(E4:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -2999,7 +3023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5628,17 +5652,17 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
@@ -5656,7 +5680,7 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5677,14 +5701,14 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5705,14 +5729,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5733,14 +5757,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5761,14 +5785,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5789,14 +5813,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5817,14 +5841,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5845,14 +5869,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5873,32 +5897,60 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="18" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B104" s="19" t="n"/>
-      <c r="C104" s="19" t="n"/>
-      <c r="D104" s="20">
-        <f>SUM(D3:D103)</f>
-        <v/>
-      </c>
-      <c r="E104" s="21">
-        <f>SUM(E3:E103)</f>
-        <v/>
-      </c>
-      <c r="F104" s="19" t="n"/>
+      <c r="B105" s="19" t="n"/>
+      <c r="C105" s="19" t="n"/>
+      <c r="D105" s="20">
+        <f>SUM(D3:D104)</f>
+        <v/>
+      </c>
+      <c r="E105" s="21">
+        <f>SUM(E3:E104)</f>
+        <v/>
+      </c>
+      <c r="F105" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A105:C105"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.014</v>
+        <v>2.995</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-15</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-16</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.733245</v>
+        <v>25.896494</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.305906</v>
+        <v>32.510851</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.556072</v>
+        <v>16.661102</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>47.982747</v>
+        <v>48.287145</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.481088</v>
+        <v>20.611018</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.12276</v>
+        <v>5.155259</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.75647</v>
+        <v>20.888147</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.413404</v>
+        <v>51.739566</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.441938</v>
+        <v>52.774624</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.202389</v>
+        <v>5.235392</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.40146</v>
+        <v>10.467446</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.378235</v>
+        <v>10.444073</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.049768</v>
+        <v>15.145242</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.351692</v>
+        <v>10.417362</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>40.952223</v>
+        <v>41.21202</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.556072</v>
+        <v>16.661102</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>52.976111</v>
+        <v>53.312187</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.859323</v>
+        <v>20.991653</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10.321831</v>
+        <v>10.387312</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>31.11</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11.353683</v>
+        <v>11.42571</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>34.22</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5.182482</v>
+        <v>5.215359</v>
       </c>
       <c r="E17" s="28" t="n">
         <v>15.62</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.859323</v>
+        <v>20.991653</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>62.87</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5.21566</v>
+        <v>5.248748</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>15.72</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>55.1858</v>
+        <v>55.535893</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2.339084</v>
+        <v>2.353923</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20.846052</v>
+        <v>20.978297</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.556072</v>
+        <v>16.661102</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2149,7 +2149,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2268,7 +2268,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2387,7 +2387,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2506,7 +2506,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2625,7 +2625,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2744,7 +2744,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2863,7 +2863,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2982,7 +2982,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.108162</v>
+        <v>1.115192</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>79.986729</v>
+        <v>80.494157</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.625747</v>
+        <v>11.699499</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>21.997346</v>
+        <v>22.136895</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.039814</v>
+        <v>15.135225</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>126.363636</v>
+        <v>127.165275</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.167883</v>
+        <v>11.238731</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.88852</v>
+        <v>19.008347</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>16.984074</v>
+        <v>17.09182</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.576642</v>
+        <v>13.662771</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.021898</v>
+        <v>1.028381</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.645654</v>
+        <v>21.782972</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.063703</v>
+        <v>12.140234</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.704048</v>
+        <v>22.84808</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.544127</v>
+        <v>5.579299</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.475116</v>
+        <v>12.554257</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.88852</v>
+        <v>19.008347</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.098872</v>
+        <v>3.118531</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.748507</v>
+        <v>11.823038</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.183145</v>
+        <v>22.323873</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.47777</v>
+        <v>5.512521</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.88852</v>
+        <v>19.008347</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.831453</v>
+        <v>21.96995</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.398142</v>
+        <v>5.432387</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>12.979429</v>
+        <v>13.06177</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.641009</v>
+        <v>12.721202</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.071666</v>
+        <v>16.173623</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.600531</v>
+        <v>10.66778</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.738553</v>
+        <v>21.876461</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.411413</v>
+        <v>5.445743</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.184472</v>
+        <v>16.287145</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.487724</v>
+        <v>10.554257</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.169874</v>
+        <v>32.373957</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.179164</v>
+        <v>35.402337</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.092236</v>
+        <v>38.33389</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.285335</v>
+        <v>5.318865</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>147.88653</v>
+        <v>148.824708</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.852687</v>
+        <v>15.953255</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.537492</v>
+        <v>20.66778</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.071666</v>
+        <v>21.205342</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>21.011944</v>
+        <v>21.145242</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.556072</v>
+        <v>16.661102</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.743198</v>
+        <v>41.001669</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>25.948905</v>
+        <v>26.113523</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.45919</v>
+        <v>44.741235</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.119443</v>
+        <v>5.15192</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.844061</v>
+        <v>14.93823</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.733245</v>
+        <v>25.896494</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.305906</v>
+        <v>32.510851</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.556072</v>
+        <v>16.661102</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>47.982747</v>
+        <v>48.287145</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.481088</v>
+        <v>20.611018</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.12276</v>
+        <v>5.155259</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.75647</v>
+        <v>20.888147</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.413404</v>
+        <v>51.739566</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.441938</v>
+        <v>52.774624</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.202389</v>
+        <v>5.235392</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.40146</v>
+        <v>10.467446</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.378235</v>
+        <v>10.444073</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.049768</v>
+        <v>15.145242</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.351692</v>
+        <v>10.417362</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>40.952223</v>
+        <v>41.21202</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.556072</v>
+        <v>16.661102</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>52.976111</v>
+        <v>53.312187</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.859323</v>
+        <v>20.991653</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.321831</v>
+        <v>10.387312</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>31.11</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11.353683</v>
+        <v>11.42571</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>34.22</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5.182482</v>
+        <v>5.215359</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>15.62</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.859323</v>
+        <v>20.991653</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>62.87</v>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5.21566</v>
+        <v>5.248748</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>15.72</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.1858</v>
+        <v>55.535893</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.339084</v>
+        <v>2.353923</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.846052</v>
+        <v>20.978297</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.556072</v>
+        <v>16.661102</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5669,7 +5669,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>20</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>59.9</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10679,7 +10679,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.108162</v>
+        <v>1.115192</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>79.986729</v>
+        <v>80.494157</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.625747</v>
+        <v>11.699499</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>21.997346</v>
+        <v>22.136895</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -10799,7 +10799,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.039814</v>
+        <v>15.135225</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>126.363636</v>
+        <v>127.165275</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.167883</v>
+        <v>11.238731</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -10966,7 +10966,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.88852</v>
+        <v>19.008347</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -10990,7 +10990,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.984074</v>
+        <v>17.09182</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.576642</v>
+        <v>13.662771</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.021898</v>
+        <v>1.028381</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.645654</v>
+        <v>21.782972</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11086,7 +11086,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.063703</v>
+        <v>12.140234</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.704048</v>
+        <v>22.84808</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.544127</v>
+        <v>5.579299</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11182,7 +11182,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.475116</v>
+        <v>12.554257</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.88852</v>
+        <v>19.008347</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.098872</v>
+        <v>3.118531</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11349,7 +11349,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.748507</v>
+        <v>11.823038</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11397,7 +11397,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.183145</v>
+        <v>22.323873</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11421,7 +11421,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.47777</v>
+        <v>5.512521</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11540,7 +11540,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.88852</v>
+        <v>19.008347</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11588,7 +11588,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.831453</v>
+        <v>21.96995</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.398142</v>
+        <v>5.432387</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>12.979429</v>
+        <v>13.06177</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -11755,7 +11755,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.641009</v>
+        <v>12.721202</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.071666</v>
+        <v>16.173623</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.600531</v>
+        <v>10.66778</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -11851,7 +11851,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.738553</v>
+        <v>21.876461</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.411413</v>
+        <v>5.445743</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12018,7 +12018,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.184472</v>
+        <v>16.287145</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -12042,7 +12042,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.487724</v>
+        <v>10.554257</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12066,7 +12066,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.169874</v>
+        <v>32.373957</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.179164</v>
+        <v>35.402337</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12138,7 +12138,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.092236</v>
+        <v>38.33389</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12162,7 +12162,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.285335</v>
+        <v>5.318865</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.182482</v>
+        <v>25.342237</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>147.88653</v>
+        <v>148.824708</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12329,7 +12329,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.852687</v>
+        <v>15.953255</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.537492</v>
+        <v>20.66778</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.071666</v>
+        <v>21.205342</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.011944</v>
+        <v>21.145242</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.556072</v>
+        <v>16.661102</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12473,7 +12473,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.743198</v>
+        <v>41.001669</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>25.948905</v>
+        <v>26.113523</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.45919</v>
+        <v>44.741235</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12545,7 +12545,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.119443</v>
+        <v>5.15192</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.844061</v>
+        <v>14.93823</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.014</v>
+        <v>3.65</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-15</t>
+          <t>← מקור: Bank of Israel Public API (fallback)</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.733245</v>
+        <v>21.249315</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.305906</v>
+        <v>26.676712</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.556072</v>
+        <v>13.671233</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>47.982747</v>
+        <v>39.621918</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.481088</v>
+        <v>16.912329</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.12276</v>
+        <v>4.230137</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.75647</v>
+        <v>17.139726</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.413404</v>
+        <v>42.454795</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.441938</v>
+        <v>43.30411</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.202389</v>
+        <v>4.29589</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.40146</v>
+        <v>8.589041</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.378235</v>
+        <v>8.569863</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.049768</v>
+        <v>12.427397</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.351692</v>
+        <v>8.547945</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>40.952223</v>
+        <v>33.816438</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.556072</v>
+        <v>13.671233</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>52.976111</v>
+        <v>43.745205</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.859323</v>
+        <v>17.224658</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10.321831</v>
+        <v>8.523288000000001</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>31.11</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11.353683</v>
+        <v>9.375342</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>34.22</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5.182482</v>
+        <v>4.279452</v>
       </c>
       <c r="E17" s="28" t="n">
         <v>15.62</v>
@@ -1855,7 +1855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1921,19 +1921,19 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.859323</v>
+        <v>20.794521</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.87</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1945,50 +1945,50 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5.21566</v>
+        <v>45.569863</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>15.72</v>
+        <v>166.33</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>25.182482</v>
+        <v>18</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>75.90000000000001</v>
+        <v>56.49</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -2002,178 +2002,130 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>55.1858</v>
+        <v>1.931507</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>166.33</v>
+        <v>7.05</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>18</v>
+        <v>17.213699</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>56.49</v>
+        <v>62.83</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2.339084</v>
+        <v>13.671233</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>7.05</v>
+        <v>49.9</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20.846052</v>
+        <v>20</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>62.83</v>
+        <v>73</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.556072</v>
+        <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>49.9</v>
+        <v>73</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="F12" s="24" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="F13" s="29" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="20">
-        <f>SUM(D4:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="21">
-        <f>SUM(E4:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="31" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="20">
+        <f>SUM(D4:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>SUM(E4:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -2268,7 +2220,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2387,7 +2339,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2506,7 +2458,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2625,7 +2577,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2744,7 +2696,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2863,7 +2815,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2982,7 +2934,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3023,7 +2975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3090,7 +3042,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.108162</v>
+        <v>0.915068</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3118,7 +3070,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>79.986729</v>
+        <v>66.04931500000001</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3146,7 +3098,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.625747</v>
+        <v>9.6</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3174,7 +3126,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>21.997346</v>
+        <v>18.164384</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3230,7 +3182,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.039814</v>
+        <v>12.419178</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3258,7 +3210,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>126.363636</v>
+        <v>104.345205</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3286,7 +3238,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.167883</v>
+        <v>9.221918000000001</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3314,7 +3266,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.88852</v>
+        <v>15.59726</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3342,7 +3294,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>16.984074</v>
+        <v>14.024658</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3370,7 +3322,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.576642</v>
+        <v>11.210959</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3398,7 +3350,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.021898</v>
+        <v>0.843836</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3426,7 +3378,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.645654</v>
+        <v>17.873973</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3454,7 +3406,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.063703</v>
+        <v>9.961644</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3482,7 +3434,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.704048</v>
+        <v>18.747945</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3538,7 +3490,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.544127</v>
+        <v>4.578082</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3566,7 +3518,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.475116</v>
+        <v>10.30137</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3594,7 +3546,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.88852</v>
+        <v>15.59726</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3622,7 +3574,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.098872</v>
+        <v>2.558904</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3650,7 +3602,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.748507</v>
+        <v>9.701370000000001</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3706,7 +3658,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.183145</v>
+        <v>18.317808</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3734,7 +3686,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.47777</v>
+        <v>4.523288</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3762,7 +3714,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.88852</v>
+        <v>15.59726</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3818,7 +3770,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.831453</v>
+        <v>18.027397</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3846,7 +3798,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.398142</v>
+        <v>4.457534</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -3874,7 +3826,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>12.979429</v>
+        <v>10.717808</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -3902,7 +3854,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.641009</v>
+        <v>10.438356</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -3930,7 +3882,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.071666</v>
+        <v>13.271233</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -3958,7 +3910,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.600531</v>
+        <v>8.753425</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4014,7 +3966,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.738553</v>
+        <v>17.950685</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4042,7 +3994,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.411413</v>
+        <v>4.468493</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4070,7 +4022,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4098,7 +4050,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.184472</v>
+        <v>13.364384</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4126,7 +4078,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.487724</v>
+        <v>8.660273999999999</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4154,7 +4106,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.169874</v>
+        <v>26.564384</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4182,7 +4134,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.179164</v>
+        <v>29.049315</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4238,7 +4190,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.092236</v>
+        <v>31.454795</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4266,7 +4218,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.285335</v>
+        <v>4.364384</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4294,7 +4246,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4322,7 +4274,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>147.88653</v>
+        <v>122.117808</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4350,7 +4302,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.852687</v>
+        <v>13.090411</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4378,7 +4330,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.537492</v>
+        <v>16.958904</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4406,7 +4358,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.071666</v>
+        <v>17.4</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4434,7 +4386,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>21.011944</v>
+        <v>17.350685</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4462,7 +4414,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.556072</v>
+        <v>13.671233</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4518,7 +4470,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.743198</v>
+        <v>33.643836</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4546,7 +4498,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>25.948905</v>
+        <v>21.427397</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4574,7 +4526,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.45919</v>
+        <v>36.712329</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4602,7 +4554,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.119443</v>
+        <v>4.227397</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4630,7 +4582,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.844061</v>
+        <v>12.257534</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4658,7 +4610,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.733245</v>
+        <v>21.249315</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4686,7 +4638,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4714,7 +4666,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.305906</v>
+        <v>26.676712</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4742,7 +4694,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.556072</v>
+        <v>13.671233</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4770,7 +4722,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>47.982747</v>
+        <v>39.621918</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4798,7 +4750,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.481088</v>
+        <v>16.912329</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4826,7 +4778,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.12276</v>
+        <v>4.230137</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -4882,7 +4834,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.75647</v>
+        <v>17.139726</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -4910,7 +4862,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.413404</v>
+        <v>42.454795</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -4938,7 +4890,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.441938</v>
+        <v>43.30411</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -4966,7 +4918,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.202389</v>
+        <v>4.29589</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -4994,7 +4946,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.40146</v>
+        <v>8.589041</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -5022,7 +4974,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5050,7 +5002,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.378235</v>
+        <v>8.569863</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5078,7 +5030,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.049768</v>
+        <v>12.427397</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5106,7 +5058,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5134,7 +5086,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.351692</v>
+        <v>8.547945</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5162,7 +5114,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>40.952223</v>
+        <v>33.816438</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5190,7 +5142,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.556072</v>
+        <v>13.671233</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5218,7 +5170,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>52.976111</v>
+        <v>43.745205</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5246,7 +5198,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.859323</v>
+        <v>17.224658</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5302,7 +5254,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.321831</v>
+        <v>8.523288000000001</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>31.11</v>
@@ -5330,7 +5282,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11.353683</v>
+        <v>9.375342</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>34.22</v>
@@ -5386,7 +5338,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5.182482</v>
+        <v>4.279452</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>15.62</v>
@@ -5433,19 +5385,19 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.859323</v>
+        <v>20.794521</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>62.87</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -5461,19 +5413,19 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5.21566</v>
+        <v>45.569863</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>15.72</v>
+        <v>166.33</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5484,24 +5436,24 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.182482</v>
+        <v>18</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>75.90000000000001</v>
+        <v>56.49</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -5512,7 +5464,7 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
@@ -5526,10 +5478,10 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.1858</v>
+        <v>1.931507</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>166.33</v>
+        <v>7.05</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -5540,24 +5492,24 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>18</v>
+        <v>17.213699</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>56.49</v>
+        <v>62.83</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -5568,24 +5520,24 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.339084</v>
+        <v>13.671233</v>
       </c>
       <c r="E92" s="17" t="n">
-        <v>7.05</v>
+        <v>49.9</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -5596,24 +5548,24 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.846052</v>
+        <v>20</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>62.83</v>
+        <v>73</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -5624,24 +5576,24 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.556072</v>
+        <v>20</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>49.9</v>
+        <v>73</v>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -5652,35 +5604,35 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5697,18 +5649,18 @@
         <v>20</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5725,18 +5677,18 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5753,18 +5705,18 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5781,18 +5733,18 @@
         <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5809,18 +5761,18 @@
         <v>20</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5837,18 +5789,18 @@
         <v>20</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>נובמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5865,92 +5817,36 @@
         <v>20</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="B103" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C103" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E103" s="13" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t>נובמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="14" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="B104" s="15" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C104" s="15" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D104" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="F104" s="14" t="inlineStr">
-        <is>
-          <t>דצמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="18" t="inlineStr">
+      <c r="A103" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B105" s="19" t="n"/>
-      <c r="C105" s="19" t="n"/>
-      <c r="D105" s="20">
-        <f>SUM(D3:D104)</f>
-        <v/>
-      </c>
-      <c r="E105" s="21">
-        <f>SUM(E3:E104)</f>
-        <v/>
-      </c>
-      <c r="F105" s="19" t="n"/>
+      <c r="B103" s="19" t="n"/>
+      <c r="C103" s="19" t="n"/>
+      <c r="D103" s="20">
+        <f>SUM(D3:D102)</f>
+        <v/>
+      </c>
+      <c r="E103" s="21">
+        <f>SUM(E3:E102)</f>
+        <v/>
+      </c>
+      <c r="F103" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A103:C103"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A105:C105"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6041,7 +5937,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.28</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10679,7 +10575,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.108162</v>
+        <v>0.915068</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -10703,7 +10599,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>79.986729</v>
+        <v>66.04931500000001</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -10727,7 +10623,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.625747</v>
+        <v>9.6</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -10751,7 +10647,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>21.997346</v>
+        <v>18.164384</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -10799,7 +10695,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.039814</v>
+        <v>12.419178</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -10823,7 +10719,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>126.363636</v>
+        <v>104.345205</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -10847,7 +10743,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.167883</v>
+        <v>9.221918000000001</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -10966,7 +10862,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.88852</v>
+        <v>15.59726</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -10990,7 +10886,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.984074</v>
+        <v>14.024658</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -11014,7 +10910,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.576642</v>
+        <v>11.210959</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -11038,7 +10934,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.021898</v>
+        <v>0.843836</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11062,7 +10958,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.645654</v>
+        <v>17.873973</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11086,7 +10982,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.063703</v>
+        <v>9.961644</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11110,7 +11006,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.704048</v>
+        <v>18.747945</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11158,7 +11054,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.544127</v>
+        <v>4.578082</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11182,7 +11078,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.475116</v>
+        <v>10.30137</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11301,7 +11197,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.88852</v>
+        <v>15.59726</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11325,7 +11221,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.098872</v>
+        <v>2.558904</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11349,7 +11245,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.748507</v>
+        <v>9.701370000000001</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11397,7 +11293,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.183145</v>
+        <v>18.317808</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11421,7 +11317,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.47777</v>
+        <v>4.523288</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11540,7 +11436,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.88852</v>
+        <v>15.59726</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11588,7 +11484,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.831453</v>
+        <v>18.027397</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11612,7 +11508,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.398142</v>
+        <v>4.457534</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -11731,7 +11627,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>12.979429</v>
+        <v>10.717808</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -11755,7 +11651,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.641009</v>
+        <v>10.438356</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -11779,7 +11675,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.071666</v>
+        <v>13.271233</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -11803,7 +11699,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.600531</v>
+        <v>8.753425</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -11851,7 +11747,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.738553</v>
+        <v>17.950685</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -11875,7 +11771,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.411413</v>
+        <v>4.468493</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -11994,7 +11890,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12018,7 +11914,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.184472</v>
+        <v>13.364384</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -12042,7 +11938,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.487724</v>
+        <v>8.660273999999999</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12066,7 +11962,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.169874</v>
+        <v>26.564384</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12090,7 +11986,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.179164</v>
+        <v>29.049315</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12138,7 +12034,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.092236</v>
+        <v>31.454795</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12162,7 +12058,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.285335</v>
+        <v>4.364384</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12281,7 +12177,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.182482</v>
+        <v>20.794521</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12305,7 +12201,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>147.88653</v>
+        <v>122.117808</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12329,7 +12225,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.852687</v>
+        <v>13.090411</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12353,7 +12249,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.537492</v>
+        <v>16.958904</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12377,7 +12273,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.071666</v>
+        <v>17.4</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12401,7 +12297,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.011944</v>
+        <v>17.350685</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12425,7 +12321,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.556072</v>
+        <v>13.671233</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12473,7 +12369,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.743198</v>
+        <v>33.643836</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12497,7 +12393,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>25.948905</v>
+        <v>21.427397</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12521,7 +12417,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.45919</v>
+        <v>36.712329</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12545,7 +12441,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.119443</v>
+        <v>4.227397</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12569,7 +12465,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.844061</v>
+        <v>12.257534</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1855,7 +1855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2137,43 +2137,67 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="F13" s="29" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>ChatGPT Plus</t>
         </is>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D14" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E14" s="26" t="n">
         <v>59.9</v>
       </c>
-      <c r="F13" s="29" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="F14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="20">
-        <f>SUM(D4:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="21">
-        <f>SUM(E4:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="31" t="n"/>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="20">
+        <f>SUM(D4:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>SUM(E4:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3023,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5685,19 +5709,19 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>59.9</v>
+        <v>29.95</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5708,7 +5732,7 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -5729,14 +5753,14 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -5757,14 +5781,14 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5785,14 +5809,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5813,14 +5837,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5841,14 +5865,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5869,14 +5893,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5897,14 +5921,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5925,32 +5949,60 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="18" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B105" s="19" t="n"/>
-      <c r="C105" s="19" t="n"/>
-      <c r="D105" s="20">
-        <f>SUM(D3:D104)</f>
-        <v/>
-      </c>
-      <c r="E105" s="21">
-        <f>SUM(E3:E104)</f>
-        <v/>
-      </c>
-      <c r="F105" s="19" t="n"/>
+      <c r="B106" s="19" t="n"/>
+      <c r="C106" s="19" t="n"/>
+      <c r="D106" s="20">
+        <f>SUM(D3:D105)</f>
+        <v/>
+      </c>
+      <c r="E106" s="21">
+        <f>SUM(E3:E105)</f>
+        <v/>
+      </c>
+      <c r="F106" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A105:C105"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2.995</v>
+        <v>2.996</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-16</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.896494</v>
+        <v>25.88785</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.510851</v>
+        <v>32.5</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.661102</v>
+        <v>16.655541</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>48.287145</v>
+        <v>48.271028</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.611018</v>
+        <v>20.604139</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.155259</v>
+        <v>5.153538</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.888147</v>
+        <v>20.881175</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.739566</v>
+        <v>51.722296</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.774624</v>
+        <v>52.757009</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.235392</v>
+        <v>5.233645</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.467446</v>
+        <v>10.463952</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.444073</v>
+        <v>10.440587</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.145242</v>
+        <v>15.140187</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.417362</v>
+        <v>10.413885</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>41.21202</v>
+        <v>41.198264</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.661102</v>
+        <v>16.655541</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>53.312187</v>
+        <v>53.294393</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.991653</v>
+        <v>20.984646</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10.387312</v>
+        <v>10.383845</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>31.11</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11.42571</v>
+        <v>11.421896</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>34.22</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5.215359</v>
+        <v>5.213618</v>
       </c>
       <c r="E17" s="28" t="n">
         <v>15.62</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.991653</v>
+        <v>20.984646</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>62.87</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5.248748</v>
+        <v>5.246996</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>15.72</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>55.535893</v>
+        <v>55.517356</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2.353923</v>
+        <v>2.353138</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20.978297</v>
+        <v>20.971295</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.661102</v>
+        <v>16.655541</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>29.95</v>
+        <v>29.96</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2173,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -2292,7 +2292,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2411,7 +2411,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2530,7 +2530,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2649,7 +2649,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2768,7 +2768,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2887,7 +2887,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3006,7 +3006,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.115192</v>
+        <v>1.11482</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>80.494157</v>
+        <v>80.46729000000001</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.699499</v>
+        <v>11.695594</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>22.136895</v>
+        <v>22.129506</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.135225</v>
+        <v>15.130174</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>127.165275</v>
+        <v>127.12283</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.238731</v>
+        <v>11.23498</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>19.008347</v>
+        <v>19.002003</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>17.09182</v>
+        <v>17.086115</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.662771</v>
+        <v>13.658211</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.028381</v>
+        <v>1.028037</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.782972</v>
+        <v>21.775701</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.140234</v>
+        <v>12.136182</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.84808</v>
+        <v>22.840454</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.579299</v>
+        <v>5.577437</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.554257</v>
+        <v>12.550067</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>19.008347</v>
+        <v>19.002003</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.118531</v>
+        <v>3.11749</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.823038</v>
+        <v>11.819092</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.323873</v>
+        <v>22.316422</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.512521</v>
+        <v>5.510681</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>19.008347</v>
+        <v>19.002003</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.96995</v>
+        <v>21.962617</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.432387</v>
+        <v>5.430574</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>13.06177</v>
+        <v>13.05741</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.721202</v>
+        <v>12.716956</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.173623</v>
+        <v>16.168224</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.66778</v>
+        <v>10.664219</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.876461</v>
+        <v>21.869159</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.445743</v>
+        <v>5.443925</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.287145</v>
+        <v>16.281709</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.554257</v>
+        <v>10.550734</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.373957</v>
+        <v>32.363151</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.402337</v>
+        <v>35.390521</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.33389</v>
+        <v>38.321095</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.318865</v>
+        <v>5.317089</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>148.824708</v>
+        <v>148.775033</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.953255</v>
+        <v>15.947931</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.66778</v>
+        <v>20.660881</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.205342</v>
+        <v>21.198264</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>21.145242</v>
+        <v>21.138184</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.661102</v>
+        <v>16.655541</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>41.001669</v>
+        <v>40.987984</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>26.113523</v>
+        <v>26.104806</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.741235</v>
+        <v>44.726302</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.15192</v>
+        <v>5.1502</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.93823</v>
+        <v>14.933244</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.896494</v>
+        <v>25.88785</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.510851</v>
+        <v>32.5</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.661102</v>
+        <v>16.655541</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>48.287145</v>
+        <v>48.271028</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.611018</v>
+        <v>20.604139</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.155259</v>
+        <v>5.153538</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.888147</v>
+        <v>20.881175</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.739566</v>
+        <v>51.722296</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.774624</v>
+        <v>52.757009</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.235392</v>
+        <v>5.233645</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.467446</v>
+        <v>10.463952</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.444073</v>
+        <v>10.440587</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.145242</v>
+        <v>15.140187</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.417362</v>
+        <v>10.413885</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>41.21202</v>
+        <v>41.198264</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5214,7 +5214,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.661102</v>
+        <v>16.655541</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>53.312187</v>
+        <v>53.294393</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.991653</v>
+        <v>20.984646</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.387312</v>
+        <v>10.383845</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>31.11</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11.42571</v>
+        <v>11.421896</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>34.22</v>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5.215359</v>
+        <v>5.213618</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>15.62</v>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.991653</v>
+        <v>20.984646</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>62.87</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5.248748</v>
+        <v>5.246996</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>15.72</v>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.535893</v>
+        <v>55.517356</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.353923</v>
+        <v>2.353138</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.978297</v>
+        <v>20.971295</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.661102</v>
+        <v>16.655541</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5693,7 +5693,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>10</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>29.95</v>
+        <v>29.96</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>20</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>20</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.115192</v>
+        <v>1.11482</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>80.494157</v>
+        <v>80.46729000000001</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.699499</v>
+        <v>11.695594</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>22.136895</v>
+        <v>22.129506</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.135225</v>
+        <v>15.130174</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>127.165275</v>
+        <v>127.12283</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -10899,7 +10899,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.238731</v>
+        <v>11.23498</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.008347</v>
+        <v>19.002003</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11042,7 +11042,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>17.09182</v>
+        <v>17.086115</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.662771</v>
+        <v>13.658211</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -11090,7 +11090,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.028381</v>
+        <v>1.028037</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.782972</v>
+        <v>21.775701</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.140234</v>
+        <v>12.136182</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11162,7 +11162,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.84808</v>
+        <v>22.840454</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.579299</v>
+        <v>5.577437</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.554257</v>
+        <v>12.550067</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.008347</v>
+        <v>19.002003</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.118531</v>
+        <v>3.11749</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.823038</v>
+        <v>11.819092</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.323873</v>
+        <v>22.316422</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.512521</v>
+        <v>5.510681</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.008347</v>
+        <v>19.002003</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.96995</v>
+        <v>21.962617</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11664,7 +11664,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.432387</v>
+        <v>5.430574</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -11783,7 +11783,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>13.06177</v>
+        <v>13.05741</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.721202</v>
+        <v>12.716956</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.173623</v>
+        <v>16.168224</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -11855,7 +11855,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.66778</v>
+        <v>10.664219</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.876461</v>
+        <v>21.869159</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.445743</v>
+        <v>5.443925</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -12046,7 +12046,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12070,7 +12070,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.287145</v>
+        <v>16.281709</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -12094,7 +12094,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.554257</v>
+        <v>10.550734</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12118,7 +12118,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.373957</v>
+        <v>32.363151</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12142,7 +12142,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.402337</v>
+        <v>35.390521</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12190,7 +12190,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.33389</v>
+        <v>38.321095</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12214,7 +12214,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.318865</v>
+        <v>5.317089</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.342237</v>
+        <v>25.333778</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12357,7 +12357,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>148.824708</v>
+        <v>148.775033</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12381,7 +12381,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.953255</v>
+        <v>15.947931</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.66778</v>
+        <v>20.660881</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.205342</v>
+        <v>21.198264</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.145242</v>
+        <v>21.138184</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12477,7 +12477,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.661102</v>
+        <v>16.655541</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>41.001669</v>
+        <v>40.987984</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>26.113523</v>
+        <v>26.104806</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.741235</v>
+        <v>44.726302</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.15192</v>
+        <v>5.1502</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.93823</v>
+        <v>14.933244</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1400,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1701,24 +1701,24 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Pro – Mar 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10.383845</v>
+        <v>16.655541</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>31.11</v>
+        <v>49.9</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -1730,115 +1730,139 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11.421896</v>
+        <v>10.383845</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>34.22</v>
+        <v>31.11</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>9</v>
+        <v>11.421896</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>28.06</v>
+        <v>34.22</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>5.213618</v>
+        <v>9</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>15.62</v>
+        <v>28.06</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Lite plan</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>5.213618</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="F18" s="24" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Dzine</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Video Top-Up</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D19" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E19" s="28" t="n">
         <v>62.37</v>
       </c>
-      <c r="F18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="F19" s="29" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="20">
-        <f>SUM(D4:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>SUM(E4:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="31" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="20">
+        <f>SUM(D4:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>SUM(E4:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -1926,14 +1950,14 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.984646</v>
+        <v>10.493992</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>62.87</v>
+        <v>31.44</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -1945,19 +1969,19 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Business Plus – Mar 2026 (₪75.90)</t>
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>5.246996</v>
+        <v>25.333778</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>15.72</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1969,146 +1993,146 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Business Plus – Mar 2026 (₪75.90)</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>25.333778</v>
+        <v>55.517356</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>75.90000000000001</v>
+        <v>166.33</v>
       </c>
       <c r="F6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>55.517356</v>
+        <v>18</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>166.33</v>
+        <v>56.49</v>
       </c>
       <c r="F7" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Meta (Ads)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>18</v>
+        <v>2.353138</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>56.49</v>
+        <v>7.05</v>
       </c>
       <c r="F8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Meta (Ads)</t>
+          <t>IONOS</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Facebook Ads</t>
+          <t>Instant Domain</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2.353138</v>
+        <v>20.971295</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>7.05</v>
+        <v>62.83</v>
       </c>
       <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>IONOS</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Instant Domain</t>
+          <t>capcut_pro_discount1</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>20.971295</v>
+        <v>16.655541</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>62.83</v>
+        <v>49.9</v>
       </c>
       <c r="F10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>capcut_pro_discount1</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.655541</v>
+        <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>49.9</v>
+        <v>59.92</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -2118,14 +2142,14 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>59.92</v>
+        <v>29.96</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2137,43 +2161,43 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>29.96</v>
+        <v>59.92</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>20</v>
+        <v>16.655541</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>59.92</v>
+        <v>49.9</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -3047,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5312,24 +5336,24 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Pro – Mar 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.383845</v>
+        <v>16.655541</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>31.11</v>
+        <v>49.9</v>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -5345,19 +5369,19 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Eleven Labs</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Creator (first month 50% off)</t>
+          <t>Credit purchase</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>11.421896</v>
+        <v>10.383845</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>34.22</v>
+        <v>31.11</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -5368,24 +5392,24 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Eleven Labs</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Creator (first month 50% off)</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>9</v>
+        <v>11.421896</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>28.06</v>
+        <v>34.22</v>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -5396,24 +5420,24 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Lite plan</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>5.213618</v>
+        <v>9</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>15.62</v>
+        <v>28.06</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
@@ -5424,24 +5448,24 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Dzine</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Video Top-Up</t>
+          <t>Lite plan</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>20</v>
+        <v>5.213618</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>62.37</v>
+        <v>15.62</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -5452,28 +5476,28 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Dzine</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Claude Pro</t>
+          <t>Video Top-Up</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>20.984646</v>
+        <v>20</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>62.87</v>
+        <v>62.37</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מרץ 2026</t>
         </is>
       </c>
     </row>
@@ -5490,14 +5514,14 @@
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Credit purchase</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>5.246996</v>
+        <v>10.493992</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>15.72</v>
+        <v>31.44</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -5686,7 +5710,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Claude Pro</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
@@ -5714,7 +5738,7 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D96" s="16" t="n">
@@ -5760,35 +5784,35 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>20</v>
+        <v>16.655541</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>59.92</v>
+        <v>49.9</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -5809,14 +5833,14 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5837,14 +5861,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5865,14 +5889,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5893,14 +5917,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5921,14 +5945,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5949,14 +5973,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -5977,32 +6001,60 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="18" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B106" s="19" t="n"/>
-      <c r="C106" s="19" t="n"/>
-      <c r="D106" s="20">
-        <f>SUM(D3:D105)</f>
-        <v/>
-      </c>
-      <c r="E106" s="21">
-        <f>SUM(E3:E105)</f>
-        <v/>
-      </c>
-      <c r="F106" s="19" t="n"/>
+      <c r="B107" s="19" t="n"/>
+      <c r="C107" s="19" t="n"/>
+      <c r="D107" s="20">
+        <f>SUM(D3:D106)</f>
+        <v/>
+      </c>
+      <c r="E107" s="21">
+        <f>SUM(E3:E106)</f>
+        <v/>
+      </c>
+      <c r="F107" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A107:C107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
+          <t>CapCut (₪49.9)</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -2201,28 +2201,52 @@
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Pro – Apr 2026 (₪49.90)</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>16.655541</v>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="31" t="n"/>
-      <c r="D15" s="20">
-        <f>SUM(D4:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="21">
-        <f>SUM(E4:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="31" t="n"/>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="20">
+        <f>SUM(D4:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>SUM(E4:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -3071,7 +3095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5794,7 +5818,7 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
+          <t>CapCut (₪49.9)</t>
         </is>
       </c>
       <c r="D98" s="16" t="n">
@@ -5812,35 +5836,35 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>20</v>
+        <v>16.655541</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>59.92</v>
+        <v>49.9</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5861,14 +5885,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5889,14 +5913,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5917,14 +5941,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5945,14 +5969,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5973,14 +5997,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6001,14 +6025,14 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6029,32 +6053,60 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E107" s="13" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="18" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B107" s="19" t="n"/>
-      <c r="C107" s="19" t="n"/>
-      <c r="D107" s="20">
-        <f>SUM(D3:D106)</f>
-        <v/>
-      </c>
-      <c r="E107" s="21">
-        <f>SUM(E3:E106)</f>
-        <v/>
-      </c>
-      <c r="F107" s="19" t="n"/>
+      <c r="B108" s="19" t="n"/>
+      <c r="C108" s="19" t="n"/>
+      <c r="D108" s="20">
+        <f>SUM(D3:D107)</f>
+        <v/>
+      </c>
+      <c r="E108" s="21">
+        <f>SUM(E3:E107)</f>
+        <v/>
+      </c>
+      <c r="F108" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A108:C108"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>CapCut (₪49.9)</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -2201,52 +2201,28 @@
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>CapCut</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="n">
-        <v>16.655541</v>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="F15" s="29" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="20">
-        <f>SUM(D4:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>SUM(E4:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="31" t="n"/>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="20">
+        <f>SUM(D4:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>SUM(E4:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -3095,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5818,7 +5794,7 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>CapCut (₪49.9)</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D98" s="16" t="n">
@@ -5836,35 +5812,35 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>16.655541</v>
+        <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>49.9</v>
+        <v>59.92</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5885,14 +5861,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5913,14 +5889,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5941,14 +5917,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5969,14 +5945,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5997,14 +5973,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6025,14 +6001,14 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>נובמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6053,60 +6029,32 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C107" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E107" s="13" t="n">
-        <v>59.92</v>
-      </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="18" t="inlineStr">
+      <c r="A107" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B108" s="19" t="n"/>
-      <c r="C108" s="19" t="n"/>
-      <c r="D108" s="20">
-        <f>SUM(D3:D107)</f>
-        <v/>
-      </c>
-      <c r="E108" s="21">
-        <f>SUM(E3:E107)</f>
-        <v/>
-      </c>
-      <c r="F108" s="19" t="n"/>
+      <c r="B107" s="19" t="n"/>
+      <c r="C107" s="19" t="n"/>
+      <c r="D107" s="20">
+        <f>SUM(D3:D106)</f>
+        <v/>
+      </c>
+      <c r="E107" s="21">
+        <f>SUM(E3:E106)</f>
+        <v/>
+      </c>
+      <c r="F107" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A107:C107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>CapCut (₪49.9)</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -2201,52 +2201,28 @@
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>CapCut</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="n">
-        <v>16.655541</v>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="F15" s="29" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="20">
-        <f>SUM(D4:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>SUM(E4:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="31" t="n"/>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="20">
+        <f>SUM(D4:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>SUM(E4:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -3095,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5818,7 +5794,7 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>CapCut (₪49.9)</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D98" s="16" t="n">
@@ -5836,35 +5812,35 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>16.655541</v>
+        <v>20</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>49.9</v>
+        <v>59.92</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5885,14 +5861,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5913,14 +5889,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5941,14 +5917,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5969,14 +5945,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5997,14 +5973,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6025,14 +6001,14 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>נובמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6053,60 +6029,32 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C107" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E107" s="13" t="n">
-        <v>59.92</v>
-      </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="18" t="inlineStr">
+      <c r="A107" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B108" s="19" t="n"/>
-      <c r="C108" s="19" t="n"/>
-      <c r="D108" s="20">
-        <f>SUM(D3:D107)</f>
-        <v/>
-      </c>
-      <c r="E108" s="21">
-        <f>SUM(E3:E107)</f>
-        <v/>
-      </c>
-      <c r="F108" s="19" t="n"/>
+      <c r="B107" s="19" t="n"/>
+      <c r="C107" s="19" t="n"/>
+      <c r="D107" s="20">
+        <f>SUM(D3:D106)</f>
+        <v/>
+      </c>
+      <c r="E107" s="21">
+        <f>SUM(E3:E106)</f>
+        <v/>
+      </c>
+      <c r="F107" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A107:C107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2201,28 +2201,52 @@
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Prepaid extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="F15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="31" t="n"/>
-      <c r="D15" s="20">
-        <f>SUM(D4:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="21">
-        <f>SUM(E4:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="31" t="n"/>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="20">
+        <f>SUM(D4:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>SUM(E4:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -3071,7 +3095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5812,35 +5836,35 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>59.92</v>
+        <v>14.98</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5861,14 +5885,14 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -5889,14 +5913,14 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5917,14 +5941,14 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5945,14 +5969,14 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5973,14 +5997,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6001,14 +6025,14 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6029,32 +6053,60 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E107" s="13" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="18" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B107" s="19" t="n"/>
-      <c r="C107" s="19" t="n"/>
-      <c r="D107" s="20">
-        <f>SUM(D3:D106)</f>
-        <v/>
-      </c>
-      <c r="E107" s="21">
-        <f>SUM(E3:E106)</f>
-        <v/>
-      </c>
-      <c r="F107" s="19" t="n"/>
+      <c r="B108" s="19" t="n"/>
+      <c r="C108" s="19" t="n"/>
+      <c r="D108" s="20">
+        <f>SUM(D3:D107)</f>
+        <v/>
+      </c>
+      <c r="E108" s="21">
+        <f>SUM(E3:E107)</f>
+        <v/>
+      </c>
+      <c r="F108" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A108:C108"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2.996</v>
+        <v>3.003</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-17</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.88785</v>
+        <v>25.827506</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.5</v>
+        <v>32.424242</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>48.271028</v>
+        <v>48.158508</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.604139</v>
+        <v>20.556111</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.153538</v>
+        <v>5.141525</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.881175</v>
+        <v>20.832501</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.722296</v>
+        <v>51.601732</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.757009</v>
+        <v>52.634033</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.233645</v>
+        <v>5.221445</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.463952</v>
+        <v>10.43956</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.440587</v>
+        <v>10.41625</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.140187</v>
+        <v>15.104895</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.413885</v>
+        <v>10.38961</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>41.198264</v>
+        <v>41.102231</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>53.294393</v>
+        <v>53.170163</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.984646</v>
+        <v>20.935731</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>10.383845</v>
+        <v>10.35964</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>31.11</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>11.421896</v>
+        <v>11.395271</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>34.22</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>5.213618</v>
+        <v>5.201465</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>15.62</v>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>10.493992</v>
+        <v>10.46953</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>31.44</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>55.517356</v>
+        <v>55.387945</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>2.353138</v>
+        <v>2.347652</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.971295</v>
+        <v>20.922411</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>29.96</v>
+        <v>30.03</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2173,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -2221,32 +2221,104 @@
         <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>14.98</v>
+        <v>15.02</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Prepaid extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="F17" s="29" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="F18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="20">
-        <f>SUM(D4:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>SUM(E4:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="31" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="20">
+        <f>SUM(D4:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>SUM(E4:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -2340,7 +2412,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2459,7 +2531,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2578,7 +2650,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2697,7 +2769,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2816,7 +2888,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2935,7 +3007,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3054,7 +3126,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3095,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3162,7 +3234,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.11482</v>
+        <v>1.112221</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3190,7 +3262,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>80.46729000000001</v>
+        <v>80.27972</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3218,7 +3290,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.695594</v>
+        <v>11.668332</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3246,7 +3318,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>22.129506</v>
+        <v>22.077922</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3302,7 +3374,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.130174</v>
+        <v>15.094905</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3330,7 +3402,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>127.12283</v>
+        <v>126.826507</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3358,7 +3430,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.23498</v>
+        <v>11.208791</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3386,7 +3458,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>19.002003</v>
+        <v>18.957709</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3414,7 +3486,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>17.086115</v>
+        <v>17.046287</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3442,7 +3514,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.658211</v>
+        <v>13.626374</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3470,7 +3542,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.028037</v>
+        <v>1.025641</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3498,7 +3570,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.775701</v>
+        <v>21.724942</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3526,7 +3598,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.136182</v>
+        <v>12.107892</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3554,7 +3626,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.840454</v>
+        <v>22.787213</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3610,7 +3682,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.577437</v>
+        <v>5.564436</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3638,7 +3710,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.550067</v>
+        <v>12.520813</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3666,7 +3738,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>19.002003</v>
+        <v>18.957709</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3694,7 +3766,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.11749</v>
+        <v>3.110223</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3722,7 +3794,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.819092</v>
+        <v>11.791542</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3778,7 +3850,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.316422</v>
+        <v>22.264402</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3806,7 +3878,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.510681</v>
+        <v>5.497835</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3834,7 +3906,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>19.002003</v>
+        <v>18.957709</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3890,7 +3962,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.962617</v>
+        <v>21.911422</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3918,7 +3990,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.430574</v>
+        <v>5.417915</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -3946,7 +4018,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>13.05741</v>
+        <v>13.026973</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -3974,7 +4046,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.716956</v>
+        <v>12.687313</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -4002,7 +4074,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.168224</v>
+        <v>16.130536</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -4030,7 +4102,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.664219</v>
+        <v>10.639361</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4086,7 +4158,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.869159</v>
+        <v>21.818182</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4114,7 +4186,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.443925</v>
+        <v>5.431235</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4142,7 +4214,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4170,7 +4242,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.281709</v>
+        <v>16.243756</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4198,7 +4270,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.550734</v>
+        <v>10.526141</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4226,7 +4298,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.363151</v>
+        <v>32.287712</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4254,7 +4326,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.390521</v>
+        <v>35.308025</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4310,7 +4382,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.321095</v>
+        <v>38.231768</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4338,7 +4410,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.317089</v>
+        <v>5.304695</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4366,7 +4438,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4394,7 +4466,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>148.775033</v>
+        <v>148.428238</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4422,7 +4494,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.947931</v>
+        <v>15.910756</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4450,7 +4522,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.660881</v>
+        <v>20.612721</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4478,7 +4550,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.198264</v>
+        <v>21.148851</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4506,7 +4578,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>21.138184</v>
+        <v>21.088911</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4534,7 +4606,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4590,7 +4662,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.987984</v>
+        <v>40.892441</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4618,7 +4690,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>26.104806</v>
+        <v>26.043956</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4646,7 +4718,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.726302</v>
+        <v>44.622045</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4674,7 +4746,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.1502</v>
+        <v>5.138195</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4702,7 +4774,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.933244</v>
+        <v>14.898435</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4730,7 +4802,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.88785</v>
+        <v>25.827506</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4758,7 +4830,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4786,7 +4858,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.5</v>
+        <v>32.424242</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4814,7 +4886,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4842,7 +4914,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>48.271028</v>
+        <v>48.158508</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4870,7 +4942,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.604139</v>
+        <v>20.556111</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4898,7 +4970,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.153538</v>
+        <v>5.141525</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -4954,7 +5026,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.881175</v>
+        <v>20.832501</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -4982,7 +5054,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.722296</v>
+        <v>51.601732</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -5010,7 +5082,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.757009</v>
+        <v>52.634033</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -5038,7 +5110,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.233645</v>
+        <v>5.221445</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -5066,7 +5138,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.463952</v>
+        <v>10.43956</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -5094,7 +5166,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5122,7 +5194,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.440587</v>
+        <v>10.41625</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5150,7 +5222,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.140187</v>
+        <v>15.104895</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5178,7 +5250,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5206,7 +5278,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.413885</v>
+        <v>10.38961</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5234,7 +5306,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>41.198264</v>
+        <v>41.102231</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5262,7 +5334,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5290,7 +5362,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>53.294393</v>
+        <v>53.170163</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5318,7 +5390,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.984646</v>
+        <v>20.935731</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5374,7 +5446,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>49.9</v>
@@ -5402,7 +5474,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>10.383845</v>
+        <v>10.35964</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>31.11</v>
@@ -5430,7 +5502,7 @@
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>11.421896</v>
+        <v>11.395271</v>
       </c>
       <c r="E84" s="17" t="n">
         <v>34.22</v>
@@ -5486,7 +5558,7 @@
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>5.213618</v>
+        <v>5.201465</v>
       </c>
       <c r="E86" s="17" t="n">
         <v>15.62</v>
@@ -5542,7 +5614,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>10.493992</v>
+        <v>10.46953</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>31.44</v>
@@ -5570,7 +5642,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5598,7 +5670,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.517356</v>
+        <v>55.387945</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5654,7 +5726,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.353138</v>
+        <v>2.347652</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5682,7 +5754,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.971295</v>
+        <v>20.922411</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5710,7 +5782,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5741,7 +5813,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5769,7 +5841,7 @@
         <v>10</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>29.96</v>
+        <v>30.03</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5797,7 +5869,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5822,7 +5894,7 @@
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E98" s="17" t="n">
         <v>49.9</v>
@@ -5853,7 +5925,7 @@
         <v>5</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>14.98</v>
+        <v>15.02</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5864,91 +5936,91 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D100" s="16" t="n">
-        <v>20</v>
+        <v>15.14</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>59.92</v>
+        <v>45.47</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>59.92</v>
+        <v>30.03</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>20</v>
+        <v>10.15</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>59.92</v>
+        <v>30.48</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -5965,18 +6037,18 @@
         <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -5993,18 +6065,18 @@
         <v>20</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6021,18 +6093,18 @@
         <v>20</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6049,18 +6121,18 @@
         <v>20</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -6077,36 +6149,120 @@
         <v>20</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
+          <t>ספטמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D108" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="F108" s="14" t="inlineStr">
+        <is>
+          <t>אוקטובר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E109" s="13" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D110" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="18" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B108" s="19" t="n"/>
-      <c r="C108" s="19" t="n"/>
-      <c r="D108" s="20">
-        <f>SUM(D3:D107)</f>
-        <v/>
-      </c>
-      <c r="E108" s="21">
-        <f>SUM(E3:E107)</f>
-        <v/>
-      </c>
-      <c r="F108" s="19" t="n"/>
+      <c r="B111" s="19" t="n"/>
+      <c r="C111" s="19" t="n"/>
+      <c r="D111" s="20">
+        <f>SUM(D3:D110)</f>
+        <v/>
+      </c>
+      <c r="E111" s="21">
+        <f>SUM(E3:E110)</f>
+        <v/>
+      </c>
+      <c r="F111" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A111:C111"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A108:C108"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6197,7 +6353,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.92</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10835,7 +10991,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.11482</v>
+        <v>1.112221</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -10859,7 +11015,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>80.46729000000001</v>
+        <v>80.27972</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -10883,7 +11039,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.695594</v>
+        <v>11.668332</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -10907,7 +11063,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>22.129506</v>
+        <v>22.077922</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -10955,7 +11111,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.130174</v>
+        <v>15.094905</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -10979,7 +11135,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>127.12283</v>
+        <v>126.826507</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -11003,7 +11159,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.23498</v>
+        <v>11.208791</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -11122,7 +11278,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.002003</v>
+        <v>18.957709</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11146,7 +11302,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>17.086115</v>
+        <v>17.046287</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -11170,7 +11326,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.658211</v>
+        <v>13.626374</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -11194,7 +11350,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.028037</v>
+        <v>1.025641</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11218,7 +11374,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.775701</v>
+        <v>21.724942</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11242,7 +11398,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.136182</v>
+        <v>12.107892</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11266,7 +11422,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.840454</v>
+        <v>22.787213</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11314,7 +11470,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.577437</v>
+        <v>5.564436</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11338,7 +11494,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.550067</v>
+        <v>12.520813</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11457,7 +11613,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.002003</v>
+        <v>18.957709</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11481,7 +11637,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.11749</v>
+        <v>3.110223</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11505,7 +11661,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.819092</v>
+        <v>11.791542</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11553,7 +11709,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.316422</v>
+        <v>22.264402</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11577,7 +11733,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.510681</v>
+        <v>5.497835</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11696,7 +11852,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.002003</v>
+        <v>18.957709</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11744,7 +11900,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.962617</v>
+        <v>21.911422</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11768,7 +11924,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.430574</v>
+        <v>5.417915</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -11887,7 +12043,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>13.05741</v>
+        <v>13.026973</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -11911,7 +12067,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.716956</v>
+        <v>12.687313</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -11935,7 +12091,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.168224</v>
+        <v>16.130536</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -11959,7 +12115,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.664219</v>
+        <v>10.639361</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -12007,7 +12163,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.869159</v>
+        <v>21.818182</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -12031,7 +12187,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.443925</v>
+        <v>5.431235</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -12150,7 +12306,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12174,7 +12330,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.281709</v>
+        <v>16.243756</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -12198,7 +12354,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.550734</v>
+        <v>10.526141</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12222,7 +12378,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.363151</v>
+        <v>32.287712</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12246,7 +12402,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.390521</v>
+        <v>35.308025</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12294,7 +12450,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.321095</v>
+        <v>38.231768</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12318,7 +12474,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.317089</v>
+        <v>5.304695</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12437,7 +12593,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.333778</v>
+        <v>25.274725</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12461,7 +12617,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>148.775033</v>
+        <v>148.428238</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12485,7 +12641,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.947931</v>
+        <v>15.910756</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12509,7 +12665,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.660881</v>
+        <v>20.612721</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12533,7 +12689,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.198264</v>
+        <v>21.148851</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12557,7 +12713,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.138184</v>
+        <v>21.088911</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12581,7 +12737,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.655541</v>
+        <v>16.616717</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12629,7 +12785,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.987984</v>
+        <v>40.892441</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12653,7 +12809,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>26.104806</v>
+        <v>26.043956</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12677,7 +12833,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.726302</v>
+        <v>44.622045</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12701,7 +12857,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.1502</v>
+        <v>5.138195</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12725,7 +12881,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.933244</v>
+        <v>14.898435</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.003</v>
+        <v>2.983</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-20</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.827506</v>
+        <v>26.00067</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.424242</v>
+        <v>32.641636</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>48.158508</v>
+        <v>48.481395</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.556111</v>
+        <v>20.693932</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.141525</v>
+        <v>5.175997</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.832501</v>
+        <v>20.972176</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.601732</v>
+        <v>51.947704</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.634033</v>
+        <v>52.986926</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.221445</v>
+        <v>5.256453</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.43956</v>
+        <v>10.509554</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.41625</v>
+        <v>10.486088</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.104895</v>
+        <v>15.206168</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.38961</v>
+        <v>10.459269</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>41.102231</v>
+        <v>41.377808</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>53.170163</v>
+        <v>53.526651</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.935731</v>
+        <v>21.076098</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>10.35964</v>
+        <v>10.429098</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>31.11</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>11.395271</v>
+        <v>11.471673</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>34.22</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>5.201465</v>
+        <v>5.236339</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>15.62</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>10.46953</v>
+        <v>10.539725</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>31.44</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>55.387945</v>
+        <v>55.759303</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>2.347652</v>
+        <v>2.363393</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.922411</v>
+        <v>21.062689</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -2149,31 +2149,31 @@
         <v>10</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>30.03</v>
+        <v>29.83</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>20</v>
+        <v>16.728126</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>60.06</v>
+        <v>49.9</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2185,19 +2185,19 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
+          <t>1 $100.00 $100.00 Unused time on ChatGPT Plus Subscription after 18 Apr 2026</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.616717</v>
+        <v>81.23</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>49.9</v>
+        <v>242.31</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
@@ -2221,7 +2221,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>15.02</v>
+        <v>14.92</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -2245,7 +2245,7 @@
         <v>15.14</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>45.47</v>
+        <v>45.16</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -2269,7 +2269,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>30.03</v>
+        <v>29.83</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
@@ -2293,7 +2293,7 @@
         <v>10.15</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>30.48</v>
+        <v>30.28</v>
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
@@ -2412,7 +2412,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2531,7 +2531,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2650,7 +2650,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2769,7 +2769,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2888,7 +2888,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3007,7 +3007,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3126,7 +3126,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.112221</v>
+        <v>1.119678</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>80.27972</v>
+        <v>80.81796799999999</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.668332</v>
+        <v>11.746564</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>22.077922</v>
+        <v>22.225947</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.094905</v>
+        <v>15.196111</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>126.826507</v>
+        <v>127.676835</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.208791</v>
+        <v>11.283942</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.957709</v>
+        <v>19.084814</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>17.046287</v>
+        <v>17.160577</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.626374</v>
+        <v>13.717734</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.025641</v>
+        <v>1.032518</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.724942</v>
+        <v>21.8706</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.107892</v>
+        <v>12.189071</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.787213</v>
+        <v>22.939993</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.564436</v>
+        <v>5.601743</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.520813</v>
+        <v>12.60476</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.957709</v>
+        <v>19.084814</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.110223</v>
+        <v>3.131076</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.791542</v>
+        <v>11.8706</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.264402</v>
+        <v>22.413678</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.497835</v>
+        <v>5.534697</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.957709</v>
+        <v>19.084814</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.911422</v>
+        <v>22.058331</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.417915</v>
+        <v>5.454241</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>13.026973</v>
+        <v>13.114314</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.687313</v>
+        <v>12.772377</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.130536</v>
+        <v>16.238686</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.639361</v>
+        <v>10.710694</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.818182</v>
+        <v>21.964465</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.431235</v>
+        <v>5.46765</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.243756</v>
+        <v>16.352665</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.526141</v>
+        <v>10.596715</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.287712</v>
+        <v>32.50419</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.308025</v>
+        <v>35.544754</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.231768</v>
+        <v>38.488099</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.304695</v>
+        <v>5.340261</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>148.428238</v>
+        <v>149.423399</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.910756</v>
+        <v>16.017432</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.612721</v>
+        <v>20.750922</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.148851</v>
+        <v>21.290647</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>21.088911</v>
+        <v>21.230305</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.892441</v>
+        <v>41.166611</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>26.043956</v>
+        <v>26.218572</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.622045</v>
+        <v>44.92122</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.138195</v>
+        <v>5.172645</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.898435</v>
+        <v>14.998324</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.827506</v>
+        <v>26.00067</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.424242</v>
+        <v>32.641636</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>48.158508</v>
+        <v>48.481395</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.556111</v>
+        <v>20.693932</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.141525</v>
+        <v>5.175997</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.832501</v>
+        <v>20.972176</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.601732</v>
+        <v>51.947704</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.634033</v>
+        <v>52.986926</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.221445</v>
+        <v>5.256453</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.43956</v>
+        <v>10.509554</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.41625</v>
+        <v>10.486088</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.104895</v>
+        <v>15.206168</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.38961</v>
+        <v>10.459269</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>41.102231</v>
+        <v>41.377808</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>53.170163</v>
+        <v>53.526651</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.935731</v>
+        <v>21.076098</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>49.9</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>10.35964</v>
+        <v>10.429098</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>31.11</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>11.395271</v>
+        <v>11.471673</v>
       </c>
       <c r="E84" s="17" t="n">
         <v>34.22</v>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>5.201465</v>
+        <v>5.236339</v>
       </c>
       <c r="E86" s="17" t="n">
         <v>15.62</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>10.46953</v>
+        <v>10.539725</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>31.44</v>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.387945</v>
+        <v>55.759303</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.347652</v>
+        <v>2.363393</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.922411</v>
+        <v>21.062689</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5813,7 +5813,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>10</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>30.03</v>
+        <v>29.83</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -5852,24 +5852,24 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>20</v>
+        <v>16.728126</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>60.06</v>
+        <v>49.9</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5885,19 +5885,19 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
+          <t>1 $100.00 $100.00 Unused time on ChatGPT Plus Subscription after 18 Apr 2026</t>
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>16.616717</v>
+        <v>81.23</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>49.9</v>
+        <v>242.31</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>5</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>15.02</v>
+        <v>14.92</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>15.14</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>45.47</v>
+        <v>45.16</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>10</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>30.03</v>
+        <v>29.83</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>10.15</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>30.48</v>
+        <v>30.28</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>20</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>20</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>20</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>20</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>20</v>
       </c>
       <c r="E108" s="17" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>20</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>20</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>59.66</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.112221</v>
+        <v>1.119678</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>80.27972</v>
+        <v>80.81796799999999</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.668332</v>
+        <v>11.746564</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -11063,7 +11063,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>22.077922</v>
+        <v>22.225947</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.094905</v>
+        <v>15.196111</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>126.826507</v>
+        <v>127.676835</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.208791</v>
+        <v>11.283942</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.957709</v>
+        <v>19.084814</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>17.046287</v>
+        <v>17.160577</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.626374</v>
+        <v>13.717734</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.025641</v>
+        <v>1.032518</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.724942</v>
+        <v>21.8706</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.107892</v>
+        <v>12.189071</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11422,7 +11422,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.787213</v>
+        <v>22.939993</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.564436</v>
+        <v>5.601743</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.520813</v>
+        <v>12.60476</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -11613,7 +11613,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.957709</v>
+        <v>19.084814</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.110223</v>
+        <v>3.131076</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.791542</v>
+        <v>11.8706</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -11709,7 +11709,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.264402</v>
+        <v>22.413678</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -11733,7 +11733,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.497835</v>
+        <v>5.534697</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.957709</v>
+        <v>19.084814</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11900,7 +11900,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.911422</v>
+        <v>22.058331</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -11924,7 +11924,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.417915</v>
+        <v>5.454241</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>13.026973</v>
+        <v>13.114314</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.687313</v>
+        <v>12.772377</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.130536</v>
+        <v>16.238686</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.639361</v>
+        <v>10.710694</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.818182</v>
+        <v>21.964465</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -12187,7 +12187,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.431235</v>
+        <v>5.46765</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -12306,7 +12306,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12330,7 +12330,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.243756</v>
+        <v>16.352665</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.526141</v>
+        <v>10.596715</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.287712</v>
+        <v>32.50419</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12402,7 +12402,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.308025</v>
+        <v>35.544754</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.231768</v>
+        <v>38.488099</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12474,7 +12474,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.304695</v>
+        <v>5.340261</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.274725</v>
+        <v>25.444184</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12617,7 +12617,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>148.428238</v>
+        <v>149.423399</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.910756</v>
+        <v>16.017432</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.612721</v>
+        <v>20.750922</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.148851</v>
+        <v>21.290647</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.088911</v>
+        <v>21.230305</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.616717</v>
+        <v>16.728126</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.892441</v>
+        <v>41.166611</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>26.043956</v>
+        <v>26.218572</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -12833,7 +12833,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.622045</v>
+        <v>44.92122</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.138195</v>
+        <v>5.172645</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.898435</v>
+        <v>14.998324</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2204,31 +2204,31 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>ChatGPT Pro Subscription</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5</v>
+        <v>81.2</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>14.92</v>
+        <v>242.22</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -2238,14 +2238,14 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>15.14</v>
+        <v>5</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>45.16</v>
+        <v>14.92</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -2262,62 +2262,86 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>10</v>
+        <v>15.14</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>29.83</v>
+        <v>45.16</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Prepaid extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="F18" s="24" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D19" s="27" t="n">
         <v>10.15</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E19" s="28" t="n">
         <v>30.28</v>
       </c>
-      <c r="F18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="F19" s="29" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="20">
-        <f>SUM(D4:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>SUM(E4:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="31" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="20">
+        <f>SUM(D4:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>SUM(E4:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3167,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5908,24 +5932,24 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>ChatGPT Pro Subscription</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>5</v>
+        <v>81.2</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>14.92</v>
+        <v>242.22</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5936,7 +5960,7 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5946,14 +5970,14 @@
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D100" s="16" t="n">
-        <v>15.14</v>
+        <v>5</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>45.16</v>
+        <v>14.92</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5974,14 +5998,14 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>10</v>
+        <v>15.14</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>29.83</v>
+        <v>45.16</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5992,7 +6016,7 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -6002,14 +6026,14 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>30.28</v>
+        <v>29.83</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -6020,35 +6044,35 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D103" s="12" t="n">
-        <v>20</v>
+        <v>10.15</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>59.66</v>
+        <v>30.28</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -6069,14 +6093,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6097,14 +6121,14 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6125,14 +6149,14 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -6153,14 +6177,14 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -6181,14 +6205,14 @@
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -6209,14 +6233,14 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -6237,31 +6261,59 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="18" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B111" s="19" t="n"/>
-      <c r="C111" s="19" t="n"/>
-      <c r="D111" s="20">
-        <f>SUM(D3:D110)</f>
-        <v/>
-      </c>
-      <c r="E111" s="21">
-        <f>SUM(E3:E110)</f>
-        <v/>
-      </c>
-      <c r="F111" s="19" t="n"/>
+      <c r="B112" s="19" t="n"/>
+      <c r="C112" s="19" t="n"/>
+      <c r="D112" s="20">
+        <f>SUM(D3:D111)</f>
+        <v/>
+      </c>
+      <c r="E112" s="21">
+        <f>SUM(E3:E111)</f>
+        <v/>
+      </c>
+      <c r="F112" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A112:C112"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2190,45 +2190,45 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>1 $100.00 $100.00 Unused time on ChatGPT Plus Subscription after 18 Apr 2026</t>
+          <t>ChatGPT Pro Subscription</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>81.23</v>
+        <v>81.2</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>242.31</v>
+        <v>242.22</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Pro Subscription</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>81.2</v>
+        <v>5</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>242.22</v>
+        <v>14.92</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -2238,14 +2238,14 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>5</v>
+        <v>15.14</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.92</v>
+        <v>45.16</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -2262,21 +2262,21 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>15.14</v>
+        <v>10</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>45.16</v>
+        <v>29.83</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -2286,62 +2286,38 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>29.83</v>
+        <v>30.28</v>
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Auto recharge extra usage, Individual plan</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="E19" s="28" t="n">
-        <v>30.28</v>
-      </c>
-      <c r="F19" s="29" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n"/>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="20">
-        <f>SUM(D4:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="21">
-        <f>SUM(E4:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="31" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="20">
+        <f>SUM(D4:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>SUM(E4:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3191,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5914,14 +5890,14 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>1 $100.00 $100.00 Unused time on ChatGPT Plus Subscription after 18 Apr 2026</t>
+          <t>ChatGPT Pro Subscription</t>
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>81.23</v>
+        <v>81.2</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>242.31</v>
+        <v>242.22</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -5932,24 +5908,24 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Pro Subscription</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>81.2</v>
+        <v>5</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>242.22</v>
+        <v>14.92</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -5960,7 +5936,7 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -5970,14 +5946,14 @@
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D100" s="16" t="n">
-        <v>5</v>
+        <v>15.14</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>14.92</v>
+        <v>45.16</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -5998,14 +5974,14 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>15.14</v>
+        <v>10</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>45.16</v>
+        <v>29.83</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -6016,7 +5992,7 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -6026,14 +6002,14 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>29.83</v>
+        <v>30.28</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -6044,35 +6020,35 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D103" s="12" t="n">
-        <v>10.15</v>
+        <v>20</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>30.28</v>
+        <v>59.66</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>אפריל 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -6093,14 +6069,14 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -6121,14 +6097,14 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6149,14 +6125,14 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -6177,14 +6153,14 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -6205,14 +6181,14 @@
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -6233,14 +6209,14 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>נובמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -6261,59 +6237,31 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C111" s="11" t="inlineStr">
-        <is>
-          <t>ChatGPT Plus</t>
-        </is>
-      </c>
-      <c r="D111" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E111" s="13" t="n">
-        <v>59.66</v>
-      </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>דצמבר 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="18" t="inlineStr">
+      <c r="A111" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B112" s="19" t="n"/>
-      <c r="C112" s="19" t="n"/>
-      <c r="D112" s="20">
-        <f>SUM(D3:D111)</f>
-        <v/>
-      </c>
-      <c r="E112" s="21">
-        <f>SUM(E3:E111)</f>
-        <v/>
-      </c>
-      <c r="F112" s="19" t="n"/>
+      <c r="B111" s="19" t="n"/>
+      <c r="C111" s="19" t="n"/>
+      <c r="D111" s="20">
+        <f>SUM(D3:D110)</f>
+        <v/>
+      </c>
+      <c r="E111" s="21">
+        <f>SUM(E3:E110)</f>
+        <v/>
+      </c>
+      <c r="F111" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A111:C111"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2297,27 +2297,123 @@
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E19" s="28" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="F19" s="29" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="F20" s="24" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="F21" s="29" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Supabase</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Supabase</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>74.58</v>
+      </c>
+      <c r="F22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="20">
-        <f>SUM(D4:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>SUM(E4:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="31" t="n"/>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="20">
+        <f>SUM(D4:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>SUM(E4:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3167,7 +3263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6020,119 +6116,119 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D103" s="12" t="n">
-        <v>20</v>
+        <v>10.02</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>59.66</v>
+        <v>29.89</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D104" s="16" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>59.66</v>
+        <v>31.32</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D105" s="12" t="n">
-        <v>20</v>
+        <v>11.17</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>59.66</v>
+        <v>33.32</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D106" s="16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>59.66</v>
+        <v>74.58</v>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -6153,14 +6249,14 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -6181,14 +6277,14 @@
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -6209,14 +6305,14 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -6237,31 +6333,143 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
+          <t>אוגוסט 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>ספטמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>אוקטובר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D114" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="18" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B111" s="19" t="n"/>
-      <c r="C111" s="19" t="n"/>
-      <c r="D111" s="20">
-        <f>SUM(D3:D110)</f>
-        <v/>
-      </c>
-      <c r="E111" s="21">
-        <f>SUM(E3:E110)</f>
-        <v/>
-      </c>
-      <c r="F111" s="19" t="n"/>
+      <c r="B115" s="19" t="n"/>
+      <c r="C115" s="19" t="n"/>
+      <c r="D115" s="20">
+        <f>SUM(D3:D114)</f>
+        <v/>
+      </c>
+      <c r="E115" s="21">
+        <f>SUM(E3:E114)</f>
+        <v/>
+      </c>
+      <c r="F115" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A115:C115"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6394,7 +6602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM26"/>
+  <dimension ref="A1:AM27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9953,151 +10161,151 @@
     <row r="25">
       <c r="A25" s="36" t="inlineStr">
         <is>
-          <t>Timeless</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="C25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
         <v/>
       </c>
       <c r="D25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="E25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
         <v/>
       </c>
       <c r="F25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="G25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
         <v/>
       </c>
       <c r="H25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="I25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
         <v/>
       </c>
       <c r="J25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="K25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
         <v/>
       </c>
       <c r="L25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="M25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
         <v/>
       </c>
       <c r="N25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="O25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
         <v/>
       </c>
       <c r="P25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="Q25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
         <v/>
       </c>
       <c r="R25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="S25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
         <v/>
       </c>
       <c r="T25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="U25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
         <v/>
       </c>
       <c r="V25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="W25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
         <v/>
       </c>
       <c r="X25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Y25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
         <v/>
       </c>
       <c r="Z25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AA25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
         <v/>
       </c>
       <c r="AB25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AC25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
         <v/>
       </c>
       <c r="AD25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AE25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
         <v/>
       </c>
       <c r="AF25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AG25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
         <v/>
       </c>
       <c r="AH25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AI25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
         <v/>
       </c>
       <c r="AJ25" s="37">
-        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AK25" s="38">
-        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Supabase",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
         <v/>
       </c>
       <c r="AL25" s="39">
@@ -10109,162 +10317,321 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>Timeless</t>
+        </is>
+      </c>
+      <c r="B26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <v/>
+      </c>
+      <c r="C26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2025")</f>
+        <v/>
+      </c>
+      <c r="D26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <v/>
+      </c>
+      <c r="E26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2025")</f>
+        <v/>
+      </c>
+      <c r="F26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="G26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="H26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <v/>
+      </c>
+      <c r="I26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2025")</f>
+        <v/>
+      </c>
+      <c r="J26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="K26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="L26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="M26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2025")</f>
+        <v/>
+      </c>
+      <c r="N26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <v/>
+      </c>
+      <c r="O26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ינואר 2026")</f>
+        <v/>
+      </c>
+      <c r="P26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"פברואר 2026")</f>
+        <v/>
+      </c>
+      <c r="R26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <v/>
+      </c>
+      <c r="S26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מרץ 2026")</f>
+        <v/>
+      </c>
+      <c r="T26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <v/>
+      </c>
+      <c r="U26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אפריל 2026")</f>
+        <v/>
+      </c>
+      <c r="V26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="W26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"מאי 2026")</f>
+        <v/>
+      </c>
+      <c r="X26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Y26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יוני 2026")</f>
+        <v/>
+      </c>
+      <c r="Z26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AA26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"יולי 2026")</f>
+        <v/>
+      </c>
+      <c r="AB26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AC26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוגוסט 2026")</f>
+        <v/>
+      </c>
+      <c r="AD26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AE26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"ספטמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AF26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AG26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"אוקטובר 2026")</f>
+        <v/>
+      </c>
+      <c r="AH26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AI26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"נובמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="42">
+        <f>SUMIFS('כל ההוצאות'!$D:$D,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AK26" s="43">
+        <f>SUMIFS('כל ההוצאות'!$E:$E,'כל ההוצאות'!$B:$B,"Timeless",'כל ההוצאות'!$F:$F,"דצמבר 2026")</f>
+        <v/>
+      </c>
+      <c r="AL26" s="39">
+        <f>SUM(B26,D26,F26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26,AB26,AD26,AF26,AH26,AJ26)</f>
+        <v/>
+      </c>
+      <c r="AM26" s="40">
+        <f>SUM(C26,E26,G26,I26,K26,M26,O26,Q26,S26,U26,W26,Y26,AA26,AC26,AE26,AG26,AI26,AK26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודשי</t>
         </is>
       </c>
-      <c r="B26" s="20">
-        <f>SUM(B5:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="21">
-        <f>SUM(C5:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="20">
-        <f>SUM(D5:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>SUM(E5:E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="20">
-        <f>SUM(F5:F25)</f>
-        <v/>
-      </c>
-      <c r="G26" s="21">
-        <f>SUM(G5:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="20">
-        <f>SUM(H5:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="21">
-        <f>SUM(I5:I25)</f>
-        <v/>
-      </c>
-      <c r="J26" s="20">
-        <f>SUM(J5:J25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="21">
-        <f>SUM(K5:K25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="20">
-        <f>SUM(L5:L25)</f>
-        <v/>
-      </c>
-      <c r="M26" s="21">
-        <f>SUM(M5:M25)</f>
-        <v/>
-      </c>
-      <c r="N26" s="20">
-        <f>SUM(N5:N25)</f>
-        <v/>
-      </c>
-      <c r="O26" s="21">
-        <f>SUM(O5:O25)</f>
-        <v/>
-      </c>
-      <c r="P26" s="20">
-        <f>SUM(P5:P25)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="21">
-        <f>SUM(Q5:Q25)</f>
-        <v/>
-      </c>
-      <c r="R26" s="20">
-        <f>SUM(R5:R25)</f>
-        <v/>
-      </c>
-      <c r="S26" s="21">
-        <f>SUM(S5:S25)</f>
-        <v/>
-      </c>
-      <c r="T26" s="20">
-        <f>SUM(T5:T25)</f>
-        <v/>
-      </c>
-      <c r="U26" s="21">
-        <f>SUM(U5:U25)</f>
-        <v/>
-      </c>
-      <c r="V26" s="20">
-        <f>SUM(V5:V25)</f>
-        <v/>
-      </c>
-      <c r="W26" s="21">
-        <f>SUM(W5:W25)</f>
-        <v/>
-      </c>
-      <c r="X26" s="20">
-        <f>SUM(X5:X25)</f>
-        <v/>
-      </c>
-      <c r="Y26" s="21">
-        <f>SUM(Y5:Y25)</f>
-        <v/>
-      </c>
-      <c r="Z26" s="20">
-        <f>SUM(Z5:Z25)</f>
-        <v/>
-      </c>
-      <c r="AA26" s="21">
-        <f>SUM(AA5:AA25)</f>
-        <v/>
-      </c>
-      <c r="AB26" s="20">
-        <f>SUM(AB5:AB25)</f>
-        <v/>
-      </c>
-      <c r="AC26" s="21">
-        <f>SUM(AC5:AC25)</f>
-        <v/>
-      </c>
-      <c r="AD26" s="20">
-        <f>SUM(AD5:AD25)</f>
-        <v/>
-      </c>
-      <c r="AE26" s="21">
-        <f>SUM(AE5:AE25)</f>
-        <v/>
-      </c>
-      <c r="AF26" s="20">
-        <f>SUM(AF5:AF25)</f>
-        <v/>
-      </c>
-      <c r="AG26" s="21">
-        <f>SUM(AG5:AG25)</f>
-        <v/>
-      </c>
-      <c r="AH26" s="20">
-        <f>SUM(AH5:AH25)</f>
-        <v/>
-      </c>
-      <c r="AI26" s="21">
-        <f>SUM(AI5:AI25)</f>
-        <v/>
-      </c>
-      <c r="AJ26" s="20">
-        <f>SUM(AJ5:AJ25)</f>
-        <v/>
-      </c>
-      <c r="AK26" s="21">
-        <f>SUM(AK5:AK25)</f>
-        <v/>
-      </c>
-      <c r="AL26" s="44">
-        <f>SUM(AL5:AL25)</f>
-        <v/>
-      </c>
-      <c r="AM26" s="45">
-        <f>SUM(AM5:AM25)</f>
+      <c r="B27" s="20">
+        <f>SUM(B5:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="21">
+        <f>SUM(C5:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="20">
+        <f>SUM(D5:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f>SUM(E5:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="20">
+        <f>SUM(F5:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="21">
+        <f>SUM(G5:G26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="20">
+        <f>SUM(H5:H26)</f>
+        <v/>
+      </c>
+      <c r="I27" s="21">
+        <f>SUM(I5:I26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="20">
+        <f>SUM(J5:J26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="21">
+        <f>SUM(K5:K26)</f>
+        <v/>
+      </c>
+      <c r="L27" s="20">
+        <f>SUM(L5:L26)</f>
+        <v/>
+      </c>
+      <c r="M27" s="21">
+        <f>SUM(M5:M26)</f>
+        <v/>
+      </c>
+      <c r="N27" s="20">
+        <f>SUM(N5:N26)</f>
+        <v/>
+      </c>
+      <c r="O27" s="21">
+        <f>SUM(O5:O26)</f>
+        <v/>
+      </c>
+      <c r="P27" s="20">
+        <f>SUM(P5:P26)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="21">
+        <f>SUM(Q5:Q26)</f>
+        <v/>
+      </c>
+      <c r="R27" s="20">
+        <f>SUM(R5:R26)</f>
+        <v/>
+      </c>
+      <c r="S27" s="21">
+        <f>SUM(S5:S26)</f>
+        <v/>
+      </c>
+      <c r="T27" s="20">
+        <f>SUM(T5:T26)</f>
+        <v/>
+      </c>
+      <c r="U27" s="21">
+        <f>SUM(U5:U26)</f>
+        <v/>
+      </c>
+      <c r="V27" s="20">
+        <f>SUM(V5:V26)</f>
+        <v/>
+      </c>
+      <c r="W27" s="21">
+        <f>SUM(W5:W26)</f>
+        <v/>
+      </c>
+      <c r="X27" s="20">
+        <f>SUM(X5:X26)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="21">
+        <f>SUM(Y5:Y26)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="20">
+        <f>SUM(Z5:Z26)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="21">
+        <f>SUM(AA5:AA26)</f>
+        <v/>
+      </c>
+      <c r="AB27" s="20">
+        <f>SUM(AB5:AB26)</f>
+        <v/>
+      </c>
+      <c r="AC27" s="21">
+        <f>SUM(AC5:AC26)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="20">
+        <f>SUM(AD5:AD26)</f>
+        <v/>
+      </c>
+      <c r="AE27" s="21">
+        <f>SUM(AE5:AE26)</f>
+        <v/>
+      </c>
+      <c r="AF27" s="20">
+        <f>SUM(AF5:AF26)</f>
+        <v/>
+      </c>
+      <c r="AG27" s="21">
+        <f>SUM(AG5:AG26)</f>
+        <v/>
+      </c>
+      <c r="AH27" s="20">
+        <f>SUM(AH5:AH26)</f>
+        <v/>
+      </c>
+      <c r="AI27" s="21">
+        <f>SUM(AI5:AI26)</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="20">
+        <f>SUM(AJ5:AJ26)</f>
+        <v/>
+      </c>
+      <c r="AK27" s="21">
+        <f>SUM(AK5:AK26)</f>
+        <v/>
+      </c>
+      <c r="AL27" s="44">
+        <f>SUM(AL5:AL26)</f>
+        <v/>
+      </c>
+      <c r="AM27" s="45">
+        <f>SUM(AM5:AM26)</f>
         <v/>
       </c>
     </row>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2156,24 +2156,24 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>16.728126</v>
+        <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>49.9</v>
+        <v>59.66</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2185,50 +2185,50 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Pro Subscription</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>81.2</v>
+        <v>16.728126</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>242.22</v>
+        <v>49.9</v>
       </c>
       <c r="F14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>ChatGPT Pro Subscription</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5</v>
+        <v>81.2</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>14.92</v>
+        <v>242.22</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -2238,14 +2238,14 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>15.14</v>
+        <v>5</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>45.16</v>
+        <v>14.92</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -2262,21 +2262,21 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>10</v>
+        <v>15.14</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>29.83</v>
+        <v>45.16</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -2286,14 +2286,14 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>30.28</v>
+        <v>29.83</v>
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="D19" s="27" t="n">
-        <v>10.02</v>
+        <v>10.15</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>29.89</v>
+        <v>30.28</v>
       </c>
       <c r="F19" s="29" t="n"/>
     </row>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>10.5</v>
+        <v>10.02</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>31.32</v>
+        <v>29.89</v>
       </c>
       <c r="F20" s="24" t="n"/>
     </row>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D21" s="27" t="n">
-        <v>11.17</v>
+        <v>10.5</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>33.32</v>
+        <v>31.32</v>
       </c>
       <c r="F21" s="29" t="n"/>
     </row>
@@ -2377,43 +2377,67 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="F22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D23" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E23" s="28" t="n">
         <v>74.58</v>
       </c>
-      <c r="F22" s="24" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="F23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="20">
-        <f>SUM(D4:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="21">
-        <f>SUM(E4:E22)</f>
-        <v/>
-      </c>
-      <c r="F23" s="31" t="n"/>
+      <c r="B24" s="31" t="n"/>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="20">
+        <f>SUM(D4:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="21">
+        <f>SUM(E4:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3263,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5948,24 +5972,24 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>CapCut</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Pro – Apr 2026 (₪49.90)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>16.728126</v>
+        <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>49.9</v>
+        <v>59.66</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5981,19 +6005,19 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>CapCut</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Pro Subscription</t>
+          <t>Pro – Apr 2026 (₪49.90)</t>
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>81.2</v>
+        <v>16.728126</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>242.22</v>
+        <v>49.9</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -6004,24 +6028,24 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>ChatGPT Pro Subscription</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>5</v>
+        <v>81.2</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>14.92</v>
+        <v>242.22</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -6032,7 +6056,7 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -6042,14 +6066,14 @@
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D100" s="16" t="n">
-        <v>15.14</v>
+        <v>5</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>45.16</v>
+        <v>14.92</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -6070,14 +6094,14 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Prepaid extra usage, Individual plan</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>10</v>
+        <v>15.14</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>29.83</v>
+        <v>45.16</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -6088,7 +6112,7 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -6098,14 +6122,14 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Auto recharge extra usage, Individual plan</t>
+          <t>Prepaid extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>30.28</v>
+        <v>29.83</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -6130,10 +6154,10 @@
         </is>
       </c>
       <c r="D103" s="12" t="n">
-        <v>10.02</v>
+        <v>10.15</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>29.89</v>
+        <v>30.28</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -6158,10 +6182,10 @@
         </is>
       </c>
       <c r="D104" s="16" t="n">
-        <v>10.5</v>
+        <v>10.02</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>31.32</v>
+        <v>29.89</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -6186,10 +6210,10 @@
         </is>
       </c>
       <c r="D105" s="12" t="n">
-        <v>11.17</v>
+        <v>10.5</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>33.32</v>
+        <v>31.32</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -6205,19 +6229,19 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D106" s="16" t="n">
-        <v>25</v>
+        <v>11.17</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>74.58</v>
+        <v>33.32</v>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
@@ -6228,35 +6252,35 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D107" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>59.66</v>
+        <v>74.58</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -6277,14 +6301,14 @@
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -6305,14 +6329,14 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -6333,14 +6357,14 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -6361,14 +6385,14 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
@@ -6389,14 +6413,14 @@
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -6417,14 +6441,14 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
@@ -6445,32 +6469,60 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="18" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B115" s="19" t="n"/>
-      <c r="C115" s="19" t="n"/>
-      <c r="D115" s="20">
-        <f>SUM(D3:D114)</f>
-        <v/>
-      </c>
-      <c r="E115" s="21">
-        <f>SUM(E3:E114)</f>
-        <v/>
-      </c>
-      <c r="F115" s="19" t="n"/>
+      <c r="B116" s="19" t="n"/>
+      <c r="C116" s="19" t="n"/>
+      <c r="D116" s="20">
+        <f>SUM(D3:D115)</f>
+        <v/>
+      </c>
+      <c r="E116" s="21">
+        <f>SUM(E3:E115)</f>
+        <v/>
+      </c>
+      <c r="F116" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A115:C115"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A116:C116"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2417,27 +2417,51 @@
       </c>
       <c r="F23" s="29" t="n"/>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="F24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B24" s="31" t="n"/>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="20">
-        <f>SUM(D4:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>SUM(E4:E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="31" t="n"/>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="20">
+        <f>SUM(D4:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>SUM(E4:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3287,7 +3311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6280,35 +6304,35 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D108" s="16" t="n">
-        <v>20</v>
+        <v>15.57</v>
       </c>
       <c r="E108" s="17" t="n">
-        <v>59.66</v>
+        <v>46.45</v>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -6329,14 +6353,14 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -6357,14 +6381,14 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -6385,14 +6409,14 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
@@ -6413,14 +6437,14 @@
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -6441,14 +6465,14 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
@@ -6469,14 +6493,14 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -6497,32 +6521,60 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="18" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B116" s="19" t="n"/>
-      <c r="C116" s="19" t="n"/>
-      <c r="D116" s="20">
-        <f>SUM(D3:D115)</f>
-        <v/>
-      </c>
-      <c r="E116" s="21">
-        <f>SUM(E3:E115)</f>
-        <v/>
-      </c>
-      <c r="F116" s="19" t="n"/>
+      <c r="B117" s="19" t="n"/>
+      <c r="C117" s="19" t="n"/>
+      <c r="D117" s="20">
+        <f>SUM(D3:D116)</f>
+        <v/>
+      </c>
+      <c r="E117" s="21">
+        <f>SUM(E3:E116)</f>
+        <v/>
+      </c>
+      <c r="F117" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A117:C117"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A116:C116"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2441,27 +2441,51 @@
       </c>
       <c r="F24" s="24" t="n"/>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="F25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B25" s="31" t="n"/>
-      <c r="C25" s="31" t="n"/>
-      <c r="D25" s="20">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="21">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="31" t="n"/>
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="20">
+        <f>SUM(D4:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>SUM(E4:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3311,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6332,35 +6356,35 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D109" s="12" t="n">
-        <v>20</v>
+        <v>10.74</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>59.66</v>
+        <v>32.04</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -6381,14 +6405,14 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -6409,14 +6433,14 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
@@ -6437,14 +6461,14 @@
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -6465,14 +6489,14 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
@@ -6493,14 +6517,14 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -6521,14 +6545,14 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
@@ -6549,31 +6573,59 @@
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="18" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B117" s="19" t="n"/>
-      <c r="C117" s="19" t="n"/>
-      <c r="D117" s="20">
-        <f>SUM(D3:D116)</f>
-        <v/>
-      </c>
-      <c r="E117" s="21">
-        <f>SUM(E3:E116)</f>
-        <v/>
-      </c>
-      <c r="F117" s="19" t="n"/>
+      <c r="B118" s="19" t="n"/>
+      <c r="C118" s="19" t="n"/>
+      <c r="D118" s="20">
+        <f>SUM(D3:D117)</f>
+        <v/>
+      </c>
+      <c r="E118" s="21">
+        <f>SUM(E3:E117)</f>
+        <v/>
+      </c>
+      <c r="F118" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A118:C118"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2.983</v>
+        <v>3.005</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-21</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>26.00067</v>
+        <v>25.810316</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.641636</v>
+        <v>32.402662</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>48.481395</v>
+        <v>48.126456</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.693932</v>
+        <v>20.542429</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.175997</v>
+        <v>5.138103</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.972176</v>
+        <v>20.818636</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.947704</v>
+        <v>51.567388</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.986926</v>
+        <v>52.599002</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.256453</v>
+        <v>5.21797</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.509554</v>
+        <v>10.432612</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.486088</v>
+        <v>10.409318</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.206168</v>
+        <v>15.094842</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.459269</v>
+        <v>10.382696</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>41.377808</v>
+        <v>41.074875</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>53.526651</v>
+        <v>53.134775</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>21.076098</v>
+        <v>20.921797</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>10.429098</v>
+        <v>10.352745</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>31.11</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>11.471673</v>
+        <v>11.387687</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>34.22</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>5.236339</v>
+        <v>5.198003</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>15.62</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>10.539725</v>
+        <v>10.462562</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>31.44</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>55.759303</v>
+        <v>55.351082</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>2.363393</v>
+        <v>2.34609</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.062689</v>
+        <v>20.908486</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>29.83</v>
+        <v>30.05</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2173,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -2221,7 +2221,7 @@
         <v>81.2</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>242.22</v>
+        <v>244.01</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.92</v>
+        <v>15.02</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -2269,7 +2269,7 @@
         <v>15.14</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>45.16</v>
+        <v>45.5</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
@@ -2293,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>29.83</v>
+        <v>30.05</v>
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
@@ -2317,7 +2317,7 @@
         <v>10.15</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>30.28</v>
+        <v>30.5</v>
       </c>
       <c r="F19" s="29" t="n"/>
     </row>
@@ -2341,7 +2341,7 @@
         <v>10.02</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>29.89</v>
+        <v>30.11</v>
       </c>
       <c r="F20" s="24" t="n"/>
     </row>
@@ -2365,7 +2365,7 @@
         <v>10.5</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>31.32</v>
+        <v>31.55</v>
       </c>
       <c r="F21" s="29" t="n"/>
     </row>
@@ -2389,7 +2389,7 @@
         <v>11.17</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>33.32</v>
+        <v>33.57</v>
       </c>
       <c r="F22" s="24" t="n"/>
     </row>
@@ -2413,7 +2413,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="28" t="n">
-        <v>74.58</v>
+        <v>75.12</v>
       </c>
       <c r="F23" s="29" t="n"/>
     </row>
@@ -2437,7 +2437,7 @@
         <v>15.57</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>46.45</v>
+        <v>46.79</v>
       </c>
       <c r="F24" s="24" t="n"/>
     </row>
@@ -2461,7 +2461,7 @@
         <v>10.74</v>
       </c>
       <c r="E25" s="28" t="n">
-        <v>32.04</v>
+        <v>32.27</v>
       </c>
       <c r="F25" s="29" t="n"/>
     </row>
@@ -2580,7 +2580,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2699,7 +2699,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2818,7 +2818,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2937,7 +2937,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3056,7 +3056,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3175,7 +3175,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3294,7 +3294,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.119678</v>
+        <v>1.111481</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>80.81796799999999</v>
+        <v>80.22629000000001</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.746564</v>
+        <v>11.660566</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>22.225947</v>
+        <v>22.063228</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.196111</v>
+        <v>15.084859</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>127.676835</v>
+        <v>126.742097</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.283942</v>
+        <v>11.201331</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>19.084814</v>
+        <v>18.945092</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>17.160577</v>
+        <v>17.034942</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.717734</v>
+        <v>13.617304</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.032518</v>
+        <v>1.024958</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.8706</v>
+        <v>21.710483</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.189071</v>
+        <v>12.099834</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.939993</v>
+        <v>22.772047</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.601743</v>
+        <v>5.560732</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.60476</v>
+        <v>12.512479</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>19.084814</v>
+        <v>18.945092</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.131076</v>
+        <v>3.108153</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.8706</v>
+        <v>11.783694</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.413678</v>
+        <v>22.249584</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.534697</v>
+        <v>5.494176</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>19.084814</v>
+        <v>18.945092</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>22.058331</v>
+        <v>21.896839</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.454241</v>
+        <v>5.414309</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>13.114314</v>
+        <v>13.018303</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.772377</v>
+        <v>12.678869</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.238686</v>
+        <v>16.1198</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.710694</v>
+        <v>10.63228</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.964465</v>
+        <v>21.803661</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.46765</v>
+        <v>5.427621</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.352665</v>
+        <v>16.232945</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.596715</v>
+        <v>10.519135</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.50419</v>
+        <v>32.266223</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.544754</v>
+        <v>35.284526</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.488099</v>
+        <v>38.206323</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.340261</v>
+        <v>5.301165</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>149.423399</v>
+        <v>148.329451</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>16.017432</v>
+        <v>15.900166</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.750922</v>
+        <v>20.599002</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.290647</v>
+        <v>21.134775</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>21.230305</v>
+        <v>21.074875</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>41.166611</v>
+        <v>40.865225</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>26.218572</v>
+        <v>26.026622</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.92122</v>
+        <v>44.592346</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.172645</v>
+        <v>5.134775</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.998324</v>
+        <v>14.888519</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>26.00067</v>
+        <v>25.810316</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.641636</v>
+        <v>32.402662</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>48.481395</v>
+        <v>48.126456</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.693932</v>
+        <v>20.542429</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.175997</v>
+        <v>5.138103</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.972176</v>
+        <v>20.818636</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.947704</v>
+        <v>51.567388</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.986926</v>
+        <v>52.599002</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.256453</v>
+        <v>5.21797</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.509554</v>
+        <v>10.432612</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.486088</v>
+        <v>10.409318</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.206168</v>
+        <v>15.094842</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.459269</v>
+        <v>10.382696</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>41.377808</v>
+        <v>41.074875</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>53.526651</v>
+        <v>53.134775</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>21.076098</v>
+        <v>20.921797</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>49.9</v>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>10.429098</v>
+        <v>10.352745</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>31.11</v>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>11.471673</v>
+        <v>11.387687</v>
       </c>
       <c r="E84" s="17" t="n">
         <v>34.22</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>5.236339</v>
+        <v>5.198003</v>
       </c>
       <c r="E86" s="17" t="n">
         <v>15.62</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>10.539725</v>
+        <v>10.462562</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>31.44</v>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.759303</v>
+        <v>55.351082</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.363393</v>
+        <v>2.34609</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>21.062689</v>
+        <v>20.908486</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -5981,7 +5981,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>10</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>29.83</v>
+        <v>30.05</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E98" s="17" t="n">
         <v>49.9</v>
@@ -6093,7 +6093,7 @@
         <v>81.2</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>242.22</v>
+        <v>244.01</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>5</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>14.92</v>
+        <v>15.02</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>15.14</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>45.16</v>
+        <v>45.5</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>10</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>29.83</v>
+        <v>30.05</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>10.15</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>30.28</v>
+        <v>30.5</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>10.02</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>29.89</v>
+        <v>30.11</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>10.5</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>31.32</v>
+        <v>31.55</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>11.17</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>33.32</v>
+        <v>33.57</v>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>25</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>74.58</v>
+        <v>75.12</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>15.57</v>
       </c>
       <c r="E108" s="17" t="n">
-        <v>46.45</v>
+        <v>46.79</v>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>10.74</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>32.04</v>
+        <v>32.27</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>20</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>20</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>20</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>20</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>20</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>20</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>20</v>
       </c>
       <c r="E116" s="17" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>20</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>59.66</v>
+        <v>60.1</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11514,7 +11514,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.119678</v>
+        <v>1.111481</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>80.81796799999999</v>
+        <v>80.22629000000001</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -11562,7 +11562,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.746564</v>
+        <v>11.660566</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>22.225947</v>
+        <v>22.063228</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -11634,7 +11634,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.196111</v>
+        <v>15.084859</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>127.676835</v>
+        <v>126.742097</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.283942</v>
+        <v>11.201331</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.084814</v>
+        <v>18.945092</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>17.160577</v>
+        <v>17.034942</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.717734</v>
+        <v>13.617304</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.032518</v>
+        <v>1.024958</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.8706</v>
+        <v>21.710483</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11921,7 +11921,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.189071</v>
+        <v>12.099834</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.939993</v>
+        <v>22.772047</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -11993,7 +11993,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.601743</v>
+        <v>5.560732</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.60476</v>
+        <v>12.512479</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.084814</v>
+        <v>18.945092</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.131076</v>
+        <v>3.108153</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -12184,7 +12184,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.8706</v>
+        <v>11.783694</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.413678</v>
+        <v>22.249584</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -12256,7 +12256,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.534697</v>
+        <v>5.494176</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -12375,7 +12375,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19.084814</v>
+        <v>18.945092</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -12423,7 +12423,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>22.058331</v>
+        <v>21.896839</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -12447,7 +12447,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.454241</v>
+        <v>5.414309</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -12566,7 +12566,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>13.114314</v>
+        <v>13.018303</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.772377</v>
+        <v>12.678869</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.238686</v>
+        <v>16.1198</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -12638,7 +12638,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.710694</v>
+        <v>10.63228</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.964465</v>
+        <v>21.803661</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -12710,7 +12710,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.46765</v>
+        <v>5.427621</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.352665</v>
+        <v>16.232945</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.596715</v>
+        <v>10.519135</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.50419</v>
+        <v>32.266223</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.544754</v>
+        <v>35.284526</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -12973,7 +12973,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.488099</v>
+        <v>38.206323</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -12997,7 +12997,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.340261</v>
+        <v>5.301165</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.444184</v>
+        <v>25.257903</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -13140,7 +13140,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>149.423399</v>
+        <v>148.329451</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -13164,7 +13164,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.017432</v>
+        <v>15.900166</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.750922</v>
+        <v>20.599002</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -13212,7 +13212,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.290647</v>
+        <v>21.134775</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -13236,7 +13236,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.230305</v>
+        <v>21.074875</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.728126</v>
+        <v>16.605657</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>41.166611</v>
+        <v>40.865225</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -13332,7 +13332,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>26.218572</v>
+        <v>26.026622</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -13356,7 +13356,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.92122</v>
+        <v>44.592346</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -13380,7 +13380,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.172645</v>
+        <v>5.134775</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -13404,7 +13404,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.998324</v>
+        <v>14.888519</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2465,27 +2465,51 @@
       </c>
       <c r="F25" s="29" t="n"/>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Auto recharge extra usage, Individual plan</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="F26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>סה"כ חודש"</t>
         </is>
       </c>
-      <c r="B26" s="31" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="20">
-        <f>SUM(D4:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>SUM(E4:E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="31" t="n"/>
+      <c r="B27" s="31" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="20">
+        <f>SUM(D4:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f>SUM(E4:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
@@ -3335,7 +3359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6384,35 +6408,35 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Auto recharge extra usage, Individual plan</t>
         </is>
       </c>
       <c r="D110" s="16" t="n">
-        <v>20</v>
+        <v>10.16</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>60.1</v>
+        <v>30.53</v>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>מאי 2026</t>
+          <t>אפריל 2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -6433,14 +6457,14 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>יוני 2026</t>
+          <t>מאי 2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
@@ -6461,14 +6485,14 @@
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>יולי 2026</t>
+          <t>יוני 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -6489,14 +6513,14 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>אוגוסט 2026</t>
+          <t>יולי 2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
@@ -6517,14 +6541,14 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר 2026</t>
+          <t>אוגוסט 2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -6545,14 +6569,14 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>אוקטובר 2026</t>
+          <t>ספטמבר 2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
@@ -6573,14 +6597,14 @@
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
-          <t>נובמבר 2026</t>
+          <t>אוקטובר 2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -6601,32 +6625,60 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
+          <t>נובמבר 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="B118" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F118" s="14" t="inlineStr">
+        <is>
           <t>דצמבר 2026</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="18" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="18" t="inlineStr">
         <is>
           <t>סה"כ"</t>
         </is>
       </c>
-      <c r="B118" s="19" t="n"/>
-      <c r="C118" s="19" t="n"/>
-      <c r="D118" s="20">
-        <f>SUM(D3:D117)</f>
-        <v/>
-      </c>
-      <c r="E118" s="21">
-        <f>SUM(E3:E117)</f>
-        <v/>
-      </c>
-      <c r="F118" s="19" t="n"/>
+      <c r="B119" s="19" t="n"/>
+      <c r="C119" s="19" t="n"/>
+      <c r="D119" s="20">
+        <f>SUM(D3:D118)</f>
+        <v/>
+      </c>
+      <c r="E119" s="21">
+        <f>SUM(E3:E118)</f>
+        <v/>
+      </c>
+      <c r="F119" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A118:C118"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A119:C119"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.005</v>
+        <v>3.003</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-23</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.810316</v>
+        <v>25.827506</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.402662</v>
+        <v>32.424242</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>48.126456</v>
+        <v>48.158508</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.542429</v>
+        <v>20.556111</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.138103</v>
+        <v>5.141525</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.818636</v>
+        <v>20.832501</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.567388</v>
+        <v>51.601732</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.599002</v>
+        <v>52.634033</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.21797</v>
+        <v>5.221445</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.432612</v>
+        <v>10.43956</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.409318</v>
+        <v>10.41625</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.094842</v>
+        <v>15.104895</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.382696</v>
+        <v>10.38961</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>41.074875</v>
+        <v>41.102231</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>53.134775</v>
+        <v>53.170163</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.921797</v>
+        <v>20.935731</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>10.352745</v>
+        <v>10.35964</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>31.11</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>11.387687</v>
+        <v>11.395271</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>34.22</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>5.198003</v>
+        <v>5.201465</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>15.62</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>10.462562</v>
+        <v>10.46953</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>31.44</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>55.351082</v>
+        <v>55.387945</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>2.34609</v>
+        <v>2.347652</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.908486</v>
+        <v>20.922411</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>30.05</v>
+        <v>30.03</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2173,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -2221,7 +2221,7 @@
         <v>81.2</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>244.01</v>
+        <v>243.84</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -2269,7 +2269,7 @@
         <v>15.14</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>45.5</v>
+        <v>45.47</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
@@ -2293,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>30.05</v>
+        <v>30.03</v>
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
@@ -2317,7 +2317,7 @@
         <v>10.15</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>30.5</v>
+        <v>30.48</v>
       </c>
       <c r="F19" s="29" t="n"/>
     </row>
@@ -2341,7 +2341,7 @@
         <v>10.02</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>30.11</v>
+        <v>30.09</v>
       </c>
       <c r="F20" s="24" t="n"/>
     </row>
@@ -2365,7 +2365,7 @@
         <v>10.5</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>31.55</v>
+        <v>31.53</v>
       </c>
       <c r="F21" s="29" t="n"/>
     </row>
@@ -2389,7 +2389,7 @@
         <v>11.17</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>33.57</v>
+        <v>33.54</v>
       </c>
       <c r="F22" s="24" t="n"/>
     </row>
@@ -2413,7 +2413,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="28" t="n">
-        <v>75.12</v>
+        <v>75.08</v>
       </c>
       <c r="F23" s="29" t="n"/>
     </row>
@@ -2437,7 +2437,7 @@
         <v>15.57</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>46.79</v>
+        <v>46.76</v>
       </c>
       <c r="F24" s="24" t="n"/>
     </row>
@@ -2461,7 +2461,7 @@
         <v>10.74</v>
       </c>
       <c r="E25" s="28" t="n">
-        <v>32.27</v>
+        <v>32.25</v>
       </c>
       <c r="F25" s="29" t="n"/>
     </row>
@@ -2485,7 +2485,7 @@
         <v>10.16</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>30.53</v>
+        <v>30.51</v>
       </c>
       <c r="F26" s="24" t="n"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2723,7 +2723,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2842,7 +2842,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2961,7 +2961,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3080,7 +3080,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3199,7 +3199,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3318,7 +3318,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.111481</v>
+        <v>1.112221</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>80.22629000000001</v>
+        <v>80.27972</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.660566</v>
+        <v>11.668332</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>22.063228</v>
+        <v>22.077922</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.084859</v>
+        <v>15.094905</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>126.742097</v>
+        <v>126.826507</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.201331</v>
+        <v>11.208791</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.945092</v>
+        <v>18.957709</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>17.034942</v>
+        <v>17.046287</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.617304</v>
+        <v>13.626374</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.024958</v>
+        <v>1.025641</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.710483</v>
+        <v>21.724942</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.099834</v>
+        <v>12.107892</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.772047</v>
+        <v>22.787213</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.560732</v>
+        <v>5.564436</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.512479</v>
+        <v>12.520813</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.945092</v>
+        <v>18.957709</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.108153</v>
+        <v>3.110223</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.783694</v>
+        <v>11.791542</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.249584</v>
+        <v>22.264402</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.494176</v>
+        <v>5.497835</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.945092</v>
+        <v>18.957709</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.896839</v>
+        <v>21.911422</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.414309</v>
+        <v>5.417915</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>13.018303</v>
+        <v>13.026973</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.678869</v>
+        <v>12.687313</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.1198</v>
+        <v>16.130536</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.63228</v>
+        <v>10.639361</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.803661</v>
+        <v>21.818182</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.427621</v>
+        <v>5.431235</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.232945</v>
+        <v>16.243756</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.519135</v>
+        <v>10.526141</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.266223</v>
+        <v>32.287712</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.284526</v>
+        <v>35.308025</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.206323</v>
+        <v>38.231768</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.301165</v>
+        <v>5.304695</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>148.329451</v>
+        <v>148.428238</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.900166</v>
+        <v>15.910756</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.599002</v>
+        <v>20.612721</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.134775</v>
+        <v>21.148851</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>21.074875</v>
+        <v>21.088911</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.865225</v>
+        <v>40.892441</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>26.026622</v>
+        <v>26.043956</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.592346</v>
+        <v>44.622045</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.134775</v>
+        <v>5.138195</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.888519</v>
+        <v>14.898435</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.810316</v>
+        <v>25.827506</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.402662</v>
+        <v>32.424242</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>48.126456</v>
+        <v>48.158508</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.542429</v>
+        <v>20.556111</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.138103</v>
+        <v>5.141525</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.818636</v>
+        <v>20.832501</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.567388</v>
+        <v>51.601732</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.599002</v>
+        <v>52.634033</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.21797</v>
+        <v>5.221445</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.432612</v>
+        <v>10.43956</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.409318</v>
+        <v>10.41625</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.094842</v>
+        <v>15.104895</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.382696</v>
+        <v>10.38961</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>41.074875</v>
+        <v>41.102231</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>53.134775</v>
+        <v>53.170163</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.921797</v>
+        <v>20.935731</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>49.9</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>10.352745</v>
+        <v>10.35964</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>31.11</v>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>11.387687</v>
+        <v>11.395271</v>
       </c>
       <c r="E84" s="17" t="n">
         <v>34.22</v>
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>5.198003</v>
+        <v>5.201465</v>
       </c>
       <c r="E86" s="17" t="n">
         <v>15.62</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>10.462562</v>
+        <v>10.46953</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>31.44</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.351082</v>
+        <v>55.387945</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.34609</v>
+        <v>2.347652</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.908486</v>
+        <v>20.922411</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -6005,7 +6005,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>10</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>30.05</v>
+        <v>30.03</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E98" s="17" t="n">
         <v>49.9</v>
@@ -6117,7 +6117,7 @@
         <v>81.2</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>244.01</v>
+        <v>243.84</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>15.14</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>45.5</v>
+        <v>45.47</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>10</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>30.05</v>
+        <v>30.03</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>10.15</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>30.5</v>
+        <v>30.48</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>10.02</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>30.11</v>
+        <v>30.09</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>10.5</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>31.55</v>
+        <v>31.53</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>11.17</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>33.57</v>
+        <v>33.54</v>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>25</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>75.12</v>
+        <v>75.08</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>15.57</v>
       </c>
       <c r="E108" s="17" t="n">
-        <v>46.79</v>
+        <v>46.76</v>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>10.74</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>32.27</v>
+        <v>32.25</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>10.16</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>30.53</v>
+        <v>30.51</v>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>20</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>20</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>20</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>20</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>20</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>20</v>
       </c>
       <c r="E116" s="17" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>20</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>20</v>
       </c>
       <c r="E118" s="17" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F118" s="14" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.1</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11566,7 +11566,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.111481</v>
+        <v>1.112221</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -11590,7 +11590,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>80.22629000000001</v>
+        <v>80.27972</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.660566</v>
+        <v>11.668332</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>22.063228</v>
+        <v>22.077922</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.084859</v>
+        <v>15.094905</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>126.742097</v>
+        <v>126.826507</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.201331</v>
+        <v>11.208791</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.945092</v>
+        <v>18.957709</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11877,7 +11877,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>17.034942</v>
+        <v>17.046287</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -11901,7 +11901,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.617304</v>
+        <v>13.626374</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.024958</v>
+        <v>1.025641</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.710483</v>
+        <v>21.724942</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11973,7 +11973,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.099834</v>
+        <v>12.107892</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.772047</v>
+        <v>22.787213</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.560732</v>
+        <v>5.564436</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.512479</v>
+        <v>12.520813</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -12188,7 +12188,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.945092</v>
+        <v>18.957709</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.108153</v>
+        <v>3.110223</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -12236,7 +12236,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.783694</v>
+        <v>11.791542</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.249584</v>
+        <v>22.264402</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -12308,7 +12308,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.494176</v>
+        <v>5.497835</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.945092</v>
+        <v>18.957709</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.896839</v>
+        <v>21.911422</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.414309</v>
+        <v>5.417915</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>13.018303</v>
+        <v>13.026973</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.678869</v>
+        <v>12.687313</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -12666,7 +12666,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.1198</v>
+        <v>16.130536</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -12690,7 +12690,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.63228</v>
+        <v>10.639361</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.803661</v>
+        <v>21.818182</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -12762,7 +12762,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.427621</v>
+        <v>5.431235</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.232945</v>
+        <v>16.243756</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.519135</v>
+        <v>10.526141</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.266223</v>
+        <v>32.287712</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.284526</v>
+        <v>35.308025</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.206323</v>
+        <v>38.231768</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.301165</v>
+        <v>5.304695</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -13168,7 +13168,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.257903</v>
+        <v>25.274725</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -13192,7 +13192,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>148.329451</v>
+        <v>148.428238</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -13216,7 +13216,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.900166</v>
+        <v>15.910756</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.599002</v>
+        <v>20.612721</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -13264,7 +13264,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.134775</v>
+        <v>21.148851</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.074875</v>
+        <v>21.088911</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -13312,7 +13312,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.605657</v>
+        <v>16.616717</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.865225</v>
+        <v>40.892441</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>26.026622</v>
+        <v>26.043956</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -13408,7 +13408,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.592346</v>
+        <v>44.622045</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -13432,7 +13432,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.134775</v>
+        <v>5.138195</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.888519</v>
+        <v>14.898435</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.003</v>
+        <v>3.65</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-24</t>
+          <t>← מקור: Bank of Israel Public API (fallback)</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.827506</v>
+        <v>21.249315</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>32.424242</v>
+        <v>26.676712</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>48.158508</v>
+        <v>39.621918</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.556111</v>
+        <v>16.912329</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.141525</v>
+        <v>4.230137</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.832501</v>
+        <v>17.139726</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>51.601732</v>
+        <v>42.454795</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>52.634033</v>
+        <v>43.30411</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.221445</v>
+        <v>4.29589</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10.43956</v>
+        <v>8.589041</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>10.41625</v>
+        <v>8.569863</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.104895</v>
+        <v>12.427397</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10.38961</v>
+        <v>8.547945</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>41.102231</v>
+        <v>33.816438</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>53.170163</v>
+        <v>43.745205</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>20.935731</v>
+        <v>17.224658</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>10.35964</v>
+        <v>8.523288000000001</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>31.11</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>11.395271</v>
+        <v>9.375342</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>34.22</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>5.201465</v>
+        <v>4.279452</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>15.62</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>10.46953</v>
+        <v>8.613699</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>31.44</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>55.387945</v>
+        <v>45.569863</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>2.347652</v>
+        <v>1.931507</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>20.922411</v>
+        <v>17.213699</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>30.03</v>
+        <v>36.5</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2173,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -2221,7 +2221,7 @@
         <v>81.2</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>243.84</v>
+        <v>296.38</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>15.02</v>
+        <v>18.25</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -2269,7 +2269,7 @@
         <v>15.14</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>45.47</v>
+        <v>55.26</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
@@ -2293,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>30.03</v>
+        <v>36.5</v>
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
@@ -2317,7 +2317,7 @@
         <v>10.15</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>30.48</v>
+        <v>37.05</v>
       </c>
       <c r="F19" s="29" t="n"/>
     </row>
@@ -2341,7 +2341,7 @@
         <v>10.02</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>30.09</v>
+        <v>36.57</v>
       </c>
       <c r="F20" s="24" t="n"/>
     </row>
@@ -2365,7 +2365,7 @@
         <v>10.5</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>31.53</v>
+        <v>38.32</v>
       </c>
       <c r="F21" s="29" t="n"/>
     </row>
@@ -2389,7 +2389,7 @@
         <v>11.17</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>33.54</v>
+        <v>40.77</v>
       </c>
       <c r="F22" s="24" t="n"/>
     </row>
@@ -2413,7 +2413,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="28" t="n">
-        <v>75.08</v>
+        <v>91.25</v>
       </c>
       <c r="F23" s="29" t="n"/>
     </row>
@@ -2437,7 +2437,7 @@
         <v>15.57</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>46.76</v>
+        <v>56.83</v>
       </c>
       <c r="F24" s="24" t="n"/>
     </row>
@@ -2461,7 +2461,7 @@
         <v>10.74</v>
       </c>
       <c r="E25" s="28" t="n">
-        <v>32.25</v>
+        <v>39.2</v>
       </c>
       <c r="F25" s="29" t="n"/>
     </row>
@@ -2485,7 +2485,7 @@
         <v>10.16</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>30.51</v>
+        <v>37.08</v>
       </c>
       <c r="F26" s="24" t="n"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2723,7 +2723,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2842,7 +2842,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2961,7 +2961,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3080,7 +3080,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3199,7 +3199,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3318,7 +3318,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.112221</v>
+        <v>0.915068</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>80.27972</v>
+        <v>66.04931500000001</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>11.668332</v>
+        <v>9.6</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>22.077922</v>
+        <v>18.164384</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>15.094905</v>
+        <v>12.419178</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>126.826507</v>
+        <v>104.345205</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11.208791</v>
+        <v>9.221918000000001</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>18.957709</v>
+        <v>15.59726</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>17.046287</v>
+        <v>14.024658</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13.626374</v>
+        <v>11.210959</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1.025641</v>
+        <v>0.843836</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>21.724942</v>
+        <v>17.873973</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>12.107892</v>
+        <v>9.961644</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>22.787213</v>
+        <v>18.747945</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5.564436</v>
+        <v>4.578082</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>12.520813</v>
+        <v>10.30137</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>18.957709</v>
+        <v>15.59726</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>3.110223</v>
+        <v>2.558904</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11.791542</v>
+        <v>9.701370000000001</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>22.264402</v>
+        <v>18.317808</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>5.497835</v>
+        <v>4.523288</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>18.957709</v>
+        <v>15.59726</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>21.911422</v>
+        <v>18.027397</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>5.417915</v>
+        <v>4.457534</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>13.026973</v>
+        <v>10.717808</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>12.687313</v>
+        <v>10.438356</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>16.130536</v>
+        <v>13.271233</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>10.639361</v>
+        <v>8.753425</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>21.818182</v>
+        <v>17.950685</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>5.431235</v>
+        <v>4.468493</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>16.243756</v>
+        <v>13.364384</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>10.526141</v>
+        <v>8.660273999999999</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>32.287712</v>
+        <v>26.564384</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>35.308025</v>
+        <v>29.049315</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>38.231768</v>
+        <v>31.454795</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>5.304695</v>
+        <v>4.364384</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>148.428238</v>
+        <v>122.117808</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445.73</v>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>15.910756</v>
+        <v>13.090411</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>47.78</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>20.612721</v>
+        <v>16.958904</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>61.9</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>21.148851</v>
+        <v>17.4</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>63.51</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>21.088911</v>
+        <v>17.350685</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>63.33</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>49.9</v>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>40.892441</v>
+        <v>33.643836</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>122.8</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>26.043956</v>
+        <v>21.427397</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>78.20999999999999</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>44.622045</v>
+        <v>36.712329</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>134</v>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>5.138195</v>
+        <v>4.227397</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15.43</v>
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="D58" s="16" t="n">
-        <v>14.898435</v>
+        <v>12.257534</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>44.74</v>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>25.827506</v>
+        <v>21.249315</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>77.56</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>32.424242</v>
+        <v>26.676712</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>97.37</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>49.9</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>48.158508</v>
+        <v>39.621918</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>144.62</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>20.556111</v>
+        <v>16.912329</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>61.73</v>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5.141525</v>
+        <v>4.230137</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>15.44</v>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>20.832501</v>
+        <v>17.139726</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>62.56</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>51.601732</v>
+        <v>42.454795</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>154.96</v>
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>52.634033</v>
+        <v>43.30411</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>158.06</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>5.221445</v>
+        <v>4.29589</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>15.68</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>10.43956</v>
+        <v>8.589041</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>31.35</v>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>75.90000000000001</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>10.41625</v>
+        <v>8.569863</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>31.28</v>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>15.104895</v>
+        <v>12.427397</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>45.36</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="D76" s="16" t="n">
-        <v>10.38961</v>
+        <v>8.547945</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>31.2</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>41.102231</v>
+        <v>33.816438</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>123.43</v>
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="D78" s="16" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>49.9</v>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>53.170163</v>
+        <v>43.745205</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>159.67</v>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="D80" s="16" t="n">
-        <v>20.935731</v>
+        <v>17.224658</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>62.87</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="D82" s="16" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>49.9</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>10.35964</v>
+        <v>8.523288000000001</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>31.11</v>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>11.395271</v>
+        <v>9.375342</v>
       </c>
       <c r="E84" s="17" t="n">
         <v>34.22</v>
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>5.201465</v>
+        <v>4.279452</v>
       </c>
       <c r="E86" s="17" t="n">
         <v>15.62</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>10.46953</v>
+        <v>8.613699</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>31.44</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>75.90000000000001</v>
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>55.387945</v>
+        <v>45.569863</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>166.33</v>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>2.347652</v>
+        <v>1.931507</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>7.05</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>20.922411</v>
+        <v>17.213699</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>62.83</v>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>49.9</v>
@@ -6005,7 +6005,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>10</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>30.03</v>
+        <v>36.5</v>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E98" s="17" t="n">
         <v>49.9</v>
@@ -6117,7 +6117,7 @@
         <v>81.2</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>243.84</v>
+        <v>296.38</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>5</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>15.02</v>
+        <v>18.25</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>15.14</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>45.47</v>
+        <v>55.26</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>10</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>30.03</v>
+        <v>36.5</v>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>10.15</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>30.48</v>
+        <v>37.05</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>10.02</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>30.09</v>
+        <v>36.57</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>10.5</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>31.53</v>
+        <v>38.32</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>11.17</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>33.54</v>
+        <v>40.77</v>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>25</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>75.08</v>
+        <v>91.25</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>15.57</v>
       </c>
       <c r="E108" s="17" t="n">
-        <v>46.76</v>
+        <v>56.83</v>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>10.74</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>32.25</v>
+        <v>39.2</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>10.16</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>30.51</v>
+        <v>37.08</v>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>20</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>20</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>20</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>20</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>20</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>20</v>
       </c>
       <c r="E116" s="17" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>20</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>20</v>
       </c>
       <c r="E118" s="17" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F118" s="14" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -11566,7 +11566,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1.112221</v>
+        <v>0.915068</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>3.34</v>
@@ -11590,7 +11590,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>80.27972</v>
+        <v>66.04931500000001</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>241.08</v>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.668332</v>
+        <v>9.6</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.04</v>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>22.077922</v>
+        <v>18.164384</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>66.3</v>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>15.094905</v>
+        <v>12.419178</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>45.33</v>
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>126.826507</v>
+        <v>104.345205</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>380.86</v>
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11.208791</v>
+        <v>9.221918000000001</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>33.66</v>
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.957709</v>
+        <v>15.59726</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -11877,7 +11877,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>17.046287</v>
+        <v>14.024658</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>51.19</v>
@@ -11901,7 +11901,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13.626374</v>
+        <v>11.210959</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>40.92</v>
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1.025641</v>
+        <v>0.843836</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3.08</v>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.724942</v>
+        <v>17.873973</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>65.23999999999999</v>
@@ -11973,7 +11973,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>12.107892</v>
+        <v>9.961644</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>36.36</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22.787213</v>
+        <v>18.747945</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>68.43000000000001</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>5.564436</v>
+        <v>4.578082</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>16.71</v>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12.520813</v>
+        <v>10.30137</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>37.6</v>
@@ -12188,7 +12188,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.957709</v>
+        <v>15.59726</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3.110223</v>
+        <v>2.558904</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>9.34</v>
@@ -12236,7 +12236,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>11.791542</v>
+        <v>9.701370000000001</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>35.41</v>
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>22.264402</v>
+        <v>18.317808</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>66.86</v>
@@ -12308,7 +12308,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5.497835</v>
+        <v>4.523288</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>16.51</v>
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18.957709</v>
+        <v>15.59726</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>56.93</v>
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21.911422</v>
+        <v>18.027397</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>65.8</v>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5.417915</v>
+        <v>4.457534</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>16.27</v>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>13.026973</v>
+        <v>10.717808</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>39.12</v>
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>12.687313</v>
+        <v>10.438356</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>38.1</v>
@@ -12666,7 +12666,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.130536</v>
+        <v>13.271233</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>48.44</v>
@@ -12690,7 +12690,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10.639361</v>
+        <v>8.753425</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>31.95</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.818182</v>
+        <v>17.950685</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>65.52</v>
@@ -12762,7 +12762,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>5.431235</v>
+        <v>4.468493</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>16.31</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>16.243756</v>
+        <v>13.364384</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>48.78</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>10.526141</v>
+        <v>8.660273999999999</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>31.61</v>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>32.287712</v>
+        <v>26.564384</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>96.95999999999999</v>
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>35.308025</v>
+        <v>29.049315</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>106.03</v>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>38.231768</v>
+        <v>31.454795</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>114.81</v>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>5.304695</v>
+        <v>4.364384</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>15.93</v>
@@ -13168,7 +13168,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>25.274725</v>
+        <v>20.794521</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -13192,7 +13192,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>148.428238</v>
+        <v>122.117808</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>445.73</v>
@@ -13216,7 +13216,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.910756</v>
+        <v>13.090411</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>47.78</v>
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.612721</v>
+        <v>16.958904</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>61.9</v>
@@ -13264,7 +13264,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21.148851</v>
+        <v>17.4</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>63.51</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>21.088911</v>
+        <v>17.350685</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>63.33</v>
@@ -13312,7 +13312,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16.616717</v>
+        <v>13.671233</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>40.892441</v>
+        <v>33.643836</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>122.8</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>26.043956</v>
+        <v>21.427397</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>78.20999999999999</v>
@@ -13408,7 +13408,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>44.622045</v>
+        <v>36.712329</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>134</v>
@@ -13432,7 +13432,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.138195</v>
+        <v>4.227397</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.43</v>
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.898435</v>
+        <v>12.257534</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>44.74</v>

--- a/AI_Tools_Expenses_2025_2026.xlsx
+++ b/AI_Tools_Expenses_2025_2026.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="21" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הגדרות" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כל ההוצאות" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ינואר 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פברואר 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מרץ 2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אפריל 2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מאי 2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יוני 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="יולי 2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוגוסט 2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספטמבר 2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אוקטובר 2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נובמבר 2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דצמבר 2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום חודשי" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח שנתי" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,14 +481,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -512,7 +512,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -540,8 +540,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -567,8 +567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -609,9 +609,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.65</v>
+        <v>3.003</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>← מקור: Bank of Israel Public API (fallback)</t>
+          <t>← מקור: Bank of Israel Public API | עודכן: 2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>21.249315</v>
+        <v>25.827506</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>77.56</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>20.794521</v>
+        <v>25.274725</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>26.676712</v>
+        <v>32.424242</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>97.37</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>13.671233</v>
+        <v>16.616717</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>49.9</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>39.621918</v>
+        <v>48.158508</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>144.62</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>16.912329</v>
+        <v>20.556111</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>61.73</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>4.230137</v>
+        <v>5.141525</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>15.44</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>17.139726</v>
+        <v>20.832501</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.56</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>42.454795</v>
+        <v>51.601732</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>154.96</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43.30411</v>
+        <v>52.634033</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>158.06</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>4.29589</v>
+        <v>5.221445</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>15.68</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>8.589041</v>
+        <v>10.43956</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>31.35</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.794521</v>
+        <v>25.274725</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>75.90000000000001</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>8.569863</v>
+        <v>10.41625</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>31.28</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>12.427397</v>
+        <v>15.104895</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>45.36</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.794521</v>
+        <v>25.274725</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>75.90000000000001</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>8.547945</v>
+        <v>10.38961</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>31.2</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>33.816438</v>
+        <v>41.102231</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>123.43</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>13.671233</v>
+        <v>16.616717</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>43.745205</v>
+        <v>53.170163</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>159.67</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>17.224658</v>
+        <v>20.935731</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>62.87</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>13.671233</v>
+        <v>16.616717</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>8.523288000000001</v>
+        <v>10.35964</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>31.11</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>9.375342</v>
+        <v>11.395271</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>34.22</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>4.279452</v>
+        <v>5.201465</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>15.62</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D4" s="25" t="n">
-        <v>8.613699</v>
+        <v>10.46953</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>31.44</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>20.794521</v>
+        <v>25.274725</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>75.90000000000001</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>45.569863</v>
+        <v>55.387945</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>166.33</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1.931507</v>
+        <v>2.347652</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>7.05</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>17.213699</v>
+        <v>20.922411</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>62.83</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>13.671233</v>
+        <v>16.616717</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>49.9</v>
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F11" s="29" t="n"/>
     </row>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>36.5</v>
+        <v>30.03</v>
       </c>
       <c r="F12" s="24" t="n"/>
     </row>
@@ -2173,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F13" s="29" t="n"/>
     </row>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>13.671233</v>
+        <v>16.616717</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>49.9</v>
@@ -2221,7 +2221,7 @@
         <v>81.2</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>296.38</v>
+        <v>243.84</v>
       </c>
       <c r="F15" s="29" t="n"/>
     </row>
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>18.25</v>
+        <v>15.02</v>
       </c>
       <c r="F16" s="24" t="n"/>
     </row>
@@ -2269,7 +2269,7 @@
         <v>15.14</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>55.26</v>
+        <v>45.47</v>
       </c>
       <c r="F17" s="29" t="n"/>
     </row>
@@ -2293,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>36.5</v>
+        <v>30.03</v>
       </c>
       <c r="F18" s="24" t="n"/>
     </row>
@@ -2317,7 +2317,7 @@
         <v>10.15</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>37.05</v>
+        <v>30.48</v>
       </c>
       <c r="F19" s="29" t="n"/>
     </row>
@@ -2341,7 +2341,7 @@
         <v>10.02</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>36.57</v>
+        <v>30.09</v>
       </c>
       <c r="F20" s="24" t="n"/>
     </row>
@@ -2365,7 +2365,7 @@
         <v>10.5</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>38.32</v>
+        <v>31.53</v>
       </c>
       <c r="F21" s="29" t="n"/>
     </row>
@@ -2389,7 +2389,7 @@
         <v>11.17</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>40.77</v>
+        <v>33.54</v>
       </c>
       <c r="F22" s="24" t="n"/>
     </row>
@@ -2413,7 +2413,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="28" t="n">
-        <v>91.25</v>
+        <v>75.08</v>
       </c>
       <c r="F23" s="29" t="n"/>
     </row>
@@ -2437,7 +2437,7 @@
         <v>15.57</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>56.83</v>
+        <v>46.76</v>
       </c>
       <c r="F24" s="24" t="n"/>
     </row>
@@ -2461,7 +2461,7 @@
         <v>10.74</v>
       </c>
       <c r="E25" s="28" t="n">
-        <v>39.2</v>
+        <v>32.25</v>
       </c>
       <c r="F25" s="29" t="n"/>
     </row>
@@ -2485,7 +2485,7 @@
         <v>10.16</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>37.08</v>
+        <v>30.51</v>
       </c>
       <c r="F26" s="24" t="n"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2723,7 +2723,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2842,7 +2842,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -2961,7 +2961,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3080,7 +3080,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3199,7 +3199,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3318,7 +3318,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>73</v>
+        <v>60.06</v>
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>0.915068</v>
+        <v>1.112221</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>3.34</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>66.04931500000001</v>
+        <v>80.27972</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>241.08</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>9.6</v>
+        <v>11.668332</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>35.04</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>18.164384</v>
+        <v>22.077922</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>66.3</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>12.419178</v>
+        <v>15.094905</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>45.33</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>104.345205</v>
+        <v>126.826507</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>380.86</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9.221918000000001</v>
+        <v>11.208791</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>33.66</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>15.59726</v>
+        <v>18.957709</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>56.93</v>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>14.024658</v>
+        <v>17.046287</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>51.19</v>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>11.210959</v>
+        <v>13.626374</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>40.92</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.843836</v>
+        <v>1.025641</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>3.08</v>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>17.873973</v>
+        <v>21.724942</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>65.23999999999999</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>9.961644</v>
+        <v>12.107892</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>36.36</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>18.747945</v>
+        <v>22.787213</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>68.43000000000001</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>4.578082</v>
+        <v>5.564436</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>16.71</v>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>10.30137</v>
+        <v>12.520813</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>37.6</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>15.59726</v>
+        <v>18.957709</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>56.93</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>2.558904</v>
+        <v>3.110223</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>9.34</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>9.701370000000001</v>
+        <v>11.791542</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>35.41</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>18.317808</v>
+        <v>22.264402</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>66.86</v>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>4.523288</v>
+        <v>5.497835</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>16.51</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>15.59726</v>
+        <v>18.957709</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>56.93</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>18.027397</v>
+        <v>21.911422</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>65.8</v>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>4.457534</v>
+        <v>5.417915</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>16.27</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>10.717808</v>
+        <v>13.026973</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>39.12</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>10.438356</v>
+        <v>12.687313</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>38.1</v>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>13.271233</v>
+        <v>16.130536</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>48.44</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>8.753425</v>
+        <v>10.639361</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>31.95</v>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>17.950685</v>
+        <v>21.818182</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>65.52</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>4.468493</v>
+        <v>5.431235</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>16.31</v>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>20.794521</v>
+        <v>25.274725</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>13.364384</v>
+        <v>16.243756</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>48.78</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>8.660273999999999</v>
+        <v>10.526141</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>31.61</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>26.564384</v>
+        <v>32.287712</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96.95999999999999</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>29.049315</v>
+        <v>35.308025</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>106.03</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>31.454795</v>
+        <v>38.231768</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>114.81</v>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>4.364384</v>
+        <v>5.304695</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>15.93</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>20.794521</v>
+        <v>25.274725</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>75.90000000000001</v>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>122.117808</v>
+        <v>148.428238</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>445